--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -1498,9 +1498,19 @@
           <t>13.6%</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>1412376</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-41.0%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-36.1%</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
     </row>
@@ -1534,9 +1544,19 @@
           <t>21.1%</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>958914</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>+81.4%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>+137.9%</t>
+        </is>
+      </c>
       <c r="M22" t="n">
         <v>43424</v>
       </c>
@@ -1578,9 +1598,19 @@
           <t>17.9%</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>2892074</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-11.0%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>958914</v>
+        <v>1479698</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+81.4%</t>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+137.9%</t>
+          <t>+31.5%</t>
         </is>
       </c>
       <c r="M22" t="n">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -668,11 +668,11 @@
         <v>-46215</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1486,11 +1486,11 @@
         <v>544651</v>
       </c>
       <c r="G21" t="n">
-        <v>37194</v>
+        <v>76782</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1586,11 +1586,11 @@
         <v>2076133</v>
       </c>
       <c r="G23" t="n">
-        <v>37194</v>
+        <v>76782</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1614,7 +1614,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>含协同37194元 | 普陀明细456896元 | 康博嘉43424元 | 退费率19.3%</t>
+          <t>含协同76782元 | 普陀明细456896元 | 康博嘉43424元 | 退费率19.3%</t>
         </is>
       </c>
     </row>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,38 +503,38 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>74781</v>
+        <v>77011</v>
       </c>
       <c r="E2" t="n">
-        <v>43382</v>
+        <v>44005</v>
       </c>
       <c r="F2" t="n">
-        <v>31399</v>
+        <v>33005</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>306228</v>
+        <v>308000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -555,38 +555,38 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>14430</v>
+        <v>18785</v>
       </c>
       <c r="E3" t="n">
-        <v>18154</v>
+        <v>24874</v>
       </c>
       <c r="F3" t="n">
-        <v>-3724</v>
+        <v>-6089</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>39885</v>
+        <v>41395</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-63.8%</t>
+          <t>-54.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-120.0%</t>
+          <t>-142.9%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -607,38 +607,38 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>163371</v>
+        <v>197067</v>
       </c>
       <c r="E4" t="n">
-        <v>30315</v>
+        <v>81119</v>
       </c>
       <c r="F4" t="n">
-        <v>133055</v>
+        <v>115947</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>207350</v>
+        <v>225139</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -659,29 +659,29 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>22943</v>
+        <v>23309</v>
       </c>
       <c r="E5" t="n">
         <v>69159</v>
       </c>
       <c r="F5" t="n">
-        <v>-46215</v>
+        <v>-45849</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>278889</v>
+        <v>284571</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-117.5%</t>
+          <t>-117.3%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -711,38 +711,38 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>117284</v>
+        <v>135037</v>
       </c>
       <c r="E6" t="n">
-        <v>15437</v>
+        <v>41016</v>
       </c>
       <c r="F6" t="n">
-        <v>101846</v>
+        <v>94020</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>26391</v>
+        <v>32521</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+344.4%</t>
+          <t>+315.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+570.6%</t>
+          <t>+414.9%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -763,38 +763,38 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>91112</v>
+        <v>117462</v>
       </c>
       <c r="E7" t="n">
-        <v>37261</v>
+        <v>37267</v>
       </c>
       <c r="F7" t="n">
-        <v>53851</v>
+        <v>80195</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>182040</v>
+        <v>182211</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -815,38 +815,38 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>78852</v>
+        <v>169398</v>
       </c>
       <c r="E8" t="n">
-        <v>14960</v>
+        <v>15007</v>
       </c>
       <c r="F8" t="n">
-        <v>63892</v>
+        <v>154391</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>100310</v>
+        <v>114620</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>+47.8%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+35.1%</t>
+          <t>+199.6%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -867,38 +867,38 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>270721</v>
+        <v>317341</v>
       </c>
       <c r="E9" t="n">
-        <v>60174</v>
+        <v>53574</v>
       </c>
       <c r="F9" t="n">
-        <v>210547</v>
+        <v>263767</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>271283</v>
+        <v>295883</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+7.3%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+168.9%</t>
+          <t>+195.5%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -919,23 +919,23 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>502848</v>
+        <v>563265</v>
       </c>
       <c r="E10" t="n">
         <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>502829</v>
+        <v>563246</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -943,18 +943,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+1108.9%</t>
+          <t>+1254.1%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1237.4%</t>
+          <t>+1528.0%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>含普陀明细(456896元)</t>
+          <t>含普陀明细(517294元)</t>
         </is>
       </c>
     </row>
@@ -973,36 +973,36 @@
         <v>700000</v>
       </c>
       <c r="D11" t="n">
-        <v>199696</v>
+        <v>214684</v>
       </c>
       <c r="E11" t="n">
-        <v>1800</v>
+        <v>8800</v>
       </c>
       <c r="F11" t="n">
-        <v>197896</v>
+        <v>205884</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>167496</v>
+        <v>187913</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+19.2%</t>
+          <t>+14.2%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+43.9%</t>
+          <t>+31.9%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1023,36 +1023,36 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>35614</v>
+        <v>38614</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>35614</v>
+        <v>38605</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>126788</v>
+        <v>127784</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-69.8%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-59.8%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1073,36 +1073,36 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>214431</v>
+        <v>223068</v>
       </c>
       <c r="E13" t="n">
-        <v>4056</v>
+        <v>14056</v>
       </c>
       <c r="F13" t="n">
-        <v>210375</v>
+        <v>209012</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>64911</v>
+        <v>127816</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+230.3%</t>
+          <t>+74.5%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-7776.0%</t>
+          <t>-700.9%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1123,36 +1123,36 @@
         <v>850000</v>
       </c>
       <c r="D14" t="n">
-        <v>180041</v>
+        <v>190041</v>
       </c>
       <c r="E14" t="n">
         <v>25781</v>
       </c>
       <c r="F14" t="n">
-        <v>154260</v>
+        <v>164260</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>118398</v>
+        <v>139236</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+52.1%</t>
+          <t>+36.5%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+75.9%</t>
+          <t>+72.0%</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1175,23 +1175,23 @@
         <v>450000</v>
       </c>
       <c r="D15" t="n">
-        <v>86520</v>
+        <v>126918</v>
       </c>
       <c r="E15" t="n">
         <v>299</v>
       </c>
       <c r="F15" t="n">
-        <v>86221</v>
+        <v>126619</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+18.5%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+34.8%</t>
+          <t>+120.7%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1225,40 +1225,40 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>164643</v>
+        <v>166547</v>
       </c>
       <c r="E16" t="n">
         <v>299</v>
       </c>
       <c r="F16" t="n">
-        <v>164344</v>
+        <v>166248</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>129370</v>
+        <v>129968</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+27.3%</t>
+          <t>+28.1%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+41.0%</t>
+          <t>+41.9%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>22900</v>
+        <v>23201</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
@@ -1277,40 +1277,40 @@
         <v>850000</v>
       </c>
       <c r="D17" t="n">
-        <v>117915</v>
+        <v>123246</v>
       </c>
       <c r="E17" t="n">
-        <v>143159</v>
+        <v>143178</v>
       </c>
       <c r="F17" t="n">
-        <v>-25243</v>
+        <v>-19931</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>115294</v>
+        <v>142512</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-131.9%</t>
+          <t>-118.7%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4143</v>
+        <v>4726</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
@@ -1329,23 +1329,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>96514</v>
+        <v>97456</v>
       </c>
       <c r="E18" t="n">
         <v>16937</v>
       </c>
       <c r="F18" t="n">
-        <v>79577</v>
+        <v>80519</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1353,16 +1353,16 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+26.6%</t>
+          <t>+27.9%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+592.6%</t>
+          <t>+895.2%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>13098</v>
+        <v>13642</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -1381,23 +1381,23 @@
         <v>260000</v>
       </c>
       <c r="D19" t="n">
-        <v>98788</v>
+        <v>110788</v>
       </c>
       <c r="E19" t="n">
         <v>15277</v>
       </c>
       <c r="F19" t="n">
-        <v>83511</v>
+        <v>95511</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+522.4%</t>
+          <t>+598.0%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+428.0%</t>
+          <t>+503.9%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1431,36 +1431,36 @@
         <v>400000</v>
       </c>
       <c r="D20" t="n">
-        <v>42095</v>
+        <v>50693</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>42095</v>
+        <v>50693</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29988</v>
+        <v>41988</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+40.4%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+2374.7%</t>
+          <t>+270.0%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1477,38 +1477,38 @@
         <v>6150000</v>
       </c>
       <c r="D21" t="n">
-        <v>833494</v>
+        <v>1055410</v>
       </c>
       <c r="E21" t="n">
-        <v>288842</v>
+        <v>366021</v>
       </c>
       <c r="F21" t="n">
-        <v>544651</v>
+        <v>689387</v>
       </c>
       <c r="G21" t="n">
         <v>76782</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1412376</v>
+        <v>1484340</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1525,44 +1525,44 @@
         <v>8260000</v>
       </c>
       <c r="D22" t="n">
-        <v>1739105</v>
+        <v>1905320</v>
       </c>
       <c r="E22" t="n">
-        <v>207627</v>
+        <v>224655</v>
       </c>
       <c r="F22" t="n">
-        <v>1531479</v>
+        <v>1680666</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1479698</v>
+        <v>1655887</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+17.5%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+31.5%</t>
+          <t>+38.0%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>43424</v>
+        <v>44852</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>康博嘉5店(深圳13098,广州3283,武汉4143,杭州22900)</t>
+          <t>康博嘉5店(武汉4726,深圳13642,杭州23201,广州3283)</t>
         </is>
       </c>
     </row>
@@ -1577,44 +1577,44 @@
         <v>14410000</v>
       </c>
       <c r="D23" t="n">
-        <v>2572604</v>
+        <v>2960734</v>
       </c>
       <c r="E23" t="n">
-        <v>496470</v>
+        <v>590677</v>
       </c>
       <c r="F23" t="n">
-        <v>2076133</v>
+        <v>2370056</v>
       </c>
       <c r="G23" t="n">
         <v>76782</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2892074</v>
+        <v>3140227</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+14.9%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>含协同76782元 | 普陀明细456896元 | 康博嘉43424元 | 退费率19.3%</t>
+          <t>含协同76782元 | 普陀明细517294元 | 康博嘉44852元 | 退费率20.0%</t>
         </is>
       </c>
     </row>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,38 +503,38 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>77011</v>
+        <v>79688</v>
       </c>
       <c r="E2" t="n">
-        <v>44005</v>
+        <v>73989</v>
       </c>
       <c r="F2" t="n">
-        <v>33005</v>
+        <v>5698</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>308000</v>
+        <v>342047</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-96.5%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -555,38 +555,38 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>18785</v>
+        <v>19175</v>
       </c>
       <c r="E3" t="n">
-        <v>24874</v>
+        <v>24912</v>
       </c>
       <c r="F3" t="n">
-        <v>-6089</v>
+        <v>-5737</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>41395</v>
+        <v>41974</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-54.6%</t>
+          <t>-54.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-142.9%</t>
+          <t>-139.0%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -607,38 +607,38 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>197067</v>
+        <v>220255</v>
       </c>
       <c r="E4" t="n">
-        <v>81119</v>
+        <v>91493</v>
       </c>
       <c r="F4" t="n">
-        <v>115947</v>
+        <v>128761</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>225139</v>
+        <v>237280</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -659,10 +659,10 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>23309</v>
+        <v>23347</v>
       </c>
       <c r="E5" t="n">
-        <v>69159</v>
+        <v>69197</v>
       </c>
       <c r="F5" t="n">
         <v>-45849</v>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>284571</v>
+        <v>284590</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -711,38 +711,38 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>135037</v>
+        <v>143565</v>
       </c>
       <c r="E6" t="n">
-        <v>41016</v>
+        <v>41506</v>
       </c>
       <c r="F6" t="n">
-        <v>94020</v>
+        <v>102058</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>32521</v>
+        <v>34287</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+315.2%</t>
+          <t>+318.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+414.9%</t>
+          <t>+411.0%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -763,38 +763,38 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>117462</v>
+        <v>132509</v>
       </c>
       <c r="E7" t="n">
-        <v>37267</v>
+        <v>37324</v>
       </c>
       <c r="F7" t="n">
-        <v>80195</v>
+        <v>95185</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>182211</v>
+        <v>182703</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -815,38 +815,38 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>169398</v>
+        <v>174229</v>
       </c>
       <c r="E8" t="n">
-        <v>15007</v>
+        <v>15136</v>
       </c>
       <c r="F8" t="n">
-        <v>154391</v>
+        <v>159093</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>114620</v>
+        <v>115582</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+47.8%</t>
+          <t>+50.7%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+199.6%</t>
+          <t>+203.3%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -867,25 +867,25 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>317341</v>
+        <v>366721</v>
       </c>
       <c r="E9" t="n">
         <v>53574</v>
       </c>
       <c r="F9" t="n">
-        <v>263767</v>
+        <v>313147</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -893,12 +893,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+7.3%</t>
+          <t>+23.9%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+195.5%</t>
+          <t>+250.9%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -919,42 +919,42 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>563265</v>
+        <v>603723</v>
       </c>
       <c r="E10" t="n">
         <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>563246</v>
+        <v>603704</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>41597</v>
+        <v>41995</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+1254.1%</t>
+          <t>+1337.6%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1528.0%</t>
+          <t>+1625.1%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>含普陀明细(517294元)</t>
+          <t>含普陀明细(557752元)</t>
         </is>
       </c>
     </row>
@@ -973,36 +973,36 @@
         <v>700000</v>
       </c>
       <c r="D11" t="n">
-        <v>214684</v>
+        <v>258878</v>
       </c>
       <c r="E11" t="n">
-        <v>8800</v>
+        <v>20800</v>
       </c>
       <c r="F11" t="n">
-        <v>205884</v>
+        <v>238078</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>187913</v>
+        <v>195509</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+14.2%</t>
+          <t>+32.4%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+31.9%</t>
+          <t>+40.3%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1023,36 +1023,36 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>38614</v>
+        <v>52313</v>
       </c>
       <c r="E12" t="n">
         <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>38605</v>
+        <v>52304</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>127784</v>
+        <v>137784</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-69.8%</t>
+          <t>-62.0%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-59.8%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1073,36 +1073,36 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>223068</v>
+        <v>270755</v>
       </c>
       <c r="E13" t="n">
         <v>14056</v>
       </c>
       <c r="F13" t="n">
-        <v>209012</v>
+        <v>256699</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>127816</v>
+        <v>177802</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+74.5%</t>
+          <t>+52.3%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-700.9%</t>
+          <t>+3233.6%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1123,36 +1123,36 @@
         <v>850000</v>
       </c>
       <c r="D14" t="n">
-        <v>190041</v>
+        <v>216221</v>
       </c>
       <c r="E14" t="n">
-        <v>25781</v>
+        <v>30761</v>
       </c>
       <c r="F14" t="n">
-        <v>164260</v>
+        <v>185460</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>139236</v>
+        <v>150836</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+36.5%</t>
+          <t>+43.3%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+72.0%</t>
+          <t>+73.2%</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1175,36 +1175,36 @@
         <v>450000</v>
       </c>
       <c r="D15" t="n">
-        <v>126918</v>
+        <v>134314</v>
       </c>
       <c r="E15" t="n">
         <v>299</v>
       </c>
       <c r="F15" t="n">
-        <v>126619</v>
+        <v>134015</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>72983</v>
+        <v>100220</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+73.9%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+120.7%</t>
+          <t>+58.4%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1225,23 +1225,23 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>166547</v>
+        <v>185595</v>
       </c>
       <c r="E16" t="n">
         <v>299</v>
       </c>
       <c r="F16" t="n">
-        <v>166248</v>
+        <v>185296</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+28.1%</t>
+          <t>+42.8%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+41.9%</t>
+          <t>+58.2%</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1277,36 +1277,36 @@
         <v>850000</v>
       </c>
       <c r="D17" t="n">
-        <v>123246</v>
+        <v>130765</v>
       </c>
       <c r="E17" t="n">
         <v>143178</v>
       </c>
       <c r="F17" t="n">
-        <v>-19931</v>
+        <v>-12412</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>142512</v>
+        <v>153510</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-118.7%</t>
+          <t>-110.6%</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1329,40 +1329,40 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>97456</v>
+        <v>110005</v>
       </c>
       <c r="E18" t="n">
         <v>16937</v>
       </c>
       <c r="F18" t="n">
-        <v>80519</v>
+        <v>93068</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>76217</v>
+        <v>90617</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+27.9%</t>
+          <t>+21.4%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+895.2%</t>
+          <t>+313.8%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>13642</v>
+        <v>15793</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15872</v>
+        <v>15891</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+598.0%</t>
+          <t>+597.2%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+503.9%</t>
+          <t>+503.2%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1431,23 +1431,23 @@
         <v>400000</v>
       </c>
       <c r="D20" t="n">
-        <v>50693</v>
+        <v>57489</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="F20" t="n">
-        <v>50693</v>
+        <v>47289</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+36.9%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+270.0%</t>
+          <t>+245.1%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -1477,38 +1477,38 @@
         <v>6150000</v>
       </c>
       <c r="D21" t="n">
-        <v>1055410</v>
+        <v>1159489</v>
       </c>
       <c r="E21" t="n">
-        <v>366021</v>
+        <v>407131</v>
       </c>
       <c r="F21" t="n">
-        <v>689387</v>
+        <v>752356</v>
       </c>
       <c r="G21" t="n">
         <v>76782</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1484340</v>
+        <v>1534346</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1525,44 +1525,44 @@
         <v>8260000</v>
       </c>
       <c r="D22" t="n">
-        <v>1905320</v>
+        <v>2130846</v>
       </c>
       <c r="E22" t="n">
-        <v>224655</v>
+        <v>251835</v>
       </c>
       <c r="F22" t="n">
-        <v>1680666</v>
+        <v>1879012</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1655887</v>
+        <v>1889501</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+38.0%</t>
+          <t>+29.6%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>44852</v>
+        <v>47003</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>康博嘉5店(武汉4726,深圳13642,杭州23201,广州3283)</t>
+          <t>康博嘉5店(深圳15793,武汉4726,杭州23201,广州3283)</t>
         </is>
       </c>
     </row>
@@ -1577,44 +1577,44 @@
         <v>14410000</v>
       </c>
       <c r="D23" t="n">
-        <v>2960734</v>
+        <v>3290338</v>
       </c>
       <c r="E23" t="n">
-        <v>590677</v>
+        <v>658967</v>
       </c>
       <c r="F23" t="n">
-        <v>2370056</v>
+        <v>2631371</v>
       </c>
       <c r="G23" t="n">
         <v>76782</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3140227</v>
+        <v>3423847</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>含协同76782元 | 普陀明细517294元 | 康博嘉44852元 | 退费率20.0%</t>
+          <t>含协同76782元 | 普陀明细557752元 | 康博嘉47003元 | 退费率20.0%</t>
         </is>
       </c>
     </row>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,25 +503,19 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>79688</v>
+        <v>109898</v>
       </c>
       <c r="E2" t="n">
-        <v>73989</v>
+        <v>74071</v>
       </c>
       <c r="F2" t="n">
-        <v>5698</v>
-      </c>
-      <c r="G2" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>8.8%</t>
-        </is>
-      </c>
+        <v>35826</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -555,25 +549,19 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19175</v>
+        <v>19573</v>
       </c>
       <c r="E3" t="n">
-        <v>24912</v>
+        <v>24918</v>
       </c>
       <c r="F3" t="n">
-        <v>-5737</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
+        <v>-5345</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -607,25 +595,19 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>220255</v>
+        <v>219748</v>
       </c>
       <c r="E4" t="n">
-        <v>91493</v>
+        <v>96943</v>
       </c>
       <c r="F4" t="n">
-        <v>128761</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10398</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>28.8%</t>
-        </is>
-      </c>
+        <v>122804</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -659,25 +641,19 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>23347</v>
+        <v>192385</v>
       </c>
       <c r="E5" t="n">
         <v>69197</v>
       </c>
       <c r="F5" t="n">
-        <v>-45849</v>
-      </c>
-      <c r="G5" t="n">
-        <v>39588</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>9.7%</t>
-        </is>
-      </c>
+        <v>123188</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -711,25 +687,19 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>143565</v>
+        <v>147918</v>
       </c>
       <c r="E6" t="n">
-        <v>41506</v>
+        <v>46623</v>
       </c>
       <c r="F6" t="n">
-        <v>102058</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
-      </c>
+        <v>101295</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -763,25 +733,19 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>132509</v>
+        <v>147817</v>
       </c>
       <c r="E7" t="n">
-        <v>37324</v>
+        <v>38333</v>
       </c>
       <c r="F7" t="n">
-        <v>95185</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>24.1%</t>
-        </is>
-      </c>
+        <v>109484</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -815,25 +779,19 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>174229</v>
+        <v>183271</v>
       </c>
       <c r="E8" t="n">
-        <v>15136</v>
+        <v>19192</v>
       </c>
       <c r="F8" t="n">
-        <v>159093</v>
-      </c>
-      <c r="G8" t="n">
-        <v>18796</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>29.7%</t>
-        </is>
-      </c>
+        <v>164079</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -867,25 +825,19 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>366721</v>
+        <v>419321</v>
       </c>
       <c r="E9" t="n">
         <v>53574</v>
       </c>
       <c r="F9" t="n">
-        <v>313147</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>21.6%</t>
-        </is>
-      </c>
+        <v>365747</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -919,23 +871,23 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>603723</v>
+        <v>800599</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>603704</v>
+        <v>800599</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -943,7 +895,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+1337.6%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -952,11 +904,7 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>含普陀明细(557752元)</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -973,13 +921,13 @@
         <v>700000</v>
       </c>
       <c r="D11" t="n">
-        <v>258878</v>
+        <v>261354</v>
       </c>
       <c r="E11" t="n">
         <v>20800</v>
       </c>
       <c r="F11" t="n">
-        <v>238078</v>
+        <v>240554</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1023,23 +971,23 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>52313</v>
+        <v>77711</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>24809</v>
       </c>
       <c r="F12" t="n">
-        <v>52304</v>
+        <v>52902</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1073,23 +1021,23 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>270755</v>
+        <v>283570</v>
       </c>
       <c r="E13" t="n">
-        <v>14056</v>
+        <v>20656</v>
       </c>
       <c r="F13" t="n">
-        <v>256699</v>
+        <v>262914</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1123,23 +1071,23 @@
         <v>850000</v>
       </c>
       <c r="D14" t="n">
-        <v>216221</v>
+        <v>218307</v>
       </c>
       <c r="E14" t="n">
-        <v>30761</v>
+        <v>36761</v>
       </c>
       <c r="F14" t="n">
-        <v>185460</v>
+        <v>181546</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1147,7 +1095,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+43.3%</t>
+          <t>+41.2%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1156,7 +1104,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>3283</v>
+        <v>3971</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
@@ -1175,23 +1123,23 @@
         <v>450000</v>
       </c>
       <c r="D15" t="n">
-        <v>134314</v>
+        <v>138916</v>
       </c>
       <c r="E15" t="n">
-        <v>299</v>
+        <v>1979</v>
       </c>
       <c r="F15" t="n">
-        <v>134015</v>
+        <v>136937</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1225,23 +1173,23 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>185595</v>
+        <v>196791</v>
       </c>
       <c r="E16" t="n">
-        <v>299</v>
+        <v>19466</v>
       </c>
       <c r="F16" t="n">
-        <v>185296</v>
+        <v>177325</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1249,7 +1197,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+42.8%</t>
+          <t>+24.9%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1277,23 +1225,23 @@
         <v>850000</v>
       </c>
       <c r="D17" t="n">
-        <v>130765</v>
+        <v>131104</v>
       </c>
       <c r="E17" t="n">
-        <v>143178</v>
+        <v>143498</v>
       </c>
       <c r="F17" t="n">
-        <v>-12412</v>
+        <v>-12393</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1301,7 +1249,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1329,23 +1277,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>110005</v>
+        <v>110973</v>
       </c>
       <c r="E18" t="n">
-        <v>16937</v>
+        <v>17549</v>
       </c>
       <c r="F18" t="n">
-        <v>93068</v>
+        <v>93424</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1353,7 +1301,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+21.4%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1362,7 +1310,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>15793</v>
+        <v>16761</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
@@ -1381,23 +1329,23 @@
         <v>260000</v>
       </c>
       <c r="D19" t="n">
-        <v>110788</v>
+        <v>128468</v>
       </c>
       <c r="E19" t="n">
         <v>15277</v>
       </c>
       <c r="F19" t="n">
-        <v>95511</v>
+        <v>113191</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1431,23 +1379,23 @@
         <v>400000</v>
       </c>
       <c r="D20" t="n">
-        <v>57489</v>
+        <v>69489</v>
       </c>
       <c r="E20" t="n">
         <v>10200</v>
       </c>
       <c r="F20" t="n">
-        <v>47289</v>
+        <v>59289</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1469,48 +1417,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>线上合计</t>
+          <t>销售合计</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>6150000</v>
+        <v>4450000</v>
       </c>
       <c r="D21" t="n">
-        <v>1159489</v>
+        <v>1020610</v>
       </c>
       <c r="E21" t="n">
-        <v>407131</v>
+        <v>369277</v>
       </c>
       <c r="F21" t="n">
-        <v>752356</v>
-      </c>
-      <c r="G21" t="n">
-        <v>76782</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>18.9%</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>1534346</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-24.4%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-15.7%</t>
-        </is>
-      </c>
+        <v>651331</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
     </row>
@@ -1525,46 +1453,22 @@
         <v>8260000</v>
       </c>
       <c r="D22" t="n">
-        <v>2130846</v>
+        <v>2417282</v>
       </c>
       <c r="E22" t="n">
-        <v>251835</v>
+        <v>310995</v>
       </c>
       <c r="F22" t="n">
-        <v>1879012</v>
+        <v>2106288</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>25.8%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>25.8%</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>1889501</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>+12.8%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>+29.6%</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>47003</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>康博嘉5店(深圳15793,武汉4726,杭州23201,广州3283)</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1577,46 +1481,22 @@
         <v>14410000</v>
       </c>
       <c r="D23" t="n">
-        <v>3290338</v>
+        <v>3857213</v>
       </c>
       <c r="E23" t="n">
-        <v>658967</v>
+        <v>733846</v>
       </c>
       <c r="F23" t="n">
-        <v>2631371</v>
-      </c>
-      <c r="G23" t="n">
-        <v>76782</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>23.4%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>22.8%</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>3423847</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>-3.9%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>+12.3%</t>
-        </is>
-      </c>
+        <v>3123366</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>含协同76782元 | 普陀明细557752元 | 康博嘉47003元 | 退费率20.0%</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,42 +449,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>协同双计(元)</t>
+          <t>完成率(不含)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>完成率(含协同)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>完成率(不含)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>环比收入(元)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>环比增速</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>环比净流水增速</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
           <t>康博嘉(元)</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>备注</t>
         </is>
       </c>
     </row>
@@ -511,28 +481,12 @@
       <c r="F2" t="n">
         <v>35826</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>342047</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-76.7%</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-96.5%</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -557,28 +511,12 @@
       <c r="F3" t="n">
         <v>-5345</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>41974</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-54.3%</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-139.0%</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,28 +541,12 @@
       <c r="F4" t="n">
         <v>122804</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>27.5%</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>27.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>237280</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-7.2%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-30.3%</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,28 +571,12 @@
       <c r="F5" t="n">
         <v>123188</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>29.6%</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>284590</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-91.8%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-117.3%</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -695,28 +601,12 @@
       <c r="F6" t="n">
         <v>101295</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>21.1%</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>34287</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>+318.7%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>+411.0%</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -741,28 +631,12 @@
       <c r="F7" t="n">
         <v>109484</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>27.0%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>182703</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-27.5%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-9.7%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -787,28 +661,12 @@
       <c r="F8" t="n">
         <v>164079</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>28.2%</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>115582</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>+50.7%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>+203.3%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -833,28 +691,12 @@
       <c r="F9" t="n">
         <v>365747</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>24.7%</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>295883</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>+23.9%</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>+250.9%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -879,32 +721,12 @@
       <c r="F10" t="n">
         <v>800599</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>41995</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>+9.5%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>+1625.1%</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -914,47 +736,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>700000</v>
+        <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>261354</v>
+        <v>77711</v>
       </c>
       <c r="E11" t="n">
-        <v>20800</v>
+        <v>24809</v>
       </c>
       <c r="F11" t="n">
-        <v>240554</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>37.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>37.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>195509</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>+32.4%</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>+40.3%</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>52902</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>17.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -964,47 +766,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>77711</v>
+        <v>138916</v>
       </c>
       <c r="E12" t="n">
-        <v>24809</v>
+        <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>52902</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>137784</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>-62.0%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-50.6%</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>136937</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>30.9%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1014,47 +796,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>800000</v>
+        <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>283570</v>
+        <v>218307</v>
       </c>
       <c r="E13" t="n">
-        <v>20656</v>
+        <v>36761</v>
       </c>
       <c r="F13" t="n">
-        <v>262914</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>35.0%</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>177802</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>+52.3%</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>+3233.6%</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>181546</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>25.7%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>3971</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1064,49 +828,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>850000</v>
+        <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>218307</v>
+        <v>110973</v>
       </c>
       <c r="E14" t="n">
-        <v>36761</v>
+        <v>17549</v>
       </c>
       <c r="F14" t="n">
-        <v>181546</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>26.0%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>26.0%</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>150836</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>+41.2%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>+73.2%</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>3971</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>93424</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>13.9%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>16761</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1116,47 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>450000</v>
+        <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>138916</v>
+        <v>128468</v>
       </c>
       <c r="E15" t="n">
-        <v>1979</v>
+        <v>15277</v>
       </c>
       <c r="F15" t="n">
-        <v>136937</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>31.0%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>31.0%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>100220</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>+34.0%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>+58.4%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>113191</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1166,49 +890,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700000</v>
+        <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>196791</v>
+        <v>69489</v>
       </c>
       <c r="E16" t="n">
-        <v>19466</v>
+        <v>10200</v>
       </c>
       <c r="F16" t="n">
-        <v>177325</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>129968</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>+24.9%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>+58.2%</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>23201</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>59289</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>17.4%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1218,49 +920,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>850000</v>
+        <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>131104</v>
+        <v>196791</v>
       </c>
       <c r="E17" t="n">
-        <v>143498</v>
+        <v>19466</v>
       </c>
       <c r="F17" t="n">
-        <v>-12393</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15.0%</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>153510</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>-17.9%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-110.6%</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>4726</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>177325</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>23201</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1270,49 +952,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>110973</v>
+        <v>283570</v>
       </c>
       <c r="E18" t="n">
-        <v>17549</v>
+        <v>20656</v>
       </c>
       <c r="F18" t="n">
-        <v>93424</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>14.0%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>14.0%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>90617</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>+4.0%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>+313.8%</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>16761</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>262914</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>35.4%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1322,47 +982,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>260000</v>
+        <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>128468</v>
+        <v>131104</v>
       </c>
       <c r="E19" t="n">
-        <v>15277</v>
+        <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>113191</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>49.0%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>49.0%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>15891</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>+597.2%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>+503.2%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>-12393</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>5046</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1372,131 +1014,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>400000</v>
+        <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>69489</v>
+        <v>261354</v>
       </c>
       <c r="E20" t="n">
-        <v>10200</v>
+        <v>20800</v>
       </c>
       <c r="F20" t="n">
-        <v>59289</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>17.0%</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>41988</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>+36.9%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>+245.1%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>销售合计</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4450000</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1020610</v>
-      </c>
-      <c r="E21" t="n">
-        <v>369277</v>
-      </c>
-      <c r="F21" t="n">
-        <v>651331</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>门店合计</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>8260000</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2417282</v>
-      </c>
-      <c r="E22" t="n">
-        <v>310995</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2106288</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>南区总计</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>14410000</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3857213</v>
-      </c>
-      <c r="E23" t="n">
-        <v>733846</v>
-      </c>
-      <c r="F23" t="n">
-        <v>3123366</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>240554</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -473,17 +473,17 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>109898</v>
+        <v>138402</v>
       </c>
       <c r="E2" t="n">
-        <v>74071</v>
+        <v>136369</v>
       </c>
       <c r="F2" t="n">
-        <v>35826</v>
+        <v>2032</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -503,17 +503,17 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19573</v>
+        <v>20291</v>
       </c>
       <c r="E3" t="n">
-        <v>24918</v>
+        <v>25136</v>
       </c>
       <c r="F3" t="n">
-        <v>-5345</v>
+        <v>-4844</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -533,17 +533,17 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>219748</v>
+        <v>249236</v>
       </c>
       <c r="E4" t="n">
-        <v>96943</v>
+        <v>110359</v>
       </c>
       <c r="F4" t="n">
-        <v>122804</v>
+        <v>138876</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -563,17 +563,17 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>192385</v>
+        <v>236399</v>
       </c>
       <c r="E5" t="n">
-        <v>69197</v>
+        <v>69235</v>
       </c>
       <c r="F5" t="n">
-        <v>123188</v>
+        <v>167164</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -593,17 +593,17 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>147918</v>
+        <v>176308</v>
       </c>
       <c r="E6" t="n">
-        <v>46623</v>
+        <v>46713</v>
       </c>
       <c r="F6" t="n">
-        <v>101295</v>
+        <v>129595</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -623,17 +623,17 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>147817</v>
+        <v>162906</v>
       </c>
       <c r="E7" t="n">
         <v>38333</v>
       </c>
       <c r="F7" t="n">
-        <v>109484</v>
+        <v>124573</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -653,17 +653,17 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>183271</v>
+        <v>189181</v>
       </c>
       <c r="E8" t="n">
-        <v>19192</v>
+        <v>25944</v>
       </c>
       <c r="F8" t="n">
-        <v>164079</v>
+        <v>163237</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -683,17 +683,17 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>419321</v>
+        <v>437731</v>
       </c>
       <c r="E9" t="n">
-        <v>53574</v>
+        <v>83374</v>
       </c>
       <c r="F9" t="n">
-        <v>365747</v>
+        <v>354357</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -713,17 +713,17 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>800599</v>
+        <v>840964</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>800599</v>
+        <v>840964</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -743,17 +743,17 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>77711</v>
+        <v>112403</v>
       </c>
       <c r="E11" t="n">
         <v>24809</v>
       </c>
       <c r="F11" t="n">
-        <v>52902</v>
+        <v>87594</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -773,17 +773,17 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>138916</v>
+        <v>149314</v>
       </c>
       <c r="E12" t="n">
         <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>136937</v>
+        <v>147335</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -803,21 +803,21 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>218307</v>
+        <v>250326</v>
       </c>
       <c r="E13" t="n">
-        <v>36761</v>
+        <v>59561</v>
       </c>
       <c r="F13" t="n">
-        <v>181546</v>
+        <v>190765</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3971</v>
+        <v>5694</v>
       </c>
     </row>
     <row r="14">
@@ -835,17 +835,17 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>110973</v>
+        <v>119769</v>
       </c>
       <c r="E14" t="n">
         <v>17549</v>
       </c>
       <c r="F14" t="n">
-        <v>93424</v>
+        <v>102220</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -867,10 +867,10 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>128468</v>
+        <v>128497</v>
       </c>
       <c r="E15" t="n">
-        <v>15277</v>
+        <v>15306</v>
       </c>
       <c r="F15" t="n">
         <v>113191</v>
@@ -897,17 +897,17 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>69489</v>
+        <v>73687</v>
       </c>
       <c r="E16" t="n">
         <v>10200</v>
       </c>
       <c r="F16" t="n">
-        <v>59289</v>
+        <v>63487</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -927,17 +927,17 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>196791</v>
+        <v>206492</v>
       </c>
       <c r="E17" t="n">
         <v>19466</v>
       </c>
       <c r="F17" t="n">
-        <v>177325</v>
+        <v>187026</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -959,17 +959,17 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>283570</v>
+        <v>333275</v>
       </c>
       <c r="E18" t="n">
-        <v>20656</v>
+        <v>35556</v>
       </c>
       <c r="F18" t="n">
-        <v>262914</v>
+        <v>297719</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -989,17 +989,17 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>131104</v>
+        <v>131502</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>-12393</v>
+        <v>-11995</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1021,17 +1021,17 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>261354</v>
+        <v>257036</v>
       </c>
       <c r="E20" t="n">
-        <v>20800</v>
+        <v>13800</v>
       </c>
       <c r="F20" t="n">
-        <v>240554</v>
+        <v>243236</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -713,17 +713,17 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>840964</v>
+        <v>822566</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>840964</v>
+        <v>822566</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>257036</v>
+        <v>282434</v>
       </c>
       <c r="E20" t="n">
-        <v>13800</v>
+        <v>20800</v>
       </c>
       <c r="F20" t="n">
-        <v>243236</v>
+        <v>261634</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -473,17 +473,17 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>138402</v>
+        <v>147117</v>
       </c>
       <c r="E2" t="n">
-        <v>136369</v>
+        <v>141387</v>
       </c>
       <c r="F2" t="n">
-        <v>2032</v>
+        <v>5729</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -503,17 +503,17 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20291</v>
+        <v>20685</v>
       </c>
       <c r="E3" t="n">
-        <v>25136</v>
+        <v>25174</v>
       </c>
       <c r="F3" t="n">
-        <v>-4844</v>
+        <v>-4488</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -533,17 +533,17 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>249236</v>
+        <v>269519</v>
       </c>
       <c r="E4" t="n">
-        <v>110359</v>
+        <v>110444</v>
       </c>
       <c r="F4" t="n">
-        <v>138876</v>
+        <v>159074</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -563,17 +563,17 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>236399</v>
+        <v>241463</v>
       </c>
       <c r="E5" t="n">
-        <v>69235</v>
+        <v>106052</v>
       </c>
       <c r="F5" t="n">
-        <v>167164</v>
+        <v>135411</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -593,17 +593,17 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>176308</v>
+        <v>192883</v>
       </c>
       <c r="E6" t="n">
-        <v>46713</v>
+        <v>48617</v>
       </c>
       <c r="F6" t="n">
-        <v>129595</v>
+        <v>144266</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -623,17 +623,17 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>162906</v>
+        <v>167916</v>
       </c>
       <c r="E7" t="n">
-        <v>38333</v>
+        <v>38351</v>
       </c>
       <c r="F7" t="n">
-        <v>124573</v>
+        <v>129565</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -653,17 +653,17 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>189181</v>
+        <v>213469</v>
       </c>
       <c r="E8" t="n">
-        <v>25944</v>
+        <v>27703</v>
       </c>
       <c r="F8" t="n">
-        <v>163237</v>
+        <v>185766</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -683,17 +683,17 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>437731</v>
+        <v>565827</v>
       </c>
       <c r="E9" t="n">
-        <v>83374</v>
+        <v>136924</v>
       </c>
       <c r="F9" t="n">
-        <v>354357</v>
+        <v>428903</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -743,17 +743,17 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>112403</v>
+        <v>123100</v>
       </c>
       <c r="E11" t="n">
-        <v>24809</v>
+        <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>87594</v>
+        <v>97992</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -803,17 +803,17 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>250326</v>
+        <v>251724</v>
       </c>
       <c r="E13" t="n">
         <v>59561</v>
       </c>
       <c r="F13" t="n">
-        <v>190765</v>
+        <v>192163</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -835,17 +835,17 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>119769</v>
+        <v>129361</v>
       </c>
       <c r="E14" t="n">
-        <v>17549</v>
+        <v>17578</v>
       </c>
       <c r="F14" t="n">
-        <v>102220</v>
+        <v>111783</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -867,17 +867,17 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>128497</v>
+        <v>130575</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>113191</v>
+        <v>115269</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -927,17 +927,17 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>206492</v>
+        <v>235988</v>
       </c>
       <c r="E17" t="n">
-        <v>19466</v>
+        <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>187026</v>
+        <v>200122</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -959,17 +959,17 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>333275</v>
+        <v>345194</v>
       </c>
       <c r="E18" t="n">
-        <v>35556</v>
+        <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>297719</v>
+        <v>293638</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -989,17 +989,17 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>131502</v>
+        <v>172871</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>-11995</v>
+        <v>29373</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1021,17 +1021,17 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>282434</v>
+        <v>328034</v>
       </c>
       <c r="E20" t="n">
-        <v>20800</v>
+        <v>68000</v>
       </c>
       <c r="F20" t="n">
-        <v>261634</v>
+        <v>260034</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -473,17 +473,17 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>147117</v>
+        <v>152458</v>
       </c>
       <c r="E2" t="n">
-        <v>141387</v>
+        <v>141434</v>
       </c>
       <c r="F2" t="n">
-        <v>5729</v>
+        <v>11023</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -503,17 +503,17 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20685</v>
+        <v>20954</v>
       </c>
       <c r="E3" t="n">
-        <v>25174</v>
+        <v>25202</v>
       </c>
       <c r="F3" t="n">
-        <v>-4488</v>
+        <v>-4247</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -533,17 +533,17 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>269519</v>
+        <v>300692</v>
       </c>
       <c r="E4" t="n">
-        <v>110444</v>
+        <v>110614</v>
       </c>
       <c r="F4" t="n">
-        <v>159074</v>
+        <v>190077</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -563,17 +563,17 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>241463</v>
+        <v>241492</v>
       </c>
       <c r="E5" t="n">
         <v>106052</v>
       </c>
       <c r="F5" t="n">
-        <v>135411</v>
+        <v>135440</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -593,17 +593,17 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>192883</v>
+        <v>194727</v>
       </c>
       <c r="E6" t="n">
-        <v>48617</v>
+        <v>49416</v>
       </c>
       <c r="F6" t="n">
-        <v>144266</v>
+        <v>145311</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -623,17 +623,17 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>167916</v>
+        <v>168381</v>
       </c>
       <c r="E7" t="n">
-        <v>38351</v>
+        <v>38389</v>
       </c>
       <c r="F7" t="n">
-        <v>129565</v>
+        <v>129992</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -653,13 +653,13 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>213469</v>
+        <v>213516</v>
       </c>
       <c r="E8" t="n">
-        <v>27703</v>
+        <v>27797</v>
       </c>
       <c r="F8" t="n">
-        <v>185766</v>
+        <v>185719</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -683,17 +683,17 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>565827</v>
+        <v>575827</v>
       </c>
       <c r="E9" t="n">
         <v>136924</v>
       </c>
       <c r="F9" t="n">
-        <v>428903</v>
+        <v>438903</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -743,17 +743,17 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>123100</v>
+        <v>135100</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>97992</v>
+        <v>109992</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -773,17 +773,17 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>149314</v>
+        <v>190906</v>
       </c>
       <c r="E12" t="n">
         <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>147335</v>
+        <v>188927</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -803,17 +803,17 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>251724</v>
+        <v>260039</v>
       </c>
       <c r="E13" t="n">
         <v>59561</v>
       </c>
       <c r="F13" t="n">
-        <v>192163</v>
+        <v>200478</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -835,17 +835,17 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>129361</v>
+        <v>162961</v>
       </c>
       <c r="E14" t="n">
         <v>17578</v>
       </c>
       <c r="F14" t="n">
-        <v>111783</v>
+        <v>145383</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -867,17 +867,17 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>130575</v>
+        <v>132963</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>115269</v>
+        <v>117657</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -897,17 +897,17 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>73687</v>
+        <v>173061</v>
       </c>
       <c r="E16" t="n">
         <v>10200</v>
       </c>
       <c r="F16" t="n">
-        <v>63487</v>
+        <v>162861</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -927,17 +927,17 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>235988</v>
+        <v>249780</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>200122</v>
+        <v>213914</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -959,17 +959,17 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>345194</v>
+        <v>361309</v>
       </c>
       <c r="E18" t="n">
         <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>293638</v>
+        <v>309753</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -989,17 +989,17 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>172871</v>
+        <v>180788</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>29373</v>
+        <v>37290</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1021,17 +1021,17 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>328034</v>
+        <v>343028</v>
       </c>
       <c r="E20" t="n">
         <v>68000</v>
       </c>
       <c r="F20" t="n">
-        <v>260034</v>
+        <v>275028</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -593,13 +593,13 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>194727</v>
+        <v>194756</v>
       </c>
       <c r="E6" t="n">
         <v>49416</v>
       </c>
       <c r="F6" t="n">
-        <v>145311</v>
+        <v>145340</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,10 +449,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>协同双计(元)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>完成率(含协同)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>完成率(不含)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>康博嘉(元)</t>
         </is>
@@ -481,12 +491,20 @@
       <c r="F2" t="n">
         <v>11023</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,12 +529,20 @@
       <c r="F3" t="n">
         <v>-4247</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>21.0%</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21.0%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -541,12 +567,20 @@
       <c r="F4" t="n">
         <v>190077</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>10398</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>37.6%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,12 +605,20 @@
       <c r="F5" t="n">
         <v>135440</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>39588</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>43.2%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>37.2%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -601,12 +643,20 @@
       <c r="F6" t="n">
         <v>145340</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>45600</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>27.8%</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -631,12 +681,20 @@
       <c r="F7" t="n">
         <v>129992</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>30.6%</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -661,12 +719,20 @@
       <c r="F8" t="n">
         <v>185719</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>18796</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>32.8%</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -691,12 +757,20 @@
       <c r="F9" t="n">
         <v>438903</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>33.9%</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -721,12 +795,18 @@
       <c r="F10" t="n">
         <v>822566</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>41.1%</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>41.1%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -751,12 +831,18 @@
       <c r="F11" t="n">
         <v>109992</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -781,12 +867,18 @@
       <c r="F12" t="n">
         <v>188927</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>42.4%</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>42.4%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -811,12 +903,18 @@
       <c r="F13" t="n">
         <v>200478</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>30.6%</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>5694</v>
       </c>
     </row>
@@ -843,12 +941,18 @@
       <c r="F14" t="n">
         <v>145383</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>20.4%</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20.4%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>16761</v>
       </c>
     </row>
@@ -875,12 +979,18 @@
       <c r="F15" t="n">
         <v>117657</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>51.1%</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>51.1%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -905,12 +1015,18 @@
       <c r="F16" t="n">
         <v>162861</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>43.3%</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>43.3%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -935,12 +1051,18 @@
       <c r="F17" t="n">
         <v>213914</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>35.7%</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>23201</v>
       </c>
     </row>
@@ -967,12 +1089,18 @@
       <c r="F18" t="n">
         <v>309753</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>45.2%</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>45.2%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -997,12 +1125,18 @@
       <c r="F19" t="n">
         <v>37290</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>21.3%</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21.3%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>5046</v>
       </c>
     </row>
@@ -1029,12 +1163,18 @@
       <c r="F20" t="n">
         <v>275028</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>49.0%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,21 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>环比收入(元)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>环比增速</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>环比净流水增速</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>康博嘉(元)</t>
         </is>
       </c>
@@ -504,7 +519,20 @@
           <t>15.2%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>489596</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-68.9%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-94.0%</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -542,7 +570,20 @@
           <t>21.0%</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>52936</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-60.4%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-136.1%</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -580,7 +621,20 @@
           <t>37.6%</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>338450</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-11.2%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-17.4%</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -618,7 +672,20 @@
           <t>37.2%</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>353683</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-31.7%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-49.8%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -656,7 +723,20 @@
           <t>27.8%</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>132308</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>+47.2%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>+33.3%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -694,7 +774,20 @@
           <t>30.6%</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>245117</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-31.3%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-11.5%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -732,7 +825,20 @@
           <t>32.8%</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>281619</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-24.2%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>+7.5%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -770,7 +876,20 @@
           <t>33.9%</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>419457</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>+37.3%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>+207.4%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -806,7 +925,20 @@
           <t>41.1%</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>850659</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-3.3%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-3.3%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -842,7 +974,20 @@
           <t>30.0%</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>224984</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-40.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-43.1%</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -878,7 +1023,20 @@
           <t>42.4%</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>132608</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>+44.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>+61.5%</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -915,6 +1073,19 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>341172</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-23.8%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-32.6%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
         <v>5694</v>
       </c>
     </row>
@@ -953,6 +1124,19 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>254608</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-36.0%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-15.3%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>16761</v>
       </c>
     </row>
@@ -990,7 +1174,20 @@
           <t>51.1%</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>53958</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>+146.4%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>+118.4%</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1026,7 +1223,20 @@
           <t>43.3%</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>72782</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>+137.8%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>+272.7%</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1063,6 +1273,19 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>169696</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>+47.2%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>+49.3%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
         <v>23201</v>
       </c>
     </row>
@@ -1100,7 +1323,20 @@
           <t>45.2%</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>481872</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-25.0%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1137,6 +1373,19 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>318999</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-43.3%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-86.0%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
         <v>5046</v>
       </c>
     </row>
@@ -1174,7 +1423,20 @@
           <t>49.0%</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>301372</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>+13.8%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>+2.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,10 +474,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>环比净收入(元)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>环比净流水增速</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>康博嘉(元)</t>
         </is>
@@ -527,12 +532,15 @@
           <t>-68.9%</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="n">
+        <v>182745</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>-94.0%</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,12 +586,15 @@
           <t>-60.4%</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>11750</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>-136.1%</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,12 +640,15 @@
           <t>-11.2%</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>229985</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>-17.4%</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -680,12 +694,15 @@
           <t>-31.7%</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>269766</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>-49.8%</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -731,12 +748,15 @@
           <t>+47.2%</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>109009</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>+33.3%</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -782,12 +802,15 @@
           <t>-31.3%</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>146904</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>-11.5%</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -833,12 +856,15 @@
           <t>-24.2%</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>172720</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>+7.5%</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -884,12 +910,15 @@
           <t>+37.3%</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>142766</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>+207.4%</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -933,12 +962,15 @@
           <t>-3.3%</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>850659</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>-3.3%</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -982,12 +1014,15 @@
           <t>-40.0%</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>193146</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>-43.1%</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1031,12 +1066,15 @@
           <t>+44.0%</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>116989</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>+61.5%</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,12 +1118,15 @@
           <t>-23.8%</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>297417</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>-32.6%</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>5694</v>
       </c>
     </row>
@@ -1131,12 +1172,15 @@
           <t>-36.0%</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>171730</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>-15.3%</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>16761</v>
       </c>
     </row>
@@ -1182,12 +1226,15 @@
           <t>+146.4%</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>53872</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>+118.4%</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1231,12 +1278,15 @@
           <t>+137.8%</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="n">
+        <v>43699</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>+272.7%</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1280,12 +1330,15 @@
           <t>+47.2%</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="n">
+        <v>143255</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>+49.3%</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>23201</v>
       </c>
     </row>
@@ -1331,12 +1384,15 @@
           <t>-25.0%</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="n">
+        <v>311695</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>-0.6%</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1380,12 +1436,15 @@
           <t>-43.3%</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="n">
+        <v>266921</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>-86.0%</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>5046</v>
       </c>
     </row>
@@ -1431,12 +1490,15 @@
           <t>+13.8%</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="n">
+        <v>269592</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>+2.0%</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,41 +503,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>152458</v>
+        <v>223057</v>
       </c>
       <c r="E2" t="n">
-        <v>141434</v>
+        <v>145970</v>
       </c>
       <c r="F2" t="n">
-        <v>11023</v>
+        <v>77086</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>489596</v>
+        <v>520957</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-57.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>182745</v>
+        <v>180343</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-94.0%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -557,41 +557,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20954</v>
+        <v>19889</v>
       </c>
       <c r="E3" t="n">
-        <v>25202</v>
+        <v>25030</v>
       </c>
       <c r="F3" t="n">
-        <v>-4247</v>
+        <v>-5140</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>52936</v>
+        <v>43229</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-60.4%</t>
+          <t>-54.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11750</v>
+        <v>1999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-136.1%</t>
+          <t>-357.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -611,41 +611,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>300692</v>
+        <v>340979</v>
       </c>
       <c r="E4" t="n">
-        <v>110614</v>
+        <v>115969</v>
       </c>
       <c r="F4" t="n">
-        <v>190077</v>
+        <v>225009</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>338450</v>
+        <v>361312</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>229985</v>
+        <v>252659</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -665,41 +665,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>241492</v>
+        <v>391449</v>
       </c>
       <c r="E5" t="n">
         <v>106052</v>
       </c>
       <c r="F5" t="n">
-        <v>135440</v>
+        <v>285397</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>353683</v>
+        <v>423340</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>269766</v>
+        <v>339404</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -719,41 +719,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>194756</v>
+        <v>198996</v>
       </c>
       <c r="E6" t="n">
-        <v>49416</v>
+        <v>57694</v>
       </c>
       <c r="F6" t="n">
-        <v>145340</v>
+        <v>141302</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>132308</v>
+        <v>139498</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+47.2%</t>
+          <t>+42.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>109009</v>
+        <v>104347</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+33.3%</t>
+          <t>+35.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -773,41 +773,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>168381</v>
+        <v>230370</v>
       </c>
       <c r="E7" t="n">
-        <v>38389</v>
+        <v>58681</v>
       </c>
       <c r="F7" t="n">
-        <v>129992</v>
+        <v>171689</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>245117</v>
+        <v>330797</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>146904</v>
+        <v>192965</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -827,41 +827,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>213516</v>
+        <v>276643</v>
       </c>
       <c r="E8" t="n">
-        <v>27797</v>
+        <v>33123</v>
       </c>
       <c r="F8" t="n">
-        <v>185719</v>
+        <v>243520</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>281619</v>
+        <v>317837</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>172720</v>
+        <v>198775</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+22.5%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -881,41 +881,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>575827</v>
+        <v>612146</v>
       </c>
       <c r="E9" t="n">
-        <v>136924</v>
+        <v>140924</v>
       </c>
       <c r="F9" t="n">
-        <v>438903</v>
+        <v>471222</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>419457</v>
+        <v>609057</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+37.3%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>142766</v>
+        <v>327566</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+207.4%</t>
+          <t>+43.9%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -935,39 +935,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>822566</v>
+        <v>1118761</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>822566</v>
+        <v>1118761</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>850659</v>
+        <v>947520</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+18.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>850659</v>
+        <v>947520</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+18.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -987,39 +987,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>135100</v>
+        <v>169833</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>109992</v>
+        <v>144725</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>224984</v>
+        <v>226382</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>193146</v>
+        <v>194544</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1039,39 +1039,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>190906</v>
+        <v>202119</v>
       </c>
       <c r="E12" t="n">
         <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>188927</v>
+        <v>200140</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>132608</v>
+        <v>213020</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+44.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>116989</v>
+        <v>197401</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+61.5%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1091,43 +1091,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>260039</v>
+        <v>297977</v>
       </c>
       <c r="E13" t="n">
         <v>59561</v>
       </c>
       <c r="F13" t="n">
-        <v>200478</v>
+        <v>238416</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>341172</v>
+        <v>367962</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>297417</v>
+        <v>324207</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5694</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="14">
@@ -1145,35 +1145,35 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>162961</v>
+        <v>214688</v>
       </c>
       <c r="E14" t="n">
-        <v>17578</v>
+        <v>18378</v>
       </c>
       <c r="F14" t="n">
-        <v>145383</v>
+        <v>196310</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>254608</v>
+        <v>314627</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>171730</v>
+        <v>231749</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>16761</v>
+        <v>47702</v>
       </c>
     </row>
     <row r="15">
@@ -1199,39 +1199,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>132963</v>
+        <v>134176</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>117657</v>
+        <v>118870</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>53958</v>
+        <v>61964</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+146.4%</t>
+          <t>+116.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>53872</v>
+        <v>61878</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+118.4%</t>
+          <t>+92.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1251,23 +1251,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>173061</v>
+        <v>213446</v>
       </c>
       <c r="E16" t="n">
         <v>10200</v>
       </c>
       <c r="F16" t="n">
-        <v>162861</v>
+        <v>203246</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+137.8%</t>
+          <t>+193.3%</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+272.7%</t>
+          <t>+365.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1303,43 +1303,43 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>249780</v>
+        <v>257611</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>213914</v>
+        <v>221745</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>169696</v>
+        <v>215296</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+47.2%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>143255</v>
+        <v>188855</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+49.3%</t>
+          <t>+17.4%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>23201</v>
+        <v>24031</v>
       </c>
     </row>
     <row r="18">
@@ -1357,39 +1357,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>361309</v>
+        <v>386981</v>
       </c>
       <c r="E18" t="n">
         <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>309753</v>
+        <v>335425</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>481872</v>
+        <v>489072</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>311695</v>
+        <v>289930</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+15.7%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1409,43 +1409,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>180788</v>
+        <v>201978</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>37290</v>
+        <v>58480</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>318999</v>
+        <v>330958</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>266921</v>
+        <v>253580</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-86.0%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5046</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="20">
@@ -1463,39 +1463,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>343028</v>
+        <v>367724</v>
       </c>
       <c r="E20" t="n">
-        <v>68000</v>
+        <v>73000</v>
       </c>
       <c r="F20" t="n">
-        <v>275028</v>
+        <v>294724</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>301372</v>
+        <v>319983</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+13.8%</t>
+          <t>+14.9%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>269592</v>
+        <v>283184</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,41 +503,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>223057</v>
+        <v>177958</v>
       </c>
       <c r="E2" t="n">
-        <v>145970</v>
+        <v>141557</v>
       </c>
       <c r="F2" t="n">
-        <v>77086</v>
+        <v>36400</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>520957</v>
+        <v>489596</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-63.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>180343</v>
+        <v>182745</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -557,41 +557,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19889</v>
+        <v>15875</v>
       </c>
       <c r="E3" t="n">
-        <v>25030</v>
+        <v>25024</v>
       </c>
       <c r="F3" t="n">
-        <v>-5140</v>
+        <v>-9148</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>43229</v>
+        <v>42976</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-63.1%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1999</v>
+        <v>1790</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-357.1%</t>
+          <t>-611.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -611,41 +611,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>340979</v>
+        <v>289068</v>
       </c>
       <c r="E4" t="n">
-        <v>115969</v>
+        <v>110671</v>
       </c>
       <c r="F4" t="n">
-        <v>225009</v>
+        <v>178396</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>361312</v>
+        <v>338450</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>252659</v>
+        <v>229985</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -665,41 +665,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>391449</v>
+        <v>324974</v>
       </c>
       <c r="E5" t="n">
         <v>106052</v>
       </c>
       <c r="F5" t="n">
-        <v>285397</v>
+        <v>218922</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>423340</v>
+        <v>353683</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>339404</v>
+        <v>269766</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -719,41 +719,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>198996</v>
+        <v>196193</v>
       </c>
       <c r="E6" t="n">
-        <v>57694</v>
+        <v>49631</v>
       </c>
       <c r="F6" t="n">
-        <v>141302</v>
+        <v>146562</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>139498</v>
+        <v>132308</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+42.7%</t>
+          <t>+48.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>104347</v>
+        <v>109009</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+35.4%</t>
+          <t>+34.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -773,41 +773,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>230370</v>
+        <v>200489</v>
       </c>
       <c r="E7" t="n">
-        <v>58681</v>
+        <v>38586</v>
       </c>
       <c r="F7" t="n">
-        <v>171689</v>
+        <v>161903</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>330797</v>
+        <v>255077</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>192965</v>
+        <v>156864</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>+3.2%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -827,41 +827,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>276643</v>
+        <v>217769</v>
       </c>
       <c r="E8" t="n">
-        <v>33123</v>
+        <v>33114</v>
       </c>
       <c r="F8" t="n">
-        <v>243520</v>
+        <v>184655</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>317837</v>
+        <v>281619</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>198775</v>
+        <v>172720</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -881,41 +881,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>612146</v>
+        <v>587346</v>
       </c>
       <c r="E9" t="n">
-        <v>140924</v>
+        <v>136924</v>
       </c>
       <c r="F9" t="n">
-        <v>471222</v>
+        <v>450422</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>609057</v>
+        <v>419457</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+40.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>327566</v>
+        <v>142766</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+43.9%</t>
+          <t>+215.5%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -935,39 +935,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1118761</v>
+        <v>1148313</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1118761</v>
+        <v>1148313</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>947520</v>
+        <v>850659</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+18.1%</t>
+          <t>+35.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>947520</v>
+        <v>850659</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+18.1%</t>
+          <t>+35.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -987,39 +987,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>169833</v>
+        <v>151700</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>144725</v>
+        <v>126592</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>226382</v>
+        <v>224984</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>194544</v>
+        <v>193146</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1039,39 +1039,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202119</v>
+        <v>191702</v>
       </c>
       <c r="E12" t="n">
         <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>200140</v>
+        <v>189723</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>213020</v>
+        <v>132608</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>+44.6%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>197401</v>
+        <v>116989</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+62.2%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1091,43 +1091,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>297977</v>
+        <v>267336</v>
       </c>
       <c r="E13" t="n">
         <v>59561</v>
       </c>
       <c r="F13" t="n">
-        <v>238416</v>
+        <v>207775</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>367962</v>
+        <v>341172</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>324207</v>
+        <v>297417</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7737</v>
+        <v>5694</v>
       </c>
     </row>
     <row r="14">
@@ -1145,43 +1145,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>214688</v>
+        <v>204536</v>
       </c>
       <c r="E14" t="n">
         <v>18378</v>
       </c>
       <c r="F14" t="n">
-        <v>196310</v>
+        <v>186158</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>314627</v>
+        <v>254608</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>231749</v>
+        <v>171730</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>47702</v>
+        <v>46744</v>
       </c>
     </row>
     <row r="15">
@@ -1199,39 +1199,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>134176</v>
+        <v>132963</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>118870</v>
+        <v>117657</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>61964</v>
+        <v>53958</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+116.5%</t>
+          <t>+146.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>61878</v>
+        <v>53872</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+92.1%</t>
+          <t>+118.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1303,39 +1303,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>257611</v>
+        <v>256910</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>221745</v>
+        <v>221044</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>215296</v>
+        <v>169696</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+51.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>188855</v>
+        <v>143255</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+17.4%</t>
+          <t>+54.3%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1357,39 +1357,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>386981</v>
+        <v>379683</v>
       </c>
       <c r="E18" t="n">
         <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>335425</v>
+        <v>328127</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>489072</v>
+        <v>481872</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>289930</v>
+        <v>311695</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+15.7%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1409,39 +1409,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>201978</v>
+        <v>186580</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>58480</v>
+        <v>43082</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>330958</v>
+        <v>318999</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>253580</v>
+        <v>266921</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-83.9%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1463,39 +1463,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>367724</v>
+        <v>365128</v>
       </c>
       <c r="E20" t="n">
-        <v>73000</v>
+        <v>68000</v>
       </c>
       <c r="F20" t="n">
-        <v>294724</v>
+        <v>297128</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>319983</v>
+        <v>301372</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>+21.2%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>283184</v>
+        <v>269592</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+10.2%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,41 +503,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>177958</v>
+        <v>223057</v>
       </c>
       <c r="E2" t="n">
-        <v>141557</v>
+        <v>145970</v>
       </c>
       <c r="F2" t="n">
-        <v>36400</v>
+        <v>77086</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>489596</v>
+        <v>520957</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-57.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>182745</v>
+        <v>180343</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-57.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -557,41 +557,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>15875</v>
+        <v>19889</v>
       </c>
       <c r="E3" t="n">
-        <v>25024</v>
+        <v>25030</v>
       </c>
       <c r="F3" t="n">
-        <v>-9148</v>
+        <v>-5140</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>42976</v>
+        <v>43229</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-54.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1790</v>
+        <v>1999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-611.0%</t>
+          <t>-357.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -611,41 +611,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>289068</v>
+        <v>340979</v>
       </c>
       <c r="E4" t="n">
-        <v>110671</v>
+        <v>115969</v>
       </c>
       <c r="F4" t="n">
-        <v>178396</v>
+        <v>225009</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>338450</v>
+        <v>361312</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>229985</v>
+        <v>252659</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -665,41 +665,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>324974</v>
+        <v>391449</v>
       </c>
       <c r="E5" t="n">
         <v>106052</v>
       </c>
       <c r="F5" t="n">
-        <v>218922</v>
+        <v>285397</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>353683</v>
+        <v>423340</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>269766</v>
+        <v>339404</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -719,41 +719,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>196193</v>
+        <v>198996</v>
       </c>
       <c r="E6" t="n">
-        <v>49631</v>
+        <v>57694</v>
       </c>
       <c r="F6" t="n">
-        <v>146562</v>
+        <v>141302</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>132308</v>
+        <v>139498</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+48.3%</t>
+          <t>+42.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>109009</v>
+        <v>104347</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+34.4%</t>
+          <t>+35.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -773,41 +773,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>200489</v>
+        <v>230370</v>
       </c>
       <c r="E7" t="n">
-        <v>38586</v>
+        <v>58681</v>
       </c>
       <c r="F7" t="n">
-        <v>161903</v>
+        <v>171689</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>255077</v>
+        <v>330797</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>156864</v>
+        <v>192965</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -827,41 +827,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>217769</v>
+        <v>276643</v>
       </c>
       <c r="E8" t="n">
-        <v>33114</v>
+        <v>33123</v>
       </c>
       <c r="F8" t="n">
-        <v>184655</v>
+        <v>243520</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>281619</v>
+        <v>317837</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>172720</v>
+        <v>198775</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+6.9%</t>
+          <t>+22.5%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -881,41 +881,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>587346</v>
+        <v>612146</v>
       </c>
       <c r="E9" t="n">
-        <v>136924</v>
+        <v>140924</v>
       </c>
       <c r="F9" t="n">
-        <v>450422</v>
+        <v>471222</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>419457</v>
+        <v>609057</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+40.0%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>142766</v>
+        <v>327566</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+215.5%</t>
+          <t>+43.9%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -935,39 +935,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1148313</v>
+        <v>1118761</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1148313</v>
+        <v>1118761</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>850659</v>
+        <v>947520</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+35.0%</t>
+          <t>+18.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>850659</v>
+        <v>947520</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+35.0%</t>
+          <t>+18.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -987,39 +987,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>151700</v>
+        <v>169833</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>126592</v>
+        <v>144725</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>224984</v>
+        <v>226382</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>193146</v>
+        <v>194544</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1039,39 +1039,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>191702</v>
+        <v>202119</v>
       </c>
       <c r="E12" t="n">
         <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>189723</v>
+        <v>200140</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>132608</v>
+        <v>213020</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+44.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>116989</v>
+        <v>197401</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+62.2%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1091,43 +1091,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>267336</v>
+        <v>297977</v>
       </c>
       <c r="E13" t="n">
         <v>59561</v>
       </c>
       <c r="F13" t="n">
-        <v>207775</v>
+        <v>238416</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>341172</v>
+        <v>367962</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>297417</v>
+        <v>324207</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5694</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="14">
@@ -1145,43 +1145,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>204536</v>
+        <v>214688</v>
       </c>
       <c r="E14" t="n">
         <v>18378</v>
       </c>
       <c r="F14" t="n">
-        <v>186158</v>
+        <v>196310</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>254608</v>
+        <v>314627</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>171730</v>
+        <v>231749</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+8.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>46744</v>
+        <v>47702</v>
       </c>
     </row>
     <row r="15">
@@ -1199,39 +1199,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>132963</v>
+        <v>134176</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>117657</v>
+        <v>118870</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>53958</v>
+        <v>61964</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+146.4%</t>
+          <t>+116.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>53872</v>
+        <v>61878</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+118.4%</t>
+          <t>+92.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1303,39 +1303,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>256910</v>
+        <v>257611</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>221044</v>
+        <v>221745</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>169696</v>
+        <v>215296</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+51.4%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>143255</v>
+        <v>188855</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+54.3%</t>
+          <t>+17.4%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1357,39 +1357,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>379683</v>
+        <v>386981</v>
       </c>
       <c r="E18" t="n">
         <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>328127</v>
+        <v>335425</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>481872</v>
+        <v>489072</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>311695</v>
+        <v>289930</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+15.7%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1409,39 +1409,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>186580</v>
+        <v>201978</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>43082</v>
+        <v>58480</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>318999</v>
+        <v>330958</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>266921</v>
+        <v>253580</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-83.9%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1463,39 +1463,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>365128</v>
+        <v>367724</v>
       </c>
       <c r="E20" t="n">
-        <v>68000</v>
+        <v>73000</v>
       </c>
       <c r="F20" t="n">
-        <v>297128</v>
+        <v>294724</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>301372</v>
+        <v>319983</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+21.2%</t>
+          <t>+14.9%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>269592</v>
+        <v>283184</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+10.2%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -935,23 +935,23 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1118761</v>
+        <v>1001391</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1118761</v>
+        <v>1001391</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -959,7 +959,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+18.1%</t>
+          <t>+5.7%</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+18.1%</t>
+          <t>+5.7%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -890,11 +890,11 @@
         <v>471222</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>88806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -955,19 +955,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>947520</v>
+        <v>807309</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+5.7%</t>
+          <t>+24.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>947520</v>
+        <v>807309</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+5.7%</t>
+          <t>+24.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,41 +503,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>223057</v>
+        <v>233339</v>
       </c>
       <c r="E2" t="n">
-        <v>145970</v>
+        <v>151243</v>
       </c>
       <c r="F2" t="n">
-        <v>77086</v>
+        <v>82095</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>520957</v>
+        <v>521120</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-57.2%</t>
+          <t>-55.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>180343</v>
+        <v>180392</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-57.3%</t>
+          <t>-54.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -557,41 +557,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>19889</v>
+        <v>20351</v>
       </c>
       <c r="E3" t="n">
-        <v>25030</v>
+        <v>27035</v>
       </c>
       <c r="F3" t="n">
-        <v>-5140</v>
+        <v>-6683</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>43229</v>
+        <v>43971</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-53.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1999</v>
+        <v>2669</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-357.1%</t>
+          <t>-350.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -611,41 +611,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>340979</v>
+        <v>391271</v>
       </c>
       <c r="E4" t="n">
-        <v>115969</v>
+        <v>117731</v>
       </c>
       <c r="F4" t="n">
-        <v>225009</v>
+        <v>273539</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>361312</v>
+        <v>389335</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>252659</v>
+        <v>280553</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -665,41 +665,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>391449</v>
+        <v>397481</v>
       </c>
       <c r="E5" t="n">
-        <v>106052</v>
+        <v>106071</v>
       </c>
       <c r="F5" t="n">
-        <v>285397</v>
+        <v>291410</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>423340</v>
+        <v>490592</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>339404</v>
+        <v>406656</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -719,41 +719,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>198996</v>
+        <v>203275</v>
       </c>
       <c r="E6" t="n">
-        <v>57694</v>
+        <v>63093</v>
       </c>
       <c r="F6" t="n">
-        <v>141302</v>
+        <v>140182</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>139498</v>
+        <v>150367</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+42.7%</t>
+          <t>+35.2%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>104347</v>
+        <v>115043</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+35.4%</t>
+          <t>+21.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -773,41 +773,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>230370</v>
+        <v>233541</v>
       </c>
       <c r="E7" t="n">
-        <v>58681</v>
+        <v>58719</v>
       </c>
       <c r="F7" t="n">
-        <v>171689</v>
+        <v>174822</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>330797</v>
+        <v>338272</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>192965</v>
+        <v>200440</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -827,41 +827,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>276643</v>
+        <v>289043</v>
       </c>
       <c r="E8" t="n">
-        <v>33123</v>
+        <v>33199</v>
       </c>
       <c r="F8" t="n">
-        <v>243520</v>
+        <v>255844</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>317837</v>
+        <v>326900</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>198775</v>
+        <v>207661</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>+23.2%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -881,41 +881,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>612146</v>
+        <v>669666</v>
       </c>
       <c r="E9" t="n">
-        <v>140924</v>
+        <v>146924</v>
       </c>
       <c r="F9" t="n">
-        <v>471222</v>
+        <v>522742</v>
       </c>
       <c r="G9" t="n">
         <v>88806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>609057</v>
+        <v>668657</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>327566</v>
+        <v>387166</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+43.9%</t>
+          <t>+35.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -935,39 +935,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1001391</v>
+        <v>2003627</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1001391</v>
+        <v>2003627</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>807309</v>
+        <v>887195</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+24.0%</t>
+          <t>+125.8%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>807309</v>
+        <v>887195</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+24.0%</t>
+          <t>+125.8%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -987,39 +987,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>169833</v>
+        <v>186033</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>144725</v>
+        <v>160925</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>226382</v>
+        <v>226780</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>194544</v>
+        <v>194942</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1039,39 +1039,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202119</v>
+        <v>202517</v>
       </c>
       <c r="E12" t="n">
         <v>1979</v>
       </c>
       <c r="F12" t="n">
-        <v>200140</v>
+        <v>200538</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>213020</v>
+        <v>217000</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>197401</v>
+        <v>201381</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1091,43 +1091,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>297977</v>
+        <v>309005</v>
       </c>
       <c r="E13" t="n">
-        <v>59561</v>
+        <v>61761</v>
       </c>
       <c r="F13" t="n">
-        <v>238416</v>
+        <v>247244</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>367962</v>
+        <v>398375</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>324207</v>
+        <v>354620</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7737</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="14">
@@ -1145,13 +1145,13 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>214688</v>
+        <v>214429</v>
       </c>
       <c r="E14" t="n">
         <v>18378</v>
       </c>
       <c r="F14" t="n">
-        <v>196310</v>
+        <v>196051</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1165,23 +1165,23 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>314627</v>
+        <v>354421</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>231749</v>
+        <v>271543</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>47702</v>
+        <v>47026</v>
       </c>
     </row>
     <row r="15">
@@ -1199,39 +1199,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>134176</v>
+        <v>155694</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>118870</v>
+        <v>140388</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>61964</v>
+        <v>102764</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+116.5%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>61878</v>
+        <v>102678</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+92.1%</t>
+          <t>+36.7%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1251,39 +1251,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>213446</v>
+        <v>218434</v>
       </c>
       <c r="E16" t="n">
         <v>10200</v>
       </c>
       <c r="F16" t="n">
-        <v>203246</v>
+        <v>208234</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>72782</v>
+        <v>127780</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+193.3%</t>
+          <t>+70.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>43699</v>
+        <v>98697</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+365.1%</t>
+          <t>+111.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1303,39 +1303,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>257611</v>
+        <v>258047</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>221745</v>
+        <v>222181</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>215296</v>
+        <v>231970</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+11.2%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>188855</v>
+        <v>205529</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+17.4%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1357,39 +1357,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>386981</v>
+        <v>391172</v>
       </c>
       <c r="E18" t="n">
         <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>335425</v>
+        <v>339616</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>489072</v>
+        <v>499470</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>289930</v>
+        <v>300243</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+15.7%</t>
+          <t>+13.1%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1409,43 +1409,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>201978</v>
+        <v>213091</v>
       </c>
       <c r="E19" t="n">
         <v>143498</v>
       </c>
       <c r="F19" t="n">
-        <v>58480</v>
+        <v>69593</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>330958</v>
+        <v>339656</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-37.3%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>253580</v>
+        <v>262278</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6942</v>
+        <v>7657</v>
       </c>
     </row>
     <row r="20">
@@ -1463,39 +1463,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>367724</v>
+        <v>368141</v>
       </c>
       <c r="E20" t="n">
         <v>73000</v>
       </c>
       <c r="F20" t="n">
-        <v>294724</v>
+        <v>295141</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>319983</v>
+        <v>370979</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>283184</v>
+        <v>334180</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -935,23 +935,23 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>2003627</v>
+        <v>1027177</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2003627</v>
+        <v>1027177</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -959,7 +959,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+125.8%</t>
+          <t>+15.8%</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+125.8%</t>
+          <t>+15.8%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,41 +503,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>233339</v>
+        <v>233638</v>
       </c>
       <c r="E2" t="n">
-        <v>151243</v>
+        <v>151290</v>
       </c>
       <c r="F2" t="n">
-        <v>82095</v>
+        <v>82347</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>521120</v>
+        <v>577590</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-59.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>180392</v>
+        <v>232575</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-64.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>43971</v>
+        <v>44408</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-53.7%</t>
+          <t>-54.2%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2669</v>
+        <v>3002</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-350.4%</t>
+          <t>-322.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -611,41 +611,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>391271</v>
+        <v>393033</v>
       </c>
       <c r="E4" t="n">
-        <v>117731</v>
+        <v>122034</v>
       </c>
       <c r="F4" t="n">
-        <v>273539</v>
+        <v>270998</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>389335</v>
+        <v>396520</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>280553</v>
+        <v>287559</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -665,41 +665,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>397481</v>
+        <v>399527</v>
       </c>
       <c r="E5" t="n">
-        <v>106071</v>
+        <v>106176</v>
       </c>
       <c r="F5" t="n">
-        <v>291410</v>
+        <v>293351</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>490592</v>
+        <v>524239</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>406656</v>
+        <v>440303</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -719,41 +719,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>203275</v>
+        <v>212385</v>
       </c>
       <c r="E6" t="n">
-        <v>63093</v>
+        <v>63477</v>
       </c>
       <c r="F6" t="n">
-        <v>140182</v>
+        <v>148908</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>150367</v>
+        <v>158812</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+35.2%</t>
+          <t>+33.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>115043</v>
+        <v>123354</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+21.9%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -773,41 +773,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>233541</v>
+        <v>245788</v>
       </c>
       <c r="E7" t="n">
-        <v>58719</v>
+        <v>61614</v>
       </c>
       <c r="F7" t="n">
-        <v>174822</v>
+        <v>184174</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>338272</v>
+        <v>339956</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>200440</v>
+        <v>202115</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -827,41 +827,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>289043</v>
+        <v>290524</v>
       </c>
       <c r="E8" t="n">
-        <v>33199</v>
+        <v>33303</v>
       </c>
       <c r="F8" t="n">
-        <v>255844</v>
+        <v>257221</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>326900</v>
+        <v>328452</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>207661</v>
+        <v>209112</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+23.2%</t>
+          <t>+23.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -881,41 +881,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>669666</v>
+        <v>680573</v>
       </c>
       <c r="E9" t="n">
         <v>146924</v>
       </c>
       <c r="F9" t="n">
-        <v>522742</v>
+        <v>533649</v>
       </c>
       <c r="G9" t="n">
         <v>88806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>668657</v>
+        <v>698486</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>387166</v>
+        <v>416995</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+35.0%</t>
+          <t>+28.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -935,39 +935,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1027177</v>
+        <v>1081485</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1027177</v>
+        <v>1081485</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>887195</v>
+        <v>968885</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+15.8%</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>887195</v>
+        <v>968885</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+15.8%</t>
+          <t>+11.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -987,39 +987,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>186033</v>
+        <v>214233</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>160925</v>
+        <v>189125</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>226780</v>
+        <v>227378</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>194942</v>
+        <v>195521</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1039,39 +1039,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202517</v>
+        <v>202915</v>
       </c>
       <c r="E12" t="n">
-        <v>1979</v>
+        <v>1998</v>
       </c>
       <c r="F12" t="n">
-        <v>200538</v>
+        <v>200917</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>217000</v>
+        <v>228194</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>201381</v>
+        <v>212575</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1091,43 +1091,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>309005</v>
+        <v>336875</v>
       </c>
       <c r="E13" t="n">
-        <v>61761</v>
+        <v>65761</v>
       </c>
       <c r="F13" t="n">
-        <v>247244</v>
+        <v>271114</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>398375</v>
+        <v>417171</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>354620</v>
+        <v>373416</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>8765</v>
+        <v>9419</v>
       </c>
     </row>
     <row r="14">
@@ -1145,39 +1145,39 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>214429</v>
+        <v>216621</v>
       </c>
       <c r="E14" t="n">
         <v>18378</v>
       </c>
       <c r="F14" t="n">
-        <v>196051</v>
+        <v>198243</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>354421</v>
+        <v>479274</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-54.8%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>271543</v>
+        <v>396377</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1199,39 +1199,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>155694</v>
+        <v>164092</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>140388</v>
+        <v>148786</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>102764</v>
+        <v>117644</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+39.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>102678</v>
+        <v>117558</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+36.7%</t>
+          <t>+26.6%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1271,19 +1271,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>127780</v>
+        <v>134797</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+70.9%</t>
+          <t>+62.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>98697</v>
+        <v>105714</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+111.0%</t>
+          <t>+97.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1303,39 +1303,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>258047</v>
+        <v>288451</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>222181</v>
+        <v>252585</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>231970</v>
+        <v>232368</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+11.2%</t>
+          <t>+24.1%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>205529</v>
+        <v>205927</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+22.7%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1357,39 +1357,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>391172</v>
+        <v>419490</v>
       </c>
       <c r="E18" t="n">
         <v>51556</v>
       </c>
       <c r="F18" t="n">
-        <v>339616</v>
+        <v>367934</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>499470</v>
+        <v>539760</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>300243</v>
+        <v>340533</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>+8.0%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1409,39 +1409,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>213091</v>
+        <v>224526</v>
       </c>
       <c r="E19" t="n">
-        <v>143498</v>
+        <v>143527</v>
       </c>
       <c r="F19" t="n">
-        <v>69593</v>
+        <v>80999</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>339656</v>
+        <v>359656</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>262278</v>
+        <v>282278</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1463,13 +1463,13 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>368141</v>
+        <v>368539</v>
       </c>
       <c r="E20" t="n">
         <v>73000</v>
       </c>
       <c r="F20" t="n">
-        <v>295141</v>
+        <v>295539</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>370979</v>
+        <v>393177</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>334180</v>
+        <v>356378</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -503,41 +503,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>233638</v>
+        <v>303384</v>
       </c>
       <c r="E2" t="n">
-        <v>151290</v>
+        <v>155459</v>
       </c>
       <c r="F2" t="n">
-        <v>82347</v>
+        <v>147924</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>577590</v>
+        <v>599977</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-59.5%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>232575</v>
+        <v>248659</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-64.6%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -557,13 +557,13 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20351</v>
+        <v>20389</v>
       </c>
       <c r="E3" t="n">
-        <v>27035</v>
+        <v>30421</v>
       </c>
       <c r="F3" t="n">
-        <v>-6683</v>
+        <v>-10031</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>44408</v>
+        <v>44992</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-54.2%</t>
+          <t>-54.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3002</v>
+        <v>3476</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-322.6%</t>
+          <t>-388.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -611,41 +611,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>393033</v>
+        <v>408358</v>
       </c>
       <c r="E4" t="n">
-        <v>122034</v>
+        <v>123086</v>
       </c>
       <c r="F4" t="n">
-        <v>270998</v>
+        <v>285271</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>396520</v>
+        <v>432281</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>287559</v>
+        <v>318386</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -665,13 +665,13 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>399527</v>
+        <v>399845</v>
       </c>
       <c r="E5" t="n">
         <v>106176</v>
       </c>
       <c r="F5" t="n">
-        <v>293351</v>
+        <v>293669</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>524239</v>
+        <v>556036</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>440303</v>
+        <v>434100</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -719,41 +719,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>212385</v>
+        <v>253411</v>
       </c>
       <c r="E6" t="n">
-        <v>63477</v>
+        <v>64218</v>
       </c>
       <c r="F6" t="n">
-        <v>148908</v>
+        <v>189193</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>158812</v>
+        <v>223847</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+33.7%</t>
+          <t>+13.2%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>123354</v>
+        <v>188287</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -773,41 +773,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>245788</v>
+        <v>258264</v>
       </c>
       <c r="E7" t="n">
-        <v>61614</v>
+        <v>62250</v>
       </c>
       <c r="F7" t="n">
-        <v>184174</v>
+        <v>196014</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>339956</v>
+        <v>396282</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>202115</v>
+        <v>251416</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -827,41 +827,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>290524</v>
+        <v>292471</v>
       </c>
       <c r="E8" t="n">
-        <v>33303</v>
+        <v>33474</v>
       </c>
       <c r="F8" t="n">
-        <v>257221</v>
+        <v>258997</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>328452</v>
+        <v>336376</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>209112</v>
+        <v>207731</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+23.0%</t>
+          <t>+24.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -881,41 +881,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>680573</v>
+        <v>670632</v>
       </c>
       <c r="E9" t="n">
-        <v>146924</v>
+        <v>160124</v>
       </c>
       <c r="F9" t="n">
-        <v>533649</v>
+        <v>510508</v>
       </c>
       <c r="G9" t="n">
         <v>88806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>698486</v>
+        <v>782886</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>416995</v>
+        <v>462995</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+28.0%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -935,39 +935,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1081485</v>
+        <v>1107289</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1081485</v>
+        <v>1107289</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>968885</v>
+        <v>987408</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+12.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>968885</v>
+        <v>987408</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+11.6%</t>
+          <t>+12.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -987,39 +987,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>214233</v>
+        <v>231252</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>189125</v>
+        <v>206144</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>227378</v>
+        <v>259599</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>195521</v>
+        <v>227742</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1039,39 +1039,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>202915</v>
+        <v>246715</v>
       </c>
       <c r="E12" t="n">
         <v>1998</v>
       </c>
       <c r="F12" t="n">
-        <v>200917</v>
+        <v>244717</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>228194</v>
+        <v>228592</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>212575</v>
+        <v>212973</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>+14.9%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1091,43 +1091,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>336875</v>
+        <v>379795</v>
       </c>
       <c r="E13" t="n">
-        <v>65761</v>
+        <v>76509</v>
       </c>
       <c r="F13" t="n">
-        <v>271114</v>
+        <v>303286</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>417171</v>
+        <v>418982</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>-9.4%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>375227</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>-19.2%</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>373416</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-27.4%</t>
-        </is>
-      </c>
       <c r="N13" t="n">
-        <v>9419</v>
+        <v>9639</v>
       </c>
     </row>
     <row r="14">
@@ -1145,13 +1145,13 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>216621</v>
+        <v>217019</v>
       </c>
       <c r="E14" t="n">
-        <v>18378</v>
+        <v>21378</v>
       </c>
       <c r="F14" t="n">
-        <v>198243</v>
+        <v>195641</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>479274</v>
+        <v>512933</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-54.8%</t>
+          <t>-57.7%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>396377</v>
+        <v>430036</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-54.5%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1199,39 +1199,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>164092</v>
+        <v>164490</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>148786</v>
+        <v>149184</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>117644</v>
+        <v>176842</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+39.5%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>117558</v>
+        <v>176756</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+26.6%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1251,23 +1251,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>218434</v>
+        <v>218833</v>
       </c>
       <c r="E16" t="n">
-        <v>10200</v>
+        <v>43000</v>
       </c>
       <c r="F16" t="n">
-        <v>208234</v>
+        <v>175833</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+62.0%</t>
+          <t>+62.3%</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+97.0%</t>
+          <t>+66.3%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1303,39 +1303,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>288451</v>
+        <v>296047</v>
       </c>
       <c r="E17" t="n">
         <v>35866</v>
       </c>
       <c r="F17" t="n">
-        <v>252585</v>
+        <v>260181</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>232368</v>
+        <v>251002</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+24.1%</t>
+          <t>+17.9%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>205927</v>
+        <v>224533</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+22.7%</t>
+          <t>+15.9%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1357,39 +1357,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>419490</v>
+        <v>420707</v>
       </c>
       <c r="E18" t="n">
-        <v>51556</v>
+        <v>115542</v>
       </c>
       <c r="F18" t="n">
-        <v>367934</v>
+        <v>305165</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>539760</v>
+        <v>548514</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>340533</v>
+        <v>349287</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+8.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1409,39 +1409,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>224526</v>
+        <v>232443</v>
       </c>
       <c r="E19" t="n">
         <v>143527</v>
       </c>
       <c r="F19" t="n">
-        <v>80999</v>
+        <v>88916</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>359656</v>
+        <v>426666</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>282278</v>
+        <v>349288</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1463,39 +1463,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>368539</v>
+        <v>385933</v>
       </c>
       <c r="E20" t="n">
-        <v>73000</v>
+        <v>76000</v>
       </c>
       <c r="F20" t="n">
-        <v>295539</v>
+        <v>309933</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>393177</v>
+        <v>415177</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>356378</v>
+        <v>378378</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -987,13 +987,13 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>231252</v>
+        <v>231516</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>206144</v>
+        <v>206408</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1019,10 +1019,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-9.5%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>-9.4%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1357,23 +1359,23 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>420707</v>
+        <v>442207</v>
       </c>
       <c r="E18" t="n">
         <v>115542</v>
       </c>
       <c r="F18" t="n">
-        <v>305165</v>
+        <v>326665</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1381,7 +1383,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1389,10 +1391,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-12.6%</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>-6.5%</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>21500</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -7,7 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上个人" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线下个案" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品主线" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产品退费" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款原因" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款分组" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款服务类型" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款省份" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电话" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协同" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1507,4 +1517,6879 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>呼出</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>90s以上</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>时长(分)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>加微信</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>销售</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>386</v>
+      </c>
+      <c r="C2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1386</v>
+      </c>
+      <c r="E2" t="n">
+        <v>74394</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>542.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>859</v>
+      </c>
+      <c r="C4" t="n">
+        <v>187</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1978.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>协同金额(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10398</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>18796</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88806</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>45600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>39588</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>销售</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>本月退费</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>退费率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本月净流水</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>李钰坤</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>128929.9</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>43.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>23298</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>105631.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>闫丽东</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>38880</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3386</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8.7%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>35494</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>唐歌</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>35820</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8366.66</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>27453.34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>何媛媛</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13620</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9.1%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>33500</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>246.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>-19880</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>于鹏飞</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60740</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40.5%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>28983</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>47.7%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>31757</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>刘学锟</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7960</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>李洋洋</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26140</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>65.3%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6140</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>张露</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7960</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>17700</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>222.4%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>-9740</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>高曌</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>120090</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>92.4%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5378</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>114712</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>黄梦妹</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>27860</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>27.9%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>27860</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>刘孟杰</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>46720</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>35.9%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4183</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>9.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>42537</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>司法</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39800</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>9960</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>29840</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>王渊亮</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>49080</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30.7%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>16710</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>34.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>32370</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>郑美琦</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>74340</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>57.2%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>49920</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>67.2%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>24420</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>梁志超</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>134776</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>44.9%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>66228</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>49.1%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>68548</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>丁蕾</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>261308.01</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>87.1%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>261308.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>周紫姻</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>陈斌斌</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>51740</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>64.7%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2596.6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>49143.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>段继宇</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7768</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>53.4%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>樊帆</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>36548</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>45.7%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3156.67</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8.6%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>33391.33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>刘俊彤</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>41529.9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>27.7%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>12179</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>29.3%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>29350.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>卢忠慧</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23688</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>33.8%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>21.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>18708</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>王蓉</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7768</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>64.1%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>严闽龙</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>26500</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>33.1%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>26500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>闫文奇</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>27860</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>22880</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>岳跃峰</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>107704</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>43.1%</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>9880</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>9.2%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>97824</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>车宏祥</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>60940</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30.5%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>29800</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>31140</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>高铭瑞</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>49780</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>49.8%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>49780</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>陈志强</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>32840</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>32.8%</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>32840</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>关万辉</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>51420</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>49420</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>刘士明</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>56438</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>37.6%</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>11580</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>44858</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>肖伟</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>108800</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>101100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>郑理</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>26500</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>33.1%</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4980</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>21520</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>张孟蝶</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>81260</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>48574</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>59.8%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>32686</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>江敏</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>54320</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>27.2%</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>18.4%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>44320</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>武存英</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>19300</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>19300</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>王航</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>180000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>91100</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>27.2%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>66300</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>李天阳</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D39" t="n">
+        <v>46400</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>46.4%</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>41450</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>姜人荷</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D40" t="n">
+        <v>76108</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>63.4%</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7.9%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>70108</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>安百柠</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>33380</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>33380</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>冯岚</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>21298</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>17.7%</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>21298</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>郑鲁</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>61920</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>57920</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>张天昂</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>-13200</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>周玉枝</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>86488</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>86.5%</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>86488</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>龙少海</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D46" t="n">
+        <v>66000</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>37.6%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>41200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分院</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>个案经理</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>完成率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>本月退费</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>退费率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>本月净流水</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>陈新星</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>134000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23796</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>15218</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>8578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>田婉丽</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>116462</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>116.5%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>116462</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>罗晗</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15373</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>64.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>15373</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>林峻民</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8786</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>8786</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>朱锋剑</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18796</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20.9%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>18796</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>孙君兰</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>38739.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>29.8%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>320</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>38419.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>李雅玲</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>89200</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>74.3%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>86500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>陈紫灵</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>49287.58</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>41.1%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>140400</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>284.9%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>-91112.42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>米兰兰</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>33400</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>55.7%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>33400</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>胡梦莉</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>陈洁</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>113141</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>37.7%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>113141</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>李怡慧</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>119117</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>39.7%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>119117</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>王倩雅</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>260313.46</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>65.1%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>260313.46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>韦微</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>113419.74</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>45.4%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>113419.74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>李浩然</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>120706</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>48.3%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>120706</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>李菲菲</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>149454</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>49.8%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>149454</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>唐晟</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>14174</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>28.3%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>14174</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>余佼</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>79956</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>79956</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>王凯</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25198</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>50.4%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>25198</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>韩雪</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>58396.00000000001</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>58.4%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>58396.00000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>陈翔宇</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>28080</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>28.1%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>28080</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>岳伟伟</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>280000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>173258</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>67588</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>39.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>105670</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>陶雯</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7796</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>6998</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>89.8%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>赵越</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>73000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>145360.01</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>199.1%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>22400</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>15.4%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>122960.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>余婉丽</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>398</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>王秋</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>81774</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>73774</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>钟燕红</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>270000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>181610.15</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>67.3%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>40580</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>141030.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>田奇</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>50804.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>50804.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>李明</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>89184</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>74.3%</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>14.6%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>76184</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>苏怡意</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>30646.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4398</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>14.4%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>26248.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>姜玮</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>26008</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>18008</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>李家慧</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>陈静</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>86990</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>72.5%</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>86990</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>李颜君</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1592</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>谌黎平</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>87392</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>218.5%</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>87392</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>马春兰</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>21592</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>27.0%</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>7.8%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>19912</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>蔡清霞</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>47794</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>119.5%</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>47794</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>吴静文</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>许冰</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D40" t="n">
+        <v>120386</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7.3%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>111586</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>白蕾</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16588</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>16588</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>王芊雅</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>21398</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10.7%</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>25200</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>117.8%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>-3802</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>刘沁</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>77852</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>51.9%</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>77852</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>褚月月</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D44" t="n">
+        <v>77454</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>51.6%</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>77454</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>黄雅晴</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>68520</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>68520</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>郑巨光</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D46" t="n">
+        <v>71896</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>35.9%</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>71896</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>陈舒羽</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D47" t="n">
+        <v>81780</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>81780</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>沈悦</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D48" t="n">
+        <v>51222</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>42.7%</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>51222</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>尹欢</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D49" t="n">
+        <v>8398</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>76.2%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>庄鑫</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>张回</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>66.0%</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>陈月娇</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D52" t="n">
+        <v>85988</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>71.7%</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>28.8%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>61188</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>刘玉静</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D53" t="n">
+        <v>91674</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>43.7%</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>91674</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>杨红瑞</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>107400</v>
+      </c>
+      <c r="D54" t="n">
+        <v>42198</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>42198</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>普元媛</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2796</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>马奇君</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>33.0%</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>曾妍妍</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23086</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>34.7%</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>15086</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>张虹</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D58" t="n">
+        <v>64778</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>54.0%</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>24800</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>38.3%</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>39978</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>朱碧丹</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D59" t="n">
+        <v>116370</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>10200</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>106170</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>王钰尧</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D60" t="n">
+        <v>14588</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>14588</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>邓璐</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>334800</v>
+      </c>
+      <c r="D61" t="n">
+        <v>111452.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>111452.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>马雅丽</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>204401</v>
+      </c>
+      <c r="D62" t="n">
+        <v>20745.22</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1212</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>19533.22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>周思若</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>259200</v>
+      </c>
+      <c r="D63" t="n">
+        <v>83370.98</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>32.2%</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>15200</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>68170.98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>袁登玉</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>20796</v>
+      </c>
+      <c r="D64" t="n">
+        <v>398</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>邝玉萍</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>15378</v>
+      </c>
+      <c r="D65" t="n">
+        <v>996</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>主线</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>子结构</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>成交额(元)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>单数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>线上(元)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>线下(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程线</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1420465.02</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3868</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1226619.02</v>
+      </c>
+      <c r="F2" t="n">
+        <v>193846</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程线</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>正价课</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1307628</v>
+      </c>
+      <c r="D3" t="n">
+        <v>269</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1117528</v>
+      </c>
+      <c r="F3" t="n">
+        <v>190100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程线</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>引流品</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>112837.02</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3599</v>
+      </c>
+      <c r="E4" t="n">
+        <v>109091.02</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>咨询线</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2506303.81</v>
+      </c>
+      <c r="D5" t="n">
+        <v>514</v>
+      </c>
+      <c r="E5" t="n">
+        <v>545033.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1961270.01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>咨询线</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>老客</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1764019.01</v>
+      </c>
+      <c r="D6" t="n">
+        <v>321</v>
+      </c>
+      <c r="E6" t="n">
+        <v>49820</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1714199.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>咨询线</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>新客</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>722284.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>192</v>
+      </c>
+      <c r="E7" t="n">
+        <v>495213.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>227071</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>医疗线</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1873476.82</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1371</v>
+      </c>
+      <c r="E8" t="n">
+        <v>29334.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1844142.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>医疗线</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>复诊</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1159018.68</v>
+      </c>
+      <c r="D9" t="n">
+        <v>718</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11126.88</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1147891.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>医疗线</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>初诊</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>712458.14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>652</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18207.82</v>
+      </c>
+      <c r="F10" t="n">
+        <v>694250.3199999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>菌群线</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>432400</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43</v>
+      </c>
+      <c r="E11" t="n">
+        <v>198400</v>
+      </c>
+      <c r="F11" t="n">
+        <v>234000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>考证</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>603258.8100000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" t="n">
+        <v>396334.81</v>
+      </c>
+      <c r="F12" t="n">
+        <v>206924</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>309454</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>189254</v>
+      </c>
+      <c r="F13" t="n">
+        <v>120200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>工作坊</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>（合计）</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>21780</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>21780</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>主线</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>成交额(元)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>退费总额(元)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>当月退(元)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>当月退费率(%)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>历年退(元)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>历年退费率(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程线</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1420465.02</v>
+      </c>
+      <c r="C2" t="n">
+        <v>224232.57</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21039</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F2" t="n">
+        <v>203193.57</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>咨询线</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2506303.81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>368353.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>398</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>367955.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.68</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>医疗线</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1873476.82</v>
+      </c>
+      <c r="C4" t="n">
+        <v>633303.5699999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1829</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>631474.5699999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33.71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>菌群线</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>432400</v>
+      </c>
+      <c r="C5" t="n">
+        <v>261800</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>261800</v>
+      </c>
+      <c r="G5" t="n">
+        <v>60.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>考证</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>603258.8100000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>152193.07</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2017.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F6" t="n">
+        <v>150175.17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>309454</v>
+      </c>
+      <c r="C7" t="n">
+        <v>378280</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>358280</v>
+      </c>
+      <c r="G7" t="n">
+        <v>115.78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>工作坊</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>21780</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>large_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>279</v>
+      </c>
+      <c r="C2" t="n">
+        <v>921229.51</v>
+      </c>
+      <c r="D2" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C3" t="n">
+        <v>253155</v>
+      </c>
+      <c r="D3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>329</v>
+      </c>
+      <c r="C4" t="n">
+        <v>108366.46</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C5" t="n">
+        <v>40592.67</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>39548</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>25358</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>82</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11776.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C9" t="n">
+        <v>951</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>价格问题</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>676</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" t="n">
+        <v>209</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>教材问题</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>未填写原因</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>笔数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>金额(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>141174</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8950</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>66673</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D6" t="n">
+        <v>63714.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>51</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14604.66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5206</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>143100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>59083</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>81</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22727.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>48</v>
+      </c>
+      <c r="D19" t="n">
+        <v>19359.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10252</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7002</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>未填写原因</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>103486</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>72514</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" t="n">
+        <v>33614</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>62737</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13598</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>价格问题</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>54800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>47</v>
+      </c>
+      <c r="D41" t="n">
+        <v>38991.6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>85</v>
+      </c>
+      <c r="D42" t="n">
+        <v>13163.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6988</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>18</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3783.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
+        <v>820.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>价格问题</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>教材问题</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>24</v>
+      </c>
+      <c r="D50" t="n">
+        <v>30164</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>29800</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>19</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>价格问题</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>24800</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>35567</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>40</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14110</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>48</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10485</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>12</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16</v>
+      </c>
+      <c r="D71" t="n">
+        <v>14467</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>11980</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>24800</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16819</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>15218</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>分享咨询</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C2" t="n">
+        <v>268140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>肠道菌群移植</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>261800</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>夏令营</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>237920</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>心灯—长程课</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>143404</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>青少年家庭同行者计划</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>142974.66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>户外营地（户外组专用）</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>136400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" t="n">
+        <v>71400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>家庭守护计划</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33594</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>少年说倾听计划</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>23160</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>少年说陪伴计划</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>71</v>
+      </c>
+      <c r="C2" t="n">
+        <v>219955</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>156</v>
+      </c>
+      <c r="C3" t="n">
+        <v>216779.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>116</v>
+      </c>
+      <c r="C4" t="n">
+        <v>174118</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>139806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>121734</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C7" t="n">
+        <v>116901.91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65437</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>54957</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>48649.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>37695</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>35036</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>保留地址</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>23</v>
+      </c>
+      <c r="C13" t="n">
+        <v>29465.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>27</v>
+      </c>
+      <c r="C14" t="n">
+        <v>25249</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" t="n">
+        <v>24357</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>56</v>
+      </c>
+      <c r="C16" t="n">
+        <v>17386</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>303384</v>
+        <v>358707</v>
       </c>
       <c r="E2" t="n">
-        <v>155459</v>
+        <v>186034</v>
       </c>
       <c r="F2" t="n">
-        <v>147924</v>
+        <v>172672</v>
       </c>
       <c r="G2" t="n">
         <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>599977</v>
+        <v>628595</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>248659</v>
+        <v>211163</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,41 +567,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20389</v>
+        <v>20493</v>
       </c>
       <c r="E3" t="n">
-        <v>30421</v>
+        <v>35429</v>
       </c>
       <c r="F3" t="n">
-        <v>-10031</v>
+        <v>-14935</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>44992</v>
+        <v>55135</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-62.8%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3476</v>
+        <v>4530</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-388.6%</t>
+          <t>-429.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>408358</v>
+        <v>523438</v>
       </c>
       <c r="E4" t="n">
-        <v>123086</v>
+        <v>125376</v>
       </c>
       <c r="F4" t="n">
-        <v>285271</v>
+        <v>398062</v>
       </c>
       <c r="G4" t="n">
         <v>10398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>432281</v>
+        <v>503396</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>318386</v>
+        <v>338812</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>399845</v>
+        <v>410568</v>
       </c>
       <c r="E5" t="n">
-        <v>106176</v>
+        <v>106195</v>
       </c>
       <c r="F5" t="n">
-        <v>293669</v>
+        <v>304373</v>
       </c>
       <c r="G5" t="n">
         <v>39588</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>556036</v>
+        <v>598929</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>434100</v>
+        <v>460948</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>253411</v>
+        <v>284437</v>
       </c>
       <c r="E6" t="n">
-        <v>64218</v>
+        <v>70080</v>
       </c>
       <c r="F6" t="n">
-        <v>189193</v>
+        <v>214356</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>223847</v>
+        <v>255345</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>+11.4%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>188287</v>
+        <v>215188</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>258264</v>
+        <v>288379</v>
       </c>
       <c r="E7" t="n">
-        <v>62250</v>
+        <v>63732</v>
       </c>
       <c r="F7" t="n">
-        <v>196014</v>
+        <v>224647</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>396282</v>
+        <v>486952</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-40.8%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>251416</v>
+        <v>308991</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>292471</v>
+        <v>311321</v>
       </c>
       <c r="E8" t="n">
-        <v>33474</v>
+        <v>65388</v>
       </c>
       <c r="F8" t="n">
-        <v>258997</v>
+        <v>245933</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>50.8%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>45.0%</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>336376</v>
+        <v>401556</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>207731</v>
+        <v>238889</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+24.7%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>670632</v>
+        <v>738629</v>
       </c>
       <c r="E9" t="n">
-        <v>160124</v>
+        <v>170124</v>
       </c>
       <c r="F9" t="n">
-        <v>510508</v>
+        <v>568505</v>
       </c>
       <c r="G9" t="n">
         <v>88806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>782886</v>
+        <v>926545</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>462995</v>
+        <v>555531</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1107289</v>
+        <v>1385492</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1107289</v>
+        <v>1385492</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>987408</v>
+        <v>1095253</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+12.1%</t>
+          <t>+26.5%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>987408</v>
+        <v>1095253</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+12.1%</t>
+          <t>+26.5%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,43 +997,43 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>231516</v>
+        <v>258196</v>
       </c>
       <c r="E11" t="n">
         <v>25108</v>
       </c>
       <c r="F11" t="n">
-        <v>206408</v>
+        <v>233088</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>259599</v>
+        <v>297469</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>227742</v>
+        <v>265612</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>264</v>
+        <v>712</v>
       </c>
     </row>
     <row r="12">
@@ -1051,39 +1051,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>246715</v>
+        <v>284528</v>
       </c>
       <c r="E12" t="n">
         <v>1998</v>
       </c>
       <c r="F12" t="n">
-        <v>244717</v>
+        <v>282530</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>228592</v>
+        <v>238668</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+7.9%</t>
+          <t>+19.2%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>212973</v>
+        <v>223049</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+14.9%</t>
+          <t>+26.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,43 +1103,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>379795</v>
+        <v>502163</v>
       </c>
       <c r="E13" t="n">
         <v>76509</v>
       </c>
       <c r="F13" t="n">
-        <v>303286</v>
+        <v>425654</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>418982</v>
+        <v>526381</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>375227</v>
+        <v>482438</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>9639</v>
+        <v>15491</v>
       </c>
     </row>
     <row r="14">
@@ -1157,43 +1157,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>217019</v>
+        <v>334007</v>
       </c>
       <c r="E14" t="n">
-        <v>21378</v>
+        <v>31378</v>
       </c>
       <c r="F14" t="n">
-        <v>195641</v>
+        <v>302629</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>512933</v>
+        <v>542519</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-57.7%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>430036</v>
+        <v>417822</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>47026</v>
+        <v>56422</v>
       </c>
     </row>
     <row r="15">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>164490</v>
+        <v>171426</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>149184</v>
+        <v>156120</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>176842</v>
+        <v>204897</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>176756</v>
+        <v>204811</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>218833</v>
+        <v>250448</v>
       </c>
       <c r="E16" t="n">
         <v>43000</v>
       </c>
       <c r="F16" t="n">
-        <v>175833</v>
+        <v>207448</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>134797</v>
+        <v>148993</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+62.3%</t>
+          <t>+68.1%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>105714</v>
+        <v>111910</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+66.3%</t>
+          <t>+85.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,43 +1315,43 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>296047</v>
+        <v>381202</v>
       </c>
       <c r="E17" t="n">
-        <v>35866</v>
+        <v>42366</v>
       </c>
       <c r="F17" t="n">
-        <v>260181</v>
+        <v>338836</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>251002</v>
+        <v>292641</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+17.9%</t>
+          <t>+30.3%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>224533</v>
+        <v>266113</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+15.9%</t>
+          <t>+27.3%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>24031</v>
+        <v>24133</v>
       </c>
     </row>
     <row r="18">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>442207</v>
+        <v>542985</v>
       </c>
       <c r="E18" t="n">
-        <v>115542</v>
+        <v>128005</v>
       </c>
       <c r="F18" t="n">
-        <v>326665</v>
+        <v>414980</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>548514</v>
+        <v>572721</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>349287</v>
+        <v>361495</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>+14.8%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,43 +1423,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>232443</v>
+        <v>300393</v>
       </c>
       <c r="E19" t="n">
         <v>143527</v>
       </c>
       <c r="F19" t="n">
-        <v>88916</v>
+        <v>156866</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>426666</v>
+        <v>902384</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-66.7%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>349288</v>
+        <v>815506</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7657</v>
+        <v>9811</v>
       </c>
     </row>
     <row r="20">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>385933</v>
+        <v>490146</v>
       </c>
       <c r="E20" t="n">
         <v>76000</v>
       </c>
       <c r="F20" t="n">
-        <v>309933</v>
+        <v>414146</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>415177</v>
+        <v>498381</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>378378</v>
+        <v>435082</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" t="n">
-        <v>1386</v>
+        <v>812.7</v>
       </c>
       <c r="E2" t="n">
-        <v>74394</v>
+        <v>46958</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>542.8</v>
+        <v>37.1</v>
       </c>
       <c r="E3" t="n">
-        <v>676</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>859</v>
+        <v>768</v>
       </c>
       <c r="C4" t="n">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="D4" t="n">
-        <v>1978.9</v>
+        <v>1256.2</v>
       </c>
       <c r="E4" t="n">
-        <v>6679</v>
+        <v>2727</v>
       </c>
     </row>
   </sheetData>
@@ -1769,23 +1769,23 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>128929.9</v>
+        <v>170869.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23298</v>
+        <v>53098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>105631.9</v>
+        <v>117771.9</v>
       </c>
     </row>
     <row r="3">
@@ -1871,11 +1871,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>13620</v>
+        <v>21580</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>246.0%</t>
+          <t>155.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-19880</v>
+        <v>-11920</v>
       </c>
     </row>
     <row r="6">
@@ -1905,11 +1905,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>60740</v>
+        <v>61740</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1917,11 +1917,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>31757</v>
+        <v>32757</v>
       </c>
     </row>
     <row r="7">
@@ -1947,15 +1947,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7960</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="8">
@@ -2041,11 +2041,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>120090</v>
+        <v>183290</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>141.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2053,11 +2053,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>114712</v>
+        <v>177912</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2075,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
     </row>
     <row r="12">
@@ -2109,11 +2109,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>46720</v>
+        <v>66520</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2121,11 +2121,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>42537</v>
+        <v>62337</v>
       </c>
     </row>
     <row r="13">
@@ -2211,11 +2211,11 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>74340</v>
+        <v>94140</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24420</v>
+        <v>44220</v>
       </c>
     </row>
     <row r="16">
@@ -2313,11 +2313,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="19">
@@ -2381,11 +2381,11 @@
         <v>80000</v>
       </c>
       <c r="D20" t="n">
-        <v>7768</v>
+        <v>15728</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2393,11 +2393,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3618</v>
+        <v>11578</v>
       </c>
     </row>
     <row r="21">
@@ -2457,15 +2457,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12179</v>
+        <v>15779</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>29350.9</v>
+        <v>25750.9</v>
       </c>
     </row>
     <row r="23">
@@ -2551,11 +2551,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>26500</v>
+        <v>38440</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>26500</v>
+        <v>38440</v>
       </c>
     </row>
     <row r="26">
@@ -2585,11 +2585,11 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>27860</v>
+        <v>31840</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2597,11 +2597,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22880</v>
+        <v>26860</v>
       </c>
     </row>
     <row r="27">
@@ -2619,11 +2619,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>107704</v>
+        <v>111684</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2631,11 +2631,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>97824</v>
+        <v>101804</v>
       </c>
     </row>
     <row r="28">
@@ -2653,11 +2653,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>60940</v>
+        <v>64920</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>31140</v>
+        <v>35120</v>
       </c>
     </row>
     <row r="29">
@@ -2687,11 +2687,11 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>49780</v>
+        <v>64600</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>49780</v>
+        <v>64600</v>
       </c>
     </row>
     <row r="30">
@@ -2721,11 +2721,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>32840</v>
+        <v>42840</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>32840</v>
+        <v>42840</v>
       </c>
     </row>
     <row r="31">
@@ -2763,15 +2763,15 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49420</v>
+        <v>34420</v>
       </c>
     </row>
     <row r="32">
@@ -2797,15 +2797,15 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11580</v>
+        <v>21580</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>44858</v>
+        <v>34858</v>
       </c>
     </row>
     <row r="33">
@@ -2823,11 +2823,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>108800</v>
+        <v>115400</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2835,11 +2835,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>101100</v>
+        <v>107700</v>
       </c>
     </row>
     <row r="34">
@@ -2865,15 +2865,15 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4980</v>
+        <v>11580</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21520</v>
+        <v>14920</v>
       </c>
     </row>
     <row r="35">
@@ -2891,11 +2891,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>81260</v>
+        <v>114260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>32686</v>
+        <v>65686</v>
       </c>
     </row>
     <row r="36">
@@ -2925,11 +2925,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>54320</v>
+        <v>58280</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2937,11 +2937,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>44320</v>
+        <v>48280</v>
       </c>
     </row>
     <row r="37">
@@ -2959,11 +2959,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>19300</v>
+        <v>20800</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19300</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="38">
@@ -2993,11 +2993,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>91100</v>
+        <v>112520</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>66300</v>
+        <v>87720</v>
       </c>
     </row>
     <row r="39">
@@ -3265,11 +3265,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>66000</v>
+        <v>67000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>41200</v>
+        <v>42200</v>
       </c>
     </row>
   </sheetData>
@@ -3355,11 +3355,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>23796</v>
+        <v>24194</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3367,11 +3367,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8578</v>
+        <v>8976</v>
       </c>
     </row>
     <row r="3">
@@ -3389,11 +3389,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>116462</v>
+        <v>120922</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>116462</v>
+        <v>120922</v>
       </c>
     </row>
     <row r="4">
@@ -3423,11 +3423,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>15373</v>
+        <v>15771</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15373</v>
+        <v>15771</v>
       </c>
     </row>
     <row r="5">
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>38739.7</v>
+        <v>40054.26</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38419.7</v>
+        <v>39734.26</v>
       </c>
     </row>
     <row r="8">
@@ -3559,11 +3559,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>89200</v>
+        <v>104600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3571,11 +3571,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>86500</v>
+        <v>101900</v>
       </c>
     </row>
     <row r="9">
@@ -3593,11 +3593,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>49287.58</v>
+        <v>91495.16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3605,11 +3605,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>284.9%</t>
+          <t>153.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-91112.42</v>
+        <v>-48904.84</v>
       </c>
     </row>
     <row r="10">
@@ -3627,11 +3627,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>33400</v>
+        <v>34200</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>33400</v>
+        <v>34200</v>
       </c>
     </row>
     <row r="11">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>113141</v>
+        <v>140594</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>113141</v>
+        <v>140594</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>119117</v>
+        <v>127107</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>119117</v>
+        <v>127107</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>260313.46</v>
+        <v>342616.53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>260313.46</v>
+        <v>342616.53</v>
       </c>
     </row>
     <row r="15">
@@ -3797,11 +3797,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>113419.74</v>
+        <v>132533.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>113419.74</v>
+        <v>132533.74</v>
       </c>
     </row>
     <row r="16">
@@ -3831,11 +3831,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>120706</v>
+        <v>155847</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>120706</v>
+        <v>155847</v>
       </c>
     </row>
     <row r="17">
@@ -3865,11 +3865,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>149454</v>
+        <v>187218</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>149454</v>
+        <v>187218</v>
       </c>
     </row>
     <row r="18">
@@ -3933,11 +3933,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>79956</v>
+        <v>109956</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>79956</v>
+        <v>109956</v>
       </c>
     </row>
     <row r="20">
@@ -4001,11 +4001,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>58396.00000000001</v>
+        <v>58794.00000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>58396.00000000001</v>
+        <v>58794.00000000001</v>
       </c>
     </row>
     <row r="22">
@@ -4043,15 +4043,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>12444.48</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>28080</v>
+        <v>15635.52</v>
       </c>
     </row>
     <row r="23">
@@ -4069,11 +4069,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>173258</v>
+        <v>198748</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>105670</v>
+        <v>131160</v>
       </c>
     </row>
     <row r="24">
@@ -4103,11 +4103,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>7796</v>
+        <v>53192.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>798</v>
+        <v>46194.01</v>
       </c>
     </row>
     <row r="25">
@@ -4137,11 +4137,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>145360.01</v>
+        <v>148357.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>199.1%</t>
+          <t>203.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4149,11 +4149,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>122960.01</v>
+        <v>125957.01</v>
       </c>
     </row>
     <row r="26">
@@ -4171,11 +4171,11 @@
         <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>398</v>
+        <v>5358</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>398</v>
+        <v>5358</v>
       </c>
     </row>
     <row r="27">
@@ -4205,11 +4205,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>81774</v>
+        <v>106168</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4217,11 +4217,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>73774</v>
+        <v>98168</v>
       </c>
     </row>
     <row r="28">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>181610.15</v>
+        <v>218157.55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>141030.15</v>
+        <v>177577.55</v>
       </c>
     </row>
     <row r="29">
@@ -4273,11 +4273,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>50804.3</v>
+        <v>70808.89999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>50804.3</v>
+        <v>70808.89999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4307,11 +4307,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>89184</v>
+        <v>97484</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>76184</v>
+        <v>84484</v>
       </c>
     </row>
     <row r="31">
@@ -4341,11 +4341,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>30646.2</v>
+        <v>41746.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>26248.2</v>
+        <v>37348.2</v>
       </c>
     </row>
     <row r="32">
@@ -4375,11 +4375,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>26008</v>
+        <v>26406</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4387,11 +4387,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>18008</v>
+        <v>18406</v>
       </c>
     </row>
     <row r="33">
@@ -4409,11 +4409,11 @@
         <v>50000</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34">
@@ -4443,11 +4443,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>86990</v>
+        <v>107388</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>86990</v>
+        <v>107388</v>
       </c>
     </row>
     <row r="35">
@@ -4477,11 +4477,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>1592</v>
+        <v>8192</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1592</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="36">
@@ -4511,11 +4511,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>87392</v>
+        <v>87790</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>218.5%</t>
+          <t>219.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>87392</v>
+        <v>87790</v>
       </c>
     </row>
     <row r="37">
@@ -4545,11 +4545,11 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>21592</v>
+        <v>41990</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4557,11 +4557,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>19912</v>
+        <v>40310</v>
       </c>
     </row>
     <row r="38">
@@ -4579,11 +4579,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>47794</v>
+        <v>37794</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47794</v>
+        <v>37794</v>
       </c>
     </row>
     <row r="39">
@@ -4647,11 +4647,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>120386</v>
+        <v>137186</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4659,11 +4659,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>111586</v>
+        <v>128386</v>
       </c>
     </row>
     <row r="41">
@@ -4681,11 +4681,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>16588</v>
+        <v>66588</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>16588</v>
+        <v>66588</v>
       </c>
     </row>
     <row r="42">
@@ -4715,11 +4715,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>21398</v>
+        <v>21796</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4727,11 +4727,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-3802</v>
+        <v>-3404</v>
       </c>
     </row>
     <row r="43">
@@ -4749,11 +4749,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>77852</v>
+        <v>79250</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>77852</v>
+        <v>79250</v>
       </c>
     </row>
     <row r="44">
@@ -4783,11 +4783,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>77454</v>
+        <v>98052</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>77454</v>
+        <v>98052</v>
       </c>
     </row>
     <row r="45">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>68520</v>
+        <v>97219.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>68520</v>
+        <v>97219.2</v>
       </c>
     </row>
     <row r="46">
@@ -4851,11 +4851,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>71896</v>
+        <v>126896</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>71896</v>
+        <v>126896</v>
       </c>
     </row>
     <row r="47">
@@ -4885,11 +4885,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>81780</v>
+        <v>83178</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>81780</v>
+        <v>83178</v>
       </c>
     </row>
     <row r="48">
@@ -5055,11 +5055,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>85988</v>
+        <v>86784</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>61188</v>
+        <v>61984</v>
       </c>
     </row>
     <row r="53">
@@ -5089,11 +5089,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>91674</v>
+        <v>99674</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>91674</v>
+        <v>99674</v>
       </c>
     </row>
     <row r="54">
@@ -5123,11 +5123,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>42198</v>
+        <v>58596</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>42198</v>
+        <v>58596</v>
       </c>
     </row>
     <row r="55">
@@ -5157,11 +5157,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>2796</v>
+        <v>3796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2796</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="56">
@@ -5225,11 +5225,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>23086</v>
+        <v>35086</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5237,11 +5237,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>15086</v>
+        <v>27086</v>
       </c>
     </row>
     <row r="58">
@@ -5259,11 +5259,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>64778</v>
+        <v>77176</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5271,11 +5271,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>39978</v>
+        <v>52376</v>
       </c>
     </row>
     <row r="59">
@@ -5293,11 +5293,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>116370</v>
+        <v>122768</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5305,11 +5305,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>106170</v>
+        <v>112568</v>
       </c>
     </row>
     <row r="60">
@@ -5327,11 +5327,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>14588</v>
+        <v>15388</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>14588</v>
+        <v>15388</v>
       </c>
     </row>
     <row r="61">
@@ -5361,23 +5361,23 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>111452.1</v>
+        <v>172052.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>111452.1</v>
+        <v>162052.6</v>
       </c>
     </row>
     <row r="62">
@@ -5395,11 +5395,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>20745.22</v>
+        <v>55410.62</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5407,11 +5407,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>19533.22</v>
+        <v>54198.62</v>
       </c>
     </row>
     <row r="63">
@@ -5429,11 +5429,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>83370.98</v>
+        <v>105093.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>68170.98</v>
+        <v>89893.48</v>
       </c>
     </row>
     <row r="64">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1420465.02</v>
+        <v>1603988.02</v>
       </c>
       <c r="D2" t="n">
-        <v>3868</v>
+        <v>4936</v>
       </c>
       <c r="E2" t="n">
-        <v>1226619.02</v>
+        <v>1368605.02</v>
       </c>
       <c r="F2" t="n">
-        <v>193846</v>
+        <v>235383</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1307628</v>
+        <v>1464424</v>
       </c>
       <c r="D3" t="n">
-        <v>269</v>
+        <v>318</v>
       </c>
       <c r="E3" t="n">
-        <v>1117528</v>
+        <v>1233025</v>
       </c>
       <c r="F3" t="n">
-        <v>190100</v>
+        <v>231399</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>112837.02</v>
+        <v>139564.02</v>
       </c>
       <c r="D4" t="n">
-        <v>3599</v>
+        <v>4618</v>
       </c>
       <c r="E4" t="n">
-        <v>109091.02</v>
+        <v>135580.02</v>
       </c>
       <c r="F4" t="n">
-        <v>3746</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2506303.81</v>
+        <v>3211975.82</v>
       </c>
       <c r="D5" t="n">
-        <v>514</v>
+        <v>637</v>
       </c>
       <c r="E5" t="n">
-        <v>545033.8</v>
+        <v>696471.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1961270.01</v>
+        <v>2515504.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1764019.01</v>
+        <v>2297007.02</v>
       </c>
       <c r="D6" t="n">
-        <v>321</v>
+        <v>411</v>
       </c>
       <c r="E6" t="n">
-        <v>49820</v>
+        <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>1714199.01</v>
+        <v>2180567.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>722284.8</v>
+        <v>894968.8</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="E7" t="n">
-        <v>495213.8</v>
+        <v>580031.8</v>
       </c>
       <c r="F7" t="n">
-        <v>227071</v>
+        <v>314937</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1873476.82</v>
+        <v>2236888.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1371</v>
+        <v>1739</v>
       </c>
       <c r="E8" t="n">
-        <v>29334.7</v>
+        <v>34369.45</v>
       </c>
       <c r="F8" t="n">
-        <v>1844142.12</v>
+        <v>2202519.31</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1159018.68</v>
+        <v>1387351.92</v>
       </c>
       <c r="D9" t="n">
-        <v>718</v>
+        <v>903</v>
       </c>
       <c r="E9" t="n">
-        <v>11126.88</v>
+        <v>12634.63</v>
       </c>
       <c r="F9" t="n">
-        <v>1147891.8</v>
+        <v>1374717.29</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>712458.14</v>
+        <v>847536.84</v>
       </c>
       <c r="D10" t="n">
-        <v>652</v>
+        <v>835</v>
       </c>
       <c r="E10" t="n">
-        <v>18207.82</v>
+        <v>21734.82</v>
       </c>
       <c r="F10" t="n">
-        <v>694250.3199999999</v>
+        <v>825802.02</v>
       </c>
     </row>
     <row r="11">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>432400</v>
+        <v>482000</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>198400</v>
+        <v>224200</v>
       </c>
       <c r="F11" t="n">
-        <v>234000</v>
+        <v>257800</v>
       </c>
     </row>
     <row r="12">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>309454</v>
+        <v>310454</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>189254</v>
+        <v>190254</v>
       </c>
       <c r="F13" t="n">
         <v>120200</v>
@@ -5862,16 +5862,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21780</v>
+        <v>33660</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>21780</v>
+        <v>25740</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7920</v>
       </c>
     </row>
   </sheetData>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1420465.02</v>
+        <v>1603988.02</v>
       </c>
       <c r="C2" t="n">
-        <v>224232.57</v>
+        <v>246272.58</v>
       </c>
       <c r="D2" t="n">
-        <v>21039</v>
+        <v>27781.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="F2" t="n">
-        <v>203193.57</v>
+        <v>218491.57</v>
       </c>
       <c r="G2" t="n">
-        <v>14.3</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="3">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2506303.81</v>
+        <v>3211975.82</v>
       </c>
       <c r="C3" t="n">
-        <v>368353.9</v>
+        <v>439328.28</v>
       </c>
       <c r="D3" t="n">
-        <v>398</v>
+        <v>25398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02</v>
+        <v>0.79</v>
       </c>
       <c r="F3" t="n">
-        <v>367955.9</v>
+        <v>413930.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.68</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="4">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1873476.82</v>
+        <v>2236888.76</v>
       </c>
       <c r="C4" t="n">
-        <v>633303.5699999999</v>
+        <v>633773.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>1829</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>631474.5699999999</v>
+        <v>631944.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>33.71</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="5">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>432400</v>
+        <v>482000</v>
       </c>
       <c r="C5" t="n">
         <v>261800</v>
@@ -6022,7 +6022,7 @@
         <v>261800</v>
       </c>
       <c r="G5" t="n">
-        <v>60.55</v>
+        <v>54.32</v>
       </c>
     </row>
     <row r="6">
@@ -6057,22 +6057,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>309454</v>
+        <v>310454</v>
       </c>
       <c r="C7" t="n">
-        <v>378280</v>
+        <v>408080</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.46</v>
+        <v>6.44</v>
       </c>
       <c r="F7" t="n">
-        <v>358280</v>
+        <v>388080</v>
       </c>
       <c r="G7" t="n">
-        <v>115.78</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21780</v>
+        <v>33660</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="C2" t="n">
-        <v>921229.51</v>
+        <v>978817.51</v>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>253155</v>
+        <v>264735</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -6175,45 +6175,45 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>329</v>
+        <v>413</v>
       </c>
       <c r="C4" t="n">
-        <v>108366.46</v>
+        <v>128775.37</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>40592.67</v>
+        <v>61992.48</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>39548</v>
+        <v>40782.67</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>11776.8</v>
+        <v>12345.8</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -6251,30 +6251,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>951</v>
+        <v>10975</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>676</v>
+        <v>980</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6319,10 +6319,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6367,7 +6367,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6376,46 +6376,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>141174</v>
+        <v>93644.00999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>10000</v>
+        <v>66673</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>8950</v>
+        <v>14832.66</v>
       </c>
     </row>
     <row r="5">
@@ -6426,14 +6426,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>66673</v>
+        <v>5206</v>
       </c>
     </row>
     <row r="6">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>63714.01</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="7">
@@ -6462,14 +6462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>14604.66</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="8">
@@ -6480,14 +6480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5206</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -6498,68 +6498,68 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>4169</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>998</v>
+        <v>141174</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>18950</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13">
@@ -6637,73 +6637,73 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>59083</v>
+        <v>103486</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>22727.9</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>19359.9</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>10252</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
@@ -6714,14 +6714,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>7002</v>
+        <v>59083</v>
       </c>
     </row>
     <row r="22">
@@ -6732,14 +6732,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>4221</v>
+        <v>24745.9</v>
       </c>
     </row>
     <row r="23">
@@ -6750,14 +6750,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>397</v>
+        <v>19549.9</v>
       </c>
     </row>
     <row r="24">
@@ -6768,14 +6768,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>10309</v>
       </c>
     </row>
     <row r="25">
@@ -6786,86 +6786,86 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>103486</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>8000</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>4000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>未填写原因</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D41" t="n">
-        <v>38991.6</v>
+        <v>42813.6</v>
       </c>
     </row>
     <row r="42">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D42" t="n">
-        <v>13163.9</v>
+        <v>14705.81</v>
       </c>
     </row>
     <row r="43">
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D44" t="n">
-        <v>3783.67</v>
+        <v>3840.67</v>
       </c>
     </row>
     <row r="45">
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D45" t="n">
-        <v>820.9</v>
+        <v>934.9</v>
       </c>
     </row>
     <row r="46">
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>318</v>
+        <v>617</v>
       </c>
     </row>
     <row r="47">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48">
@@ -7231,79 +7231,79 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>30164</v>
+        <v>25704</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D51" t="n">
-        <v>29800</v>
+        <v>24186</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>1761</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>299</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7312,16 +7312,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D54" t="n">
-        <v>93</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7330,16 +7330,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>57</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7348,16 +7348,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>57</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7375,169 +7375,169 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D58" t="n">
-        <v>24800</v>
+        <v>30206</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>10200</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D60" t="n">
-        <v>8000</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>35567</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>299</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>14110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>10485</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>4980</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>2470</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7546,64 +7546,64 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1046</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>345</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>42067</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71">
@@ -7614,14 +7614,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>14467</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="72">
@@ -7632,14 +7632,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D72" t="n">
-        <v>11980</v>
+        <v>14495</v>
       </c>
     </row>
     <row r="73">
@@ -7735,55 +7735,55 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>24800</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>299</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="81">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>16819</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82">
@@ -7812,56 +7812,56 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3000</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>118</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>29</v>
+        <v>299</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>15218</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -7884,14 +7884,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>59</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="87">
@@ -7902,50 +7902,50 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1680</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>318</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="90">
@@ -7987,7 +7987,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7999,7 +7999,25 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -8040,10 +8058,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>268140</v>
+        <v>307584.48</v>
       </c>
     </row>
     <row r="3">
@@ -8075,14 +8093,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>143404</v>
+        <v>166200</v>
       </c>
     </row>
     <row r="6">
@@ -8092,23 +8110,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>142974.66</v>
+        <v>147954.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>136400</v>
+        <v>143404</v>
       </c>
     </row>
     <row r="8">
@@ -8118,10 +8136,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>71400</v>
+        <v>87900</v>
       </c>
     </row>
     <row r="9">
@@ -8131,10 +8149,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>33594</v>
+        <v>48594</v>
       </c>
     </row>
     <row r="10">
@@ -8144,10 +8162,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>23160</v>
+        <v>29760</v>
       </c>
     </row>
     <row r="11">
@@ -8197,27 +8215,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="C2" t="n">
-        <v>219955</v>
+        <v>237849.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>216779.5</v>
+        <v>226915</v>
       </c>
     </row>
     <row r="4">
@@ -8227,10 +8245,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
-        <v>174118</v>
+        <v>203969.48</v>
       </c>
     </row>
     <row r="5">
@@ -8240,10 +8258,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>139806</v>
+        <v>146901</v>
       </c>
     </row>
     <row r="6">
@@ -8253,10 +8271,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>121734</v>
+        <v>121772</v>
       </c>
     </row>
     <row r="7">
@@ -8266,10 +8284,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>116901.91</v>
+        <v>116950.81</v>
       </c>
     </row>
     <row r="8">
@@ -8327,66 +8345,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>35036</v>
+        <v>35638.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>保留地址</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>29465.9</v>
+        <v>35055</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C14" t="n">
-        <v>25249</v>
+        <v>29952.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>保留地址</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>24357</v>
+        <v>29535.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C16" t="n">
-        <v>17386</v>
+        <v>25617.01</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -522,11 +522,11 @@
         <v>172672</v>
       </c>
       <c r="G2" t="n">
-        <v>8000</v>
+        <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -630,11 +630,11 @@
         <v>398062</v>
       </c>
       <c r="G4" t="n">
-        <v>10398</v>
+        <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -684,11 +684,11 @@
         <v>304373</v>
       </c>
       <c r="G5" t="n">
-        <v>39588</v>
+        <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,11 +900,11 @@
         <v>568505</v>
       </c>
       <c r="G9" t="n">
-        <v>88806</v>
+        <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1641,31 +1641,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10398</v>
+        <v>108806</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18796</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88806</v>
+        <v>18796</v>
       </c>
     </row>
     <row r="5">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8000</v>
+        <v>12988</v>
       </c>
     </row>
     <row r="6">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39588</v>
+        <v>158352</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C2" t="n">
-        <v>978817.51</v>
+        <v>893517.51</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>264735</v>
+        <v>243935</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C4" t="n">
-        <v>128775.37</v>
+        <v>125795.37</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>25358</v>
+        <v>20358</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -8058,36 +8058,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>307584.48</v>
+        <v>300484.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>261800</v>
+        <v>207120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>237920</v>
+        <v>195400</v>
       </c>
     </row>
     <row r="5">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>87900</v>
+        <v>87700</v>
       </c>
     </row>
     <row r="9">
@@ -8171,14 +8171,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>认知9周+年卡</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>19800</v>
+        <v>16199</v>
       </c>
     </row>
   </sheetData>
@@ -8215,27 +8215,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>183</v>
+        <v>92</v>
       </c>
       <c r="C2" t="n">
-        <v>237849.5</v>
+        <v>226915</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="C3" t="n">
-        <v>226915</v>
+        <v>192249.5</v>
       </c>
     </row>
     <row r="4">
@@ -8245,10 +8245,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" t="n">
-        <v>203969.48</v>
+        <v>183169.48</v>
       </c>
     </row>
     <row r="5">
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>146901</v>
+        <v>140301</v>
       </c>
     </row>
     <row r="6">
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>116950.81</v>
+        <v>84550.81</v>
       </c>
     </row>
     <row r="8">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>65437</v>
+        <v>59937</v>
       </c>
     </row>
     <row r="9">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>358707</v>
+        <v>396266</v>
       </c>
       <c r="E2" t="n">
-        <v>186034</v>
+        <v>251415</v>
       </c>
       <c r="F2" t="n">
-        <v>172672</v>
+        <v>144850</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>628595</v>
+        <v>658657</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>211163</v>
+        <v>227526</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,13 +567,13 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20493</v>
+        <v>20518</v>
       </c>
       <c r="E3" t="n">
-        <v>35429</v>
+        <v>35448</v>
       </c>
       <c r="F3" t="n">
-        <v>-14935</v>
+        <v>-14929</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>55135</v>
+        <v>55328</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-62.8%</t>
+          <t>-62.9%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4530</v>
+        <v>4723</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-429.7%</t>
+          <t>-416.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>523438</v>
+        <v>633382</v>
       </c>
       <c r="E4" t="n">
-        <v>125376</v>
+        <v>158586</v>
       </c>
       <c r="F4" t="n">
-        <v>398062</v>
+        <v>474796</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>503396</v>
+        <v>577633</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>338812</v>
+        <v>397646</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+17.5%</t>
+          <t>+19.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>410568</v>
+        <v>421312</v>
       </c>
       <c r="E5" t="n">
-        <v>106195</v>
+        <v>111094</v>
       </c>
       <c r="F5" t="n">
-        <v>304373</v>
+        <v>310218</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>598929</v>
+        <v>602871</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>460948</v>
+        <v>380795</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>284437</v>
+        <v>290941</v>
       </c>
       <c r="E6" t="n">
-        <v>70080</v>
+        <v>75540</v>
       </c>
       <c r="F6" t="n">
-        <v>214356</v>
+        <v>215400</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>255345</v>
+        <v>260846</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+11.4%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>215188</v>
+        <v>220242</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>288379</v>
+        <v>299151</v>
       </c>
       <c r="E7" t="n">
-        <v>63732</v>
+        <v>68243</v>
       </c>
       <c r="F7" t="n">
-        <v>224647</v>
+        <v>230908</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>486952</v>
+        <v>565510</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-40.8%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>308991</v>
+        <v>379651</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-39.2%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>311321</v>
+        <v>345862</v>
       </c>
       <c r="E8" t="n">
-        <v>65388</v>
+        <v>76166</v>
       </c>
       <c r="F8" t="n">
-        <v>245933</v>
+        <v>269696</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>401556</v>
+        <v>412685</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>238889</v>
+        <v>244777</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+10.2%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>738629</v>
+        <v>788848</v>
       </c>
       <c r="E9" t="n">
-        <v>170124</v>
+        <v>190872</v>
       </c>
       <c r="F9" t="n">
-        <v>568505</v>
+        <v>597976</v>
       </c>
       <c r="G9" t="n">
         <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>926545</v>
+        <v>1080733</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>555531</v>
+        <v>698321</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1385492</v>
+        <v>1389928</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1385492</v>
+        <v>1389928</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1095253</v>
+        <v>1131263</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+26.5%</t>
+          <t>+22.9%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1095253</v>
+        <v>1131263</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+26.5%</t>
+          <t>+22.9%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,23 +997,23 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>258196</v>
+        <v>267697</v>
       </c>
       <c r="E11" t="n">
-        <v>25108</v>
+        <v>41908</v>
       </c>
       <c r="F11" t="n">
-        <v>233088</v>
+        <v>225789</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1021,15 +1021,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>265612</v>
+        <v>260612</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1051,39 +1051,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>284528</v>
+        <v>325324</v>
       </c>
       <c r="E12" t="n">
-        <v>1998</v>
+        <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>282530</v>
+        <v>323096</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>238668</v>
+        <v>249464</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+19.2%</t>
+          <t>+30.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>223049</v>
+        <v>229845</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+40.6%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,43 +1103,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>502163</v>
+        <v>539386</v>
       </c>
       <c r="E13" t="n">
-        <v>76509</v>
+        <v>76609</v>
       </c>
       <c r="F13" t="n">
-        <v>425654</v>
+        <v>462777</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>526381</v>
+        <v>566881</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>482438</v>
+        <v>522938</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>15491</v>
+        <v>15595</v>
       </c>
     </row>
     <row r="14">
@@ -1157,39 +1157,39 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>334007</v>
+        <v>350904</v>
       </c>
       <c r="E14" t="n">
-        <v>31378</v>
+        <v>45378</v>
       </c>
       <c r="F14" t="n">
-        <v>302629</v>
+        <v>305526</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>542519</v>
+        <v>567205</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>417822</v>
+        <v>438508</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1211,13 +1211,13 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>171426</v>
+        <v>171445</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>156120</v>
+        <v>156139</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>204897</v>
+        <v>204926</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>204811</v>
+        <v>204840</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>250448</v>
+        <v>283665</v>
       </c>
       <c r="E16" t="n">
         <v>43000</v>
       </c>
       <c r="F16" t="n">
-        <v>207448</v>
+        <v>240665</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>148993</v>
+        <v>154993</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+68.1%</t>
+          <t>+83.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>111910</v>
+        <v>117910</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+85.4%</t>
+          <t>+104.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,39 +1315,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>381202</v>
+        <v>382432</v>
       </c>
       <c r="E17" t="n">
         <v>42366</v>
       </c>
       <c r="F17" t="n">
-        <v>338836</v>
+        <v>340066</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>292641</v>
+        <v>293679</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+30.3%</t>
+          <t>+30.2%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>266113</v>
+        <v>265932</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+27.3%</t>
+          <t>+27.9%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>542985</v>
+        <v>572024</v>
       </c>
       <c r="E18" t="n">
         <v>128005</v>
       </c>
       <c r="F18" t="n">
-        <v>414980</v>
+        <v>444019</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>572721</v>
+        <v>585536</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>361495</v>
+        <v>359201</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+14.8%</t>
+          <t>+23.6%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,43 +1423,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>300393</v>
+        <v>302632</v>
       </c>
       <c r="E19" t="n">
-        <v>143527</v>
+        <v>145527</v>
       </c>
       <c r="F19" t="n">
-        <v>156866</v>
+        <v>157105</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>902384</v>
+        <v>906741</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-66.6%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>815506</v>
+        <v>806663</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.5%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>9811</v>
+        <v>10454</v>
       </c>
     </row>
     <row r="20">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>490146</v>
+        <v>587045</v>
       </c>
       <c r="E20" t="n">
-        <v>76000</v>
+        <v>87100</v>
       </c>
       <c r="F20" t="n">
-        <v>414146</v>
+        <v>499945</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>498381</v>
+        <v>538181</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>+9.1%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>435082</v>
+        <v>474882</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>+5.3%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>427</v>
+        <v>554</v>
       </c>
       <c r="C2" t="n">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n">
-        <v>812.7</v>
+        <v>1535.6</v>
       </c>
       <c r="E2" t="n">
-        <v>46958</v>
+        <v>98281</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>37.1</v>
+        <v>642.7</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>768</v>
+        <v>702</v>
       </c>
       <c r="C4" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="D4" t="n">
-        <v>1256.2</v>
+        <v>1410</v>
       </c>
       <c r="E4" t="n">
-        <v>2727</v>
+        <v>3313</v>
       </c>
     </row>
   </sheetData>
@@ -1777,15 +1777,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>53098</v>
+        <v>63098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>117771.9</v>
+        <v>107771.9</v>
       </c>
     </row>
     <row r="3">
@@ -1803,19 +1803,19 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>38880</v>
+        <v>68680</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3386</v>
+        <v>33186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1837,23 +1837,23 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>35820</v>
+        <v>39800</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8366.66</v>
+        <v>13346.66</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>27453.34</v>
+        <v>26453.34</v>
       </c>
     </row>
     <row r="5">
@@ -1879,15 +1879,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33500</v>
+        <v>53892</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>155.2%</t>
+          <t>249.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-11920</v>
+        <v>-32312</v>
       </c>
     </row>
     <row r="6">
@@ -1973,23 +1973,23 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>26140</v>
+        <v>30120</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>20000</v>
+        <v>23386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6140</v>
+        <v>6734</v>
       </c>
     </row>
     <row r="9">
@@ -2041,11 +2041,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>183290</v>
+        <v>195230</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>141.0%</t>
+          <t>150.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2053,11 +2053,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>177912</v>
+        <v>189852</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2075,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="12">
@@ -2109,11 +2109,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>66520</v>
+        <v>82440</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2121,11 +2121,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>62337</v>
+        <v>78257</v>
       </c>
     </row>
     <row r="13">
@@ -2143,23 +2143,23 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>39800</v>
+        <v>55720</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9960</v>
+        <v>34760</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>29840</v>
+        <v>20960</v>
       </c>
     </row>
     <row r="14">
@@ -2177,11 +2177,11 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>49080</v>
+        <v>72960</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2189,11 +2189,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>32370</v>
+        <v>56250</v>
       </c>
     </row>
     <row r="15">
@@ -2211,23 +2211,23 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>94140</v>
+        <v>128920</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>49920</v>
+        <v>56520</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>44220</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="16">
@@ -2253,15 +2253,15 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>66228</v>
+        <v>71108</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>68548</v>
+        <v>63668</v>
       </c>
     </row>
     <row r="17">
@@ -2313,11 +2313,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>10398</v>
+        <v>20796</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10398</v>
+        <v>20796</v>
       </c>
     </row>
     <row r="19">
@@ -2457,15 +2457,15 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15779</v>
+        <v>16779</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>25750.9</v>
+        <v>24750.9</v>
       </c>
     </row>
     <row r="23">
@@ -2585,11 +2585,11 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2597,11 +2597,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>26860</v>
+        <v>30840</v>
       </c>
     </row>
     <row r="27">
@@ -2653,11 +2653,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>64920</v>
+        <v>68900</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>35120</v>
+        <v>39100</v>
       </c>
     </row>
     <row r="29">
@@ -2721,23 +2721,23 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>42840</v>
+        <v>55178</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4183.33</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>42840</v>
+        <v>50994.67</v>
       </c>
     </row>
     <row r="31">
@@ -2789,11 +2789,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>56438</v>
+        <v>70418</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2801,11 +2801,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34858</v>
+        <v>48838</v>
       </c>
     </row>
     <row r="33">
@@ -2823,23 +2823,23 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>115400</v>
+        <v>119380</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7700</v>
+        <v>14200</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>107700</v>
+        <v>105180</v>
       </c>
     </row>
     <row r="34">
@@ -2857,11 +2857,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>26500</v>
+        <v>30480</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2869,11 +2869,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14920</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="35">
@@ -2891,11 +2891,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>114260</v>
+        <v>120860</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>65686</v>
+        <v>72286</v>
       </c>
     </row>
     <row r="36">
@@ -2925,11 +2925,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>58280</v>
+        <v>82080</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2937,11 +2937,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>48280</v>
+        <v>72080</v>
       </c>
     </row>
     <row r="37">
@@ -2967,15 +2967,15 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>20800</v>
+        <v>14200</v>
       </c>
     </row>
     <row r="38">
@@ -2993,23 +2993,23 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>112520</v>
+        <v>119120</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>24800</v>
+        <v>38550</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>87720</v>
+        <v>80570</v>
       </c>
     </row>
     <row r="39">
@@ -3163,11 +3163,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>61920</v>
+        <v>68520</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3175,11 +3175,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>57920</v>
+        <v>64520</v>
       </c>
     </row>
     <row r="44">
@@ -3265,11 +3265,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>67000</v>
+        <v>73600</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>42200</v>
+        <v>48800</v>
       </c>
     </row>
   </sheetData>
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>40054.26</v>
+        <v>41338.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39734.26</v>
+        <v>41018.32</v>
       </c>
     </row>
     <row r="8">
@@ -3559,11 +3559,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>104600</v>
+        <v>105400</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>101900</v>
+        <v>102700</v>
       </c>
     </row>
     <row r="9">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>140594</v>
+        <v>153540</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>140594</v>
+        <v>153540</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>127107</v>
+        <v>131234</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>127107</v>
+        <v>131234</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>342616.53</v>
+        <v>349943.53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>342616.53</v>
+        <v>349943.53</v>
       </c>
     </row>
     <row r="15">
@@ -3933,11 +3933,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>109956</v>
+        <v>94956</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>109956</v>
+        <v>94956</v>
       </c>
     </row>
     <row r="20">
@@ -4035,11 +4035,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>28080</v>
+        <v>44478</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15635.52</v>
+        <v>32033.52</v>
       </c>
     </row>
     <row r="23">
@@ -4103,11 +4103,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>53192.01</v>
+        <v>53590.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>46194.01</v>
+        <v>46592.01</v>
       </c>
     </row>
     <row r="25">
@@ -4137,11 +4137,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>148357.01</v>
+        <v>153755.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>203.2%</t>
+          <t>210.6%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4149,11 +4149,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>125957.01</v>
+        <v>131355.01</v>
       </c>
     </row>
     <row r="26">
@@ -4205,11 +4205,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>106168</v>
+        <v>113166</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4217,11 +4217,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>98168</v>
+        <v>105166</v>
       </c>
     </row>
     <row r="28">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>218157.55</v>
+        <v>247261.65</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>177577.55</v>
+        <v>206681.65</v>
       </c>
     </row>
     <row r="29">
@@ -4341,23 +4341,23 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>41746.2</v>
+        <v>44846.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4398</v>
+        <v>4498</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>37348.2</v>
+        <v>40348.2</v>
       </c>
     </row>
     <row r="32">
@@ -4375,11 +4375,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>26406</v>
+        <v>31406</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4387,11 +4387,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>18406</v>
+        <v>23406</v>
       </c>
     </row>
     <row r="33">
@@ -4443,23 +4443,23 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>107388</v>
+        <v>137786</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>107388</v>
+        <v>137556</v>
       </c>
     </row>
     <row r="35">
@@ -4477,11 +4477,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>8192</v>
+        <v>8590</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8192</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="36">
@@ -4579,11 +4579,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>37794</v>
+        <v>47794</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>37794</v>
+        <v>47794</v>
       </c>
     </row>
     <row r="39">
@@ -4689,15 +4689,15 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>66588</v>
+        <v>56588</v>
       </c>
     </row>
     <row r="42">
@@ -4749,11 +4749,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>79250</v>
+        <v>99050</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>79250</v>
+        <v>99050</v>
       </c>
     </row>
     <row r="44">
@@ -4783,11 +4783,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>98052</v>
+        <v>168452</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>112.3%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>98052</v>
+        <v>168452</v>
       </c>
     </row>
     <row r="45">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>97219.2</v>
+        <v>98019.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>97219.2</v>
+        <v>98019.2</v>
       </c>
     </row>
     <row r="46">
@@ -5055,11 +5055,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>86784</v>
+        <v>95284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>61984</v>
+        <v>70484</v>
       </c>
     </row>
     <row r="53">
@@ -5097,15 +5097,15 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>99674</v>
+        <v>82874</v>
       </c>
     </row>
     <row r="54">
@@ -5123,11 +5123,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>58596</v>
+        <v>59596</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>58596</v>
+        <v>59596</v>
       </c>
     </row>
     <row r="55">
@@ -5225,11 +5225,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>35086</v>
+        <v>59886</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5237,11 +5237,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>27086</v>
+        <v>51886</v>
       </c>
     </row>
     <row r="58">
@@ -5259,11 +5259,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>77176</v>
+        <v>85574</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5271,11 +5271,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>52376</v>
+        <v>60774</v>
       </c>
     </row>
     <row r="59">
@@ -5361,11 +5361,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>172052.6</v>
+        <v>180052.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>162052.6</v>
+        <v>170052.6</v>
       </c>
     </row>
     <row r="62">
@@ -5395,23 +5395,23 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>55410.62</v>
+        <v>63410.62</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1212</v>
+        <v>15212</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>54198.62</v>
+        <v>48198.62</v>
       </c>
     </row>
     <row r="63">
@@ -5429,11 +5429,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>105093.48</v>
+        <v>105691.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>89893.48</v>
+        <v>90491.48</v>
       </c>
     </row>
     <row r="64">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1603988.02</v>
+        <v>1769102.02</v>
       </c>
       <c r="D2" t="n">
-        <v>4936</v>
+        <v>5331</v>
       </c>
       <c r="E2" t="n">
-        <v>1368605.02</v>
+        <v>1525017.02</v>
       </c>
       <c r="F2" t="n">
-        <v>235383</v>
+        <v>244085</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1464424</v>
+        <v>1620374</v>
       </c>
       <c r="D3" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="E3" t="n">
-        <v>1233025</v>
+        <v>1380676</v>
       </c>
       <c r="F3" t="n">
-        <v>231399</v>
+        <v>239698</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>139564.02</v>
+        <v>148728.02</v>
       </c>
       <c r="D4" t="n">
-        <v>4618</v>
+        <v>4966</v>
       </c>
       <c r="E4" t="n">
-        <v>135580.02</v>
+        <v>144341.02</v>
       </c>
       <c r="F4" t="n">
-        <v>3984</v>
+        <v>4387</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3211975.82</v>
+        <v>3421271.82</v>
       </c>
       <c r="D5" t="n">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="E5" t="n">
-        <v>696471.8</v>
+        <v>744087.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2515504.02</v>
+        <v>2677184.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2297007.02</v>
+        <v>2437697.02</v>
       </c>
       <c r="D6" t="n">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2180567.02</v>
+        <v>2321257.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>894968.8</v>
+        <v>963574.8</v>
       </c>
       <c r="D7" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E7" t="n">
-        <v>580031.8</v>
+        <v>627647.8</v>
       </c>
       <c r="F7" t="n">
-        <v>314937</v>
+        <v>335927</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2236888.76</v>
+        <v>2347040.34</v>
       </c>
       <c r="D8" t="n">
-        <v>1739</v>
+        <v>1869</v>
       </c>
       <c r="E8" t="n">
-        <v>34369.45</v>
+        <v>35069.45</v>
       </c>
       <c r="F8" t="n">
-        <v>2202519.31</v>
+        <v>2311970.89</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1387351.92</v>
+        <v>1433111.29</v>
       </c>
       <c r="D9" t="n">
-        <v>903</v>
+        <v>1023</v>
       </c>
       <c r="E9" t="n">
-        <v>12634.63</v>
+        <v>13134.63</v>
       </c>
       <c r="F9" t="n">
-        <v>1374717.29</v>
+        <v>1419976.66</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>847536.84</v>
+        <v>911929.05</v>
       </c>
       <c r="D10" t="n">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="E10" t="n">
-        <v>21734.82</v>
+        <v>21934.82</v>
       </c>
       <c r="F10" t="n">
-        <v>825802.02</v>
+        <v>889994.23</v>
       </c>
     </row>
     <row r="11">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>482000</v>
+        <v>601000</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>224200</v>
+        <v>248000</v>
       </c>
       <c r="F11" t="n">
-        <v>257800</v>
+        <v>353000</v>
       </c>
     </row>
     <row r="12">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>310454</v>
+        <v>342234</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>190254</v>
+        <v>222034</v>
       </c>
       <c r="F13" t="n">
         <v>120200</v>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1603988.02</v>
+        <v>1769102.02</v>
       </c>
       <c r="C2" t="n">
-        <v>246272.58</v>
+        <v>281958.91</v>
       </c>
       <c r="D2" t="n">
-        <v>27781.01</v>
+        <v>31061.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>218491.57</v>
+        <v>250897.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.62</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="3">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3211975.82</v>
+        <v>3421271.82</v>
       </c>
       <c r="C3" t="n">
-        <v>439328.28</v>
+        <v>524698.28</v>
       </c>
       <c r="D3" t="n">
-        <v>25398</v>
+        <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.79</v>
+        <v>1.04</v>
       </c>
       <c r="F3" t="n">
-        <v>413930.28</v>
+        <v>489200.28</v>
       </c>
       <c r="G3" t="n">
-        <v>12.89</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="4">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2236888.76</v>
+        <v>2347040.34</v>
       </c>
       <c r="C4" t="n">
-        <v>633773.5699999999</v>
+        <v>754690.5699999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1829</v>
+        <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>631944.5699999999</v>
+        <v>752661.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>28.25</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="5">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>482000</v>
+        <v>601000</v>
       </c>
       <c r="C5" t="n">
-        <v>261800</v>
+        <v>286600</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6019,10 +6019,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>261800</v>
+        <v>286600</v>
       </c>
       <c r="G5" t="n">
-        <v>54.32</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="6">
@@ -6035,7 +6035,7 @@
         <v>603258.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>152193.07</v>
+        <v>157073.07</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -6044,10 +6044,10 @@
         <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>150175.17</v>
+        <v>155055.17</v>
       </c>
       <c r="G6" t="n">
-        <v>24.89</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="7">
@@ -6057,22 +6057,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>310454</v>
+        <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>408080</v>
+        <v>437880</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.44</v>
+        <v>5.84</v>
       </c>
       <c r="F7" t="n">
-        <v>388080</v>
+        <v>417880</v>
       </c>
       <c r="G7" t="n">
-        <v>125</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="8">
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="C2" t="n">
-        <v>893517.51</v>
+        <v>934780.51</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>243935</v>
+        <v>292533</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6175,26 +6175,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="C4" t="n">
-        <v>125795.37</v>
+        <v>171786.37</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>61992.48</v>
+        <v>77331.67</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -6203,17 +6203,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>40782.67</v>
+        <v>74492.48</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>20358</v>
+        <v>24541.33</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>12345.8</v>
+        <v>12440.8</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>980</v>
+        <v>1037</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>93644.00999999999</v>
+        <v>112573.01</v>
       </c>
     </row>
     <row r="3">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D4" t="n">
-        <v>14832.66</v>
+        <v>44727.66</v>
       </c>
     </row>
     <row r="5">
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>5206</v>
+        <v>15225</v>
       </c>
     </row>
     <row r="6">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4169</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="7">
@@ -6462,14 +6462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1415</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="8">
@@ -6480,14 +6480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="9">
@@ -6498,32 +6498,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>141174</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -6534,14 +6534,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>18950</v>
+        <v>154924</v>
       </c>
     </row>
     <row r="12">
@@ -6552,92 +6552,92 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>10000</v>
+        <v>18950</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>143100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>6998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>83883</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>31431.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6646,64 +6646,64 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>103486</v>
+        <v>19996.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>20444.48</v>
+        <v>11586</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>4019</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="21">
@@ -6714,14 +6714,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>59083</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22">
@@ -6732,14 +6732,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>24745.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -6750,146 +6750,146 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>未填写原因</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>19549.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>10309</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7021</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4221</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>397</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>103486</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>72514</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6898,28 +6898,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>33614</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
@@ -6930,56 +6930,56 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>72514</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>62737</v>
+        <v>38494</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>13598</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6988,28 +6988,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -7056,176 +7056,176 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>6000</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>42813.6</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>14705.81</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>6988</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3840.67</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>934.9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D46" t="n">
-        <v>617</v>
+        <v>30705</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="D47" t="n">
-        <v>105</v>
+        <v>25761</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="50">
@@ -7236,14 +7236,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>25704</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="51">
@@ -7254,14 +7254,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>24186</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="52">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>6619</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53">
@@ -7290,194 +7290,194 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>4980</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D54" t="n">
-        <v>2489</v>
+        <v>44063.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="D55" t="n">
-        <v>1046</v>
+        <v>14743.81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>345</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>27</v>
       </c>
       <c r="D58" t="n">
-        <v>30206</v>
+        <v>3974.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D59" t="n">
-        <v>29800</v>
+        <v>972.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>3144</v>
+        <v>617</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>299</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>114</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
@@ -7488,14 +7488,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D64" t="n">
-        <v>57</v>
+        <v>30225</v>
       </c>
     </row>
     <row r="65">
@@ -7506,128 +7506,128 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>19</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D66" t="n">
-        <v>24800</v>
+        <v>7579</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>10200</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>8000</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>42067</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>299</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>16960</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7636,190 +7636,190 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>14495</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>3851</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>66</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>19</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>19</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>16819</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>10000</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>3000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D81" t="n">
-        <v>118</v>
+        <v>42067</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>29</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83">
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>24800</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="84">
@@ -7879,144 +7879,270 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>15218</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D87" t="n">
-        <v>59</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D88" t="n">
-        <v>29</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>7019</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>19.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1680</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="n">
+        <v>15218</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>7019</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2</v>
+      </c>
+      <c r="D100" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8058,36 +8184,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
-        <v>300484.48</v>
+        <v>329132.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>207120</v>
+        <v>220200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>195400</v>
+        <v>207120</v>
       </c>
     </row>
     <row r="5">
@@ -8097,10 +8223,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>166200</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="6">
@@ -8110,10 +8236,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
-        <v>147954.66</v>
+        <v>160503.99</v>
       </c>
     </row>
     <row r="7">
@@ -8123,10 +8249,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>143404</v>
+        <v>148284</v>
       </c>
     </row>
     <row r="8">
@@ -8136,10 +8262,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>87700</v>
+        <v>122430</v>
       </c>
     </row>
     <row r="9">
@@ -8149,10 +8275,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>48594</v>
+        <v>62486</v>
       </c>
     </row>
     <row r="10">
@@ -8162,23 +8288,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>29760</v>
+        <v>42960</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>认知9周+年卡</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>16199</v>
+        <v>19800</v>
       </c>
     </row>
   </sheetData>
@@ -8219,10 +8345,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C2" t="n">
-        <v>226915</v>
+        <v>231186</v>
       </c>
     </row>
     <row r="3">
@@ -8232,10 +8358,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C3" t="n">
-        <v>192249.5</v>
+        <v>206591.5</v>
       </c>
     </row>
     <row r="4">
@@ -8245,10 +8371,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C4" t="n">
-        <v>183169.48</v>
+        <v>191254.48</v>
       </c>
     </row>
     <row r="5">
@@ -8258,10 +8384,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>140301</v>
+        <v>156996</v>
       </c>
     </row>
     <row r="6">
@@ -8271,10 +8397,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>121772</v>
+        <v>128391</v>
       </c>
     </row>
     <row r="7">
@@ -8284,10 +8410,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>84550.81</v>
+        <v>118592.81</v>
       </c>
     </row>
     <row r="8">
@@ -8297,10 +8423,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>59937</v>
+        <v>64323</v>
       </c>
     </row>
     <row r="9">
@@ -8323,49 +8449,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>48649.9</v>
+        <v>48678.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>37695</v>
+        <v>42436.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>35638.9</v>
+        <v>40582</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>35055</v>
+        <v>37695</v>
       </c>
     </row>
     <row r="14">
@@ -8375,36 +8501,36 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C14" t="n">
-        <v>29952.66</v>
+        <v>36552.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>保留地址</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>29535.9</v>
+        <v>35638.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>25617.01</v>
+        <v>35055</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>396266</v>
+        <v>414285</v>
       </c>
       <c r="E2" t="n">
-        <v>251415</v>
+        <v>251988</v>
       </c>
       <c r="F2" t="n">
-        <v>144850</v>
+        <v>162296</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>658657</v>
+        <v>658807</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>227526</v>
+        <v>227543</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,41 +567,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20518</v>
+        <v>20556</v>
       </c>
       <c r="E3" t="n">
         <v>35448</v>
       </c>
       <c r="F3" t="n">
-        <v>-14929</v>
+        <v>-14891</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>55328</v>
+        <v>55868</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>-63.2%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4723</v>
+        <v>5188</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-416.1%</t>
+          <t>-387.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>633382</v>
+        <v>656623</v>
       </c>
       <c r="E4" t="n">
-        <v>158586</v>
+        <v>166289</v>
       </c>
       <c r="F4" t="n">
-        <v>474796</v>
+        <v>490333</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>577633</v>
+        <v>599829</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>397646</v>
+        <v>419640</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+19.4%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>421312</v>
+        <v>429517</v>
       </c>
       <c r="E5" t="n">
-        <v>111094</v>
+        <v>111294</v>
       </c>
       <c r="F5" t="n">
-        <v>310218</v>
+        <v>318223</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>602871</v>
+        <v>602947</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>380795</v>
+        <v>380871</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>290941</v>
+        <v>311882</v>
       </c>
       <c r="E6" t="n">
-        <v>75540</v>
+        <v>80952</v>
       </c>
       <c r="F6" t="n">
-        <v>215400</v>
+        <v>230929</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>260846</v>
+        <v>262622</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+18.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>220242</v>
+        <v>221790</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>299151</v>
+        <v>304463</v>
       </c>
       <c r="E7" t="n">
-        <v>68243</v>
+        <v>75283</v>
       </c>
       <c r="F7" t="n">
-        <v>230908</v>
+        <v>229180</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>565510</v>
+        <v>566208</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-46.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>379651</v>
+        <v>380296</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-39.2%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>345862</v>
+        <v>364289</v>
       </c>
       <c r="E8" t="n">
-        <v>76166</v>
+        <v>81517</v>
       </c>
       <c r="F8" t="n">
-        <v>269696</v>
+        <v>282772</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>412685</v>
+        <v>426600</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>244777</v>
+        <v>258635</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+10.2%</t>
+          <t>+9.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>788848</v>
+        <v>811497</v>
       </c>
       <c r="E9" t="n">
-        <v>190872</v>
+        <v>216270</v>
       </c>
       <c r="F9" t="n">
-        <v>597976</v>
+        <v>595227</v>
       </c>
       <c r="G9" t="n">
         <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1080733</v>
+        <v>1145833</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>698321</v>
+        <v>763421</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1389928</v>
+        <v>1410537</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1389928</v>
+        <v>1410537</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1131263</v>
+        <v>1213392</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+22.9%</t>
+          <t>+16.2%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1131263</v>
+        <v>1213392</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+22.9%</t>
+          <t>+16.2%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,39 +997,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>267697</v>
+        <v>290091</v>
       </c>
       <c r="E11" t="n">
-        <v>41908</v>
+        <v>45908</v>
       </c>
       <c r="F11" t="n">
-        <v>225789</v>
+        <v>244183</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>297469</v>
+        <v>343088</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>260612</v>
+        <v>306231</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1051,13 +1051,13 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>325324</v>
+        <v>325343</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>323096</v>
+        <v>323115</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>249464</v>
+        <v>250260</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+30.4%</t>
+          <t>+30.0%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>229845</v>
+        <v>230641</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+40.6%</t>
+          <t>+40.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,39 +1103,39 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>539386</v>
+        <v>540830</v>
       </c>
       <c r="E13" t="n">
         <v>76609</v>
       </c>
       <c r="F13" t="n">
-        <v>462777</v>
+        <v>464221</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>566881</v>
+        <v>576919</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>522938</v>
+        <v>532976</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1157,43 +1157,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>350904</v>
+        <v>369612</v>
       </c>
       <c r="E14" t="n">
         <v>45378</v>
       </c>
       <c r="F14" t="n">
-        <v>305526</v>
+        <v>324234</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>567205</v>
+        <v>615399</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>438508</v>
+        <v>486696</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>56422</v>
+        <v>56654</v>
       </c>
     </row>
     <row r="15">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>171445</v>
+        <v>181405</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>156139</v>
+        <v>166099</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>204926</v>
+        <v>205004</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>204840</v>
+        <v>204918</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>283665</v>
+        <v>302861</v>
       </c>
       <c r="E16" t="n">
-        <v>43000</v>
+        <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>240665</v>
+        <v>249861</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>154993</v>
+        <v>155591</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+83.0%</t>
+          <t>+94.7%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>117910</v>
+        <v>118508</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+104.1%</t>
+          <t>+110.8%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,39 +1315,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>382432</v>
+        <v>383807</v>
       </c>
       <c r="E17" t="n">
         <v>42366</v>
       </c>
       <c r="F17" t="n">
-        <v>340066</v>
+        <v>341441</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>293679</v>
+        <v>313698</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+30.2%</t>
+          <t>+22.3%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>265932</v>
+        <v>285951</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+27.9%</t>
+          <t>+19.4%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>572024</v>
+        <v>602062</v>
       </c>
       <c r="E18" t="n">
         <v>128005</v>
       </c>
       <c r="F18" t="n">
-        <v>444019</v>
+        <v>474057</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>585536</v>
+        <v>595934</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>+1.0%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>359201</v>
+        <v>369599</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+23.6%</t>
+          <t>+28.3%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,43 +1423,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>302632</v>
+        <v>313887</v>
       </c>
       <c r="E19" t="n">
         <v>145527</v>
       </c>
       <c r="F19" t="n">
-        <v>157105</v>
+        <v>168360</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>906741</v>
+        <v>911058</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-65.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>806663</v>
+        <v>810980</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-80.5%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10454</v>
+        <v>10890</v>
       </c>
     </row>
     <row r="20">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>587045</v>
+        <v>637819</v>
       </c>
       <c r="E20" t="n">
         <v>87100</v>
       </c>
       <c r="F20" t="n">
-        <v>499945</v>
+        <v>550719</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>538181</v>
+        <v>589379</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+9.1%</t>
+          <t>+8.2%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>474882</v>
+        <v>526080</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C2" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D2" t="n">
-        <v>1535.6</v>
+        <v>1365</v>
       </c>
       <c r="E2" t="n">
-        <v>98281</v>
+        <v>97929</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>642.7</v>
+        <v>579.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1527</v>
+        <v>19238</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>702</v>
+        <v>564</v>
       </c>
       <c r="C4" t="n">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="D4" t="n">
-        <v>1410</v>
+        <v>1216.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3313</v>
+        <v>7500</v>
       </c>
     </row>
   </sheetData>
@@ -1837,11 +1837,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>39800</v>
+        <v>35820</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1849,11 +1849,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26453.34</v>
+        <v>22473.34</v>
       </c>
     </row>
     <row r="5">
@@ -1871,11 +1871,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>21580</v>
+        <v>41380</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>249.7%</t>
+          <t>130.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-32312</v>
+        <v>-12512</v>
       </c>
     </row>
     <row r="6">
@@ -1981,15 +1981,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23386</v>
+        <v>25775</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6734</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="9">
@@ -2041,23 +2041,23 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>195230</v>
+        <v>203190</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>150.2%</t>
+          <t>156.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5378</v>
+        <v>8765</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>189852</v>
+        <v>194425</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2075,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>35820</v>
+        <v>31840</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35820</v>
+        <v>31840</v>
       </c>
     </row>
     <row r="12">
@@ -2109,11 +2109,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>82440</v>
+        <v>86420</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2121,11 +2121,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>78257</v>
+        <v>82237</v>
       </c>
     </row>
     <row r="13">
@@ -2177,11 +2177,11 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>72960</v>
+        <v>80920</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2189,11 +2189,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>56250</v>
+        <v>64210</v>
       </c>
     </row>
     <row r="15">
@@ -2219,15 +2219,15 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>56520</v>
+        <v>59906</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>72400</v>
+        <v>69014</v>
       </c>
     </row>
     <row r="16">
@@ -2245,11 +2245,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>134776</v>
+        <v>140544</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2257,11 +2257,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>63668</v>
+        <v>69436</v>
       </c>
     </row>
     <row r="17">
@@ -2279,11 +2279,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>261308.01</v>
+        <v>263288.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>261308.01</v>
+        <v>263288.01</v>
       </c>
     </row>
     <row r="18">
@@ -2347,23 +2347,23 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>51740</v>
+        <v>59700</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2596.6</v>
+        <v>7576.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>49143.4</v>
+        <v>52123.4</v>
       </c>
     </row>
     <row r="20">
@@ -2415,11 +2415,11 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>36548</v>
+        <v>40528</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>33391.33</v>
+        <v>37371.33</v>
       </c>
     </row>
     <row r="22">
@@ -2551,11 +2551,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>38440</v>
+        <v>46400</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>38440</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="26">
@@ -2619,23 +2619,23 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>111684</v>
+        <v>115944</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>9880</v>
+        <v>13380</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>101804</v>
+        <v>102564</v>
       </c>
     </row>
     <row r="28">
@@ -2721,11 +2721,11 @@
         <v>100000</v>
       </c>
       <c r="D30" t="n">
-        <v>55178</v>
+        <v>59158</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>50994.67</v>
+        <v>54974.67</v>
       </c>
     </row>
     <row r="31">
@@ -2789,11 +2789,11 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>70418</v>
+        <v>78378</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2801,11 +2801,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>48838</v>
+        <v>56798</v>
       </c>
     </row>
     <row r="33">
@@ -2857,23 +2857,23 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>30480</v>
+        <v>34460</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11580</v>
+        <v>16560</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18900</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="35">
@@ -2891,11 +2891,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>120860</v>
+        <v>124820</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>72286</v>
+        <v>76246</v>
       </c>
     </row>
     <row r="36">
@@ -2925,11 +2925,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>82080</v>
+        <v>94960</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2937,11 +2937,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>72080</v>
+        <v>84960</v>
       </c>
     </row>
     <row r="37">
@@ -2993,11 +2993,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>119120</v>
+        <v>121610</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>80570</v>
+        <v>83060</v>
       </c>
     </row>
     <row r="39">
@@ -3061,23 +3061,23 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>76108</v>
+        <v>79408</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6000</v>
+        <v>16398</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>70108</v>
+        <v>63010</v>
       </c>
     </row>
     <row r="41">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>13200</v>
+        <v>17200</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>-13200</v>
+        <v>-17200</v>
       </c>
     </row>
     <row r="45">
@@ -3273,15 +3273,15 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>24800</v>
+        <v>35800</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>48800</v>
+        <v>37800</v>
       </c>
     </row>
   </sheetData>
@@ -3355,11 +3355,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>24194</v>
+        <v>28154</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3367,11 +3367,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8976</v>
+        <v>12936</v>
       </c>
     </row>
     <row r="3">
@@ -3389,11 +3389,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>120922</v>
+        <v>126922</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>120.9%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>120922</v>
+        <v>126922</v>
       </c>
     </row>
     <row r="4">
@@ -3593,11 +3593,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>91495.16</v>
+        <v>101930.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3605,11 +3605,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>153.5%</t>
+          <t>137.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-48904.84</v>
+        <v>-38469.08</v>
       </c>
     </row>
     <row r="10">
@@ -3627,11 +3627,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>34200</v>
+        <v>35000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>34200</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="11">
@@ -3933,11 +3933,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>94956</v>
+        <v>116936</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94956</v>
+        <v>116936</v>
       </c>
     </row>
     <row r="20">
@@ -4001,11 +4001,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>58794.00000000001</v>
+        <v>60774.00000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>58794.00000000001</v>
+        <v>60774.00000000001</v>
       </c>
     </row>
     <row r="22">
@@ -4069,11 +4069,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>198748</v>
+        <v>218748</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>131160</v>
+        <v>151160</v>
       </c>
     </row>
     <row r="24">
@@ -4103,11 +4103,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>53590.01</v>
+        <v>63590.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>46592.01</v>
+        <v>56592.01</v>
       </c>
     </row>
     <row r="25">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>247261.65</v>
+        <v>247659.65</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>206681.65</v>
+        <v>207079.65</v>
       </c>
     </row>
     <row r="29">
@@ -4273,11 +4273,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>70808.89999999999</v>
+        <v>71406.89999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>70808.89999999999</v>
+        <v>71406.89999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4647,11 +4647,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>137186</v>
+        <v>143186</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4659,11 +4659,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>128386</v>
+        <v>134386</v>
       </c>
     </row>
     <row r="41">
@@ -4681,11 +4681,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>66588</v>
+        <v>66986</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4693,11 +4693,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>56588</v>
+        <v>56986</v>
       </c>
     </row>
     <row r="42">
@@ -4749,11 +4749,11 @@
         <v>150000</v>
       </c>
       <c r="D43" t="n">
-        <v>99050</v>
+        <v>105650</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>99050</v>
+        <v>105650</v>
       </c>
     </row>
     <row r="44">
@@ -4783,11 +4783,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>168452</v>
+        <v>184248</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>168452</v>
+        <v>184248</v>
       </c>
     </row>
     <row r="45">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>98019.2</v>
+        <v>98617.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98019.2</v>
+        <v>98617.2</v>
       </c>
     </row>
     <row r="46">
@@ -4885,11 +4885,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>83178</v>
+        <v>83576</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>83178</v>
+        <v>83576</v>
       </c>
     </row>
     <row r="48">
@@ -4919,11 +4919,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>51222</v>
+        <v>51620</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51222</v>
+        <v>51620</v>
       </c>
     </row>
     <row r="49">
@@ -5055,23 +5055,23 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>95284</v>
+        <v>103284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>24800</v>
+        <v>28800</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>70484</v>
+        <v>74484</v>
       </c>
     </row>
     <row r="53">
@@ -5089,11 +5089,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>99674</v>
+        <v>114068</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5101,11 +5101,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>82874</v>
+        <v>97268</v>
       </c>
     </row>
     <row r="54">
@@ -5259,23 +5259,23 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>85574</v>
+        <v>91574</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>24800</v>
+        <v>34800</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>60774</v>
+        <v>56774</v>
       </c>
     </row>
     <row r="59">
@@ -5327,11 +5327,11 @@
         <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>15388</v>
+        <v>28584</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>15388</v>
+        <v>28584</v>
       </c>
     </row>
     <row r="61">
@@ -5361,11 +5361,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>180052.6</v>
+        <v>181732.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>170052.6</v>
+        <v>171732.6</v>
       </c>
     </row>
     <row r="62">
@@ -5395,11 +5395,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>63410.62</v>
+        <v>63642.52</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5407,11 +5407,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48198.62</v>
+        <v>48430.52</v>
       </c>
     </row>
     <row r="63">
@@ -5429,11 +5429,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>105691.48</v>
+        <v>106089.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>90491.48</v>
+        <v>90889.48</v>
       </c>
     </row>
     <row r="64">
@@ -5497,11 +5497,11 @@
         <v>15378</v>
       </c>
       <c r="D65" t="n">
-        <v>996</v>
+        <v>17394</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>996</v>
+        <v>17394</v>
       </c>
     </row>
   </sheetData>
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1769102.02</v>
+        <v>1857331.02</v>
       </c>
       <c r="D2" t="n">
-        <v>5331</v>
+        <v>5760</v>
       </c>
       <c r="E2" t="n">
-        <v>1525017.02</v>
+        <v>1611042.02</v>
       </c>
       <c r="F2" t="n">
-        <v>244085</v>
+        <v>246289</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1620374</v>
+        <v>1695575</v>
       </c>
       <c r="D3" t="n">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="E3" t="n">
-        <v>1380676</v>
+        <v>1454178</v>
       </c>
       <c r="F3" t="n">
-        <v>239698</v>
+        <v>241397</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>148728.02</v>
+        <v>161756.02</v>
       </c>
       <c r="D4" t="n">
-        <v>4966</v>
+        <v>5369</v>
       </c>
       <c r="E4" t="n">
-        <v>144341.02</v>
+        <v>156864.02</v>
       </c>
       <c r="F4" t="n">
-        <v>4387</v>
+        <v>4892</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3421271.82</v>
+        <v>3577641.82</v>
       </c>
       <c r="D5" t="n">
-        <v>674</v>
+        <v>708</v>
       </c>
       <c r="E5" t="n">
         <v>744087.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2677184.02</v>
+        <v>2833554.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2437697.02</v>
+        <v>2551081.02</v>
       </c>
       <c r="D6" t="n">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2321257.02</v>
+        <v>2434641.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>963574.8</v>
+        <v>1006560.8</v>
       </c>
       <c r="D7" t="n">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E7" t="n">
         <v>627647.8</v>
       </c>
       <c r="F7" t="n">
-        <v>335927</v>
+        <v>378913</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2347040.34</v>
+        <v>2372956.94</v>
       </c>
       <c r="D8" t="n">
-        <v>1869</v>
+        <v>1893</v>
       </c>
       <c r="E8" t="n">
-        <v>35069.45</v>
+        <v>35328.79</v>
       </c>
       <c r="F8" t="n">
-        <v>2311970.89</v>
+        <v>2337628.15</v>
       </c>
     </row>
     <row r="9">
@@ -5742,13 +5742,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1433111.29</v>
+        <v>1433272.63</v>
       </c>
       <c r="D9" t="n">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="E9" t="n">
-        <v>13134.63</v>
+        <v>13295.97</v>
       </c>
       <c r="F9" t="n">
         <v>1419976.66</v>
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>911929.05</v>
+        <v>937684.3100000001</v>
       </c>
       <c r="D10" t="n">
-        <v>845</v>
+        <v>867</v>
       </c>
       <c r="E10" t="n">
-        <v>21934.82</v>
+        <v>22032.82</v>
       </c>
       <c r="F10" t="n">
-        <v>889994.23</v>
+        <v>915651.49</v>
       </c>
     </row>
     <row r="11">
@@ -5790,13 +5790,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>601000</v>
+        <v>603000</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>248000</v>
+        <v>250000</v>
       </c>
       <c r="F11" t="n">
         <v>353000</v>
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>603258.8100000001</v>
+        <v>608045.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>396334.81</v>
+        <v>401121.81</v>
       </c>
       <c r="F12" t="n">
         <v>206924</v>
@@ -5862,16 +5862,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33660</v>
+        <v>65340</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>25740</v>
+        <v>49500</v>
       </c>
       <c r="F14" t="n">
-        <v>7920</v>
+        <v>15840</v>
       </c>
     </row>
   </sheetData>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1769102.02</v>
+        <v>1857331.02</v>
       </c>
       <c r="C2" t="n">
-        <v>281958.91</v>
+        <v>304737.91</v>
       </c>
       <c r="D2" t="n">
-        <v>31061.01</v>
+        <v>34640.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="F2" t="n">
-        <v>250897.9</v>
+        <v>270097.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14.18</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="3">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3421271.82</v>
+        <v>3577641.82</v>
       </c>
       <c r="C3" t="n">
-        <v>524698.28</v>
+        <v>567596.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="F3" t="n">
-        <v>489200.28</v>
+        <v>532098.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.3</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="4">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2347040.34</v>
+        <v>2372956.94</v>
       </c>
       <c r="C4" t="n">
-        <v>754690.5699999999</v>
+        <v>761070.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -5994,10 +5994,10 @@
         <v>0.09</v>
       </c>
       <c r="F4" t="n">
-        <v>752661.5699999999</v>
+        <v>759041.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>32.07</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="5">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>601000</v>
+        <v>603000</v>
       </c>
       <c r="C5" t="n">
         <v>286600</v>
@@ -6022,7 +6022,7 @@
         <v>286600</v>
       </c>
       <c r="G5" t="n">
-        <v>47.69</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="6">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>603258.8100000001</v>
+        <v>608045.8100000001</v>
       </c>
       <c r="C6" t="n">
         <v>157073.07</v>
@@ -6047,7 +6047,7 @@
         <v>155055.17</v>
       </c>
       <c r="G6" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="7">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33660</v>
+        <v>65340</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C2" t="n">
-        <v>934780.51</v>
+        <v>970415.51</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>292533</v>
+        <v>303533</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="C4" t="n">
-        <v>171786.37</v>
+        <v>189558.37</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -6191,10 +6191,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
-        <v>77331.67</v>
+        <v>78226.67</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>12440.8</v>
+        <v>12777.8</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>10975</v>
+        <v>10994</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>112573.01</v>
+        <v>112630.01</v>
       </c>
     </row>
     <row r="3">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D4" t="n">
-        <v>44727.66</v>
+        <v>44805.66</v>
       </c>
     </row>
     <row r="5">
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>15225</v>
+        <v>15663</v>
       </c>
     </row>
     <row r="6">
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>154924</v>
+        <v>169322</v>
       </c>
     </row>
     <row r="12">
@@ -6570,14 +6570,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>10000</v>
+        <v>17998</v>
       </c>
     </row>
     <row r="14">
@@ -6588,14 +6588,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6998</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="15">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D16" t="n">
-        <v>31431.9</v>
+        <v>35549.9</v>
       </c>
     </row>
     <row r="17">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
-        <v>19996.9</v>
+        <v>23543.9</v>
       </c>
     </row>
     <row r="18">
@@ -6682,10 +6682,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>7021</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="20">
@@ -6750,32 +6750,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>未填写原因</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>143100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -6786,14 +6786,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2000</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="26">
@@ -6804,14 +6804,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="27">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
@@ -6840,32 +6840,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>103486</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>20444.48</v>
+        <v>103486</v>
       </c>
     </row>
     <row r="31">
@@ -6894,14 +6894,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>4019</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="32">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>56</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>72514</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>38494</v>
+        <v>72514</v>
       </c>
     </row>
     <row r="35">
@@ -6966,14 +6966,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>38494</v>
       </c>
     </row>
     <row r="36">
@@ -6984,14 +6984,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7015,19 +7015,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>54800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -7038,14 +7038,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>15200</v>
+        <v>54800</v>
       </c>
     </row>
     <row r="40">
@@ -7056,14 +7056,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>11100</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="41">
@@ -7074,86 +7074,86 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>6000</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>62837</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>13598</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D44" t="n">
-        <v>115</v>
+        <v>30798</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="46">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>30705</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="47">
@@ -7182,14 +7182,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>25761</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="48">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>9163.33</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="49">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>6619</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50">
@@ -7236,68 +7236,68 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>2489</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="D51" t="n">
-        <v>1065</v>
+        <v>44082.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="D52" t="n">
-        <v>345</v>
+        <v>19799.81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="54">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D54" t="n">
-        <v>44063.6</v>
+        <v>4012.67</v>
       </c>
     </row>
     <row r="55">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>14743.81</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="56">
@@ -7344,14 +7344,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D56" t="n">
-        <v>6988</v>
+        <v>1271.9</v>
       </c>
     </row>
     <row r="57">
@@ -7362,14 +7362,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>4000</v>
+        <v>617</v>
       </c>
     </row>
     <row r="58">
@@ -7380,14 +7380,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>3974.67</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59">
@@ -7398,14 +7398,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>972.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -7416,86 +7416,86 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>617</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>105</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>57</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>30225</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D65" t="n">
-        <v>29800</v>
+        <v>33744</v>
       </c>
     </row>
     <row r="66">
@@ -7524,14 +7524,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>7579</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="67">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="D67" t="n">
-        <v>299</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="68">
@@ -7560,14 +7560,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>131</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69">
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70">
@@ -7596,14 +7596,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71">
@@ -7614,254 +7614,254 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>16819</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>14000</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>3000</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>118</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>29</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>24800</v>
+        <v>299</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>10200</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>8000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>42067</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>299</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>41600</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>299</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7870,28 +7870,28 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>9</v>
+        <v>42067</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>16960</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87">
@@ -7902,14 +7902,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>14514</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="88">
@@ -7920,14 +7920,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D88" t="n">
-        <v>3851</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="89">
@@ -7938,14 +7938,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>66</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="90">
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -8005,19 +8005,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>59</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="95">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>7019</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>57</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="98">
@@ -8100,32 +8100,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>19.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1910</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="100">
@@ -8136,13 +8136,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>2</v>
       </c>
       <c r="D100" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8184,10 +8202,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
-        <v>329132.48</v>
+        <v>367632.48</v>
       </c>
     </row>
     <row r="3">
@@ -8236,10 +8254,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C6" t="n">
-        <v>160503.99</v>
+        <v>179625.99</v>
       </c>
     </row>
     <row r="7">
@@ -8262,10 +8280,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>122430</v>
+        <v>126828</v>
       </c>
     </row>
     <row r="9">
@@ -8345,10 +8363,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C2" t="n">
-        <v>231186</v>
+        <v>235004</v>
       </c>
     </row>
     <row r="3">
@@ -8358,10 +8376,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="C3" t="n">
-        <v>206591.5</v>
+        <v>222898.5</v>
       </c>
     </row>
     <row r="4">
@@ -8371,10 +8389,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C4" t="n">
-        <v>191254.48</v>
+        <v>202330.48</v>
       </c>
     </row>
     <row r="5">
@@ -8384,10 +8402,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>156996</v>
+        <v>161434</v>
       </c>
     </row>
     <row r="6">
@@ -8462,75 +8480,75 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>42436.01</v>
+        <v>42655.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
-        <v>40582</v>
+        <v>42530</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="C13" t="n">
-        <v>37695</v>
+        <v>41541.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>36552.99</v>
+        <v>40582</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>35638.9</v>
+        <v>37695</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>35055</v>
+        <v>35638.9</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>414285</v>
+        <v>421274</v>
       </c>
       <c r="E2" t="n">
-        <v>251988</v>
+        <v>252344</v>
       </c>
       <c r="F2" t="n">
-        <v>162296</v>
+        <v>168929</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>658807</v>
+        <v>704511</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>227543</v>
+        <v>273209</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,41 +567,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20556</v>
+        <v>20662</v>
       </c>
       <c r="E3" t="n">
-        <v>35448</v>
+        <v>35467</v>
       </c>
       <c r="F3" t="n">
-        <v>-14891</v>
+        <v>-14804</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>55868</v>
+        <v>56528</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-63.4%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5188</v>
+        <v>5772</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-387.0%</t>
+          <t>-356.5%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>656623</v>
+        <v>663497</v>
       </c>
       <c r="E4" t="n">
-        <v>166289</v>
+        <v>171572</v>
       </c>
       <c r="F4" t="n">
-        <v>490333</v>
+        <v>491924</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>599829</v>
+        <v>612520</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+9.5%</t>
+          <t>+8.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>419640</v>
+        <v>432227</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+13.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>429517</v>
+        <v>473344</v>
       </c>
       <c r="E5" t="n">
-        <v>111294</v>
+        <v>111332</v>
       </c>
       <c r="F5" t="n">
-        <v>318223</v>
+        <v>362012</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>602947</v>
+        <v>646747</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>380871</v>
+        <v>424671</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>311882</v>
+        <v>327663</v>
       </c>
       <c r="E6" t="n">
-        <v>80952</v>
+        <v>81645</v>
       </c>
       <c r="F6" t="n">
-        <v>230929</v>
+        <v>246017</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>262622</v>
+        <v>264080</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+18.8%</t>
+          <t>+24.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>221790</v>
+        <v>223096</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>304463</v>
+        <v>331414</v>
       </c>
       <c r="E7" t="n">
-        <v>75283</v>
+        <v>106495</v>
       </c>
       <c r="F7" t="n">
-        <v>229180</v>
+        <v>224919</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>566208</v>
+        <v>566927</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>380296</v>
+        <v>380996</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>364289</v>
+        <v>369881</v>
       </c>
       <c r="E8" t="n">
-        <v>81517</v>
+        <v>81688</v>
       </c>
       <c r="F8" t="n">
-        <v>282772</v>
+        <v>288193</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>426600</v>
+        <v>439460</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>258635</v>
+        <v>271092</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+9.3%</t>
+          <t>+6.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,25 +891,25 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>811497</v>
+        <v>880213</v>
       </c>
       <c r="E9" t="n">
-        <v>216270</v>
+        <v>219270</v>
       </c>
       <c r="F9" t="n">
-        <v>595227</v>
+        <v>660943</v>
       </c>
       <c r="G9" t="n">
         <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1410537</v>
+        <v>1484241</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1410537</v>
+        <v>1484241</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1213392</v>
+        <v>1331742</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1213392</v>
+        <v>1331742</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,43 +997,43 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>290091</v>
+        <v>303708</v>
       </c>
       <c r="E11" t="n">
         <v>45908</v>
       </c>
       <c r="F11" t="n">
-        <v>244183</v>
+        <v>257800</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>343088</v>
+        <v>343686</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>306231</v>
+        <v>306810</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>712</v>
+        <v>912</v>
       </c>
     </row>
     <row r="12">
@@ -1051,39 +1051,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>325343</v>
+        <v>325741</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>323115</v>
+        <v>323513</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>250260</v>
+        <v>287672</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+30.0%</t>
+          <t>+13.2%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>230641</v>
+        <v>268053</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+40.1%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,43 +1103,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>540830</v>
+        <v>553607</v>
       </c>
       <c r="E13" t="n">
         <v>76609</v>
       </c>
       <c r="F13" t="n">
-        <v>464221</v>
+        <v>476998</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>576919</v>
+        <v>588617</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>532976</v>
+        <v>544674</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>15595</v>
+        <v>16344</v>
       </c>
     </row>
     <row r="14">
@@ -1157,39 +1157,39 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>369612</v>
+        <v>370806</v>
       </c>
       <c r="E14" t="n">
         <v>45378</v>
       </c>
       <c r="F14" t="n">
-        <v>324234</v>
+        <v>325428</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>615399</v>
+        <v>659997</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>486696</v>
+        <v>531294</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>181405</v>
+        <v>195001</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>166099</v>
+        <v>179695</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>205004</v>
+        <v>205402</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>204918</v>
+        <v>205316</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,23 +1263,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>302861</v>
+        <v>311278</v>
       </c>
       <c r="E16" t="n">
         <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>249861</v>
+        <v>258278</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+94.7%</t>
+          <t>+100.1%</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+110.8%</t>
+          <t>+117.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,43 +1315,43 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>383807</v>
+        <v>392461</v>
       </c>
       <c r="E17" t="n">
-        <v>42366</v>
+        <v>79166</v>
       </c>
       <c r="F17" t="n">
-        <v>341441</v>
+        <v>313295</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>313698</v>
+        <v>365290</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+22.3%</t>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>285951</v>
+        <v>337543</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+19.4%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>24133</v>
+        <v>24189</v>
       </c>
     </row>
     <row r="18">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>602062</v>
+        <v>626060</v>
       </c>
       <c r="E18" t="n">
-        <v>128005</v>
+        <v>152805</v>
       </c>
       <c r="F18" t="n">
-        <v>474057</v>
+        <v>473255</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>595934</v>
+        <v>612966</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>369599</v>
+        <v>386616</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+28.3%</t>
+          <t>+22.4%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,39 +1423,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>313887</v>
+        <v>343485</v>
       </c>
       <c r="E19" t="n">
         <v>145527</v>
       </c>
       <c r="F19" t="n">
-        <v>168360</v>
+        <v>197958</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>911058</v>
+        <v>943117</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-65.5%</t>
+          <t>-63.6%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>810980</v>
+        <v>842921</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>637819</v>
+        <v>650805</v>
       </c>
       <c r="E20" t="n">
-        <v>87100</v>
+        <v>95100</v>
       </c>
       <c r="F20" t="n">
-        <v>550719</v>
+        <v>555705</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>589379</v>
+        <v>784943</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+8.2%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>526080</v>
+        <v>721644</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>551</v>
+        <v>2801</v>
       </c>
       <c r="C2" t="n">
-        <v>77</v>
+        <v>2665</v>
       </c>
       <c r="D2" t="n">
-        <v>1365</v>
+        <v>41446.6</v>
       </c>
       <c r="E2" t="n">
-        <v>97929</v>
+        <v>50804</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>272</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>260</v>
       </c>
       <c r="D3" t="n">
-        <v>579.2</v>
+        <v>6304.6</v>
       </c>
       <c r="E3" t="n">
-        <v>19238</v>
+        <v>3383</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>564</v>
+        <v>7279</v>
       </c>
       <c r="C4" t="n">
-        <v>106</v>
+        <v>6811</v>
       </c>
       <c r="D4" t="n">
-        <v>1216.3</v>
+        <v>73747.8</v>
       </c>
       <c r="E4" t="n">
-        <v>7500</v>
+        <v>4216</v>
       </c>
     </row>
   </sheetData>
@@ -1905,11 +1905,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>61740</v>
+        <v>68340</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1917,11 +1917,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32757</v>
+        <v>39357</v>
       </c>
     </row>
     <row r="7">
@@ -2049,15 +2049,15 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8765</v>
+        <v>13745</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>194425</v>
+        <v>189445</v>
       </c>
     </row>
     <row r="11">
@@ -2245,11 +2245,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>140544</v>
+        <v>183920</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2257,11 +2257,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>69436</v>
+        <v>112812</v>
       </c>
     </row>
     <row r="17">
@@ -2347,11 +2347,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>59700</v>
+        <v>63680</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2359,11 +2359,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>52123.4</v>
+        <v>56103.4</v>
       </c>
     </row>
     <row r="20">
@@ -2449,11 +2449,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>41529.9</v>
+        <v>48129.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2461,11 +2461,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>24750.9</v>
+        <v>31350.9</v>
       </c>
     </row>
     <row r="23">
@@ -2483,11 +2483,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>23688</v>
+        <v>27668</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2495,11 +2495,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>18708</v>
+        <v>22688</v>
       </c>
     </row>
     <row r="24">
@@ -2653,11 +2653,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>68900</v>
+        <v>93700</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>39100</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="29">
@@ -2695,15 +2695,15 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>64600</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="30">
@@ -2823,11 +2823,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>119380</v>
+        <v>123360</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2835,11 +2835,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>105180</v>
+        <v>109160</v>
       </c>
     </row>
     <row r="34">
@@ -2891,11 +2891,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>124820</v>
+        <v>139640</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>76246</v>
+        <v>91066</v>
       </c>
     </row>
     <row r="36">
@@ -3163,11 +3163,11 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>68520</v>
+        <v>76920</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3175,11 +3175,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>64520</v>
+        <v>72920</v>
       </c>
     </row>
     <row r="44">
@@ -3265,11 +3265,11 @@
         <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>73600</v>
+        <v>119200</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>37800</v>
+        <v>83400</v>
       </c>
     </row>
   </sheetData>
@@ -3355,11 +3355,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>28154</v>
+        <v>40552</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3367,11 +3367,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12936</v>
+        <v>25334</v>
       </c>
     </row>
     <row r="3">
@@ -3423,11 +3423,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>15771</v>
+        <v>16969</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15771</v>
+        <v>16969</v>
       </c>
     </row>
     <row r="5">
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>41338.32</v>
+        <v>46736.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3537,11 +3537,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41018.32</v>
+        <v>46416.32</v>
       </c>
     </row>
     <row r="8">
@@ -3559,11 +3559,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>105400</v>
+        <v>111600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3571,11 +3571,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>102700</v>
+        <v>108900</v>
       </c>
     </row>
     <row r="9">
@@ -3593,11 +3593,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>101930.92</v>
+        <v>119930.92</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3605,11 +3605,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>137.7%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-38469.08</v>
+        <v>-20469.08</v>
       </c>
     </row>
     <row r="10">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>153540</v>
+        <v>160607.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>153540</v>
+        <v>160607.57</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>131234</v>
+        <v>133034</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>131234</v>
+        <v>133034</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>349943.53</v>
+        <v>362051.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>349943.53</v>
+        <v>362051.74</v>
       </c>
     </row>
     <row r="15">
@@ -3797,11 +3797,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>132533.74</v>
+        <v>147722.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>132533.74</v>
+        <v>147722.74</v>
       </c>
     </row>
     <row r="16">
@@ -3831,11 +3831,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>155847</v>
+        <v>148212</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>155847</v>
+        <v>148212</v>
       </c>
     </row>
     <row r="17">
@@ -3865,11 +3865,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>187218</v>
+        <v>211319</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>187218</v>
+        <v>211319</v>
       </c>
     </row>
     <row r="18">
@@ -3933,11 +3933,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>116936</v>
+        <v>125473</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>116936</v>
+        <v>125473</v>
       </c>
     </row>
     <row r="20">
@@ -4035,11 +4035,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>44478</v>
+        <v>46278</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>32033.52</v>
+        <v>33833.52</v>
       </c>
     </row>
     <row r="23">
@@ -4069,23 +4069,23 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>218748</v>
+        <v>231948</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>67588</v>
+        <v>92388</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>151160</v>
+        <v>139560</v>
       </c>
     </row>
     <row r="24">
@@ -4103,11 +4103,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>63590.01</v>
+        <v>64988.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>56592.01</v>
+        <v>57990.01</v>
       </c>
     </row>
     <row r="25">
@@ -4171,11 +4171,11 @@
         <v>50000</v>
       </c>
       <c r="D26" t="n">
-        <v>5358</v>
+        <v>11958</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5358</v>
+        <v>11958</v>
       </c>
     </row>
     <row r="27">
@@ -4205,11 +4205,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>113166</v>
+        <v>115146</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4217,11 +4217,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>105166</v>
+        <v>107146</v>
       </c>
     </row>
     <row r="28">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>247659.65</v>
+        <v>248408.35</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>207079.65</v>
+        <v>207828.35</v>
       </c>
     </row>
     <row r="29">
@@ -4273,11 +4273,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>71406.89999999999</v>
+        <v>83406.89999999999</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>71406.89999999999</v>
+        <v>83406.89999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4511,11 +4511,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>87790</v>
+        <v>88188</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>219.5%</t>
+          <t>220.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>87790</v>
+        <v>88188</v>
       </c>
     </row>
     <row r="37">
@@ -4783,11 +4783,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>184248</v>
+        <v>185044</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>184248</v>
+        <v>185044</v>
       </c>
     </row>
     <row r="45">
@@ -4851,11 +4851,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>126896</v>
+        <v>134896</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>126896</v>
+        <v>134896</v>
       </c>
     </row>
     <row r="47">
@@ -4893,15 +4893,15 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>83576</v>
+        <v>66776</v>
       </c>
     </row>
     <row r="48">
@@ -4919,11 +4919,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>51620</v>
+        <v>52218</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51620</v>
+        <v>52218</v>
       </c>
     </row>
     <row r="49">
@@ -5089,11 +5089,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>114068</v>
+        <v>127068</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5101,11 +5101,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>97268</v>
+        <v>110268</v>
       </c>
     </row>
     <row r="54">
@@ -5123,11 +5123,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>59596</v>
+        <v>59994</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>59596</v>
+        <v>59994</v>
       </c>
     </row>
     <row r="55">
@@ -5293,11 +5293,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>122768</v>
+        <v>131166</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5305,11 +5305,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>112568</v>
+        <v>120966</v>
       </c>
     </row>
     <row r="60">
@@ -5395,11 +5395,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>63642.52</v>
+        <v>64040.52</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5407,11 +5407,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48430.52</v>
+        <v>48828.52</v>
       </c>
     </row>
     <row r="63">
@@ -5429,11 +5429,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>106089.48</v>
+        <v>106885.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>90889.48</v>
+        <v>91685.48</v>
       </c>
     </row>
     <row r="64">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1857331.02</v>
+        <v>1907541.02</v>
       </c>
       <c r="D2" t="n">
-        <v>5760</v>
+        <v>6102</v>
       </c>
       <c r="E2" t="n">
-        <v>1611042.02</v>
+        <v>1654377.02</v>
       </c>
       <c r="F2" t="n">
-        <v>246289</v>
+        <v>253164</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1695575</v>
+        <v>1734219</v>
       </c>
       <c r="D3" t="n">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="E3" t="n">
-        <v>1454178</v>
+        <v>1486165</v>
       </c>
       <c r="F3" t="n">
-        <v>241397</v>
+        <v>248054</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>161756.02</v>
+        <v>173322.02</v>
       </c>
       <c r="D4" t="n">
-        <v>5369</v>
+        <v>5688</v>
       </c>
       <c r="E4" t="n">
-        <v>156864.02</v>
+        <v>168212.02</v>
       </c>
       <c r="F4" t="n">
-        <v>4892</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3577641.82</v>
+        <v>3707035.82</v>
       </c>
       <c r="D5" t="n">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="E5" t="n">
-        <v>744087.8</v>
+        <v>758907.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2833554.02</v>
+        <v>2948128.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2551081.02</v>
+        <v>2624859.02</v>
       </c>
       <c r="D6" t="n">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2434641.02</v>
+        <v>2508419.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1006560.8</v>
+        <v>1062176.8</v>
       </c>
       <c r="D7" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E7" t="n">
-        <v>627647.8</v>
+        <v>642467.8</v>
       </c>
       <c r="F7" t="n">
-        <v>378913</v>
+        <v>419709</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2372956.94</v>
+        <v>2521367.63</v>
       </c>
       <c r="D8" t="n">
-        <v>1893</v>
+        <v>2014</v>
       </c>
       <c r="E8" t="n">
-        <v>35328.79</v>
+        <v>37235</v>
       </c>
       <c r="F8" t="n">
-        <v>2337628.15</v>
+        <v>2484132.63</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1433272.63</v>
+        <v>1522772.32</v>
       </c>
       <c r="D9" t="n">
-        <v>1025</v>
+        <v>1075</v>
       </c>
       <c r="E9" t="n">
-        <v>13295.97</v>
+        <v>13402.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1419976.66</v>
+        <v>1509370.14</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>937684.3100000001</v>
+        <v>996595.3100000001</v>
       </c>
       <c r="D10" t="n">
-        <v>867</v>
+        <v>938</v>
       </c>
       <c r="E10" t="n">
-        <v>22032.82</v>
+        <v>23832.82</v>
       </c>
       <c r="F10" t="n">
-        <v>915651.49</v>
+        <v>972762.49</v>
       </c>
     </row>
     <row r="11">
@@ -5790,13 +5790,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>603000</v>
+        <v>673400</v>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>250000</v>
+        <v>320400</v>
       </c>
       <c r="F11" t="n">
         <v>353000</v>
@@ -5814,16 +5814,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>608045.8100000001</v>
+        <v>651421.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>401121.81</v>
+        <v>445496.81</v>
       </c>
       <c r="F12" t="n">
-        <v>206924</v>
+        <v>205925</v>
       </c>
     </row>
     <row r="13">
@@ -5862,16 +5862,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65340</v>
+        <v>67320</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>49500</v>
       </c>
       <c r="F14" t="n">
-        <v>15840</v>
+        <v>17820</v>
       </c>
     </row>
   </sheetData>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1857331.02</v>
+        <v>1907541.02</v>
       </c>
       <c r="C2" t="n">
-        <v>304737.91</v>
+        <v>312709.91</v>
       </c>
       <c r="D2" t="n">
-        <v>34640.01</v>
+        <v>37632.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="F2" t="n">
-        <v>270097.9</v>
+        <v>275077.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14.54</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="3">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3577641.82</v>
+        <v>3707035.82</v>
       </c>
       <c r="C3" t="n">
-        <v>567596.28</v>
+        <v>612596.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>532098.28</v>
+        <v>577098.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.87</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="4">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2372956.94</v>
+        <v>2521367.63</v>
       </c>
       <c r="C4" t="n">
-        <v>761070.5699999999</v>
+        <v>848421.5699999999</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>759041.5699999999</v>
+        <v>846392.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>31.99</v>
+        <v>33.57</v>
       </c>
     </row>
     <row r="5">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>603000</v>
+        <v>673400</v>
       </c>
       <c r="C5" t="n">
-        <v>286600</v>
+        <v>311400</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6019,10 +6019,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>286600</v>
+        <v>311400</v>
       </c>
       <c r="G5" t="n">
-        <v>47.53</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="6">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>608045.8100000001</v>
+        <v>651421.8100000001</v>
       </c>
       <c r="C6" t="n">
         <v>157073.07</v>
@@ -6041,13 +6041,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F6" t="n">
         <v>155055.17</v>
       </c>
       <c r="G6" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="7">
@@ -6060,7 +6060,7 @@
         <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>437880</v>
+        <v>467680</v>
       </c>
       <c r="D7" t="n">
         <v>20000</v>
@@ -6069,10 +6069,10 @@
         <v>5.84</v>
       </c>
       <c r="F7" t="n">
-        <v>417880</v>
+        <v>447680</v>
       </c>
       <c r="G7" t="n">
-        <v>122.1</v>
+        <v>130.81</v>
       </c>
     </row>
     <row r="8">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65340</v>
+        <v>67320</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C2" t="n">
-        <v>970415.51</v>
+        <v>1008317.51</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>303533</v>
+        <v>333333</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="C4" t="n">
-        <v>189558.37</v>
+        <v>191977.37</v>
       </c>
       <c r="D4" t="n">
         <v>25</v>
@@ -6187,33 +6187,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>78226.67</v>
+        <v>97492.48</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="C6" t="n">
-        <v>74492.48</v>
+        <v>95102.67</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>12777.8</v>
+        <v>12815.8</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>1056</v>
+        <v>1393</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" t="n">
-        <v>44805.66</v>
+        <v>44843.66</v>
       </c>
     </row>
     <row r="5">
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>1434</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="9">
@@ -6498,14 +6498,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>57</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>18950</v>
+        <v>21950</v>
       </c>
     </row>
     <row r="13">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D16" t="n">
-        <v>35549.9</v>
+        <v>35720.9</v>
       </c>
     </row>
     <row r="17">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D17" t="n">
-        <v>23543.9</v>
+        <v>28598.9</v>
       </c>
     </row>
     <row r="18">
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>11586</v>
+        <v>11605</v>
       </c>
     </row>
     <row r="19">
@@ -6682,10 +6682,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>7040</v>
+        <v>7059</v>
       </c>
     </row>
     <row r="20">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>397</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22">
@@ -6781,7 +6781,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>143100</v>
+        <v>128286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6808,46 +6808,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>2000</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -6858,56 +6858,56 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>103486</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>20444.48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6916,28 +6916,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>4019</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35" t="n">
-        <v>38494</v>
+        <v>38513</v>
       </c>
     </row>
     <row r="36">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>248</v>
+        <v>267</v>
       </c>
     </row>
     <row r="37">
@@ -7033,259 +7033,259 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>54800</v>
+        <v>59600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>15200</v>
+        <v>33763</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D41" t="n">
-        <v>11100</v>
+        <v>12455</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>6000</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>30800</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>30798</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>9163.33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>6619</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>2489</v>
+        <v>62800</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>1265</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>364</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D51" t="n">
-        <v>44082.6</v>
+        <v>30922</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D52" t="n">
-        <v>19799.81</v>
+        <v>30809</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7294,100 +7294,100 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>6988</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>4012.67</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
-        <v>4000</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>1271.9</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>617</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>105</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -7398,14 +7398,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D59" t="n">
-        <v>57</v>
+        <v>44101.6</v>
       </c>
     </row>
     <row r="60">
@@ -7416,410 +7416,410 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>20454.81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>62837</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D62" t="n">
-        <v>13598</v>
+        <v>4031.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>115</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D64" t="n">
-        <v>59</v>
+        <v>1271.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>33744</v>
+        <v>617</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>29800</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>11062</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>299</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>150</v>
+        <v>42067</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>133</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>76</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>24800</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>18000</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>10200</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>41600</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>4009</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>299</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>16819</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>14000</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>10000</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3000</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83">
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>118</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="84">
@@ -7848,86 +7848,86 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>29</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>42067</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>299</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>16960</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>14514</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
@@ -7938,14 +7938,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>3851</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="90">
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D90" t="n">
-        <v>66</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="91">
@@ -7974,14 +7974,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D91" t="n">
-        <v>19</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="92">
@@ -7992,14 +7992,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -8023,37 +8023,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
@@ -8064,50 +8064,50 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
-        <v>29</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>7019</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99">
@@ -8118,49 +8118,85 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>19.9</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>1910</v>
+        <v>57</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>主动放弃/拍错</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C103" t="n">
         <v>2</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D103" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8202,49 +8238,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C2" t="n">
-        <v>367632.48</v>
+        <v>398632.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>220200</v>
+        <v>225800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>207120</v>
+        <v>220200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>196000</v>
+        <v>207120</v>
       </c>
     </row>
     <row r="6">
@@ -8254,36 +8290,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>179625.99</v>
+        <v>184605.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>148284</v>
+        <v>151628</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>126828</v>
+        <v>148284</v>
       </c>
     </row>
     <row r="9">
@@ -8315,14 +8351,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>线下产品</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>19800</v>
+        <v>33600</v>
       </c>
     </row>
   </sheetData>
@@ -8363,10 +8399,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C2" t="n">
-        <v>235004</v>
+        <v>271851</v>
       </c>
     </row>
     <row r="3">
@@ -8376,10 +8412,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C3" t="n">
-        <v>222898.5</v>
+        <v>253439.5</v>
       </c>
     </row>
     <row r="4">
@@ -8389,10 +8425,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C4" t="n">
-        <v>202330.48</v>
+        <v>202425.48</v>
       </c>
     </row>
     <row r="5">
@@ -8402,10 +8438,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C5" t="n">
-        <v>161434</v>
+        <v>169491</v>
       </c>
     </row>
     <row r="6">
@@ -8415,10 +8451,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>128391</v>
+        <v>128410</v>
       </c>
     </row>
     <row r="7">
@@ -8428,10 +8464,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>118592.81</v>
+        <v>118611.81</v>
       </c>
     </row>
     <row r="8">
@@ -8454,10 +8490,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>54957</v>
+        <v>57976</v>
       </c>
     </row>
     <row r="10">
@@ -8476,27 +8512,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C11" t="n">
-        <v>42655.01</v>
+        <v>43446</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>42530</v>
+        <v>42674.01</v>
       </c>
     </row>
     <row r="13">
@@ -8506,10 +8542,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C13" t="n">
-        <v>41541.99</v>
+        <v>41607.99</v>
       </c>
     </row>
     <row r="14">
@@ -8519,36 +8555,36 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>40582</v>
+        <v>40620</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C15" t="n">
-        <v>37695</v>
+        <v>38733</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>35638.9</v>
+        <v>37695</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>421274</v>
+        <v>468658</v>
       </c>
       <c r="E2" t="n">
-        <v>252344</v>
+        <v>252562</v>
       </c>
       <c r="F2" t="n">
-        <v>168929</v>
+        <v>216095</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>704511</v>
+        <v>745457</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-37.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>273209</v>
+        <v>307467</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,41 +567,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20662</v>
+        <v>20951</v>
       </c>
       <c r="E3" t="n">
         <v>35467</v>
       </c>
       <c r="F3" t="n">
-        <v>-14804</v>
+        <v>-14515</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>56528</v>
+        <v>57056</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-63.4%</t>
+          <t>-63.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5772</v>
+        <v>6224</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-356.5%</t>
+          <t>-333.2%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>663497</v>
+        <v>682632</v>
       </c>
       <c r="E4" t="n">
-        <v>171572</v>
+        <v>175795</v>
       </c>
       <c r="F4" t="n">
-        <v>491924</v>
+        <v>506836</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>612520</v>
+        <v>646604</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+8.3%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>432227</v>
+        <v>451384</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+13.8%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>473344</v>
+        <v>483217</v>
       </c>
       <c r="E5" t="n">
-        <v>111332</v>
+        <v>127387</v>
       </c>
       <c r="F5" t="n">
-        <v>362012</v>
+        <v>355830</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>646747</v>
+        <v>647132</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>424671</v>
+        <v>425037</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>327663</v>
+        <v>392958</v>
       </c>
       <c r="E6" t="n">
-        <v>81645</v>
+        <v>105617</v>
       </c>
       <c r="F6" t="n">
-        <v>246017</v>
+        <v>287340</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>264080</v>
+        <v>365666</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+24.1%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>223096</v>
+        <v>324530</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+10.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>331414</v>
+        <v>352268</v>
       </c>
       <c r="E7" t="n">
-        <v>106495</v>
+        <v>107608</v>
       </c>
       <c r="F7" t="n">
-        <v>224919</v>
+        <v>244660</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>566927</v>
+        <v>567917</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>380996</v>
+        <v>381857</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>369881</v>
+        <v>372143</v>
       </c>
       <c r="E8" t="n">
-        <v>81688</v>
+        <v>81773</v>
       </c>
       <c r="F8" t="n">
-        <v>288193</v>
+        <v>290370</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>439460</v>
+        <v>464596</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>271092</v>
+        <v>296019</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+6.3%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>880213</v>
+        <v>923993</v>
       </c>
       <c r="E9" t="n">
-        <v>219270</v>
+        <v>236268</v>
       </c>
       <c r="F9" t="n">
-        <v>660943</v>
+        <v>687725</v>
       </c>
       <c r="G9" t="n">
         <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1145833</v>
+        <v>1177233</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>763421</v>
+        <v>766021</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1484241</v>
+        <v>1525402</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1484241</v>
+        <v>1525402</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1331742</v>
+        <v>1337322</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+14.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1331742</v>
+        <v>1337322</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+14.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,39 +997,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>303708</v>
+        <v>305144</v>
       </c>
       <c r="E11" t="n">
-        <v>45908</v>
+        <v>45927</v>
       </c>
       <c r="F11" t="n">
-        <v>257800</v>
+        <v>259217</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>343686</v>
+        <v>343886</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>306810</v>
+        <v>299010</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1051,23 +1051,23 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>325741</v>
+        <v>357440</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>323513</v>
+        <v>355212</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>+24.3%</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,43 +1103,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>553607</v>
+        <v>565894</v>
       </c>
       <c r="E13" t="n">
         <v>76609</v>
       </c>
       <c r="F13" t="n">
-        <v>476998</v>
+        <v>489285</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>588617</v>
+        <v>611117</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>544674</v>
+        <v>567174</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>16344</v>
+        <v>16414</v>
       </c>
     </row>
     <row r="14">
@@ -1157,13 +1157,13 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>370806</v>
+        <v>370825</v>
       </c>
       <c r="E14" t="n">
         <v>45378</v>
       </c>
       <c r="F14" t="n">
-        <v>325428</v>
+        <v>325447</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>659997</v>
+        <v>697789</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>-46.9%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>531294</v>
+        <v>569086</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-42.8%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>195001</v>
+        <v>195418</v>
       </c>
       <c r="E15" t="n">
         <v>15306</v>
       </c>
       <c r="F15" t="n">
-        <v>179695</v>
+        <v>180112</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>205402</v>
+        <v>213800</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>205316</v>
+        <v>213714</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>311278</v>
+        <v>321278</v>
       </c>
       <c r="E16" t="n">
         <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>258278</v>
+        <v>268278</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>155591</v>
+        <v>196094</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+100.1%</t>
+          <t>+63.8%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>118508</v>
+        <v>134211</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+117.9%</t>
+          <t>+99.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,39 +1315,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>392461</v>
+        <v>427878</v>
       </c>
       <c r="E17" t="n">
-        <v>79166</v>
+        <v>80166</v>
       </c>
       <c r="F17" t="n">
-        <v>313295</v>
+        <v>347712</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>365290</v>
+        <v>402968</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+6.2%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>337543</v>
+        <v>375221</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>626060</v>
+        <v>634894</v>
       </c>
       <c r="E18" t="n">
         <v>152805</v>
       </c>
       <c r="F18" t="n">
-        <v>473255</v>
+        <v>482089</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>612966</v>
+        <v>641284</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>386616</v>
+        <v>414822</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+22.4%</t>
+          <t>+16.2%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,39 +1423,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>343485</v>
+        <v>373985</v>
       </c>
       <c r="E19" t="n">
         <v>145527</v>
       </c>
       <c r="F19" t="n">
-        <v>197958</v>
+        <v>228458</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>943117</v>
+        <v>946795</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-63.6%</t>
+          <t>-60.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>842921</v>
+        <v>837599</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>650805</v>
+        <v>689126</v>
       </c>
       <c r="E20" t="n">
         <v>95100</v>
       </c>
       <c r="F20" t="n">
-        <v>555705</v>
+        <v>594026</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>784943</v>
+        <v>785865</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>721644</v>
+        <v>721566</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2801</v>
+        <v>533</v>
       </c>
       <c r="C2" t="n">
-        <v>2665</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>41446.6</v>
+        <v>1218.9</v>
       </c>
       <c r="E2" t="n">
-        <v>50804</v>
+        <v>93263</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>260</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>6304.6</v>
+        <v>512.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3383</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7279</v>
+        <v>395</v>
       </c>
       <c r="C4" t="n">
-        <v>6811</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
-        <v>73747.8</v>
+        <v>1227.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4216</v>
+        <v>2184</v>
       </c>
     </row>
   </sheetData>
@@ -1769,11 +1769,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>170869.9</v>
+        <v>185429.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1781,11 +1781,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>107771.9</v>
+        <v>122331.9</v>
       </c>
     </row>
     <row r="3">
@@ -1837,11 +1837,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>35820</v>
+        <v>47760</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1849,11 +1849,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>22473.34</v>
+        <v>34413.34</v>
       </c>
     </row>
     <row r="5">
@@ -1871,11 +1871,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>41380</v>
+        <v>49340</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>130.2%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-12512</v>
+        <v>-4552</v>
       </c>
     </row>
     <row r="6">
@@ -1905,11 +1905,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>68340</v>
+        <v>78920</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1917,11 +1917,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39357</v>
+        <v>49937</v>
       </c>
     </row>
     <row r="7">
@@ -2041,11 +2041,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>203190</v>
+        <v>207170</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>156.3%</t>
+          <t>159.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2053,11 +2053,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>189445</v>
+        <v>193425</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2075,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>31840</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="12">
@@ -2109,11 +2109,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>86420</v>
+        <v>90400</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2121,11 +2121,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>82237</v>
+        <v>86217</v>
       </c>
     </row>
     <row r="13">
@@ -2211,23 +2211,23 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>128920</v>
+        <v>130200</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>59906</v>
+        <v>62498</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>69014</v>
+        <v>67702</v>
       </c>
     </row>
     <row r="16">
@@ -2245,11 +2245,11 @@
         <v>300000</v>
       </c>
       <c r="D16" t="n">
-        <v>183920</v>
+        <v>187708</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2257,11 +2257,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>112812</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="17">
@@ -2279,23 +2279,23 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>263288.01</v>
+        <v>267268.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>15988</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>263288.01</v>
+        <v>251280.01</v>
       </c>
     </row>
     <row r="18">
@@ -2313,11 +2313,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>20796</v>
+        <v>22776</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>20796</v>
+        <v>22776</v>
       </c>
     </row>
     <row r="19">
@@ -2347,11 +2347,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>63680</v>
+        <v>79600</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2359,11 +2359,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>56103.4</v>
+        <v>72023.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2415,23 +2415,23 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>40528</v>
+        <v>48488</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3156.67</v>
+        <v>26956.67</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>37371.33</v>
+        <v>21531.33</v>
       </c>
     </row>
     <row r="22">
@@ -2449,11 +2449,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>48129.9</v>
+        <v>60069.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2461,11 +2461,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>31350.9</v>
+        <v>43290.9</v>
       </c>
     </row>
     <row r="23">
@@ -2483,11 +2483,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>27668</v>
+        <v>35628</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2495,11 +2495,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>22688</v>
+        <v>30648</v>
       </c>
     </row>
     <row r="24">
@@ -2551,11 +2551,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>46400</v>
+        <v>66200</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>46400</v>
+        <v>66200</v>
       </c>
     </row>
     <row r="26">
@@ -2619,11 +2619,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>115944</v>
+        <v>123904</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2631,11 +2631,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>102564</v>
+        <v>110524</v>
       </c>
     </row>
     <row r="28">
@@ -2653,11 +2653,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>93700</v>
+        <v>101660</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>63900</v>
+        <v>71860</v>
       </c>
     </row>
     <row r="29">
@@ -2687,11 +2687,11 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>64600</v>
+        <v>68580</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -2699,11 +2699,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>34800</v>
+        <v>38780</v>
       </c>
     </row>
     <row r="30">
@@ -2891,23 +2891,23 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>139640</v>
+        <v>181440</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>48574</v>
+        <v>58972</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>91066</v>
+        <v>122468</v>
       </c>
     </row>
     <row r="36">
@@ -2925,11 +2925,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>94960</v>
+        <v>96940</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2937,11 +2937,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>84960</v>
+        <v>86940</v>
       </c>
     </row>
     <row r="37">
@@ -3035,15 +3035,15 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4950</v>
+        <v>11550</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>41450</v>
+        <v>34850</v>
       </c>
     </row>
     <row r="40">
@@ -3423,11 +3423,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>16969</v>
+        <v>17367</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>16969</v>
+        <v>17367</v>
       </c>
     </row>
     <row r="5">
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>46736.32</v>
+        <v>54736.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3537,11 +3537,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>46416.32</v>
+        <v>54416.32</v>
       </c>
     </row>
     <row r="8">
@@ -3559,11 +3559,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>111600</v>
+        <v>126600</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3571,11 +3571,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>108900</v>
+        <v>123900</v>
       </c>
     </row>
     <row r="9">
@@ -3627,11 +3627,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>35000</v>
+        <v>42500</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35000</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="11">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>160607.57</v>
+        <v>153188.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>160607.57</v>
+        <v>153188.57</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>133034</v>
+        <v>131734</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>133034</v>
+        <v>131734</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>362051.74</v>
+        <v>369470.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>362051.74</v>
+        <v>369470.74</v>
       </c>
     </row>
     <row r="15">
@@ -3797,11 +3797,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>147722.74</v>
+        <v>149022.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>147722.74</v>
+        <v>149022.74</v>
       </c>
     </row>
     <row r="16">
@@ -3831,11 +3831,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>148212</v>
+        <v>162373</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>148212</v>
+        <v>162373</v>
       </c>
     </row>
     <row r="17">
@@ -3865,11 +3865,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>211319</v>
+        <v>237319</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>211319</v>
+        <v>237319</v>
       </c>
     </row>
     <row r="18">
@@ -3933,11 +3933,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>125473</v>
+        <v>126871</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>125473</v>
+        <v>126871</v>
       </c>
     </row>
     <row r="20">
@@ -4035,11 +4035,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>46278</v>
+        <v>46676</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>33833.52</v>
+        <v>34231.52</v>
       </c>
     </row>
     <row r="23">
@@ -4103,11 +4103,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>64988.01</v>
+        <v>65386.01</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4115,11 +4115,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>57990.01</v>
+        <v>58388.01</v>
       </c>
     </row>
     <row r="25">
@@ -4205,11 +4205,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>115146</v>
+        <v>123146</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4217,11 +4217,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>107146</v>
+        <v>115146</v>
       </c>
     </row>
     <row r="28">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>248408.35</v>
+        <v>258477.95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>207828.35</v>
+        <v>217897.95</v>
       </c>
     </row>
     <row r="29">
@@ -4307,11 +4307,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>97484</v>
+        <v>98284</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>84484</v>
+        <v>85284</v>
       </c>
     </row>
     <row r="31">
@@ -4341,11 +4341,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>44846.2</v>
+        <v>45846.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>40348.2</v>
+        <v>41348.2</v>
       </c>
     </row>
     <row r="32">
@@ -4375,11 +4375,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>31406</v>
+        <v>31804</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4387,11 +4387,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23406</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="33">
@@ -4443,11 +4443,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>137786</v>
+        <v>147786</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>137556</v>
+        <v>147556</v>
       </c>
     </row>
     <row r="35">
@@ -4511,11 +4511,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>88188</v>
+        <v>109868</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>220.5%</t>
+          <t>274.7%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>88188</v>
+        <v>109868</v>
       </c>
     </row>
     <row r="37">
@@ -4783,11 +4783,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>185044</v>
+        <v>222844</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>148.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>185044</v>
+        <v>222844</v>
       </c>
     </row>
     <row r="45">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>98617.2</v>
+        <v>108617.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98617.2</v>
+        <v>108617.2</v>
       </c>
     </row>
     <row r="46">
@@ -4851,11 +4851,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>134896</v>
+        <v>147294</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>134896</v>
+        <v>147294</v>
       </c>
     </row>
     <row r="47">
@@ -4885,11 +4885,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>83576</v>
+        <v>84576</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>66776</v>
+        <v>67776</v>
       </c>
     </row>
     <row r="48">
@@ -4919,11 +4919,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>52218</v>
+        <v>64218</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>52218</v>
+        <v>64218</v>
       </c>
     </row>
     <row r="49">
@@ -5191,11 +5191,11 @@
         <v>20000</v>
       </c>
       <c r="D56" t="n">
-        <v>6600</v>
+        <v>7998</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>6600</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="57">
@@ -5225,11 +5225,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>59886</v>
+        <v>69886</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5237,11 +5237,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>51886</v>
+        <v>61886</v>
       </c>
     </row>
     <row r="58">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1907541.02</v>
+        <v>2052421.07</v>
       </c>
       <c r="D2" t="n">
-        <v>6102</v>
+        <v>6579</v>
       </c>
       <c r="E2" t="n">
-        <v>1654377.02</v>
+        <v>1797283.07</v>
       </c>
       <c r="F2" t="n">
-        <v>253164</v>
+        <v>255138</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1734219</v>
+        <v>1864690</v>
       </c>
       <c r="D3" t="n">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="E3" t="n">
-        <v>1486165</v>
+        <v>1614918</v>
       </c>
       <c r="F3" t="n">
-        <v>248054</v>
+        <v>249772</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>173322.02</v>
+        <v>187731.07</v>
       </c>
       <c r="D4" t="n">
-        <v>5688</v>
+        <v>6124</v>
       </c>
       <c r="E4" t="n">
-        <v>168212.02</v>
+        <v>182365.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5110</v>
+        <v>5366</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3707035.82</v>
+        <v>3915139.82</v>
       </c>
       <c r="D5" t="n">
-        <v>737</v>
+        <v>767</v>
       </c>
       <c r="E5" t="n">
-        <v>758907.8</v>
+        <v>816925.8</v>
       </c>
       <c r="F5" t="n">
-        <v>2948128.02</v>
+        <v>3098214.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2624859.02</v>
+        <v>2765655.02</v>
       </c>
       <c r="D6" t="n">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2508419.02</v>
+        <v>2649215.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1062176.8</v>
+        <v>1129484.8</v>
       </c>
       <c r="D7" t="n">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="E7" t="n">
-        <v>642467.8</v>
+        <v>700485.8</v>
       </c>
       <c r="F7" t="n">
-        <v>419709</v>
+        <v>428999</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2521367.63</v>
+        <v>2579598.23</v>
       </c>
       <c r="D8" t="n">
-        <v>2014</v>
+        <v>2027</v>
       </c>
       <c r="E8" t="n">
-        <v>37235</v>
+        <v>37435</v>
       </c>
       <c r="F8" t="n">
-        <v>2484132.63</v>
+        <v>2542163.23</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1522772.32</v>
+        <v>1579733.32</v>
       </c>
       <c r="D9" t="n">
-        <v>1075</v>
+        <v>1085</v>
       </c>
       <c r="E9" t="n">
         <v>13402.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1509370.14</v>
+        <v>1566331.14</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>996595.3100000001</v>
+        <v>997864.91</v>
       </c>
       <c r="D10" t="n">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E10" t="n">
-        <v>23832.82</v>
+        <v>24032.82</v>
       </c>
       <c r="F10" t="n">
-        <v>972762.49</v>
+        <v>973832.09</v>
       </c>
     </row>
     <row r="11">
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>651421.8100000001</v>
+        <v>655209.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
-        <v>445496.81</v>
+        <v>449284.81</v>
       </c>
       <c r="F12" t="n">
         <v>205925</v>
@@ -5862,13 +5862,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>67320</v>
+        <v>71280</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>49500</v>
+        <v>53460</v>
       </c>
       <c r="F14" t="n">
         <v>17820</v>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1907541.02</v>
+        <v>2052421.07</v>
       </c>
       <c r="C2" t="n">
-        <v>312709.91</v>
+        <v>325206.91</v>
       </c>
       <c r="D2" t="n">
-        <v>37632.01</v>
+        <v>40918.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="F2" t="n">
-        <v>275077.9</v>
+        <v>284288.9</v>
       </c>
       <c r="G2" t="n">
-        <v>14.42</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="3">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3707035.82</v>
+        <v>3915139.82</v>
       </c>
       <c r="C3" t="n">
-        <v>612596.28</v>
+        <v>623994.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="F3" t="n">
-        <v>577098.28</v>
+        <v>588496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>15.57</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="4">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2521367.63</v>
+        <v>2579598.23</v>
       </c>
       <c r="C4" t="n">
         <v>848421.5699999999</v>
@@ -5997,7 +5997,7 @@
         <v>846392.5699999999</v>
       </c>
       <c r="G4" t="n">
-        <v>33.57</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="5">
@@ -6010,7 +6010,7 @@
         <v>673400</v>
       </c>
       <c r="C5" t="n">
-        <v>311400</v>
+        <v>335200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6019,10 +6019,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>311400</v>
+        <v>335200</v>
       </c>
       <c r="G5" t="n">
-        <v>46.24</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="6">
@@ -6032,10 +6032,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>651421.8100000001</v>
+        <v>655209.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>157073.07</v>
+        <v>173061.07</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -6044,10 +6044,10 @@
         <v>0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>155055.17</v>
+        <v>171043.17</v>
       </c>
       <c r="G6" t="n">
-        <v>23.8</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="7">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67320</v>
+        <v>71280</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C2" t="n">
-        <v>1008317.51</v>
+        <v>1042501.51</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>333333</v>
+        <v>357133</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="C4" t="n">
-        <v>191977.37</v>
+        <v>196206.37</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C6" t="n">
-        <v>95102.67</v>
+        <v>95159.67</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -6239,13 +6239,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>12815.8</v>
+        <v>14171.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>1393</v>
+        <v>1431</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
-        <v>112630.01</v>
+        <v>112715.01</v>
       </c>
     </row>
     <row r="3">
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>44843.66</v>
+        <v>44919.66</v>
       </c>
     </row>
     <row r="5">
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>15663</v>
+        <v>15682</v>
       </c>
     </row>
     <row r="6">
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>1453</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="9">
@@ -6529,19 +6529,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>169322</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -6552,14 +6552,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>21950</v>
+        <v>186320</v>
       </c>
     </row>
     <row r="13">
@@ -6570,14 +6570,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>17998</v>
+        <v>21950</v>
       </c>
     </row>
     <row r="14">
@@ -6588,32 +6588,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>10000</v>
+        <v>17998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>83883</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="16">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>35720.9</v>
+        <v>83883</v>
       </c>
     </row>
     <row r="17">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="D17" t="n">
-        <v>28598.9</v>
+        <v>38502.9</v>
       </c>
     </row>
     <row r="18">
@@ -6660,14 +6660,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="D18" t="n">
-        <v>11605</v>
+        <v>28664.9</v>
       </c>
     </row>
     <row r="19">
@@ -6678,14 +6678,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>7059</v>
+        <v>11643</v>
       </c>
     </row>
     <row r="20">
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>4221</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="21">
@@ -6714,14 +6714,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>416</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="22">
@@ -6732,14 +6732,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23">
@@ -6750,14 +6750,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -6768,32 +6768,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>未填写原因</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
         <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>128286</v>
       </c>
     </row>
     <row r="26">
@@ -6804,14 +6804,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>20444.48</v>
+        <v>128286</v>
       </c>
     </row>
     <row r="27">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>4019</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="28">
@@ -6840,32 +6840,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>143100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>2000</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="31">
@@ -6894,14 +6894,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="32">
@@ -6912,14 +6912,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
@@ -6930,32 +6930,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>72514</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
@@ -6966,14 +6966,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>38513</v>
+        <v>88502</v>
       </c>
     </row>
     <row r="36">
@@ -6984,14 +6984,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>267</v>
+        <v>38580</v>
       </c>
     </row>
     <row r="37">
@@ -7002,14 +7002,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -7033,19 +7033,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>59600</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
@@ -7056,14 +7056,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>33763</v>
+        <v>59600</v>
       </c>
     </row>
     <row r="41">
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>12455</v>
+        <v>33782</v>
       </c>
     </row>
     <row r="42">
@@ -7092,14 +7092,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>299</v>
+        <v>13530</v>
       </c>
     </row>
     <row r="43">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>150</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44">
@@ -7128,14 +7128,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45">
@@ -7146,14 +7146,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46">
@@ -7164,223 +7164,223 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>62800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>15200</v>
+        <v>44101.6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>11100</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="D50" t="n">
-        <v>6000</v>
+        <v>20607.81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>30922</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D52" t="n">
-        <v>30809</v>
+        <v>4031.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>9163.33</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D54" t="n">
-        <v>6619</v>
+        <v>1271.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>2489</v>
+        <v>617</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>1284</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>383</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7393,7 +7393,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7402,208 +7402,208 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>44101.6</v>
+        <v>62800</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>20454.81</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>6988</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>4031.67</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="D63" t="n">
-        <v>4000</v>
+        <v>30979</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="D64" t="n">
-        <v>1271.9</v>
+        <v>30837</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>617</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>105</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D67" t="n">
-        <v>57</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>19</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>42067</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>20000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -7614,14 +7614,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>16800</v>
+        <v>43067</v>
       </c>
     </row>
     <row r="72">
@@ -7632,50 +7632,50 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>299</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>62837</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>13598</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75">
@@ -7686,14 +7686,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>115</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="76">
@@ -7704,50 +7704,50 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>59</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>24800</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>18000</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79">
@@ -7758,50 +7758,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>10200</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>41600</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>4009</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="82">
@@ -7812,20 +7812,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>299</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7834,28 +7834,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>16819</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>14000</v>
+        <v>318</v>
       </c>
     </row>
     <row r="85">
@@ -7866,14 +7866,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>10000</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="86">
@@ -7884,14 +7884,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="87">
@@ -7902,14 +7902,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>118</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="88">
@@ -7920,50 +7920,50 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>29</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>16960</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>14514</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91">
@@ -7974,14 +7974,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>3870</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="92">
@@ -7992,14 +7992,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>66</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="93">
@@ -8010,14 +8010,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D93" t="n">
-        <v>19</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="94">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -8059,37 +8059,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
@@ -8100,50 +8100,50 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>29</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>7019</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
@@ -8154,49 +8154,85 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>19.9</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>1910</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>主动放弃/拍错</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="C105" t="n">
         <v>2</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D105" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8238,36 +8274,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>398632.48</v>
+        <v>410030.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>225800</v>
+        <v>244000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>220200</v>
+        <v>225800</v>
       </c>
     </row>
     <row r="5">
@@ -8290,36 +8326,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
-        <v>184605.99</v>
+        <v>187197.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>151628</v>
+        <v>164272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>148284</v>
+        <v>151628</v>
       </c>
     </row>
     <row r="9">
@@ -8399,10 +8435,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C2" t="n">
-        <v>271851</v>
+        <v>272993</v>
       </c>
     </row>
     <row r="3">
@@ -8412,10 +8448,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C3" t="n">
-        <v>253439.5</v>
+        <v>256642.5</v>
       </c>
     </row>
     <row r="4">
@@ -8425,10 +8461,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C4" t="n">
-        <v>202425.48</v>
+        <v>202828.48</v>
       </c>
     </row>
     <row r="5">
@@ -8438,10 +8474,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C5" t="n">
-        <v>169491</v>
+        <v>193310</v>
       </c>
     </row>
     <row r="6">
@@ -8451,10 +8487,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>128410</v>
+        <v>135010</v>
       </c>
     </row>
     <row r="7">
@@ -8464,10 +8500,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>118611.81</v>
+        <v>118659.81</v>
       </c>
     </row>
     <row r="8">
@@ -8499,40 +8535,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>48678.9</v>
+        <v>53129.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>43446</v>
+        <v>48678.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C12" t="n">
-        <v>42674.01</v>
+        <v>43484</v>
       </c>
     </row>
     <row r="13">
@@ -8542,10 +8578,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C13" t="n">
-        <v>41607.99</v>
+        <v>41683.99</v>
       </c>
     </row>
     <row r="14">
@@ -8568,10 +8604,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15" t="n">
-        <v>38733</v>
+        <v>38780</v>
       </c>
     </row>
     <row r="16">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>468658</v>
+        <v>479612</v>
       </c>
       <c r="E2" t="n">
-        <v>252562</v>
+        <v>254102</v>
       </c>
       <c r="F2" t="n">
-        <v>216095</v>
+        <v>225509</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>745457</v>
+        <v>786207</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>307467</v>
+        <v>342179</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,41 +567,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>20951</v>
+        <v>16999</v>
       </c>
       <c r="E3" t="n">
-        <v>35467</v>
+        <v>40765</v>
       </c>
       <c r="F3" t="n">
-        <v>-14515</v>
+        <v>-23765</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>57056</v>
+        <v>57100</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-63.3%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6224</v>
+        <v>6268</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-333.2%</t>
+          <t>-479.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>682632</v>
+        <v>697528</v>
       </c>
       <c r="E4" t="n">
-        <v>175795</v>
+        <v>176805</v>
       </c>
       <c r="F4" t="n">
-        <v>506836</v>
+        <v>520722</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>646604</v>
+        <v>656218</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+6.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>451384</v>
+        <v>457227</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+12.3%</t>
+          <t>+13.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>483217</v>
+        <v>479572</v>
       </c>
       <c r="E5" t="n">
-        <v>127387</v>
+        <v>128206</v>
       </c>
       <c r="F5" t="n">
-        <v>355830</v>
+        <v>351366</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647132</v>
+        <v>647151</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>425037</v>
+        <v>425027</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>392958</v>
+        <v>402807</v>
       </c>
       <c r="E6" t="n">
-        <v>105617</v>
+        <v>110168</v>
       </c>
       <c r="F6" t="n">
-        <v>287340</v>
+        <v>292638</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>365666</v>
+        <v>385499</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>324530</v>
+        <v>343099</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>352268</v>
+        <v>371716</v>
       </c>
       <c r="E7" t="n">
-        <v>107608</v>
+        <v>107859</v>
       </c>
       <c r="F7" t="n">
-        <v>244660</v>
+        <v>263857</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>567917</v>
+        <v>570725</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-34.9%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>381857</v>
+        <v>384640</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>372143</v>
+        <v>376318</v>
       </c>
       <c r="E8" t="n">
-        <v>81773</v>
+        <v>82205</v>
       </c>
       <c r="F8" t="n">
-        <v>290370</v>
+        <v>294113</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>464596</v>
+        <v>465471</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>296019</v>
+        <v>288935</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>923993</v>
+        <v>932613</v>
       </c>
       <c r="E9" t="n">
-        <v>236268</v>
+        <v>287768</v>
       </c>
       <c r="F9" t="n">
-        <v>687725</v>
+        <v>644845</v>
       </c>
       <c r="G9" t="n">
         <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1177233</v>
+        <v>1205133</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>766021</v>
+        <v>793921</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1525402</v>
+        <v>1587682</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1525402</v>
+        <v>1587682</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1337322</v>
+        <v>1337784</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+14.1%</t>
+          <t>+18.7%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1337322</v>
+        <v>1337784</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+14.1%</t>
+          <t>+18.7%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,39 +997,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>305144</v>
+        <v>316751</v>
       </c>
       <c r="E11" t="n">
         <v>45927</v>
       </c>
       <c r="F11" t="n">
-        <v>259217</v>
+        <v>270824</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>343886</v>
+        <v>344185</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>299010</v>
+        <v>299309</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1051,39 +1051,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>357440</v>
+        <v>367838</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>355212</v>
+        <v>365610</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>287672</v>
+        <v>324492</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+24.3%</t>
+          <t>+13.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>268053</v>
+        <v>304873</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+19.9%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,39 +1103,39 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>565894</v>
+        <v>575311</v>
       </c>
       <c r="E13" t="n">
-        <v>76609</v>
+        <v>76809</v>
       </c>
       <c r="F13" t="n">
-        <v>489285</v>
+        <v>498502</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>611117</v>
+        <v>611534</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>567174</v>
+        <v>567591</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1157,39 +1157,39 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>370825</v>
+        <v>425019</v>
       </c>
       <c r="E14" t="n">
-        <v>45378</v>
+        <v>77178</v>
       </c>
       <c r="F14" t="n">
-        <v>325447</v>
+        <v>347841</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>697789</v>
+        <v>726387</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-46.9%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>569086</v>
+        <v>597684</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1211,23 +1211,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>195418</v>
+        <v>196214</v>
       </c>
       <c r="E15" t="n">
-        <v>15306</v>
+        <v>15325</v>
       </c>
       <c r="F15" t="n">
-        <v>180112</v>
+        <v>180889</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,23 +1263,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>321278</v>
+        <v>322297</v>
       </c>
       <c r="E16" t="n">
         <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>268278</v>
+        <v>269297</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+63.8%</t>
+          <t>+64.4%</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+99.9%</t>
+          <t>+100.7%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,39 +1315,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>427878</v>
+        <v>439291</v>
       </c>
       <c r="E17" t="n">
         <v>80166</v>
       </c>
       <c r="F17" t="n">
-        <v>347712</v>
+        <v>359125</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>402968</v>
+        <v>412968</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+6.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>375221</v>
+        <v>379221</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>634894</v>
+        <v>654948</v>
       </c>
       <c r="E18" t="n">
         <v>152805</v>
       </c>
       <c r="F18" t="n">
-        <v>482089</v>
+        <v>502143</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>641284</v>
+        <v>655752</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>414822</v>
+        <v>429290</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+17.0%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,39 +1423,39 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>373985</v>
+        <v>380585</v>
       </c>
       <c r="E19" t="n">
-        <v>145527</v>
+        <v>145546</v>
       </c>
       <c r="F19" t="n">
-        <v>228458</v>
+        <v>235039</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>946795</v>
+        <v>955814</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-60.5%</t>
+          <t>-60.2%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>837599</v>
+        <v>846599</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>689126</v>
+        <v>686240</v>
       </c>
       <c r="E20" t="n">
-        <v>95100</v>
+        <v>95119</v>
       </c>
       <c r="F20" t="n">
-        <v>594026</v>
+        <v>591121</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>785865</v>
+        <v>806680</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>721566</v>
+        <v>742381</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>533</v>
+        <v>583</v>
       </c>
       <c r="C2" t="n">
         <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>1218.9</v>
+        <v>1256.4</v>
       </c>
       <c r="E2" t="n">
-        <v>93263</v>
+        <v>171931</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>512.1</v>
+        <v>306.3</v>
       </c>
       <c r="E3" t="n">
-        <v>420</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>395</v>
+        <v>796</v>
       </c>
       <c r="C4" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D4" t="n">
-        <v>1227.8</v>
+        <v>1273</v>
       </c>
       <c r="E4" t="n">
-        <v>2184</v>
+        <v>2559</v>
       </c>
     </row>
   </sheetData>
@@ -1837,11 +1837,11 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>47760</v>
+        <v>43780</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1849,11 +1849,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>34413.34</v>
+        <v>30433.34</v>
       </c>
     </row>
     <row r="5">
@@ -1871,11 +1871,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>49340</v>
+        <v>57300</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-4552</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="6">
@@ -1905,11 +1905,11 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>78920</v>
+        <v>82900</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1917,11 +1917,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49937</v>
+        <v>53917</v>
       </c>
     </row>
     <row r="7">
@@ -1947,15 +1947,15 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2980</v>
+        <v>-2000</v>
       </c>
     </row>
     <row r="8">
@@ -2007,11 +2007,11 @@
         <v>30000</v>
       </c>
       <c r="D9" t="n">
-        <v>7960</v>
+        <v>3980</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2019,11 +2019,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>222.4%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-9740</v>
+        <v>-13720</v>
       </c>
     </row>
     <row r="10">
@@ -2041,11 +2041,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>207170</v>
+        <v>211150</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>159.4%</t>
+          <t>162.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2053,11 +2053,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>193425</v>
+        <v>197405</v>
       </c>
     </row>
     <row r="11">
@@ -2075,11 +2075,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>35820</v>
+        <v>39800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35820</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="12">
@@ -2143,11 +2143,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>55720</v>
+        <v>59700</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>20960</v>
+        <v>24940</v>
       </c>
     </row>
     <row r="14">
@@ -2279,23 +2279,23 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>267268.01</v>
+        <v>263288.01</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15988</v>
+        <v>16788</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>251280.01</v>
+        <v>246500.01</v>
       </c>
     </row>
     <row r="18">
@@ -2415,11 +2415,11 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>48488</v>
+        <v>60428</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>21531.33</v>
+        <v>33471.33</v>
       </c>
     </row>
     <row r="22">
@@ -2585,23 +2585,23 @@
         <v>80000</v>
       </c>
       <c r="D26" t="n">
-        <v>35820</v>
+        <v>31840</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4980</v>
+        <v>8960</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30840</v>
+        <v>22880</v>
       </c>
     </row>
     <row r="27">
@@ -2619,11 +2619,11 @@
         <v>250000</v>
       </c>
       <c r="D27" t="n">
-        <v>123904</v>
+        <v>134484</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2631,11 +2631,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>110524</v>
+        <v>121104</v>
       </c>
     </row>
     <row r="28">
@@ -2653,11 +2653,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>101660</v>
+        <v>109620</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>71860</v>
+        <v>79820</v>
       </c>
     </row>
     <row r="29">
@@ -2823,11 +2823,11 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>123360</v>
+        <v>127340</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2835,11 +2835,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>109160</v>
+        <v>113140</v>
       </c>
     </row>
     <row r="34">
@@ -2891,11 +2891,11 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>181440</v>
+        <v>206260</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2903,11 +2903,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>122468</v>
+        <v>147288</v>
       </c>
     </row>
     <row r="36">
@@ -2925,11 +2925,11 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>96940</v>
+        <v>67140</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2937,11 +2937,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>86940</v>
+        <v>57140</v>
       </c>
     </row>
     <row r="37">
@@ -2959,11 +2959,11 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>20800</v>
+        <v>27400</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14200</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="38">
@@ -2993,11 +2993,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>121610</v>
+        <v>128210</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>83060</v>
+        <v>89660</v>
       </c>
     </row>
     <row r="39">
@@ -3035,15 +3035,15 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>11550</v>
+        <v>41350</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>34850</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="40">
@@ -3069,15 +3069,15 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>16398</v>
+        <v>17298</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>63010</v>
+        <v>62110</v>
       </c>
     </row>
     <row r="41">
@@ -3129,11 +3129,11 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>21298</v>
+        <v>21698</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>21298</v>
+        <v>21698</v>
       </c>
     </row>
     <row r="43">
@@ -3239,15 +3239,15 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>20800</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>86488</v>
+        <v>65688</v>
       </c>
     </row>
     <row r="46">
@@ -3355,11 +3355,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>40552</v>
+        <v>41449</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3367,11 +3367,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>25334</v>
+        <v>26231</v>
       </c>
     </row>
     <row r="3">
@@ -3423,11 +3423,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>17367</v>
+        <v>16868</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17367</v>
+        <v>16868</v>
       </c>
     </row>
     <row r="5">
@@ -3457,11 +3457,11 @@
         <v>32000</v>
       </c>
       <c r="D5" t="n">
-        <v>8786</v>
+        <v>9184</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8786</v>
+        <v>9184</v>
       </c>
     </row>
     <row r="6">
@@ -3559,11 +3559,11 @@
         <v>120000</v>
       </c>
       <c r="D8" t="n">
-        <v>126600</v>
+        <v>133200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3571,11 +3571,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>123900</v>
+        <v>130500</v>
       </c>
     </row>
     <row r="9">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>153188.57</v>
+        <v>167718.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>153188.57</v>
+        <v>167718.57</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>131734</v>
+        <v>110514.5700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>131734</v>
+        <v>110514.5700000001</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>369470.74</v>
+        <v>389091.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>369470.74</v>
+        <v>389091.74</v>
       </c>
     </row>
     <row r="15">
@@ -3797,11 +3797,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>149022.74</v>
+        <v>174372.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>149022.74</v>
+        <v>174372.74</v>
       </c>
     </row>
     <row r="16">
@@ -3831,11 +3831,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>162373</v>
+        <v>185773</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>162373</v>
+        <v>185773</v>
       </c>
     </row>
     <row r="17">
@@ -3865,11 +3865,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>237319</v>
+        <v>237717</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>237319</v>
+        <v>237717</v>
       </c>
     </row>
     <row r="18">
@@ -4035,11 +4035,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>46676</v>
+        <v>47074</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34231.52</v>
+        <v>34629.52</v>
       </c>
     </row>
     <row r="23">
@@ -4069,11 +4069,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>231948</v>
+        <v>251168</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>139560</v>
+        <v>158780</v>
       </c>
     </row>
     <row r="24">
@@ -4205,11 +4205,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>123146</v>
+        <v>123544</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>115146</v>
+        <v>115544</v>
       </c>
     </row>
     <row r="28">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>258477.95</v>
+        <v>259075.95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>217897.95</v>
+        <v>218495.95</v>
       </c>
     </row>
     <row r="29">
@@ -4307,11 +4307,11 @@
         <v>120000</v>
       </c>
       <c r="D30" t="n">
-        <v>98284</v>
+        <v>99084</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>85284</v>
+        <v>86084</v>
       </c>
     </row>
     <row r="31">
@@ -4409,11 +4409,11 @@
         <v>50000</v>
       </c>
       <c r="D33" t="n">
-        <v>398</v>
+        <v>8398</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>398</v>
+        <v>8398</v>
       </c>
     </row>
     <row r="34">
@@ -4443,11 +4443,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>147786</v>
+        <v>148184</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>147556</v>
+        <v>147954</v>
       </c>
     </row>
     <row r="35">
@@ -4477,11 +4477,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>8590</v>
+        <v>18590</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8590</v>
+        <v>18590</v>
       </c>
     </row>
     <row r="36">
@@ -4647,11 +4647,11 @@
         <v>170000</v>
       </c>
       <c r="D40" t="n">
-        <v>143186</v>
+        <v>140186</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4659,11 +4659,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>134386</v>
+        <v>131386</v>
       </c>
     </row>
     <row r="41">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>108617.2</v>
+        <v>119613.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>108617.2</v>
+        <v>119613.2</v>
       </c>
     </row>
     <row r="46">
@@ -4885,11 +4885,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>84576</v>
+        <v>84974</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>67776</v>
+        <v>68174</v>
       </c>
     </row>
     <row r="48">
@@ -5055,11 +5055,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>103284</v>
+        <v>95284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>74484</v>
+        <v>66484</v>
       </c>
     </row>
     <row r="53">
@@ -5123,11 +5123,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>59994</v>
+        <v>69592</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>59994</v>
+        <v>69592</v>
       </c>
     </row>
     <row r="55">
@@ -5157,11 +5157,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>3796</v>
+        <v>13796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3796</v>
+        <v>13796</v>
       </c>
     </row>
     <row r="56">
@@ -5259,11 +5259,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>91574</v>
+        <v>89574</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5271,11 +5271,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>56774</v>
+        <v>54774</v>
       </c>
     </row>
     <row r="59">
@@ -5293,11 +5293,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>131166</v>
+        <v>134166</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5305,11 +5305,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>120966</v>
+        <v>123966</v>
       </c>
     </row>
     <row r="60">
@@ -5361,23 +5361,23 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>181732.6</v>
+        <v>214532.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>171732.6</v>
+        <v>194532.6</v>
       </c>
     </row>
     <row r="62">
@@ -5429,23 +5429,23 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>106885.48</v>
+        <v>128279.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>15200</v>
+        <v>37000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>91685.48</v>
+        <v>91279.48</v>
       </c>
     </row>
     <row r="64">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2052421.07</v>
+        <v>2123775.07</v>
       </c>
       <c r="D2" t="n">
-        <v>6579</v>
+        <v>6925</v>
       </c>
       <c r="E2" t="n">
-        <v>1797283.07</v>
+        <v>1861619.07</v>
       </c>
       <c r="F2" t="n">
-        <v>255138</v>
+        <v>262156</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1864690</v>
+        <v>1927088</v>
       </c>
       <c r="D3" t="n">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="E3" t="n">
-        <v>1614918</v>
+        <v>1670697</v>
       </c>
       <c r="F3" t="n">
-        <v>249772</v>
+        <v>256391</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>187731.07</v>
+        <v>196687.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6124</v>
+        <v>6447</v>
       </c>
       <c r="E4" t="n">
-        <v>182365.07</v>
+        <v>190922.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5366</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3915139.82</v>
+        <v>4010753.82</v>
       </c>
       <c r="D5" t="n">
-        <v>767</v>
+        <v>817</v>
       </c>
       <c r="E5" t="n">
-        <v>816925.8</v>
+        <v>811945.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3098214.02</v>
+        <v>3198808.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2765655.02</v>
+        <v>2871643.02</v>
       </c>
       <c r="D6" t="n">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2649215.02</v>
+        <v>2755203.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1129484.8</v>
+        <v>1119110.8</v>
       </c>
       <c r="D7" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="E7" t="n">
-        <v>700485.8</v>
+        <v>695505.8</v>
       </c>
       <c r="F7" t="n">
-        <v>428999</v>
+        <v>423605</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2579598.23</v>
+        <v>2841988.04</v>
       </c>
       <c r="D8" t="n">
-        <v>2027</v>
+        <v>2087</v>
       </c>
       <c r="E8" t="n">
-        <v>37435</v>
+        <v>38424.25</v>
       </c>
       <c r="F8" t="n">
-        <v>2542163.23</v>
+        <v>2803563.79</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1579733.32</v>
+        <v>1670814.89</v>
       </c>
       <c r="D9" t="n">
-        <v>1085</v>
+        <v>1130</v>
       </c>
       <c r="E9" t="n">
-        <v>13402.18</v>
+        <v>13802.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1566331.14</v>
+        <v>1657012.71</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>997864.91</v>
+        <v>1169173.15</v>
       </c>
       <c r="D10" t="n">
-        <v>941</v>
+        <v>956</v>
       </c>
       <c r="E10" t="n">
-        <v>24032.82</v>
+        <v>24622.07</v>
       </c>
       <c r="F10" t="n">
-        <v>973832.09</v>
+        <v>1144551.08</v>
       </c>
     </row>
     <row r="11">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>673400</v>
+        <v>698200</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
         <v>320400</v>
       </c>
       <c r="F11" t="n">
-        <v>353000</v>
+        <v>377800</v>
       </c>
     </row>
     <row r="12">
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2052421.07</v>
+        <v>2123775.07</v>
       </c>
       <c r="C2" t="n">
-        <v>325206.91</v>
+        <v>339464.91</v>
       </c>
       <c r="D2" t="n">
-        <v>40918.01</v>
+        <v>48254.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="F2" t="n">
-        <v>284288.9</v>
+        <v>291210.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.85</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="3">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3915139.82</v>
+        <v>4010753.82</v>
       </c>
       <c r="C3" t="n">
-        <v>623994.28</v>
+        <v>633994.28</v>
       </c>
       <c r="D3" t="n">
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="F3" t="n">
-        <v>588496.28</v>
+        <v>598496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>15.03</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="4">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2579598.23</v>
+        <v>2841988.04</v>
       </c>
       <c r="C4" t="n">
-        <v>848421.5699999999</v>
+        <v>1057341.57</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>846392.5699999999</v>
+        <v>1055312.57</v>
       </c>
       <c r="G4" t="n">
-        <v>32.81</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="5">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>673400</v>
+        <v>698200</v>
       </c>
       <c r="C5" t="n">
-        <v>335200</v>
+        <v>377800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6019,10 +6019,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>335200</v>
+        <v>377800</v>
       </c>
       <c r="G5" t="n">
-        <v>49.78</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="6">
@@ -6035,13 +6035,13 @@
         <v>655209.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>173061.07</v>
+        <v>173861.07</v>
       </c>
       <c r="D6" t="n">
-        <v>2017.9</v>
+        <v>2817.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="F6" t="n">
         <v>171043.17</v>
@@ -6060,13 +6060,13 @@
         <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>467680</v>
+        <v>497480</v>
       </c>
       <c r="D7" t="n">
-        <v>20000</v>
+        <v>49800</v>
       </c>
       <c r="E7" t="n">
-        <v>5.84</v>
+        <v>14.55</v>
       </c>
       <c r="F7" t="n">
         <v>447680</v>
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C2" t="n">
-        <v>1042501.51</v>
+        <v>1075449.51</v>
       </c>
       <c r="D2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C3" t="n">
+        <v>407733</v>
+      </c>
+      <c r="D3" t="n">
         <v>25</v>
-      </c>
-      <c r="C3" t="n">
-        <v>357133</v>
-      </c>
-      <c r="D3" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="C4" t="n">
-        <v>196206.37</v>
+        <v>208216.37</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C6" t="n">
-        <v>95159.67</v>
+        <v>96427.67</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>14171.8</v>
+        <v>14708.8</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>1431</v>
+        <v>1526</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6367,7 +6367,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6376,16 +6376,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>112715.01</v>
+        <v>187220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6397,31 +6397,31 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>66673</v>
+        <v>68598</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>44919.66</v>
+        <v>21950</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>15682</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>6500</v>
+        <v>112762.01</v>
       </c>
     </row>
     <row r="7">
@@ -6462,14 +6462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>4169</v>
+        <v>66673</v>
       </c>
     </row>
     <row r="8">
@@ -6480,14 +6480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="D8" t="n">
-        <v>1472</v>
+        <v>45099.66</v>
       </c>
     </row>
     <row r="9">
@@ -6498,14 +6498,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>356</v>
+        <v>16677</v>
       </c>
     </row>
     <row r="10">
@@ -6516,14 +6516,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="11">
@@ -6534,86 +6534,86 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>186320</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>21950</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>17998</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D17" t="n">
-        <v>38502.9</v>
+        <v>39221.9</v>
       </c>
     </row>
     <row r="18">
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D18" t="n">
-        <v>28664.9</v>
+        <v>28717.9</v>
       </c>
     </row>
     <row r="19">
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>8377</v>
+        <v>8596</v>
       </c>
     </row>
     <row r="21">
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>435</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D36" t="n">
-        <v>38580</v>
+        <v>39399</v>
       </c>
     </row>
     <row r="37">
@@ -7051,145 +7051,145 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="D40" t="n">
-        <v>59600</v>
+        <v>44154.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="D41" t="n">
-        <v>33782</v>
+        <v>25029.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>13530</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>299</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D44" t="n">
-        <v>169</v>
+        <v>4050.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>133</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D46" t="n">
-        <v>76</v>
+        <v>1290.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>617</v>
       </c>
     </row>
     <row r="48">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>44101.6</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>23800</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
@@ -7236,151 +7236,151 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>20607.81</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>6988</v>
+        <v>59600</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D52" t="n">
-        <v>4031.67</v>
+        <v>33839</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D53" t="n">
-        <v>4000</v>
+        <v>13689</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1271.9</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>617</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>124</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>11100</v>
+        <v>11119</v>
       </c>
     </row>
     <row r="62">
@@ -7474,10 +7474,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D63" t="n">
-        <v>30979</v>
+        <v>31373</v>
       </c>
     </row>
     <row r="64">
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D64" t="n">
-        <v>30837</v>
+        <v>30875</v>
       </c>
     </row>
     <row r="65">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>115</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78">
@@ -7740,38 +7740,38 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>59</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>24800</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7780,16 +7780,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>18000</v>
+        <v>48619</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7798,52 +7798,52 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>10200</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>41600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>4009</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7855,7 +7855,7 @@
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>318</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85">
@@ -7866,122 +7866,122 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>16819</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>14000</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>3000</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>118</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>29</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>16960</v>
+        <v>318</v>
       </c>
     </row>
     <row r="92">
@@ -7992,14 +7992,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>14514</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="93">
@@ -8010,14 +8010,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D93" t="n">
-        <v>3870</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="94">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D94" t="n">
-        <v>66</v>
+        <v>9168</v>
       </c>
     </row>
     <row r="95">
@@ -8046,14 +8046,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8095,19 +8095,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
@@ -8118,14 +8118,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>59</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="100">
@@ -8136,32 +8136,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>7019</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>57</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="103">
@@ -8190,32 +8190,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>19.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1910</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="105">
@@ -8226,13 +8226,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>2</v>
       </c>
       <c r="D105" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8287,10 +8305,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>244000</v>
+        <v>286600</v>
       </c>
     </row>
     <row r="4">
@@ -8300,10 +8318,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>225800</v>
+        <v>255600</v>
       </c>
     </row>
     <row r="5">
@@ -8326,10 +8344,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>187197.99</v>
+        <v>197152.99</v>
       </c>
     </row>
     <row r="7">
@@ -8339,10 +8357,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>164272</v>
+        <v>165072</v>
       </c>
     </row>
     <row r="8">
@@ -8352,10 +8370,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>151628</v>
+        <v>161628</v>
       </c>
     </row>
     <row r="9">
@@ -8431,27 +8449,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>127</v>
+        <v>251</v>
       </c>
       <c r="C2" t="n">
-        <v>272993</v>
+        <v>279547.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>233</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>256642.5</v>
+        <v>278086</v>
       </c>
     </row>
     <row r="4">
@@ -8461,10 +8479,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C4" t="n">
-        <v>202828.48</v>
+        <v>202964.48</v>
       </c>
     </row>
     <row r="5">
@@ -8474,10 +8492,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>193310</v>
+        <v>193714</v>
       </c>
     </row>
     <row r="6">
@@ -8500,127 +8518,127 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>118659.81</v>
+        <v>119478.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>64323</v>
+        <v>73360</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>57976</v>
+        <v>64361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>53129.01</v>
+        <v>57976</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="C11" t="n">
-        <v>48678.9</v>
+        <v>53167.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>43484</v>
+        <v>48678.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>41683.99</v>
+        <v>44031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="C14" t="n">
-        <v>40620</v>
+        <v>43141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C15" t="n">
-        <v>38780</v>
+        <v>42678.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>37695</v>
+        <v>40677</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -997,13 +997,13 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>316751</v>
+        <v>316727</v>
       </c>
       <c r="E11" t="n">
         <v>45927</v>
       </c>
       <c r="F11" t="n">
-        <v>270824</v>
+        <v>270800</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>912</v>
+        <v>888</v>
       </c>
     </row>
     <row r="12">
@@ -1103,23 +1103,23 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>575311</v>
+        <v>578559</v>
       </c>
       <c r="E13" t="n">
         <v>76809</v>
       </c>
       <c r="F13" t="n">
-        <v>498502</v>
+        <v>501750</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1135,11 +1135,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>16414</v>
+        <v>19662</v>
       </c>
     </row>
     <row r="14">
@@ -1157,23 +1157,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>425019</v>
+        <v>427649</v>
       </c>
       <c r="E14" t="n">
         <v>77178</v>
       </c>
       <c r="F14" t="n">
-        <v>347841</v>
+        <v>350471</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-41.1%</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1189,11 +1189,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>56654</v>
+        <v>59284</v>
       </c>
     </row>
     <row r="15">
@@ -1318,10 +1318,10 @@
         <v>439291</v>
       </c>
       <c r="E17" t="n">
-        <v>80166</v>
+        <v>96666</v>
       </c>
       <c r="F17" t="n">
-        <v>359125</v>
+        <v>342625</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1423,13 +1423,13 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>380585</v>
+        <v>381026</v>
       </c>
       <c r="E19" t="n">
         <v>145546</v>
       </c>
       <c r="F19" t="n">
-        <v>235039</v>
+        <v>235480</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-60.2%</t>
+          <t>-60.1%</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10890</v>
+        <v>11331</v>
       </c>
     </row>
     <row r="20">
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>54736.32</v>
+        <v>54936.32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>54416.32</v>
+        <v>54616.32</v>
       </c>
     </row>
     <row r="8">
@@ -3593,11 +3593,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>119930.92</v>
+        <v>120560.17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>99.9%</t>
+          <t>100.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3605,11 +3605,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-20469.08</v>
+        <v>-19839.83</v>
       </c>
     </row>
     <row r="10">
@@ -5361,11 +5361,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>214532.6</v>
+        <v>215067.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>194532.6</v>
+        <v>195067.5</v>
       </c>
     </row>
     <row r="62">
@@ -5395,11 +5395,11 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>64040.52</v>
+        <v>66135.72</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5407,11 +5407,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>48828.52</v>
+        <v>50923.72</v>
       </c>
     </row>
     <row r="63">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2841988.04</v>
+        <v>3004333.19</v>
       </c>
       <c r="D8" t="n">
-        <v>2087</v>
+        <v>2443</v>
       </c>
       <c r="E8" t="n">
         <v>38424.25</v>
       </c>
       <c r="F8" t="n">
-        <v>2803563.79</v>
+        <v>2965908.94</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1670814.89</v>
+        <v>1735309.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1130</v>
+        <v>1289</v>
       </c>
       <c r="E9" t="n">
         <v>13802.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1657012.71</v>
+        <v>1721506.92</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1169173.15</v>
+        <v>1265524.09</v>
       </c>
       <c r="D10" t="n">
-        <v>956</v>
+        <v>1152</v>
       </c>
       <c r="E10" t="n">
         <v>24622.07</v>
       </c>
       <c r="F10" t="n">
-        <v>1144551.08</v>
+        <v>1240902.02</v>
       </c>
     </row>
     <row r="11">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2841988.04</v>
+        <v>3004333.19</v>
       </c>
       <c r="C4" t="n">
-        <v>1057341.57</v>
+        <v>1085301.23</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -5994,10 +5994,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1055312.57</v>
+        <v>1083272.23</v>
       </c>
       <c r="G4" t="n">
-        <v>37.13</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="5">
@@ -6035,7 +6035,7 @@
         <v>655209.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>173861.07</v>
+        <v>190361.07</v>
       </c>
       <c r="D6" t="n">
         <v>2817.9</v>
@@ -6044,10 +6044,10 @@
         <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>171043.17</v>
+        <v>187543.17</v>
       </c>
       <c r="G6" t="n">
-        <v>26.11</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="7">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>479612</v>
+        <v>485022</v>
       </c>
       <c r="E2" t="n">
-        <v>254102</v>
+        <v>254224</v>
       </c>
       <c r="F2" t="n">
-        <v>225509</v>
+        <v>230797</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>786207</v>
+        <v>801440</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>342179</v>
+        <v>352271</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,10 +567,10 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>16999</v>
+        <v>17018</v>
       </c>
       <c r="E3" t="n">
-        <v>40765</v>
+        <v>40784</v>
       </c>
       <c r="F3" t="n">
         <v>-23765</v>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>57100</v>
+        <v>58325</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6268</v>
+        <v>7436</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-479.1%</t>
+          <t>-419.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>697528</v>
+        <v>707749</v>
       </c>
       <c r="E4" t="n">
-        <v>176805</v>
+        <v>176976</v>
       </c>
       <c r="F4" t="n">
-        <v>520722</v>
+        <v>530773</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>656218</v>
+        <v>690547</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+6.3%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>457227</v>
+        <v>491218</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+13.9%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,20 +675,20 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>479572</v>
+        <v>479630</v>
       </c>
       <c r="E5" t="n">
         <v>128206</v>
       </c>
       <c r="F5" t="n">
-        <v>351366</v>
+        <v>351424</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647151</v>
+        <v>658207</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>425027</v>
+        <v>406283</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>402807</v>
+        <v>412478</v>
       </c>
       <c r="E6" t="n">
-        <v>110168</v>
+        <v>110396</v>
       </c>
       <c r="F6" t="n">
-        <v>292638</v>
+        <v>302081</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>385499</v>
+        <v>425814</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>343099</v>
+        <v>383128</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>371716</v>
+        <v>372796</v>
       </c>
       <c r="E7" t="n">
-        <v>107859</v>
+        <v>108224</v>
       </c>
       <c r="F7" t="n">
-        <v>263857</v>
+        <v>264572</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>570725</v>
+        <v>578344</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-34.9%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>384640</v>
+        <v>386240</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>376318</v>
+        <v>403026</v>
       </c>
       <c r="E8" t="n">
-        <v>82205</v>
+        <v>82420</v>
       </c>
       <c r="F8" t="n">
-        <v>294113</v>
+        <v>320606</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>465471</v>
+        <v>493732</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-18.4%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>288935</v>
+        <v>317021</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>932613</v>
+        <v>944942</v>
       </c>
       <c r="E9" t="n">
-        <v>287768</v>
+        <v>287797</v>
       </c>
       <c r="F9" t="n">
-        <v>644845</v>
+        <v>657145</v>
       </c>
       <c r="G9" t="n">
         <v>108806</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1205133</v>
+        <v>1260452</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>-25.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>849240</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>-22.6%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>793921</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>-18.8%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1587682</v>
+        <v>1689045</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1587682</v>
+        <v>1689045</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1337784</v>
+        <v>1407454</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+18.7%</t>
+          <t>+20.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1337784</v>
+        <v>1407454</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+18.7%</t>
+          <t>+20.0%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,43 +997,43 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>316727</v>
+        <v>335150</v>
       </c>
       <c r="E11" t="n">
         <v>45927</v>
       </c>
       <c r="F11" t="n">
-        <v>270800</v>
+        <v>289223</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>344185</v>
+        <v>352981</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>299309</v>
+        <v>308105</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>888</v>
+        <v>912</v>
       </c>
     </row>
     <row r="12">
@@ -1051,39 +1051,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>367838</v>
+        <v>379032</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>365610</v>
+        <v>376804</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>324492</v>
+        <v>335294</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+13.4%</t>
+          <t>+13.0%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>304873</v>
+        <v>315675</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+19.9%</t>
+          <t>+19.4%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,43 +1103,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>578559</v>
+        <v>663795</v>
       </c>
       <c r="E13" t="n">
         <v>76809</v>
       </c>
       <c r="F13" t="n">
-        <v>501750</v>
+        <v>586986</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>611534</v>
+        <v>639134</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>567591</v>
+        <v>595191</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>19662</v>
+        <v>20402</v>
       </c>
     </row>
     <row r="14">
@@ -1157,43 +1157,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>427649</v>
+        <v>509092</v>
       </c>
       <c r="E14" t="n">
         <v>77178</v>
       </c>
       <c r="F14" t="n">
-        <v>350471</v>
+        <v>431914</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>726387</v>
+        <v>744804</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>597684</v>
+        <v>608101</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>59284</v>
+        <v>60329</v>
       </c>
     </row>
     <row r="15">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>196214</v>
+        <v>208612</v>
       </c>
       <c r="E15" t="n">
         <v>15325</v>
       </c>
       <c r="F15" t="n">
-        <v>180889</v>
+        <v>193287</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>213800</v>
+        <v>220596</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>213714</v>
+        <v>220510</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>322297</v>
+        <v>323491</v>
       </c>
       <c r="E16" t="n">
         <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>269297</v>
+        <v>270491</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>196094</v>
+        <v>212890</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+64.4%</t>
+          <t>+52.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>134211</v>
+        <v>151007</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+100.7%</t>
+          <t>+79.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,39 +1315,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>439291</v>
+        <v>490291</v>
       </c>
       <c r="E17" t="n">
         <v>96666</v>
       </c>
       <c r="F17" t="n">
-        <v>342625</v>
+        <v>393625</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>412968</v>
+        <v>421395</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+6.4%</t>
+          <t>+16.3%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>379221</v>
+        <v>378880</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>654948</v>
+        <v>716151</v>
       </c>
       <c r="E18" t="n">
         <v>152805</v>
       </c>
       <c r="F18" t="n">
-        <v>502143</v>
+        <v>563346</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>655752</v>
+        <v>664751</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+7.7%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>429290</v>
+        <v>438289</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+17.0%</t>
+          <t>+28.5%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,23 +1423,23 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>381026</v>
+        <v>383421</v>
       </c>
       <c r="E19" t="n">
         <v>145546</v>
       </c>
       <c r="F19" t="n">
-        <v>235480</v>
+        <v>237875</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1447,19 +1447,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-59.9%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>846599</v>
+        <v>814399</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>11331</v>
+        <v>12488</v>
       </c>
     </row>
     <row r="20">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>686240</v>
+        <v>698733</v>
       </c>
       <c r="E20" t="n">
         <v>95119</v>
       </c>
       <c r="F20" t="n">
-        <v>591121</v>
+        <v>603614</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>806680</v>
+        <v>807078</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>742381</v>
+        <v>738779</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>583</v>
+        <v>319</v>
       </c>
       <c r="C2" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>1256.4</v>
+        <v>445.8</v>
       </c>
       <c r="E2" t="n">
-        <v>171931</v>
+        <v>57961</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>306.3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1582</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="C4" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D4" t="n">
-        <v>1273</v>
+        <v>1358.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2559</v>
+        <v>2981</v>
       </c>
     </row>
   </sheetData>
@@ -1769,11 +1769,11 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>185429.9</v>
+        <v>189409.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1781,11 +1781,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>122331.9</v>
+        <v>126311.9</v>
       </c>
     </row>
     <row r="3">
@@ -2041,11 +2041,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>211150</v>
+        <v>211548</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>162.4%</t>
+          <t>162.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>197405</v>
+        <v>197803</v>
       </c>
     </row>
     <row r="11">
@@ -2109,11 +2109,11 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>90400</v>
+        <v>94380</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2121,11 +2121,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>86217</v>
+        <v>90197</v>
       </c>
     </row>
     <row r="13">
@@ -2143,11 +2143,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>59700</v>
+        <v>64680</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24940</v>
+        <v>29920</v>
       </c>
     </row>
     <row r="14">
@@ -2347,11 +2347,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>79600</v>
+        <v>83580</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2359,11 +2359,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>72023.39999999999</v>
+        <v>76003.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2483,11 +2483,11 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>35628</v>
+        <v>39608</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2495,11 +2495,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>30648</v>
+        <v>34628</v>
       </c>
     </row>
     <row r="24">
@@ -2857,11 +2857,11 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>34460</v>
+        <v>60940</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2869,11 +2869,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>17900</v>
+        <v>44380</v>
       </c>
     </row>
     <row r="35">
@@ -2993,11 +2993,11 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>128210</v>
+        <v>140210</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -3005,11 +3005,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>89660</v>
+        <v>101660</v>
       </c>
     </row>
     <row r="39">
@@ -3129,11 +3129,11 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>21698</v>
+        <v>21998</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>21698</v>
+        <v>21998</v>
       </c>
     </row>
     <row r="43">
@@ -3389,11 +3389,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>126922</v>
+        <v>127320</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>126922</v>
+        <v>127320</v>
       </c>
     </row>
     <row r="4">
@@ -3423,11 +3423,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>16868</v>
+        <v>28868</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>16868</v>
+        <v>28868</v>
       </c>
     </row>
     <row r="5">
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>54936.32</v>
+        <v>56884.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>54616.32</v>
+        <v>56564.6</v>
       </c>
     </row>
     <row r="8">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>167718.57</v>
+        <v>220339.57</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>167718.57</v>
+        <v>220339.57</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>110514.5700000001</v>
+        <v>121610.5700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>110514.5700000001</v>
+        <v>121610.5700000001</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>389091.74</v>
+        <v>394578.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>389091.74</v>
+        <v>394578.74</v>
       </c>
     </row>
     <row r="15">
@@ -3797,11 +3797,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>174372.74</v>
+        <v>204409.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>174372.74</v>
+        <v>204409.74</v>
       </c>
     </row>
     <row r="16">
@@ -3831,11 +3831,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>185773</v>
+        <v>174905</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>185773</v>
+        <v>174905</v>
       </c>
     </row>
     <row r="17">
@@ -3865,11 +3865,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>237717</v>
+        <v>248911</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>237717</v>
+        <v>248911</v>
       </c>
     </row>
     <row r="18">
@@ -4069,11 +4069,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>251168</v>
+        <v>311964</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>158780</v>
+        <v>219576</v>
       </c>
     </row>
     <row r="24">
@@ -4137,11 +4137,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>153755.01</v>
+        <v>154153.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>210.6%</t>
+          <t>211.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4149,11 +4149,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>131355.01</v>
+        <v>131753.01</v>
       </c>
     </row>
     <row r="26">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>259075.95</v>
+        <v>270093.55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>218495.95</v>
+        <v>229513.55</v>
       </c>
     </row>
     <row r="29">
@@ -4273,11 +4273,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>83406.89999999999</v>
+        <v>100906.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>83406.89999999999</v>
+        <v>100906.9</v>
       </c>
     </row>
     <row r="30">
@@ -4341,11 +4341,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>45846.2</v>
+        <v>82364.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>41348.2</v>
+        <v>77866.2</v>
       </c>
     </row>
     <row r="32">
@@ -4375,11 +4375,11 @@
         <v>130000</v>
       </c>
       <c r="D32" t="n">
-        <v>31804</v>
+        <v>51804</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4387,11 +4387,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23804</v>
+        <v>43804</v>
       </c>
     </row>
     <row r="33">
@@ -4477,11 +4477,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>18590</v>
+        <v>28590</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>18590</v>
+        <v>28590</v>
       </c>
     </row>
     <row r="36">
@@ -4511,11 +4511,11 @@
         <v>40000</v>
       </c>
       <c r="D36" t="n">
-        <v>109868</v>
+        <v>110266</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>274.7%</t>
+          <t>275.7%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>109868</v>
+        <v>110266</v>
       </c>
     </row>
     <row r="37">
@@ -4545,11 +4545,11 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>41990</v>
+        <v>42388</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>40310</v>
+        <v>40708</v>
       </c>
     </row>
     <row r="38">
@@ -4579,11 +4579,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>47794</v>
+        <v>48192</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>120.5%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>47794</v>
+        <v>48192</v>
       </c>
     </row>
     <row r="39">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>119613.2</v>
+        <v>136613.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>119613.2</v>
+        <v>136613.2</v>
       </c>
     </row>
     <row r="46">
@@ -4851,11 +4851,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>147294</v>
+        <v>165294</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>147294</v>
+        <v>165294</v>
       </c>
     </row>
     <row r="47">
@@ -4885,11 +4885,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>84974</v>
+        <v>92974</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>68174</v>
+        <v>76174</v>
       </c>
     </row>
     <row r="48">
@@ -4919,11 +4919,11 @@
         <v>120000</v>
       </c>
       <c r="D48" t="n">
-        <v>64218</v>
+        <v>72218</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>64218</v>
+        <v>72218</v>
       </c>
     </row>
     <row r="49">
@@ -5055,11 +5055,11 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>95284</v>
+        <v>113682</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5067,11 +5067,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>66484</v>
+        <v>84882</v>
       </c>
     </row>
     <row r="53">
@@ -5225,11 +5225,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>69886</v>
+        <v>70284</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>61886</v>
+        <v>62284</v>
       </c>
     </row>
     <row r="58">
@@ -5293,11 +5293,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>134166</v>
+        <v>134962</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>123966</v>
+        <v>124762</v>
       </c>
     </row>
     <row r="60">
@@ -5361,11 +5361,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>215067.5</v>
+        <v>288078.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>195067.5</v>
+        <v>268078.1</v>
       </c>
     </row>
     <row r="62">
@@ -5395,7 +5395,7 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>66135.72</v>
+        <v>66169.62</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>50923.72</v>
+        <v>50957.62</v>
       </c>
     </row>
     <row r="63">
@@ -5429,11 +5429,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>128279.48</v>
+        <v>136279.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>91279.48</v>
+        <v>99279.48000000001</v>
       </c>
     </row>
     <row r="64">
@@ -5463,11 +5463,11 @@
         <v>20796</v>
       </c>
       <c r="D64" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
     <row r="65">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2123775.07</v>
+        <v>2151970.07</v>
       </c>
       <c r="D2" t="n">
-        <v>6925</v>
+        <v>7206</v>
       </c>
       <c r="E2" t="n">
-        <v>1861619.07</v>
+        <v>1889472.07</v>
       </c>
       <c r="F2" t="n">
-        <v>262156</v>
+        <v>262498</v>
       </c>
     </row>
     <row r="3">
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1927088</v>
+        <v>1949763</v>
       </c>
       <c r="D3" t="n">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="E3" t="n">
-        <v>1670697</v>
+        <v>1693372</v>
       </c>
       <c r="F3" t="n">
         <v>256391</v>
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>196687.07</v>
+        <v>202207.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6447</v>
+        <v>6717</v>
       </c>
       <c r="E4" t="n">
-        <v>190922.07</v>
+        <v>196100.07</v>
       </c>
       <c r="F4" t="n">
-        <v>5765</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4010753.82</v>
+        <v>4357617.82</v>
       </c>
       <c r="D5" t="n">
-        <v>817</v>
+        <v>868</v>
       </c>
       <c r="E5" t="n">
-        <v>811945.8</v>
+        <v>824343.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3198808.02</v>
+        <v>3533274.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2871643.02</v>
+        <v>3146531.02</v>
       </c>
       <c r="D6" t="n">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>2755203.02</v>
+        <v>3030091.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1119110.8</v>
+        <v>1191086.8</v>
       </c>
       <c r="D7" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="E7" t="n">
-        <v>695505.8</v>
+        <v>707903.8</v>
       </c>
       <c r="F7" t="n">
-        <v>423605</v>
+        <v>483183</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3004333.19</v>
+        <v>3269813.05</v>
       </c>
       <c r="D8" t="n">
-        <v>2443</v>
+        <v>2657</v>
       </c>
       <c r="E8" t="n">
-        <v>38424.25</v>
+        <v>38869.57</v>
       </c>
       <c r="F8" t="n">
-        <v>2965908.94</v>
+        <v>3230943.48</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1735309.1</v>
+        <v>1876944.93</v>
       </c>
       <c r="D9" t="n">
-        <v>1289</v>
+        <v>1374</v>
       </c>
       <c r="E9" t="n">
         <v>13802.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1721506.92</v>
+        <v>1863142.75</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1265524.09</v>
+        <v>1389368.12</v>
       </c>
       <c r="D10" t="n">
-        <v>1152</v>
+        <v>1281</v>
       </c>
       <c r="E10" t="n">
-        <v>24622.07</v>
+        <v>25067.39</v>
       </c>
       <c r="F10" t="n">
-        <v>1240902.02</v>
+        <v>1364300.73</v>
       </c>
     </row>
     <row r="11">
@@ -5790,13 +5790,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>698200</v>
+        <v>723000</v>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>320400</v>
+        <v>345200</v>
       </c>
       <c r="F11" t="n">
         <v>377800</v>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2123775.07</v>
+        <v>2151970.07</v>
       </c>
       <c r="C2" t="n">
-        <v>339464.91</v>
+        <v>340613.91</v>
       </c>
       <c r="D2" t="n">
-        <v>48254.01</v>
+        <v>49394.01</v>
       </c>
       <c r="E2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="F2" t="n">
-        <v>291210.9</v>
+        <v>291219.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.71</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="3">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4010753.82</v>
+        <v>4357617.82</v>
       </c>
       <c r="C3" t="n">
         <v>633994.28</v>
@@ -5966,13 +5966,13 @@
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>598496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>14.92</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="4">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3004333.19</v>
+        <v>3269813.05</v>
       </c>
       <c r="C4" t="n">
-        <v>1085301.23</v>
+        <v>1185598.23</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1083272.23</v>
+        <v>1183569.23</v>
       </c>
       <c r="G4" t="n">
-        <v>36.06</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="5">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>698200</v>
+        <v>723000</v>
       </c>
       <c r="C5" t="n">
         <v>377800</v>
@@ -6022,7 +6022,7 @@
         <v>377800</v>
       </c>
       <c r="G5" t="n">
-        <v>54.11</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="6">
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C2" t="n">
-        <v>1075449.51</v>
+        <v>1075608.51</v>
       </c>
       <c r="D2" t="n">
         <v>100</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="C4" t="n">
-        <v>208216.37</v>
+        <v>209130.37</v>
       </c>
       <c r="D4" t="n">
         <v>28</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
-        <v>96427.67</v>
+        <v>96465.67</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>1526</v>
+        <v>1564</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6439,19 +6439,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>112762.01</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -6462,14 +6462,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>66673</v>
+        <v>112789.01</v>
       </c>
     </row>
     <row r="8">
@@ -6480,14 +6480,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>45099.66</v>
+        <v>66673</v>
       </c>
     </row>
     <row r="9">
@@ -6498,14 +6498,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="D9" t="n">
-        <v>16677</v>
+        <v>45137.66</v>
       </c>
     </row>
     <row r="10">
@@ -6516,14 +6516,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>6500</v>
+        <v>16715</v>
       </c>
     </row>
     <row r="11">
@@ -6534,14 +6534,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4169</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="12">
@@ -6552,14 +6552,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1771</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="13">
@@ -6570,14 +6570,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>375</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="14">
@@ -6588,14 +6588,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15">
@@ -6606,32 +6606,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>83883</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -6642,14 +6642,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>151</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>39221.9</v>
+        <v>83883</v>
       </c>
     </row>
     <row r="18">
@@ -6660,14 +6660,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="D18" t="n">
-        <v>28717.9</v>
+        <v>39335.9</v>
       </c>
     </row>
     <row r="19">
@@ -6678,14 +6678,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>11643</v>
+        <v>28774.9</v>
       </c>
     </row>
     <row r="20">
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>8596</v>
+        <v>11643</v>
       </c>
     </row>
     <row r="21">
@@ -6714,14 +6714,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D21" t="n">
-        <v>4221</v>
+        <v>8596</v>
       </c>
     </row>
     <row r="22">
@@ -6732,14 +6732,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>454</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="23">
@@ -6750,14 +6750,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>454</v>
       </c>
     </row>
     <row r="24">
@@ -6768,14 +6768,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -6786,32 +6786,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>未填写原因</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
         <v>12</v>
-      </c>
-      <c r="D26" t="n">
-        <v>128286</v>
       </c>
     </row>
     <row r="27">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>20444.48</v>
+        <v>128286</v>
       </c>
     </row>
     <row r="28">
@@ -6840,14 +6840,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>4019</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="29">
@@ -6858,32 +6858,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>143100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -6894,14 +6894,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>2000</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="32">
@@ -6912,14 +6912,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>59</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>88502</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
@@ -6984,14 +6984,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>39399</v>
+        <v>88502</v>
       </c>
     </row>
     <row r="37">
@@ -7002,14 +7002,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D37" t="n">
-        <v>267</v>
+        <v>39399</v>
       </c>
     </row>
     <row r="38">
@@ -7020,14 +7020,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -7051,19 +7051,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>44154.6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="D41" t="n">
-        <v>25029.81</v>
+        <v>44201.6</v>
       </c>
     </row>
     <row r="42">
@@ -7092,14 +7092,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="D42" t="n">
-        <v>23800</v>
+        <v>25191.81</v>
       </c>
     </row>
     <row r="43">
@@ -7110,14 +7110,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>6988</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="44">
@@ -7128,14 +7128,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>4050.67</v>
+        <v>6988</v>
       </c>
     </row>
     <row r="45">
@@ -7146,14 +7146,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>4000</v>
+        <v>4050.67</v>
       </c>
     </row>
     <row r="46">
@@ -7164,14 +7164,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1290.9</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="47">
@@ -7182,14 +7182,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D47" t="n">
-        <v>617</v>
+        <v>1290.9</v>
       </c>
     </row>
     <row r="48">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>162</v>
+        <v>617</v>
       </c>
     </row>
     <row r="49">
@@ -7218,14 +7218,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50">
@@ -7236,32 +7236,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>59600</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>33839</v>
+        <v>59600</v>
       </c>
     </row>
     <row r="53">
@@ -7290,14 +7290,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D53" t="n">
-        <v>13689</v>
+        <v>33867</v>
       </c>
     </row>
     <row r="54">
@@ -7308,14 +7308,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>299</v>
+        <v>14026</v>
       </c>
     </row>
     <row r="55">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56">
@@ -7344,14 +7344,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57">
@@ -7362,14 +7362,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>76</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>62800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
@@ -7416,14 +7416,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>15200</v>
+        <v>62800</v>
       </c>
     </row>
     <row r="61">
@@ -7434,14 +7434,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>11119</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="62">
@@ -7452,32 +7452,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>6000</v>
+        <v>11119</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>31373</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="64">
@@ -7488,14 +7488,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D64" t="n">
-        <v>30875</v>
+        <v>31588</v>
       </c>
     </row>
     <row r="65">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D65" t="n">
-        <v>9163.33</v>
+        <v>30875</v>
       </c>
     </row>
     <row r="66">
@@ -7524,14 +7524,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>6619</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="67">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>2489</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="68">
@@ -7560,14 +7560,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D68" t="n">
-        <v>1284</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="69">
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>383</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="70">
@@ -7596,32 +7596,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>383</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>43067</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
@@ -7632,14 +7632,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>20000</v>
+        <v>43067</v>
       </c>
     </row>
     <row r="73">
@@ -7650,14 +7650,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>16800</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="74">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>299</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>62837</v>
+        <v>299</v>
       </c>
     </row>
     <row r="76">
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>13598</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="77">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>200</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="78">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>115</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>59</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>48619</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>14000</v>
+        <v>48619</v>
       </c>
     </row>
     <row r="82">
@@ -7812,14 +7812,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>10000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="83">
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="84">
@@ -7848,14 +7848,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>118</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="85">
@@ -7866,32 +7866,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>29</v>
+        <v>118</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>24800</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
@@ -7902,14 +7902,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>18000</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="88">
@@ -7920,32 +7920,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>10200</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>41600</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="90">
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>4009</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="91">
@@ -7974,32 +7974,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>318</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>16960</v>
+        <v>318</v>
       </c>
     </row>
     <row r="93">
@@ -8010,14 +8010,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>14514</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="94">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D94" t="n">
-        <v>9168</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="95">
@@ -8046,14 +8046,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D95" t="n">
-        <v>66</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="96">
@@ -8064,14 +8064,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8113,19 +8113,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -8136,14 +8136,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>78</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="101">
@@ -8154,32 +8154,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>7019</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -8190,14 +8190,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>57</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="104">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>19.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1910</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="106">
@@ -8244,13 +8244,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>2</v>
       </c>
       <c r="D106" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8453,10 +8471,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C2" t="n">
-        <v>279547.5</v>
+        <v>279885.5</v>
       </c>
     </row>
     <row r="3">
@@ -8466,10 +8484,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>278086</v>
+        <v>278200</v>
       </c>
     </row>
     <row r="4">
@@ -8479,10 +8497,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C4" t="n">
-        <v>202964.48</v>
+        <v>203021.48</v>
       </c>
     </row>
     <row r="5">
@@ -8492,10 +8510,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>193714</v>
+        <v>193733</v>
       </c>
     </row>
     <row r="6">
@@ -8531,10 +8549,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>73360</v>
+        <v>73379</v>
       </c>
     </row>
     <row r="9">
@@ -8570,10 +8588,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>53167.01</v>
+        <v>53485.01</v>
       </c>
     </row>
     <row r="12">
@@ -8609,10 +8627,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C14" t="n">
-        <v>43141</v>
+        <v>43217</v>
       </c>
     </row>
     <row r="15">
@@ -8622,10 +8640,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" t="n">
-        <v>42678.99</v>
+        <v>42696.99</v>
       </c>
     </row>
     <row r="16">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>485022</v>
+        <v>487672</v>
       </c>
       <c r="E2" t="n">
-        <v>254224</v>
+        <v>254414</v>
       </c>
       <c r="F2" t="n">
-        <v>230797</v>
+        <v>233257</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>801440</v>
+        <v>813145</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>352271</v>
+        <v>363705</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,41 +567,41 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>17018</v>
+        <v>18355</v>
       </c>
       <c r="E3" t="n">
         <v>40784</v>
       </c>
       <c r="F3" t="n">
-        <v>-23765</v>
+        <v>-22428</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>58325</v>
+        <v>73649</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7436</v>
+        <v>22442</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-419.6%</t>
+          <t>-199.9%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>707749</v>
+        <v>724463</v>
       </c>
       <c r="E4" t="n">
-        <v>176976</v>
+        <v>177175</v>
       </c>
       <c r="F4" t="n">
-        <v>530773</v>
+        <v>547288</v>
       </c>
       <c r="G4" t="n">
         <v>20398</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>690547</v>
+        <v>748026</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>491218</v>
+        <v>546583</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,13 +675,13 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>479630</v>
+        <v>479649</v>
       </c>
       <c r="E5" t="n">
         <v>128206</v>
       </c>
       <c r="F5" t="n">
-        <v>351424</v>
+        <v>351443</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>658207</v>
+        <v>658376</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>406283</v>
+        <v>406452</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>412478</v>
+        <v>437064</v>
       </c>
       <c r="E6" t="n">
-        <v>110396</v>
+        <v>110825</v>
       </c>
       <c r="F6" t="n">
-        <v>302081</v>
+        <v>326238</v>
       </c>
       <c r="G6" t="n">
         <v>45600</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>425814</v>
+        <v>442708</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>383128</v>
+        <v>398517</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>372796</v>
+        <v>379528</v>
       </c>
       <c r="E7" t="n">
-        <v>108224</v>
+        <v>108907</v>
       </c>
       <c r="F7" t="n">
-        <v>264572</v>
+        <v>270621</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>578344</v>
+        <v>635064</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>386240</v>
+        <v>432951</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>403026</v>
+        <v>403535</v>
       </c>
       <c r="E8" t="n">
-        <v>82420</v>
+        <v>82515</v>
       </c>
       <c r="F8" t="n">
-        <v>320606</v>
+        <v>321020</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>493732</v>
+        <v>563038</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>317021</v>
+        <v>386148</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1260452</v>
+        <v>1336852</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>849240</v>
+        <v>919040</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1689045</v>
+        <v>1866907</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1689045</v>
+        <v>1866907</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1407454</v>
+        <v>1448987</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+20.0%</t>
+          <t>+28.8%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1407454</v>
+        <v>1448987</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+20.0%</t>
+          <t>+28.8%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,39 +997,39 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>335150</v>
+        <v>342546</v>
       </c>
       <c r="E11" t="n">
         <v>45927</v>
       </c>
       <c r="F11" t="n">
-        <v>289223</v>
+        <v>296619</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>352981</v>
+        <v>372000</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>308105</v>
+        <v>327124</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1051,39 +1051,39 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>379032</v>
+        <v>380226</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>376804</v>
+        <v>377998</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>335294</v>
+        <v>355294</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>+7.0%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>315675</v>
+        <v>335675</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+19.4%</t>
+          <t>+12.6%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,43 +1103,43 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>663795</v>
+        <v>693613</v>
       </c>
       <c r="E13" t="n">
         <v>76809</v>
       </c>
       <c r="F13" t="n">
-        <v>586986</v>
+        <v>616804</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>639134</v>
+        <v>653248</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>+6.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>595191</v>
+        <v>609305</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>20402</v>
+        <v>22983</v>
       </c>
     </row>
     <row r="14">
@@ -1157,43 +1157,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>509092</v>
+        <v>583358</v>
       </c>
       <c r="E14" t="n">
         <v>77178</v>
       </c>
       <c r="F14" t="n">
-        <v>431914</v>
+        <v>506180</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>744804</v>
+        <v>777998</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>608101</v>
+        <v>641276</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>60329</v>
+        <v>62784</v>
       </c>
     </row>
     <row r="15">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>208612</v>
+        <v>212572</v>
       </c>
       <c r="E15" t="n">
         <v>15325</v>
       </c>
       <c r="F15" t="n">
-        <v>193287</v>
+        <v>197247</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>220596</v>
+        <v>220914</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>220510</v>
+        <v>220828</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>323491</v>
+        <v>323898</v>
       </c>
       <c r="E16" t="n">
         <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>270491</v>
+        <v>270898</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>212890</v>
+        <v>213288</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+52.0%</t>
+          <t>+51.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>151007</v>
+        <v>151405</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+79.1%</t>
+          <t>+78.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,43 +1315,43 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>490291</v>
+        <v>565057</v>
       </c>
       <c r="E17" t="n">
         <v>96666</v>
       </c>
       <c r="F17" t="n">
-        <v>393625</v>
+        <v>468391</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>421395</v>
+        <v>451793</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+16.3%</t>
+          <t>+25.1%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>378880</v>
+        <v>409278</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>+14.4%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>24189</v>
+        <v>26239</v>
       </c>
     </row>
     <row r="18">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>716151</v>
+        <v>744770</v>
       </c>
       <c r="E18" t="n">
-        <v>152805</v>
+        <v>152824</v>
       </c>
       <c r="F18" t="n">
-        <v>563346</v>
+        <v>591946</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>664751</v>
+        <v>674751</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+7.7%</t>
+          <t>+10.4%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>438289</v>
+        <v>441689</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+28.5%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,43 +1423,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>383421</v>
+        <v>410851</v>
       </c>
       <c r="E19" t="n">
         <v>145546</v>
       </c>
       <c r="F19" t="n">
-        <v>237875</v>
+        <v>265305</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>955814</v>
+        <v>980298</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-59.9%</t>
+          <t>-58.1%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>814399</v>
+        <v>829283</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-68.0%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>12488</v>
+        <v>13118</v>
       </c>
     </row>
     <row r="20">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>698733</v>
+        <v>717595</v>
       </c>
       <c r="E20" t="n">
-        <v>95119</v>
+        <v>95138</v>
       </c>
       <c r="F20" t="n">
-        <v>603614</v>
+        <v>622457</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>807078</v>
+        <v>815893</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>738779</v>
+        <v>745614</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
-        <v>445.8</v>
+        <v>788.5</v>
       </c>
       <c r="E2" t="n">
-        <v>57961</v>
+        <v>73271</v>
       </c>
     </row>
     <row r="3">
@@ -1584,13 +1584,13 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>812</v>
+        <v>566</v>
       </c>
       <c r="C4" t="n">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="D4" t="n">
-        <v>1358.6</v>
+        <v>1478.8</v>
       </c>
       <c r="E4" t="n">
-        <v>2981</v>
+        <v>3450</v>
       </c>
     </row>
   </sheetData>
@@ -1973,11 +1973,11 @@
         <v>40000</v>
       </c>
       <c r="D8" t="n">
-        <v>30120</v>
+        <v>31800</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1985,11 +1985,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4345</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="9">
@@ -2041,11 +2041,11 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>211548</v>
+        <v>219508</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>162.7%</t>
+          <t>168.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2053,11 +2053,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>197803</v>
+        <v>205763</v>
       </c>
     </row>
     <row r="11">
@@ -2143,11 +2143,11 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>64680</v>
+        <v>68660</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2155,11 +2155,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>29920</v>
+        <v>33900</v>
       </c>
     </row>
     <row r="14">
@@ -2347,11 +2347,11 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>83580</v>
+        <v>91540</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2359,11 +2359,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>76003.39999999999</v>
+        <v>83963.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2449,11 +2449,11 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>60069.9</v>
+        <v>68029.89999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2461,11 +2461,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>43290.9</v>
+        <v>51250.89999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2551,11 +2551,11 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>66200</v>
+        <v>70180</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>66200</v>
+        <v>70180</v>
       </c>
     </row>
     <row r="26">
@@ -2653,11 +2653,11 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>109620</v>
+        <v>113600</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>79820</v>
+        <v>83800</v>
       </c>
     </row>
     <row r="29">
@@ -3389,11 +3389,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>127320</v>
+        <v>131280</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>131.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>127320</v>
+        <v>131280</v>
       </c>
     </row>
     <row r="4">
@@ -3525,11 +3525,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>56884.6</v>
+        <v>64884.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3537,11 +3537,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>56564.6</v>
+        <v>64564.6</v>
       </c>
     </row>
     <row r="8">
@@ -3593,11 +3593,11 @@
         <v>120000</v>
       </c>
       <c r="D9" t="n">
-        <v>120560.17</v>
+        <v>138885.26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100.5%</t>
+          <t>115.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3605,11 +3605,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-19839.83</v>
+        <v>-1514.739999999991</v>
       </c>
     </row>
     <row r="10">
@@ -3627,11 +3627,11 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>42500</v>
+        <v>43300</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>42500</v>
+        <v>43300</v>
       </c>
     </row>
     <row r="11">
@@ -3695,11 +3695,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>220339.57</v>
+        <v>259421.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>220339.57</v>
+        <v>259421.14</v>
       </c>
     </row>
     <row r="13">
@@ -3729,11 +3729,11 @@
         <v>300000</v>
       </c>
       <c r="D13" t="n">
-        <v>121610.5700000001</v>
+        <v>145375.5700000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>121610.5700000001</v>
+        <v>145375.5700000001</v>
       </c>
     </row>
     <row r="14">
@@ -3763,11 +3763,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>394578.74</v>
+        <v>437595.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>394578.74</v>
+        <v>437595.74</v>
       </c>
     </row>
     <row r="15">
@@ -3831,11 +3831,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>174905</v>
+        <v>184905</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>174905</v>
+        <v>184905</v>
       </c>
     </row>
     <row r="17">
@@ -3865,11 +3865,11 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>248911</v>
+        <v>270507</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>248911</v>
+        <v>270507</v>
       </c>
     </row>
     <row r="18">
@@ -3899,11 +3899,11 @@
         <v>50000</v>
       </c>
       <c r="D18" t="n">
-        <v>14174</v>
+        <v>19174</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14174</v>
+        <v>19174</v>
       </c>
     </row>
     <row r="19">
@@ -4001,11 +4001,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>60774.00000000001</v>
+        <v>80774</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>60774.00000000001</v>
+        <v>80774</v>
       </c>
     </row>
     <row r="22">
@@ -4069,11 +4069,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>311964</v>
+        <v>318564</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>219576</v>
+        <v>226176</v>
       </c>
     </row>
     <row r="24">
@@ -4137,11 +4137,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>154153.01</v>
+        <v>166153.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>211.2%</t>
+          <t>227.6%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4149,11 +4149,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>131753.01</v>
+        <v>143753.01</v>
       </c>
     </row>
     <row r="26">
@@ -4205,11 +4205,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>123544</v>
+        <v>133544</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4217,11 +4217,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>115544</v>
+        <v>125544</v>
       </c>
     </row>
     <row r="28">
@@ -4239,11 +4239,11 @@
         <v>270000</v>
       </c>
       <c r="D28" t="n">
-        <v>270093.55</v>
+        <v>274354.45</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4251,11 +4251,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>229513.55</v>
+        <v>233774.45</v>
       </c>
     </row>
     <row r="29">
@@ -4273,11 +4273,11 @@
         <v>150000</v>
       </c>
       <c r="D29" t="n">
-        <v>100906.9</v>
+        <v>118406.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>100906.9</v>
+        <v>118406.9</v>
       </c>
     </row>
     <row r="30">
@@ -4341,11 +4341,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>82364.2</v>
+        <v>90364.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>77866.2</v>
+        <v>85866.2</v>
       </c>
     </row>
     <row r="32">
@@ -4477,11 +4477,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>28590</v>
+        <v>28988</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28590</v>
+        <v>28988</v>
       </c>
     </row>
     <row r="36">
@@ -4545,11 +4545,11 @@
         <v>80000</v>
       </c>
       <c r="D37" t="n">
-        <v>42388</v>
+        <v>42786</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4557,11 +4557,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>40708</v>
+        <v>41106</v>
       </c>
     </row>
     <row r="38">
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40">
@@ -4681,11 +4681,11 @@
         <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>66986</v>
+        <v>77782</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4693,11 +4693,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>56986</v>
+        <v>67782</v>
       </c>
     </row>
     <row r="42">
@@ -4783,11 +4783,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>222844</v>
+        <v>230844</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>148.6%</t>
+          <t>153.9%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>222844</v>
+        <v>230844</v>
       </c>
     </row>
     <row r="45">
@@ -4817,11 +4817,11 @@
         <v>200000</v>
       </c>
       <c r="D45" t="n">
-        <v>136613.2</v>
+        <v>194663.28</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>136613.2</v>
+        <v>194663.28</v>
       </c>
     </row>
     <row r="46">
@@ -4851,11 +4851,11 @@
         <v>200000</v>
       </c>
       <c r="D46" t="n">
-        <v>165294</v>
+        <v>173294</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>165294</v>
+        <v>173294</v>
       </c>
     </row>
     <row r="47">
@@ -4885,11 +4885,11 @@
         <v>200000</v>
       </c>
       <c r="D47" t="n">
-        <v>92974</v>
+        <v>101372</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>76174</v>
+        <v>84572</v>
       </c>
     </row>
     <row r="48">
@@ -5089,11 +5089,11 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>127068</v>
+        <v>134464</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5101,11 +5101,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>110268</v>
+        <v>117664</v>
       </c>
     </row>
     <row r="54">
@@ -5259,11 +5259,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>89574</v>
+        <v>89972</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5271,11 +5271,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>54774</v>
+        <v>55172</v>
       </c>
     </row>
     <row r="59">
@@ -5361,11 +5361,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>288078.1</v>
+        <v>316931.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>268078.1</v>
+        <v>296931.5</v>
       </c>
     </row>
     <row r="62">
@@ -5429,11 +5429,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>136279.48</v>
+        <v>181673.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5441,11 +5441,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>99279.48000000001</v>
+        <v>144673.48</v>
       </c>
     </row>
     <row r="64">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2151970.07</v>
+        <v>2219355.07</v>
       </c>
       <c r="D2" t="n">
-        <v>7206</v>
+        <v>7507</v>
       </c>
       <c r="E2" t="n">
-        <v>1889472.07</v>
+        <v>1941489.07</v>
       </c>
       <c r="F2" t="n">
-        <v>262498</v>
+        <v>277866</v>
       </c>
     </row>
     <row r="3">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1949763</v>
+        <v>2006294</v>
       </c>
       <c r="D3" t="n">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="E3" t="n">
-        <v>1693372</v>
+        <v>1734985</v>
       </c>
       <c r="F3" t="n">
-        <v>256391</v>
+        <v>271309</v>
       </c>
     </row>
     <row r="4">
@@ -5622,16 +5622,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>202207.07</v>
+        <v>213061.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6717</v>
+        <v>6995</v>
       </c>
       <c r="E4" t="n">
-        <v>196100.07</v>
+        <v>206504.07</v>
       </c>
       <c r="F4" t="n">
-        <v>6107</v>
+        <v>6557</v>
       </c>
     </row>
     <row r="5">
@@ -5646,16 +5646,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4357617.82</v>
+        <v>4597291.82</v>
       </c>
       <c r="D5" t="n">
-        <v>868</v>
+        <v>911</v>
       </c>
       <c r="E5" t="n">
         <v>824343.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3533274.02</v>
+        <v>3772948.02</v>
       </c>
     </row>
     <row r="6">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3146531.02</v>
+        <v>3347011.02</v>
       </c>
       <c r="D6" t="n">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>3030091.02</v>
+        <v>3230571.02</v>
       </c>
     </row>
     <row r="7">
@@ -5694,16 +5694,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1191086.8</v>
+        <v>1230280.8</v>
       </c>
       <c r="D7" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E7" t="n">
         <v>707903.8</v>
       </c>
       <c r="F7" t="n">
-        <v>483183</v>
+        <v>522377</v>
       </c>
     </row>
     <row r="8">
@@ -5718,16 +5718,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3269813.05</v>
+        <v>3550221.13</v>
       </c>
       <c r="D8" t="n">
-        <v>2657</v>
+        <v>2809</v>
       </c>
       <c r="E8" t="n">
-        <v>38869.57</v>
+        <v>39399.56</v>
       </c>
       <c r="F8" t="n">
-        <v>3230943.48</v>
+        <v>3510821.57</v>
       </c>
     </row>
     <row r="9">
@@ -5742,16 +5742,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1876944.93</v>
+        <v>2103137.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1374</v>
+        <v>1468</v>
       </c>
       <c r="E9" t="n">
-        <v>13802.18</v>
+        <v>14302.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1863142.75</v>
+        <v>2088835.62</v>
       </c>
     </row>
     <row r="10">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1389368.12</v>
+        <v>1443583.33</v>
       </c>
       <c r="D10" t="n">
-        <v>1281</v>
+        <v>1339</v>
       </c>
       <c r="E10" t="n">
-        <v>25067.39</v>
+        <v>25097.38</v>
       </c>
       <c r="F10" t="n">
-        <v>1364300.73</v>
+        <v>1418485.95</v>
       </c>
     </row>
     <row r="11">
@@ -5862,16 +5862,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>71280</v>
+        <v>75240</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
         <v>53460</v>
       </c>
       <c r="F14" t="n">
-        <v>17820</v>
+        <v>21780</v>
       </c>
     </row>
   </sheetData>
@@ -5932,22 +5932,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2151970.07</v>
+        <v>2219355.07</v>
       </c>
       <c r="C2" t="n">
-        <v>340613.91</v>
+        <v>342247.91</v>
       </c>
       <c r="D2" t="n">
-        <v>49394.01</v>
+        <v>50990.01</v>
       </c>
       <c r="E2" t="n">
         <v>2.3</v>
       </c>
       <c r="F2" t="n">
-        <v>291219.9</v>
+        <v>291257.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.53</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="3">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4357617.82</v>
+        <v>4597291.82</v>
       </c>
       <c r="C3" t="n">
         <v>633994.28</v>
@@ -5966,13 +5966,13 @@
         <v>35498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="F3" t="n">
         <v>598496.28</v>
       </c>
       <c r="G3" t="n">
-        <v>13.73</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="4">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3269813.05</v>
+        <v>3550221.13</v>
       </c>
       <c r="C4" t="n">
-        <v>1185598.23</v>
+        <v>1253730.54</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -5994,10 +5994,10 @@
         <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1183569.23</v>
+        <v>1251701.54</v>
       </c>
       <c r="G4" t="n">
-        <v>36.2</v>
+        <v>35.26</v>
       </c>
     </row>
     <row r="5">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71280</v>
+        <v>75240</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6143,10 +6143,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C2" t="n">
-        <v>1075608.51</v>
+        <v>1075787.51</v>
       </c>
       <c r="D2" t="n">
         <v>100</v>
@@ -6175,10 +6175,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="C4" t="n">
-        <v>209130.37</v>
+        <v>210300.37</v>
       </c>
       <c r="D4" t="n">
         <v>28</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>96465.67</v>
+        <v>96598.67</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>14708.8</v>
+        <v>14727.8</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -6271,10 +6271,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>1564</v>
+        <v>1678</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6287,10 +6287,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6466,10 +6466,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="n">
-        <v>112789.01</v>
+        <v>112798.01</v>
       </c>
     </row>
     <row r="8">
@@ -6502,10 +6502,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>45137.66</v>
+        <v>45223.66</v>
       </c>
     </row>
     <row r="10">
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>16715</v>
+        <v>16791</v>
       </c>
     </row>
     <row r="11">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
@@ -6664,10 +6664,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D18" t="n">
-        <v>39335.9</v>
+        <v>39392.9</v>
       </c>
     </row>
     <row r="19">
@@ -6682,10 +6682,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D19" t="n">
-        <v>28774.9</v>
+        <v>28878.9</v>
       </c>
     </row>
     <row r="20">
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>11643</v>
+        <v>11681</v>
       </c>
     </row>
     <row r="21">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>4019</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="30">
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D41" t="n">
-        <v>44201.6</v>
+        <v>44220.6</v>
       </c>
     </row>
     <row r="42">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D42" t="n">
-        <v>25191.81</v>
+        <v>25468.81</v>
       </c>
     </row>
     <row r="43">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D47" t="n">
-        <v>1290.9</v>
+        <v>1309.9</v>
       </c>
     </row>
     <row r="48">
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D49" t="n">
-        <v>181</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50">
@@ -7294,10 +7294,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D53" t="n">
-        <v>33867</v>
+        <v>33914</v>
       </c>
     </row>
     <row r="54">
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>14026</v>
+        <v>14662</v>
       </c>
     </row>
     <row r="55">
@@ -7483,7 +7483,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>31588</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -7506,14 +7506,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D65" t="n">
-        <v>30875</v>
+        <v>31664</v>
       </c>
     </row>
     <row r="66">
@@ -7524,14 +7524,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D66" t="n">
-        <v>9163.33</v>
+        <v>30875</v>
       </c>
     </row>
     <row r="67">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>6619</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="68">
@@ -7560,14 +7560,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>2489</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="69">
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D69" t="n">
-        <v>1284</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="70">
@@ -7596,14 +7596,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>383</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="71">
@@ -7614,32 +7614,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>43067</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -7650,14 +7650,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>20000</v>
+        <v>43067</v>
       </c>
     </row>
     <row r="74">
@@ -7668,14 +7668,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>16800</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="75">
@@ -7686,32 +7686,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>299</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>62837</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77">
@@ -7722,14 +7722,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>13598</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="78">
@@ -7740,14 +7740,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>200</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="79">
@@ -7758,14 +7758,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>115</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80">
@@ -7776,32 +7776,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>59</v>
+        <v>115</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>48619</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82">
@@ -7812,14 +7812,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>14000</v>
+        <v>48619</v>
       </c>
     </row>
     <row r="83">
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>10000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="84">
@@ -7848,14 +7848,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="85">
@@ -7866,14 +7866,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>118</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="86">
@@ -7884,32 +7884,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>29</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>24800</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88">
@@ -7920,14 +7920,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>18000</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="89">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>10200</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>41600</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="91">
@@ -7974,14 +7974,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>4009</v>
+        <v>41600</v>
       </c>
     </row>
     <row r="92">
@@ -7992,32 +7992,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>318</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>16960</v>
+        <v>318</v>
       </c>
     </row>
     <row r="94">
@@ -8028,14 +8028,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>14514</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="95">
@@ -8046,14 +8046,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D95" t="n">
-        <v>9187</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="96">
@@ -8064,14 +8064,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D96" t="n">
-        <v>66</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="97">
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -8131,19 +8131,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
@@ -8154,14 +8154,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>78</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="102">
@@ -8172,32 +8172,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>7019</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104">
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>57</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="105">
@@ -8226,32 +8226,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>19.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1910</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="107">
@@ -8262,13 +8262,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>2</v>
       </c>
       <c r="D107" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8471,10 +8489,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C2" t="n">
-        <v>279885.5</v>
+        <v>280113.5</v>
       </c>
     </row>
     <row r="3">
@@ -8484,10 +8502,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C3" t="n">
-        <v>278200</v>
+        <v>278381</v>
       </c>
     </row>
     <row r="4">
@@ -8497,10 +8515,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C4" t="n">
-        <v>203021.48</v>
+        <v>203387.48</v>
       </c>
     </row>
     <row r="5">
@@ -8523,10 +8541,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>135010</v>
+        <v>135029</v>
       </c>
     </row>
     <row r="7">
@@ -8536,10 +8554,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>119478.81</v>
+        <v>119497.81</v>
       </c>
     </row>
     <row r="8">
@@ -8549,10 +8567,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>73379</v>
+        <v>73716</v>
       </c>
     </row>
     <row r="9">
@@ -8562,10 +8580,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>64361</v>
+        <v>64390</v>
       </c>
     </row>
     <row r="10">
@@ -8588,10 +8606,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>53485.01</v>
+        <v>53523.01</v>
       </c>
     </row>
     <row r="12">
@@ -8627,10 +8645,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C14" t="n">
-        <v>43217</v>
+        <v>43293</v>
       </c>
     </row>
     <row r="15">
@@ -8640,10 +8658,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" t="n">
-        <v>42696.99</v>
+        <v>42734.99</v>
       </c>
     </row>
     <row r="16">
@@ -8653,10 +8671,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" t="n">
-        <v>40677</v>
+        <v>40696</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -522,11 +522,11 @@
         <v>233257</v>
       </c>
       <c r="G2" t="n">
-        <v>12988</v>
+        <v>8000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -630,11 +630,11 @@
         <v>547288</v>
       </c>
       <c r="G4" t="n">
-        <v>20398</v>
+        <v>46198</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -684,11 +684,11 @@
         <v>351443</v>
       </c>
       <c r="G5" t="n">
-        <v>158352</v>
+        <v>163340</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -738,11 +738,11 @@
         <v>326238</v>
       </c>
       <c r="G6" t="n">
-        <v>45600</v>
+        <v>58198</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -900,11 +900,11 @@
         <v>657145</v>
       </c>
       <c r="G9" t="n">
-        <v>108806</v>
+        <v>145602</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108806</v>
+        <v>145602</v>
       </c>
     </row>
     <row r="3">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20398</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="4">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12988</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="6">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45600</v>
+        <v>58198</v>
       </c>
     </row>
     <row r="7">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>158352</v>
+        <v>163340</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -522,11 +522,11 @@
         <v>233257</v>
       </c>
       <c r="G2" t="n">
-        <v>8000</v>
+        <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8000</v>
+        <v>12988</v>
       </c>
     </row>
     <row r="6">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -684,11 +684,11 @@
         <v>351443</v>
       </c>
       <c r="G5" t="n">
-        <v>163340</v>
+        <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>163340</v>
+        <v>158352</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -1709,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1735,20 +1735,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>协同业绩(元)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>完成率(含协同)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>完成率</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>本月退费</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>退费率</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>本月净流水</t>
         </is>
@@ -1771,20 +1781,28 @@
       <c r="D2" t="n">
         <v>189409.9</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>65.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>63.1%</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>63098</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>126311.9</v>
       </c>
     </row>
@@ -1805,20 +1823,28 @@
       <c r="D3" t="n">
         <v>68680</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>34.3%</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>33186</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>48.3%</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>35494</v>
       </c>
     </row>
@@ -1839,20 +1865,28 @@
       <c r="D4" t="n">
         <v>43780</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>21.9%</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>21.9%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>13346.66</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>30.5%</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>30433.34</v>
       </c>
     </row>
@@ -1873,20 +1907,28 @@
       <c r="D5" t="n">
         <v>57300</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>4988</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>41.5%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>38.2%</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>53892</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>94.1%</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>3408</v>
       </c>
     </row>
@@ -1907,20 +1949,28 @@
       <c r="D6" t="n">
         <v>82900</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>55.3%</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>55.3%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>28983</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>35.0%</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>53917</v>
       </c>
     </row>
@@ -1941,20 +1991,28 @@
       <c r="D7" t="n">
         <v>7960</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>26.5%</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26.5%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>9960</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>125.1%</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>-2000</v>
       </c>
     </row>
@@ -1975,20 +2033,28 @@
       <c r="D8" t="n">
         <v>31800</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>79.5%</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>79.5%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>25775</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>81.1%</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>6025</v>
       </c>
     </row>
@@ -2009,20 +2075,28 @@
       <c r="D9" t="n">
         <v>3980</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>13.3%</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>17700</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>444.7%</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>-13720</v>
       </c>
     </row>
@@ -2043,20 +2117,28 @@
       <c r="D10" t="n">
         <v>219508</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>173.5%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>168.9%</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>13745</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>6.3%</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>205763</v>
       </c>
     </row>
@@ -2077,20 +2159,28 @@
       <c r="D11" t="n">
         <v>39800</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>39.8%</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>39.8%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>39800</v>
       </c>
     </row>
@@ -2111,20 +2201,28 @@
       <c r="D12" t="n">
         <v>94380</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>30198</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>95.8%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>72.6%</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>4183</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>4.4%</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>90197</v>
       </c>
     </row>
@@ -2145,20 +2243,28 @@
       <c r="D13" t="n">
         <v>68660</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>45.8%</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>34760</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>33900</v>
       </c>
     </row>
@@ -2179,20 +2285,28 @@
       <c r="D14" t="n">
         <v>80920</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>16710</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>20.7%</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>64210</v>
       </c>
     </row>
@@ -2213,20 +2327,28 @@
       <c r="D15" t="n">
         <v>130200</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>107.8%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>100.2%</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>62498</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>48.0%</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>67702</v>
       </c>
     </row>
@@ -2247,20 +2369,28 @@
       <c r="D16" t="n">
         <v>187708</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>158352</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>115.4%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>62.6%</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>71108</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>37.9%</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>116600</v>
       </c>
     </row>
@@ -2281,20 +2411,28 @@
       <c r="D17" t="n">
         <v>263288.01</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>87.8%</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>87.8%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>16788</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>6.4%</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>246500.01</v>
       </c>
     </row>
@@ -2315,20 +2453,28 @@
       <c r="D18" t="n">
         <v>22776</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>45.6%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>22776</v>
       </c>
     </row>
@@ -2349,20 +2495,28 @@
       <c r="D19" t="n">
         <v>91540</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>114.4%</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>114.4%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>7576.6</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>8.3%</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>83963.39999999999</v>
       </c>
     </row>
@@ -2383,20 +2537,28 @@
       <c r="D20" t="n">
         <v>15728</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>19.7%</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>19.7%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>4150</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>26.4%</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>11578</v>
       </c>
     </row>
@@ -2417,20 +2579,28 @@
       <c r="D21" t="n">
         <v>60428</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>75.5%</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>75.5%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>26956.67</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>33471.33</v>
       </c>
     </row>
@@ -2451,20 +2621,28 @@
       <c r="D22" t="n">
         <v>68029.89999999999</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>45600</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75.8%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>45.4%</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>16779</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>24.7%</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>51250.89999999999</v>
       </c>
     </row>
@@ -2485,20 +2663,28 @@
       <c r="D23" t="n">
         <v>39608</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>12598</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>74.6%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>56.6%</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>4980</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>12.6%</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>34628</v>
       </c>
     </row>
@@ -2519,20 +2705,28 @@
       <c r="D24" t="n">
         <v>7768</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>9.7%</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>4980</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>64.1%</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>2788</v>
       </c>
     </row>
@@ -2553,20 +2747,28 @@
       <c r="D25" t="n">
         <v>70180</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>87.7%</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>87.7%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>70180</v>
       </c>
     </row>
@@ -2587,20 +2789,28 @@
       <c r="D26" t="n">
         <v>31840</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>39.8%</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>39.8%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>8960</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>28.1%</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>22880</v>
       </c>
     </row>
@@ -2621,20 +2831,28 @@
       <c r="D27" t="n">
         <v>134484</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>13380</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>9.9%</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>121104</v>
       </c>
     </row>
@@ -2655,20 +2873,28 @@
       <c r="D28" t="n">
         <v>113600</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>56.8%</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>56.8%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>29800</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>26.2%</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>83800</v>
       </c>
     </row>
@@ -2689,20 +2915,28 @@
       <c r="D29" t="n">
         <v>68580</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>68.6%</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>68.6%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>29800</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>43.5%</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>38780</v>
       </c>
     </row>
@@ -2723,20 +2957,28 @@
       <c r="D30" t="n">
         <v>59158</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>59.2%</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>59.2%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>4183.33</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>7.1%</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>54974.67</v>
       </c>
     </row>
@@ -2757,20 +2999,28 @@
       <c r="D31" t="n">
         <v>51420</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>34.3%</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>34.3%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>17000</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>33.1%</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>34420</v>
       </c>
     </row>
@@ -2791,20 +3041,28 @@
       <c r="D32" t="n">
         <v>78378</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52.3%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>21580</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>27.5%</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>56798</v>
       </c>
     </row>
@@ -2825,20 +3083,28 @@
       <c r="D33" t="n">
         <v>127340</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>74.9%</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>74.9%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>14200</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>11.2%</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>113140</v>
       </c>
     </row>
@@ -2859,20 +3125,28 @@
       <c r="D34" t="n">
         <v>60940</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>18796</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>99.7%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>76.2%</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>16560</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>27.2%</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>44380</v>
       </c>
     </row>
@@ -2893,20 +3167,28 @@
       <c r="D35" t="n">
         <v>206260</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>103.1%</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>103.1%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>58972</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>28.6%</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>147288</v>
       </c>
     </row>
@@ -2927,20 +3209,28 @@
       <c r="D36" t="n">
         <v>67140</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>33.6%</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>33.6%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
         <v>10000</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>14.9%</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>57140</v>
       </c>
     </row>
@@ -2961,20 +3251,28 @@
       <c r="D37" t="n">
         <v>27400</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>11.0%</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>11.0%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>6600</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>24.1%</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>20800</v>
       </c>
     </row>
@@ -2995,20 +3293,28 @@
       <c r="D38" t="n">
         <v>140210</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>83.5%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>77.9%</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>38550</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>27.5%</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>101660</v>
       </c>
     </row>
@@ -3029,20 +3335,28 @@
       <c r="D39" t="n">
         <v>46400</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>46.4%</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46.4%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>41350</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>5050</v>
       </c>
     </row>
@@ -3063,20 +3377,28 @@
       <c r="D40" t="n">
         <v>79408</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>66.2%</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>66.2%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>17298</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>21.8%</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>62110</v>
       </c>
     </row>
@@ -3097,20 +3419,28 @@
       <c r="D41" t="n">
         <v>33380</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>39588</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.8%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>27.8%</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>33380</v>
       </c>
     </row>
@@ -3131,20 +3461,28 @@
       <c r="D42" t="n">
         <v>21998</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>49218</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>59.3%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>18.3%</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>21998</v>
       </c>
     </row>
@@ -3165,20 +3503,28 @@
       <c r="D43" t="n">
         <v>76920</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>16398</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>93.3%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>76.9%</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>4000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>72920</v>
       </c>
     </row>
@@ -3199,20 +3545,28 @@
       <c r="D44" t="n">
         <v>0</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>17200</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>-17200</v>
       </c>
     </row>
@@ -3233,20 +3587,28 @@
       <c r="D45" t="n">
         <v>86488</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>86.5%</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>86.5%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
         <v>20800</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>24.0%</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>65688</v>
       </c>
     </row>
@@ -3267,20 +3629,28 @@
       <c r="D46" t="n">
         <v>119200</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>30398</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>136.0%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>108.4%</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>35800</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>30.0%</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>83400</v>
       </c>
     </row>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -513,41 +513,41 @@
         <v>1000000</v>
       </c>
       <c r="D2" t="n">
-        <v>487672</v>
+        <v>657054</v>
       </c>
       <c r="E2" t="n">
-        <v>254414</v>
+        <v>254609</v>
       </c>
       <c r="F2" t="n">
-        <v>233257</v>
+        <v>402444</v>
       </c>
       <c r="G2" t="n">
         <v>12988</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>813145</v>
+        <v>826173</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>363705</v>
+        <v>376611</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -567,13 +567,13 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>18355</v>
+        <v>18393</v>
       </c>
       <c r="E3" t="n">
-        <v>40784</v>
+        <v>40813</v>
       </c>
       <c r="F3" t="n">
-        <v>-22428</v>
+        <v>-22419</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>73649</v>
+        <v>89154</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>22442</v>
+        <v>37919</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-159.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -621,41 +621,41 @@
         <v>800000</v>
       </c>
       <c r="D4" t="n">
-        <v>724463</v>
+        <v>792933</v>
       </c>
       <c r="E4" t="n">
-        <v>177175</v>
+        <v>181546</v>
       </c>
       <c r="F4" t="n">
-        <v>547288</v>
+        <v>611387</v>
       </c>
       <c r="G4" t="n">
         <v>46198</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>748026</v>
+        <v>771560</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>546583</v>
+        <v>567035</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>+7.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -675,41 +675,41 @@
         <v>650000</v>
       </c>
       <c r="D5" t="n">
-        <v>479649</v>
+        <v>483707</v>
       </c>
       <c r="E5" t="n">
-        <v>128206</v>
+        <v>128235</v>
       </c>
       <c r="F5" t="n">
-        <v>351443</v>
+        <v>355472</v>
       </c>
       <c r="G5" t="n">
         <v>158352</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>658376</v>
+        <v>662202</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>406452</v>
+        <v>410259</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -729,41 +729,41 @@
         <v>700000</v>
       </c>
       <c r="D6" t="n">
-        <v>437064</v>
+        <v>464745</v>
       </c>
       <c r="E6" t="n">
-        <v>110825</v>
+        <v>118534</v>
       </c>
       <c r="F6" t="n">
-        <v>326238</v>
+        <v>346211</v>
       </c>
       <c r="G6" t="n">
         <v>58198</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>442708</v>
+        <v>455738</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>398517</v>
+        <v>410507</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -783,41 +783,41 @@
         <v>550000</v>
       </c>
       <c r="D7" t="n">
-        <v>379528</v>
+        <v>436684</v>
       </c>
       <c r="E7" t="n">
-        <v>108907</v>
+        <v>109290</v>
       </c>
       <c r="F7" t="n">
-        <v>270621</v>
+        <v>327394</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>635064</v>
+        <v>635108</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>432951</v>
+        <v>432995</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -837,41 +837,41 @@
         <v>650000</v>
       </c>
       <c r="D8" t="n">
-        <v>403535</v>
+        <v>443340</v>
       </c>
       <c r="E8" t="n">
-        <v>82515</v>
+        <v>84564</v>
       </c>
       <c r="F8" t="n">
-        <v>321020</v>
+        <v>358776</v>
       </c>
       <c r="G8" t="n">
         <v>18796</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>563038</v>
+        <v>588895</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>386148</v>
+        <v>407466</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -891,41 +891,41 @@
         <v>1700000</v>
       </c>
       <c r="D9" t="n">
-        <v>944942</v>
+        <v>1319532</v>
       </c>
       <c r="E9" t="n">
-        <v>287797</v>
+        <v>354185</v>
       </c>
       <c r="F9" t="n">
-        <v>657145</v>
+        <v>965347</v>
       </c>
       <c r="G9" t="n">
         <v>145602</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1336852</v>
+        <v>1456252</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>919040</v>
+        <v>1038440</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -945,39 +945,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1866907</v>
+        <v>1974646</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1866907</v>
+        <v>1974646</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1448987</v>
+        <v>1515947</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+28.8%</t>
+          <t>+30.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1448987</v>
+        <v>1515947</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+28.8%</t>
+          <t>+30.3%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -997,43 +997,43 @@
         <v>450000</v>
       </c>
       <c r="D11" t="n">
-        <v>342546</v>
+        <v>447962</v>
       </c>
       <c r="E11" t="n">
-        <v>45927</v>
+        <v>76327</v>
       </c>
       <c r="F11" t="n">
-        <v>296619</v>
+        <v>371635</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>372000</v>
+        <v>463400</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>327124</v>
+        <v>418126</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>912</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="12">
@@ -1051,23 +1051,23 @@
         <v>450000</v>
       </c>
       <c r="D12" t="n">
-        <v>380226</v>
+        <v>382022</v>
       </c>
       <c r="E12" t="n">
         <v>2228</v>
       </c>
       <c r="F12" t="n">
-        <v>377998</v>
+        <v>379794</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+7.0%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+12.6%</t>
+          <t>+13.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1103,39 +1103,39 @@
         <v>850000</v>
       </c>
       <c r="D13" t="n">
-        <v>693613</v>
+        <v>701632</v>
       </c>
       <c r="E13" t="n">
-        <v>76809</v>
+        <v>76828</v>
       </c>
       <c r="F13" t="n">
-        <v>616804</v>
+        <v>624804</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>653248</v>
+        <v>676644</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>609305</v>
+        <v>632701</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1157,43 +1157,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>583358</v>
+        <v>779679</v>
       </c>
       <c r="E14" t="n">
-        <v>77178</v>
+        <v>100278</v>
       </c>
       <c r="F14" t="n">
-        <v>506180</v>
+        <v>679401</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>777998</v>
+        <v>788396</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>641276</v>
+        <v>651651</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>+4.3%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>62784</v>
+        <v>63088</v>
       </c>
     </row>
     <row r="15">
@@ -1211,39 +1211,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>212572</v>
+        <v>253829</v>
       </c>
       <c r="E15" t="n">
         <v>15325</v>
       </c>
       <c r="F15" t="n">
-        <v>197247</v>
+        <v>238504</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>220914</v>
+        <v>228592</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>+11.0%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>220828</v>
+        <v>228447</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1263,39 +1263,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>323898</v>
+        <v>364723</v>
       </c>
       <c r="E16" t="n">
         <v>53000</v>
       </c>
       <c r="F16" t="n">
-        <v>270898</v>
+        <v>311723</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>213288</v>
+        <v>225845</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+51.9%</t>
+          <t>+61.5%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>151405</v>
+        <v>163803</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+78.9%</t>
+          <t>+90.3%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1315,13 +1315,13 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>565057</v>
+        <v>565084</v>
       </c>
       <c r="E17" t="n">
         <v>96666</v>
       </c>
       <c r="F17" t="n">
-        <v>468391</v>
+        <v>468418</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1335,23 +1335,23 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>451793</v>
+        <v>452490</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+25.1%</t>
+          <t>+24.9%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>409278</v>
+        <v>409975</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>26239</v>
+        <v>26247</v>
       </c>
     </row>
     <row r="18">
@@ -1369,39 +1369,39 @@
         <v>800000</v>
       </c>
       <c r="D18" t="n">
-        <v>744770</v>
+        <v>867684</v>
       </c>
       <c r="E18" t="n">
-        <v>152824</v>
+        <v>156303</v>
       </c>
       <c r="F18" t="n">
-        <v>591946</v>
+        <v>711381</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>674751</v>
+        <v>693351</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+25.1%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>441689</v>
+        <v>451280</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+34.0%</t>
+          <t>+57.6%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1423,43 +1423,43 @@
         <v>850000</v>
       </c>
       <c r="D19" t="n">
-        <v>410851</v>
+        <v>420389</v>
       </c>
       <c r="E19" t="n">
-        <v>145546</v>
+        <v>185996</v>
       </c>
       <c r="F19" t="n">
-        <v>265305</v>
+        <v>234393</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>980298</v>
+        <v>1021002</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-58.1%</t>
+          <t>-58.8%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>829283</v>
+        <v>869981</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>13118</v>
+        <v>13458</v>
       </c>
     </row>
     <row r="20">
@@ -1477,39 +1477,39 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>717595</v>
+        <v>737671</v>
       </c>
       <c r="E20" t="n">
-        <v>95138</v>
+        <v>95157</v>
       </c>
       <c r="F20" t="n">
-        <v>622457</v>
+        <v>642514</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>105.4%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>105.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>815893</v>
+        <v>836689</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>745614</v>
+        <v>766410</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1562,16 +1562,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>278</v>
+        <v>429</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>788.5</v>
+        <v>1683.3</v>
       </c>
       <c r="E2" t="n">
-        <v>73271</v>
+        <v>211088</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1581,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>91</v>
+        <v>432.3</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>22053</v>
       </c>
     </row>
     <row r="4">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566</v>
+        <v>600</v>
       </c>
       <c r="C4" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D4" t="n">
-        <v>1478.8</v>
+        <v>1352.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3450</v>
+        <v>2283</v>
       </c>
     </row>
   </sheetData>
@@ -1779,19 +1779,19 @@
         <v>300000</v>
       </c>
       <c r="D2" t="n">
-        <v>189409.9</v>
+        <v>220309.9</v>
       </c>
       <c r="E2" t="n">
         <v>8000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1799,11 +1799,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>126311.9</v>
+        <v>157211.9</v>
       </c>
     </row>
     <row r="3">
@@ -1821,19 +1821,19 @@
         <v>200000</v>
       </c>
       <c r="D3" t="n">
-        <v>68680</v>
+        <v>119260</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1841,11 +1841,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>35494</v>
+        <v>86074</v>
       </c>
     </row>
     <row r="4">
@@ -1863,19 +1863,19 @@
         <v>200000</v>
       </c>
       <c r="D4" t="n">
-        <v>43780</v>
+        <v>48760</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>30433.34</v>
+        <v>35413.34</v>
       </c>
     </row>
     <row r="5">
@@ -1905,19 +1905,19 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>57300</v>
+        <v>71240</v>
       </c>
       <c r="E5" t="n">
         <v>4988</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1925,11 +1925,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3408</v>
+        <v>17348</v>
       </c>
     </row>
     <row r="6">
@@ -1947,19 +1947,19 @@
         <v>150000</v>
       </c>
       <c r="D6" t="n">
-        <v>82900</v>
+        <v>149660</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1967,11 +1967,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>53917</v>
+        <v>120677</v>
       </c>
     </row>
     <row r="7">
@@ -2115,31 +2115,31 @@
         <v>130000</v>
       </c>
       <c r="D10" t="n">
-        <v>219508</v>
+        <v>227468</v>
       </c>
       <c r="E10" t="n">
         <v>6000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>173.5%</t>
+          <t>179.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>168.9%</t>
+          <t>175.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13745</v>
+        <v>17894</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>205763</v>
+        <v>209574</v>
       </c>
     </row>
     <row r="11">
@@ -2157,19 +2157,19 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>39800</v>
+        <v>64700</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>39800</v>
+        <v>64700</v>
       </c>
     </row>
     <row r="12">
@@ -2199,19 +2199,19 @@
         <v>130000</v>
       </c>
       <c r="D12" t="n">
-        <v>94380</v>
+        <v>99360</v>
       </c>
       <c r="E12" t="n">
         <v>30198</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>90197</v>
+        <v>95177</v>
       </c>
     </row>
     <row r="13">
@@ -2241,19 +2241,19 @@
         <v>150000</v>
       </c>
       <c r="D13" t="n">
-        <v>68660</v>
+        <v>81600</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2261,11 +2261,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33900</v>
+        <v>46840</v>
       </c>
     </row>
     <row r="14">
@@ -2283,19 +2283,19 @@
         <v>160000</v>
       </c>
       <c r="D14" t="n">
-        <v>80920</v>
+        <v>93860</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2303,11 +2303,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>64210</v>
+        <v>77150</v>
       </c>
     </row>
     <row r="15">
@@ -2325,19 +2325,19 @@
         <v>130000</v>
       </c>
       <c r="D15" t="n">
-        <v>130200</v>
+        <v>135180</v>
       </c>
       <c r="E15" t="n">
         <v>10000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2345,11 +2345,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>67702</v>
+        <v>72682</v>
       </c>
     </row>
     <row r="16">
@@ -2409,19 +2409,19 @@
         <v>300000</v>
       </c>
       <c r="D17" t="n">
-        <v>263288.01</v>
+        <v>267088.01</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2429,11 +2429,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>246500.01</v>
+        <v>250300.01</v>
       </c>
     </row>
     <row r="18">
@@ -2493,19 +2493,19 @@
         <v>80000</v>
       </c>
       <c r="D19" t="n">
-        <v>91540</v>
+        <v>95520</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2513,11 +2513,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>83963.39999999999</v>
+        <v>87943.39999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2577,19 +2577,19 @@
         <v>80000</v>
       </c>
       <c r="D21" t="n">
-        <v>60428</v>
+        <v>68388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>85.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2597,11 +2597,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>33471.33</v>
+        <v>41431.33</v>
       </c>
     </row>
     <row r="22">
@@ -2619,31 +2619,31 @@
         <v>150000</v>
       </c>
       <c r="D22" t="n">
-        <v>68029.89999999999</v>
+        <v>72009.89999999999</v>
       </c>
       <c r="E22" t="n">
         <v>45600</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>16779</v>
+        <v>20929</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>51250.89999999999</v>
+        <v>51080.89999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2661,31 +2661,31 @@
         <v>70000</v>
       </c>
       <c r="D23" t="n">
-        <v>39608</v>
+        <v>43588</v>
       </c>
       <c r="E23" t="n">
         <v>12598</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4980</v>
+        <v>7761.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>34628</v>
+        <v>35826.8</v>
       </c>
     </row>
     <row r="24">
@@ -2745,19 +2745,19 @@
         <v>80000</v>
       </c>
       <c r="D25" t="n">
-        <v>70180</v>
+        <v>74160</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>70180</v>
+        <v>74160</v>
       </c>
     </row>
     <row r="26">
@@ -2871,19 +2871,19 @@
         <v>200000</v>
       </c>
       <c r="D28" t="n">
-        <v>113600</v>
+        <v>148440</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2891,11 +2891,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>83800</v>
+        <v>118640</v>
       </c>
     </row>
     <row r="29">
@@ -2913,19 +2913,19 @@
         <v>100000</v>
       </c>
       <c r="D29" t="n">
-        <v>68580</v>
+        <v>89382</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>38780</v>
+        <v>59582</v>
       </c>
     </row>
     <row r="30">
@@ -3039,31 +3039,31 @@
         <v>150000</v>
       </c>
       <c r="D32" t="n">
-        <v>78378</v>
+        <v>88338</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21580</v>
+        <v>23174</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>56798</v>
+        <v>65164</v>
       </c>
     </row>
     <row r="33">
@@ -3081,19 +3081,19 @@
         <v>170000</v>
       </c>
       <c r="D33" t="n">
-        <v>127340</v>
+        <v>147140</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>113140</v>
+        <v>132940</v>
       </c>
     </row>
     <row r="34">
@@ -3123,19 +3123,19 @@
         <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>60940</v>
+        <v>65920</v>
       </c>
       <c r="E34" t="n">
         <v>18796</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3143,11 +3143,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>44380</v>
+        <v>49360</v>
       </c>
     </row>
     <row r="35">
@@ -3165,19 +3165,19 @@
         <v>200000</v>
       </c>
       <c r="D35" t="n">
-        <v>206260</v>
+        <v>251860</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>147288</v>
+        <v>192888</v>
       </c>
     </row>
     <row r="36">
@@ -3207,31 +3207,31 @@
         <v>200000</v>
       </c>
       <c r="D36" t="n">
-        <v>67140</v>
+        <v>213920</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10000</v>
+        <v>46588</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>57140</v>
+        <v>167332</v>
       </c>
     </row>
     <row r="37">
@@ -3249,19 +3249,19 @@
         <v>250000</v>
       </c>
       <c r="D37" t="n">
-        <v>27400</v>
+        <v>103000</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3269,11 +3269,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>20800</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="38">
@@ -3291,19 +3291,19 @@
         <v>180000</v>
       </c>
       <c r="D38" t="n">
-        <v>140210</v>
+        <v>187310</v>
       </c>
       <c r="E38" t="n">
         <v>10000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3311,11 +3311,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>101660</v>
+        <v>148760</v>
       </c>
     </row>
     <row r="39">
@@ -3375,19 +3375,19 @@
         <v>120000</v>
       </c>
       <c r="D40" t="n">
-        <v>79408</v>
+        <v>106228</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -3395,11 +3395,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>62110</v>
+        <v>88930</v>
       </c>
     </row>
     <row r="41">
@@ -3459,19 +3459,19 @@
         <v>120000</v>
       </c>
       <c r="D42" t="n">
-        <v>21998</v>
+        <v>29998</v>
       </c>
       <c r="E42" t="n">
         <v>49218</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>21998</v>
+        <v>29998</v>
       </c>
     </row>
     <row r="43">
@@ -3501,19 +3501,19 @@
         <v>100000</v>
       </c>
       <c r="D43" t="n">
-        <v>76920</v>
+        <v>90120</v>
       </c>
       <c r="E43" t="n">
         <v>16398</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3521,11 +3521,11 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>72920</v>
+        <v>86120</v>
       </c>
     </row>
     <row r="44">
@@ -3585,31 +3585,31 @@
         <v>100000</v>
       </c>
       <c r="D45" t="n">
-        <v>86488</v>
+        <v>96488</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>20800</v>
+        <v>50600</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>65688</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="46">
@@ -3725,11 +3725,11 @@
         <v>134000</v>
       </c>
       <c r="D2" t="n">
-        <v>41449</v>
+        <v>53449</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>26231</v>
+        <v>38231</v>
       </c>
     </row>
     <row r="3">
@@ -3759,11 +3759,11 @@
         <v>100000</v>
       </c>
       <c r="D3" t="n">
-        <v>131280</v>
+        <v>143880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>131.3%</t>
+          <t>143.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>131280</v>
+        <v>143880</v>
       </c>
     </row>
     <row r="4">
@@ -3793,11 +3793,11 @@
         <v>24000</v>
       </c>
       <c r="D4" t="n">
-        <v>28868</v>
+        <v>46868</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>195.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>28868</v>
+        <v>46868</v>
       </c>
     </row>
     <row r="5">
@@ -3895,11 +3895,11 @@
         <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>64884.6</v>
+        <v>73224.69</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3907,11 +3907,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>64564.6</v>
+        <v>72904.69</v>
       </c>
     </row>
     <row r="8">
@@ -3937,15 +3937,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2700</v>
+        <v>18150</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>130500</v>
+        <v>115050</v>
       </c>
     </row>
     <row r="9">
@@ -3971,15 +3971,15 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>140400</v>
+        <v>142900</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>102.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1514.739999999991</v>
+        <v>-4014.739999999991</v>
       </c>
     </row>
     <row r="10">
@@ -3997,23 +3997,23 @@
         <v>60000</v>
       </c>
       <c r="D10" t="n">
-        <v>43300</v>
+        <v>44100</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>43300</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="11">
@@ -4065,11 +4065,11 @@
         <v>300000</v>
       </c>
       <c r="D12" t="n">
-        <v>259421.14</v>
+        <v>307177.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>259421.14</v>
+        <v>307177.14</v>
       </c>
     </row>
     <row r="13">
@@ -4133,11 +4133,11 @@
         <v>400000</v>
       </c>
       <c r="D14" t="n">
-        <v>437595.74</v>
+        <v>468749.74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>437595.74</v>
+        <v>468749.74</v>
       </c>
     </row>
     <row r="15">
@@ -4167,11 +4167,11 @@
         <v>250000</v>
       </c>
       <c r="D15" t="n">
-        <v>204409.74</v>
+        <v>206846.74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>204409.74</v>
+        <v>206846.74</v>
       </c>
     </row>
     <row r="16">
@@ -4201,11 +4201,11 @@
         <v>250000</v>
       </c>
       <c r="D16" t="n">
-        <v>184905</v>
+        <v>190303</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>184905</v>
+        <v>190303</v>
       </c>
     </row>
     <row r="17">
@@ -4303,11 +4303,11 @@
         <v>200000</v>
       </c>
       <c r="D19" t="n">
-        <v>126871</v>
+        <v>127871</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>126871</v>
+        <v>127871</v>
       </c>
     </row>
     <row r="20">
@@ -4337,11 +4337,11 @@
         <v>50000</v>
       </c>
       <c r="D20" t="n">
-        <v>25198</v>
+        <v>33596</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>25198</v>
+        <v>33596</v>
       </c>
     </row>
     <row r="21">
@@ -4371,11 +4371,11 @@
         <v>100000</v>
       </c>
       <c r="D21" t="n">
-        <v>80774</v>
+        <v>91172</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>80774</v>
+        <v>91172</v>
       </c>
     </row>
     <row r="22">
@@ -4405,11 +4405,11 @@
         <v>100000</v>
       </c>
       <c r="D22" t="n">
-        <v>47074</v>
+        <v>57074</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4417,11 +4417,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34629.52</v>
+        <v>44629.52</v>
       </c>
     </row>
     <row r="23">
@@ -4439,11 +4439,11 @@
         <v>280000</v>
       </c>
       <c r="D23" t="n">
-        <v>318564</v>
+        <v>397384</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>141.9%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4451,11 +4451,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>226176</v>
+        <v>304996</v>
       </c>
     </row>
     <row r="24">
@@ -4473,11 +4473,11 @@
         <v>120000</v>
       </c>
       <c r="D24" t="n">
-        <v>65386.01</v>
+        <v>87986.00999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>58388.01</v>
+        <v>80988.00999999999</v>
       </c>
     </row>
     <row r="25">
@@ -4507,11 +4507,11 @@
         <v>73000</v>
       </c>
       <c r="D25" t="n">
-        <v>166153.01</v>
+        <v>166949.01</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>227.6%</t>
+          <t>228.7%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4519,11 +4519,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>143753.01</v>
+        <v>144549.01</v>
       </c>
     </row>
     <row r="26">
@@ -4575,11 +4575,11 @@
         <v>100000</v>
       </c>
       <c r="D27" t="n">
-        <v>133544</v>
+        <v>143942</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>143.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4587,11 +4587,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>125544</v>
+        <v>135942</v>
       </c>
     </row>
     <row r="28">
@@ -4711,11 +4711,11 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>90364.2</v>
+        <v>98364.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4723,11 +4723,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>85866.2</v>
+        <v>93866.2</v>
       </c>
     </row>
     <row r="32">
@@ -4813,11 +4813,11 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>148184</v>
+        <v>148582</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>147954</v>
+        <v>148352</v>
       </c>
     </row>
     <row r="35">
@@ -4847,11 +4847,11 @@
         <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>28988</v>
+        <v>29386</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>28988</v>
+        <v>29386</v>
       </c>
     </row>
     <row r="36">
@@ -4949,11 +4949,11 @@
         <v>40000</v>
       </c>
       <c r="D38" t="n">
-        <v>48192</v>
+        <v>49192</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>120.5%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>48192</v>
+        <v>49192</v>
       </c>
     </row>
     <row r="39">
@@ -5085,11 +5085,11 @@
         <v>200000</v>
       </c>
       <c r="D42" t="n">
-        <v>21796</v>
+        <v>31796</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5097,11 +5097,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>115.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>-3404</v>
+        <v>6596</v>
       </c>
     </row>
     <row r="43">
@@ -5153,11 +5153,11 @@
         <v>150000</v>
       </c>
       <c r="D44" t="n">
-        <v>230844</v>
+        <v>240844</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>153.9%</t>
+          <t>160.6%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>230844</v>
+        <v>240844</v>
       </c>
     </row>
     <row r="45">
@@ -5425,23 +5425,23 @@
         <v>120000</v>
       </c>
       <c r="D52" t="n">
-        <v>113682</v>
+        <v>123182</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>28800</v>
+        <v>34400</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>84882</v>
+        <v>88782</v>
       </c>
     </row>
     <row r="53">
@@ -5459,23 +5459,23 @@
         <v>210000</v>
       </c>
       <c r="D53" t="n">
-        <v>134464</v>
+        <v>170862</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>16800</v>
+        <v>41600</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>117664</v>
+        <v>129262</v>
       </c>
     </row>
     <row r="54">
@@ -5493,11 +5493,11 @@
         <v>107400</v>
       </c>
       <c r="D54" t="n">
-        <v>69592</v>
+        <v>107592</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>69592</v>
+        <v>107592</v>
       </c>
     </row>
     <row r="55">
@@ -5527,11 +5527,11 @@
         <v>48000</v>
       </c>
       <c r="D55" t="n">
-        <v>13796</v>
+        <v>34796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13796</v>
+        <v>34796</v>
       </c>
     </row>
     <row r="56">
@@ -5595,11 +5595,11 @@
         <v>120000</v>
       </c>
       <c r="D57" t="n">
-        <v>70284</v>
+        <v>78682</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5607,11 +5607,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>62284</v>
+        <v>70682</v>
       </c>
     </row>
     <row r="58">
@@ -5629,11 +5629,11 @@
         <v>120000</v>
       </c>
       <c r="D58" t="n">
-        <v>89972</v>
+        <v>106370</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5641,11 +5641,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>55172</v>
+        <v>71570</v>
       </c>
     </row>
     <row r="59">
@@ -5663,11 +5663,11 @@
         <v>120000</v>
       </c>
       <c r="D59" t="n">
-        <v>134962</v>
+        <v>150962</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5675,11 +5675,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>124762</v>
+        <v>140762</v>
       </c>
     </row>
     <row r="60">
@@ -5731,11 +5731,11 @@
         <v>334800</v>
       </c>
       <c r="D61" t="n">
-        <v>316931.5</v>
+        <v>388931.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5743,11 +5743,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>296931.5</v>
+        <v>368931.5</v>
       </c>
     </row>
     <row r="62">
@@ -5765,23 +5765,23 @@
         <v>204401</v>
       </c>
       <c r="D62" t="n">
-        <v>66169.62</v>
+        <v>166073.12</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15212</v>
+        <v>25212</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>50957.62</v>
+        <v>140861.12</v>
       </c>
     </row>
     <row r="63">
@@ -5799,11 +5799,11 @@
         <v>259200</v>
       </c>
       <c r="D63" t="n">
-        <v>181673.48</v>
+        <v>206071.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5811,11 +5811,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>144673.48</v>
+        <v>169071.48</v>
       </c>
     </row>
     <row r="64">
@@ -5944,16 +5944,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2219355.07</v>
+        <v>2407996.07</v>
       </c>
       <c r="D2" t="n">
-        <v>7507</v>
+        <v>7879</v>
       </c>
       <c r="E2" t="n">
-        <v>1941489.07</v>
+        <v>2124393.07</v>
       </c>
       <c r="F2" t="n">
-        <v>277866</v>
+        <v>283603</v>
       </c>
     </row>
     <row r="3">
@@ -5968,16 +5968,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2006294</v>
+        <v>2185131</v>
       </c>
       <c r="D3" t="n">
-        <v>512</v>
+        <v>555</v>
       </c>
       <c r="E3" t="n">
-        <v>1734985</v>
+        <v>1908902</v>
       </c>
       <c r="F3" t="n">
-        <v>271309</v>
+        <v>276229</v>
       </c>
     </row>
     <row r="4">
@@ -5992,16 +5992,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>213061.07</v>
+        <v>222865.07</v>
       </c>
       <c r="D4" t="n">
-        <v>6995</v>
+        <v>7324</v>
       </c>
       <c r="E4" t="n">
-        <v>206504.07</v>
+        <v>215491.07</v>
       </c>
       <c r="F4" t="n">
-        <v>6557</v>
+        <v>7374</v>
       </c>
     </row>
     <row r="5">
@@ -6016,16 +6016,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4597291.82</v>
+        <v>5246931.82</v>
       </c>
       <c r="D5" t="n">
-        <v>911</v>
+        <v>980</v>
       </c>
       <c r="E5" t="n">
-        <v>824343.8</v>
+        <v>1001783.8</v>
       </c>
       <c r="F5" t="n">
-        <v>3772948.02</v>
+        <v>4245148.02</v>
       </c>
     </row>
     <row r="6">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3347011.02</v>
+        <v>3687601.02</v>
       </c>
       <c r="D6" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="E6" t="n">
         <v>116440</v>
       </c>
       <c r="F6" t="n">
-        <v>3230571.02</v>
+        <v>3571161.02</v>
       </c>
     </row>
     <row r="7">
@@ -6064,16 +6064,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1230280.8</v>
+        <v>1559330.8</v>
       </c>
       <c r="D7" t="n">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="E7" t="n">
-        <v>707903.8</v>
+        <v>885343.8</v>
       </c>
       <c r="F7" t="n">
-        <v>522377</v>
+        <v>673987</v>
       </c>
     </row>
     <row r="8">
@@ -6088,16 +6088,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3550221.13</v>
+        <v>3342840.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2809</v>
+        <v>2048</v>
       </c>
       <c r="E8" t="n">
-        <v>39399.56</v>
+        <v>41843.55</v>
       </c>
       <c r="F8" t="n">
-        <v>3510821.57</v>
+        <v>3300996.65</v>
       </c>
     </row>
     <row r="9">
@@ -6112,16 +6112,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2103137.8</v>
+        <v>2073024.51</v>
       </c>
       <c r="D9" t="n">
-        <v>1468</v>
+        <v>1127</v>
       </c>
       <c r="E9" t="n">
-        <v>14302.18</v>
+        <v>15445.18</v>
       </c>
       <c r="F9" t="n">
-        <v>2088835.62</v>
+        <v>2057579.33</v>
       </c>
     </row>
     <row r="10">
@@ -6136,16 +6136,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1443583.33</v>
+        <v>1269815.69</v>
       </c>
       <c r="D10" t="n">
-        <v>1339</v>
+        <v>921</v>
       </c>
       <c r="E10" t="n">
-        <v>25097.38</v>
+        <v>26398.37</v>
       </c>
       <c r="F10" t="n">
-        <v>1418485.95</v>
+        <v>1243417.32</v>
       </c>
     </row>
     <row r="11">
@@ -6160,16 +6160,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>723000</v>
+        <v>1139722</v>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>345200</v>
+        <v>716322</v>
       </c>
       <c r="F11" t="n">
-        <v>377800</v>
+        <v>423400</v>
       </c>
     </row>
     <row r="12">
@@ -6184,16 +6184,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>655209.8100000001</v>
+        <v>659109.8100000001</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" t="n">
-        <v>449284.81</v>
+        <v>453084.81</v>
       </c>
       <c r="F12" t="n">
-        <v>205925</v>
+        <v>206025</v>
       </c>
     </row>
     <row r="13">
@@ -6232,13 +6232,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75240</v>
+        <v>77220</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>53460</v>
+        <v>55440</v>
       </c>
       <c r="F14" t="n">
         <v>21780</v>
@@ -6302,22 +6302,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2219355.07</v>
+        <v>2407996.07</v>
       </c>
       <c r="C2" t="n">
-        <v>342247.91</v>
+        <v>357349.91</v>
       </c>
       <c r="D2" t="n">
-        <v>50990.01</v>
+        <v>52625.01</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="F2" t="n">
-        <v>291257.9</v>
+        <v>304724.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.12</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="3">
@@ -6327,22 +6327,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4597291.82</v>
+        <v>5246931.82</v>
       </c>
       <c r="C3" t="n">
-        <v>633994.28</v>
+        <v>709042.28</v>
       </c>
       <c r="D3" t="n">
-        <v>35498</v>
+        <v>39796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="F3" t="n">
-        <v>598496.28</v>
+        <v>669246.28</v>
       </c>
       <c r="G3" t="n">
-        <v>13.02</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="4">
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3550221.13</v>
+        <v>3342840.2</v>
       </c>
       <c r="C4" t="n">
-        <v>1253730.54</v>
+        <v>1275939.07</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
@@ -6364,10 +6364,10 @@
         <v>0.06</v>
       </c>
       <c r="F4" t="n">
-        <v>1251701.54</v>
+        <v>1273910.07</v>
       </c>
       <c r="G4" t="n">
-        <v>35.26</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="5">
@@ -6377,22 +6377,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>723000</v>
+        <v>1139722</v>
       </c>
       <c r="C5" t="n">
-        <v>377800</v>
+        <v>427400</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>24800</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="F5" t="n">
-        <v>377800</v>
+        <v>402600</v>
       </c>
       <c r="G5" t="n">
-        <v>52.25</v>
+        <v>35.32</v>
       </c>
     </row>
     <row r="6">
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>655209.8100000001</v>
+        <v>659109.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>190361.07</v>
+        <v>180430.27</v>
       </c>
       <c r="D6" t="n">
         <v>2817.9</v>
@@ -6414,10 +6414,10 @@
         <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>187543.17</v>
+        <v>177612.37</v>
       </c>
       <c r="G6" t="n">
-        <v>28.62</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="7">
@@ -6430,7 +6430,7 @@
         <v>342234</v>
       </c>
       <c r="C7" t="n">
-        <v>497480</v>
+        <v>529780</v>
       </c>
       <c r="D7" t="n">
         <v>49800</v>
@@ -6439,10 +6439,10 @@
         <v>14.55</v>
       </c>
       <c r="F7" t="n">
-        <v>447680</v>
+        <v>479980</v>
       </c>
       <c r="G7" t="n">
-        <v>130.81</v>
+        <v>140.25</v>
       </c>
     </row>
     <row r="8">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>75240</v>
+        <v>77220</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="C2" t="n">
-        <v>1075787.51</v>
+        <v>1202313.51</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -6529,13 +6529,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>407733</v>
+        <v>440471</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="C4" t="n">
-        <v>210300.37</v>
+        <v>219698.57</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -6561,13 +6561,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>97492.48</v>
+        <v>106692.48</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C6" t="n">
-        <v>96598.67</v>
+        <v>96798.67</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
@@ -6609,10 +6609,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>14727.8</v>
+        <v>14809.8</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>1678</v>
+        <v>2124</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>187220</v>
+        <v>249820</v>
       </c>
     </row>
     <row r="3">
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>68598</v>
+        <v>72386</v>
       </c>
     </row>
     <row r="4">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
-        <v>112798.01</v>
+        <v>112841.01</v>
       </c>
     </row>
     <row r="8">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D9" t="n">
-        <v>45223.66</v>
+        <v>45299.66</v>
       </c>
     </row>
     <row r="10">
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>16791</v>
+        <v>16829</v>
       </c>
     </row>
     <row r="11">
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>1771</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="14">
@@ -7007,91 +7007,91 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>83883</v>
+        <v>183550</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>39392.9</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>28878.9</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>11681</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>8596</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -7102,14 +7102,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>4221</v>
+        <v>83883</v>
       </c>
     </row>
     <row r="23">
@@ -7120,14 +7120,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="D23" t="n">
-        <v>454</v>
+        <v>43678.9</v>
       </c>
     </row>
     <row r="24">
@@ -7138,14 +7138,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>28906.9</v>
       </c>
     </row>
     <row r="25">
@@ -7156,14 +7156,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>11738</v>
       </c>
     </row>
     <row r="26">
@@ -7174,176 +7174,176 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>8596</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>128286</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>20444.48</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>4038</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>未填写原因</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>143100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>2000</v>
+        <v>131746</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>20444.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>38</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" t="n">
-        <v>39399</v>
+        <v>39428</v>
       </c>
     </row>
     <row r="38">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D41" t="n">
-        <v>44220.6</v>
+        <v>44282.6</v>
       </c>
     </row>
     <row r="42">
@@ -7466,10 +7466,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D42" t="n">
-        <v>25468.81</v>
+        <v>28806.01</v>
       </c>
     </row>
     <row r="43">
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>23800</v>
+        <v>27950</v>
       </c>
     </row>
     <row r="44">
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D45" t="n">
-        <v>4050.67</v>
+        <v>4117.67</v>
       </c>
     </row>
     <row r="46">
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D47" t="n">
-        <v>1309.9</v>
+        <v>1353.9</v>
       </c>
     </row>
     <row r="48">
@@ -7592,10 +7592,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D49" t="n">
-        <v>295</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50">
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D53" t="n">
-        <v>33914</v>
+        <v>34259</v>
       </c>
     </row>
     <row r="54">
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D54" t="n">
-        <v>14662</v>
+        <v>14681</v>
       </c>
     </row>
     <row r="55">
@@ -7714,14 +7714,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57">
@@ -7732,14 +7732,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58">
@@ -7781,7 +7781,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7790,52 +7790,52 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>62800</v>
+        <v>68119</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>15200</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>11119</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7847,13 +7847,13 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>6000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7862,34 +7862,34 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>31664</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7898,82 +7898,82 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D66" t="n">
-        <v>30875</v>
+        <v>62800</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>9163.33</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>6619</v>
+        <v>11138</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>2489</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1303</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -7984,14 +7984,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D71" t="n">
-        <v>383</v>
+        <v>33277</v>
       </c>
     </row>
     <row r="72">
@@ -8002,338 +8002,338 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>30913</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>43067</v>
+        <v>9163.33</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>20000</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>16800</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D76" t="n">
-        <v>299</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>62837</v>
+        <v>781</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>13598</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
-        <v>200</v>
+        <v>43067</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>115</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>59</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>48619</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D83" t="n">
-        <v>14000</v>
+        <v>62837</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>10000</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>24800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>18000</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>10200</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="91">
@@ -8344,14 +8344,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>41600</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="92">
@@ -8362,68 +8362,68 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>4009</v>
+        <v>318</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>318</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>16960</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>14514</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="96">
@@ -8434,14 +8434,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>9187</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="97">
@@ -8452,14 +8452,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D97" t="n">
-        <v>66</v>
+        <v>14514</v>
       </c>
     </row>
     <row r="98">
@@ -8470,14 +8470,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D98" t="n">
-        <v>19</v>
+        <v>9187</v>
       </c>
     </row>
     <row r="99">
@@ -8488,14 +8488,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100">
@@ -8506,74 +8506,74 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>15218</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8585,13 +8585,13 @@
         <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>7019</v>
+        <v>15218</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8600,16 +8600,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8621,13 +8621,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>19.9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8639,24 +8639,78 @@
         <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>1910</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>成都</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>主动放弃/拍错</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="C111" t="n">
         <v>2</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D111" t="n">
         <v>318</v>
       </c>
     </row>
@@ -8698,10 +8752,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C2" t="n">
-        <v>410030.48</v>
+        <v>470930.48</v>
       </c>
     </row>
     <row r="3">
@@ -8711,10 +8765,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>286600</v>
+        <v>336200</v>
       </c>
     </row>
     <row r="4">
@@ -8724,62 +8778,62 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>255600</v>
+        <v>285400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>207120</v>
+        <v>210505.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>197152.99</v>
+        <v>209620</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>165072</v>
+        <v>175776</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>161628</v>
+        <v>165072</v>
       </c>
     </row>
     <row r="9">
@@ -8855,27 +8909,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>275</v>
+        <v>160</v>
       </c>
       <c r="C2" t="n">
-        <v>280113.5</v>
+        <v>307698</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>293</v>
       </c>
       <c r="C3" t="n">
-        <v>278381</v>
+        <v>304004.5</v>
       </c>
     </row>
     <row r="4">
@@ -8885,10 +8939,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C4" t="n">
-        <v>203387.48</v>
+        <v>203450.48</v>
       </c>
     </row>
     <row r="5">
@@ -8898,75 +8952,75 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>193733</v>
+        <v>193771</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>135029</v>
+        <v>147897.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>119497.81</v>
+        <v>143029</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>73716</v>
+        <v>94190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>64390</v>
+        <v>90560</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="C10" t="n">
-        <v>57976</v>
+        <v>68428.99000000001</v>
       </c>
     </row>
     <row r="11">
@@ -8976,62 +9030,62 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C11" t="n">
-        <v>53523.01</v>
+        <v>59199.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>48678.9</v>
+        <v>58005</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>44031</v>
+        <v>48678.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>43293</v>
+        <v>44031</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C15" t="n">
-        <v>42734.99</v>
+        <v>43331</v>
       </c>
     </row>
     <row r="16">
@@ -9041,10 +9095,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>40696</v>
+        <v>40734</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -6016,16 +6016,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5246931.82</v>
+        <v>5266931.82</v>
       </c>
       <c r="D5" t="n">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E5" t="n">
         <v>1001783.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4245148.02</v>
+        <v>4265148.02</v>
       </c>
     </row>
     <row r="6">
@@ -6088,16 +6088,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3342840.2</v>
+        <v>3715549.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2048</v>
+        <v>2961</v>
       </c>
       <c r="E8" t="n">
         <v>41843.55</v>
       </c>
       <c r="F8" t="n">
-        <v>3300996.65</v>
+        <v>3673706.05</v>
       </c>
     </row>
     <row r="9">
@@ -6112,16 +6112,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2073024.51</v>
+        <v>2200361.19</v>
       </c>
       <c r="D9" t="n">
-        <v>1127</v>
+        <v>1536</v>
       </c>
       <c r="E9" t="n">
         <v>15445.18</v>
       </c>
       <c r="F9" t="n">
-        <v>2057579.33</v>
+        <v>2184916.01</v>
       </c>
     </row>
     <row r="10">
@@ -6136,16 +6136,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1269815.69</v>
+        <v>1511688.41</v>
       </c>
       <c r="D10" t="n">
-        <v>921</v>
+        <v>1423</v>
       </c>
       <c r="E10" t="n">
         <v>26398.37</v>
       </c>
       <c r="F10" t="n">
-        <v>1243417.32</v>
+        <v>1485290.04</v>
       </c>
     </row>
     <row r="11">
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5246931.82</v>
+        <v>5266931.82</v>
       </c>
       <c r="C3" t="n">
         <v>709042.28</v>
@@ -6342,7 +6342,7 @@
         <v>669246.28</v>
       </c>
       <c r="G3" t="n">
-        <v>12.76</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="4">
@@ -6352,22 +6352,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3342840.2</v>
+        <v>3715549.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1275939.07</v>
+        <v>1305783.04</v>
       </c>
       <c r="D4" t="n">
         <v>2029</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
-        <v>1273910.07</v>
+        <v>1303754.04</v>
       </c>
       <c r="G4" t="n">
-        <v>38.11</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="5">
@@ -6405,7 +6405,7 @@
         <v>659109.8100000001</v>
       </c>
       <c r="C6" t="n">
-        <v>180430.27</v>
+        <v>196930.27</v>
       </c>
       <c r="D6" t="n">
         <v>2817.9</v>
@@ -6414,10 +6414,10 @@
         <v>0.43</v>
       </c>
       <c r="F6" t="n">
-        <v>177612.37</v>
+        <v>194112.37</v>
       </c>
       <c r="G6" t="n">
-        <v>26.95</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="7">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -17,7 +17,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款服务类型" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款省份" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电话" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协同" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +496,21 @@
           <t>康博嘉(元)</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>新客净流水(元)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>老客净流水(元)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>非1V1及菌群净(元)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,47 +524,50 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1000000</v>
+        <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>657054</v>
+        <v>70600</v>
       </c>
       <c r="E2" t="n">
-        <v>254609</v>
+        <v>8524</v>
       </c>
       <c r="F2" t="n">
-        <v>402444</v>
+        <v>62076</v>
       </c>
       <c r="G2" t="n">
-        <v>12988</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>826173</v>
+        <v>30679</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>+130.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>376611</v>
+        <v>20896</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+6.9%</t>
+          <t>+197.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,47 +581,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>18393</v>
+        <v>1856</v>
       </c>
       <c r="E3" t="n">
-        <v>40813</v>
+        <v>2560</v>
       </c>
       <c r="F3" t="n">
-        <v>-22419</v>
+        <v>-704</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>18.4%</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>89154</v>
+        <v>1279</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>+45.1%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>37919</v>
+        <v>-6622</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-89.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -618,47 +634,50 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>800000</v>
+        <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>792933</v>
+        <v>61409</v>
       </c>
       <c r="E4" t="n">
-        <v>181546</v>
+        <v>37613</v>
       </c>
       <c r="F4" t="n">
-        <v>611387</v>
+        <v>23796</v>
       </c>
       <c r="G4" t="n">
-        <v>46198</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>771560</v>
+        <v>38057</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+61.4%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>567035</v>
+        <v>19285</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+7.8%</t>
+          <t>+23.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -672,47 +691,50 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>650000</v>
+        <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>483707</v>
+        <v>12292</v>
       </c>
       <c r="E5" t="n">
-        <v>128235</v>
+        <v>67219</v>
       </c>
       <c r="F5" t="n">
-        <v>355472</v>
+        <v>-54927</v>
       </c>
       <c r="G5" t="n">
-        <v>158352</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>662202</v>
+        <v>15343</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>410259</v>
+        <v>-53797</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>+2.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -726,47 +748,50 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>700000</v>
+        <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>464745</v>
+        <v>69704</v>
       </c>
       <c r="E6" t="n">
-        <v>118534</v>
+        <v>2453</v>
       </c>
       <c r="F6" t="n">
-        <v>346211</v>
+        <v>67251</v>
       </c>
       <c r="G6" t="n">
-        <v>58198</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>455738</v>
+        <v>74145</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>410507</v>
+        <v>62577</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>+7.5%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -780,47 +805,50 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>550000</v>
+        <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>436684</v>
+        <v>52078</v>
       </c>
       <c r="E7" t="n">
-        <v>109290</v>
+        <v>11386</v>
       </c>
       <c r="F7" t="n">
-        <v>327394</v>
+        <v>40692</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>635108</v>
+        <v>47184</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>+10.4%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>432995</v>
+        <v>39804</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -834,47 +862,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>650000</v>
+        <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>443340</v>
+        <v>25603</v>
       </c>
       <c r="E8" t="n">
-        <v>84564</v>
+        <v>11193</v>
       </c>
       <c r="F8" t="n">
-        <v>358776</v>
+        <v>14410</v>
       </c>
       <c r="G8" t="n">
-        <v>18796</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>588895</v>
+        <v>35887</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>407466</v>
+        <v>29387</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -888,47 +919,50 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1700000</v>
+        <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>1319532</v>
+        <v>112716</v>
       </c>
       <c r="E9" t="n">
-        <v>354185</v>
+        <v>73800</v>
       </c>
       <c r="F9" t="n">
-        <v>965347</v>
+        <v>38916</v>
       </c>
       <c r="G9" t="n">
-        <v>145602</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1456252</v>
+        <v>86240</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>+30.7%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1038440</v>
+        <v>51440</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -945,42 +979,51 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1974646</v>
+        <v>138054</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1974646</v>
+        <v>138054</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1515947</v>
+        <v>139700</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+30.3%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1515947</v>
+        <v>139700</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+30.3%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>9692</v>
+      </c>
+      <c r="P10" t="n">
+        <v>128362</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>137656</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -994,46 +1037,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>450000</v>
+        <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>447962</v>
+        <v>8203</v>
       </c>
       <c r="E11" t="n">
-        <v>76327</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>371635</v>
+        <v>8203</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>463400</v>
+        <v>30026</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>418126</v>
+        <v>30026</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1112</v>
+        <v>210</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5795</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2198</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7009</v>
       </c>
     </row>
     <row r="12">
@@ -1048,45 +1100,54 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>450000</v>
+        <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>382022</v>
+        <v>41531</v>
       </c>
       <c r="E12" t="n">
-        <v>2228</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>379794</v>
+        <v>41531</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>355294</v>
+        <v>42706</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>335675</v>
+        <v>42407</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>30735</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10796</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>337</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1100,46 +1161,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>850000</v>
+        <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>701632</v>
+        <v>63793</v>
       </c>
       <c r="E13" t="n">
-        <v>76828</v>
+        <v>67</v>
       </c>
       <c r="F13" t="n">
-        <v>624804</v>
+        <v>63726</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>676644</v>
+        <v>103167</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>632701</v>
+        <v>103108</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>22983</v>
+        <v>1677</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1053</v>
+      </c>
+      <c r="P13" t="n">
+        <v>60996</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2532</v>
       </c>
     </row>
     <row r="14">
@@ -1157,43 +1227,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>779679</v>
+        <v>10991</v>
       </c>
       <c r="E14" t="n">
-        <v>100278</v>
+        <v>5000</v>
       </c>
       <c r="F14" t="n">
-        <v>679401</v>
+        <v>5991</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>788396</v>
+        <v>41850</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>651651</v>
+        <v>41684</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-85.6%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>63088</v>
+        <v>546</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1491</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6936</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8495</v>
       </c>
     </row>
     <row r="15">
@@ -1211,42 +1290,51 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>253829</v>
+        <v>37415</v>
       </c>
       <c r="E15" t="n">
-        <v>15325</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>238504</v>
+        <v>37396</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>228592</v>
+        <v>46396</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>228447</v>
+        <v>46396</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+4.4%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>19</v>
+      </c>
+      <c r="P15" t="n">
+        <v>37377</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>27396</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1263,42 +1351,51 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>364723</v>
+        <v>20627</v>
       </c>
       <c r="E16" t="n">
-        <v>53000</v>
+        <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>311723</v>
+        <v>20229</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>225845</v>
+        <v>3301</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+61.5%</t>
+          <t>+524.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>163803</v>
+        <v>3301</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+90.3%</t>
+          <t>+512.8%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>229</v>
+      </c>
+      <c r="P16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1315,43 +1412,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>565084</v>
+        <v>76394</v>
       </c>
       <c r="E17" t="n">
-        <v>96666</v>
+        <v>4248</v>
       </c>
       <c r="F17" t="n">
-        <v>468418</v>
+        <v>72146</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>452490</v>
+        <v>54198</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+24.9%</t>
+          <t>+41.0%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>409975</v>
+        <v>47499</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+51.9%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>26247</v>
+        <v>562</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1186</v>
+      </c>
+      <c r="P17" t="n">
+        <v>70398</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="18">
@@ -1366,46 +1472,53 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>800000</v>
+        <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>867684</v>
+        <v>110819</v>
       </c>
       <c r="E18" t="n">
-        <v>156303</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>711381</v>
+        <v>110819</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>693351</v>
+        <v>62607</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+25.1%</t>
+          <t>+77.0%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>451280</v>
+        <v>62551</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+57.6%</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>21500</v>
+          <t>+77.2%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>62021</v>
+      </c>
+      <c r="P18" t="n">
+        <v>48798</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>69407</v>
       </c>
     </row>
     <row r="19">
@@ -1420,46 +1533,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>850000</v>
+        <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>420389</v>
+        <v>20819</v>
       </c>
       <c r="E19" t="n">
-        <v>185996</v>
+        <v>200</v>
       </c>
       <c r="F19" t="n">
-        <v>234393</v>
+        <v>20619</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1021002</v>
+        <v>65029</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-58.8%</t>
+          <t>-68.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>869981</v>
+        <v>-80949</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-125.5%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>13458</v>
+        <v>200</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7519</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13100</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1477,42 +1599,51 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>737671</v>
+        <v>70714</v>
       </c>
       <c r="E20" t="n">
-        <v>95157</v>
+        <v>21162</v>
       </c>
       <c r="F20" t="n">
-        <v>642514</v>
+        <v>49552</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>105.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>105.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>836689</v>
+        <v>81369</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>766410</v>
+        <v>79569</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>4956</v>
+      </c>
+      <c r="P20" t="n">
+        <v>44596</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14166</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1562,16 +1693,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>429</v>
+        <v>221</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>1683.3</v>
+        <v>947.7</v>
       </c>
       <c r="E2" t="n">
-        <v>211088</v>
+        <v>86552</v>
       </c>
     </row>
     <row r="3">
@@ -1581,16 +1712,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>432.3</v>
+        <v>332.3</v>
       </c>
       <c r="E3" t="n">
-        <v>22053</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="4">
@@ -1600,102 +1731,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="D4" t="n">
-        <v>1352.3</v>
+        <v>1401.4</v>
       </c>
       <c r="E4" t="n">
-        <v>2283</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>协同金额(元)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>145602</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>46198</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>18796</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>12988</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58198</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>158352</v>
+        <v>4389</v>
       </c>
     </row>
   </sheetData>
@@ -1709,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1776,34 +1821,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>220309.9</v>
+        <v>29780</v>
       </c>
       <c r="E2" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>63098</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>157211.9</v>
+        <v>29780</v>
       </c>
     </row>
     <row r="3">
@@ -1814,38 +1859,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200000</v>
+        <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>119260</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>33186</v>
+        <v>2589</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>86074</v>
+        <v>-2589</v>
       </c>
     </row>
     <row r="4">
@@ -1856,38 +1901,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>48760</v>
+        <v>9960</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13346.66</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>35413.34</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="5">
@@ -1898,38 +1943,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>71240</v>
+        <v>19920</v>
       </c>
       <c r="E5" t="n">
-        <v>4988</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>53892</v>
+        <v>3700</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17348</v>
+        <v>16220</v>
       </c>
     </row>
     <row r="6">
@@ -1940,240 +1985,240 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>149660</v>
+        <v>4980</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>28983</v>
+        <v>1680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>120677</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>刘学锟</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30000</v>
+        <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>7960</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>李洋洋</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40000</v>
+        <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>31800</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>25775</v>
+        <v>6600</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6025</v>
+        <v>-6600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>张露</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-13720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>肖伟</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>130000</v>
+        <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>227468</v>
+        <v>16560</v>
       </c>
       <c r="E10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>179.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>175.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17894</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>209574</v>
+        <v>16560</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>64700</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -2181,293 +2226,293 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>64700</v>
+        <v>-3980</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>130000</v>
+        <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>99360</v>
+        <v>10000</v>
       </c>
       <c r="E12" t="n">
-        <v>30198</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4183</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>95177</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>江敏</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>81600</v>
+        <v>1980</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>34760</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>46840</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>160000</v>
+        <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>93860</v>
+        <v>30000</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16710</v>
+        <v>6600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>77150</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>郑美琦</t>
+          <t>李天阳</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>130000</v>
+        <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>135180</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62498</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>72682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>梁志超</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>300000</v>
+        <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>187708</v>
+        <v>24800</v>
       </c>
       <c r="E16" t="n">
-        <v>158352</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>71108</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>116600</v>
+        <v>24800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>丁蕾</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="D17" t="n">
-        <v>267088.01</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16788</v>
+        <v>45600</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>250300.01</v>
+        <v>-45600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周紫姻</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50000</v>
+        <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>22776</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2475,289 +2520,289 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>22776</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>陈斌斌</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>95520</v>
+        <v>27800</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7576.6</v>
+        <v>16600</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>87943.39999999999</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>段继宇</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>15728</v>
+        <v>6600</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4150</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11578</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>樊帆</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>68388</v>
+        <v>10000</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>26956.67</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>41431.33</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>72009.89999999999</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20929</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>51080.89999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>70000</v>
+        <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>43588</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>12598</v>
+        <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7761.2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>35826.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>王蓉</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>80000</v>
+        <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>7768</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4980</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>74160</v>
+        <v>398</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2769,889 +2814,679 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>74160</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>闫文奇</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>31840</v>
+        <v>23338</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8960</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>22880</v>
+        <v>23338</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>黄梦妹</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>250000</v>
+        <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>134484</v>
+        <v>4980</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13380</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>121104</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>200000</v>
+        <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>148440</v>
+        <v>4980</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>29800</v>
+        <v>18600</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>373.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>118640</v>
+        <v>-13620</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>高铭瑞</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100000</v>
+        <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>89382</v>
+        <v>4980</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>29800</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>59582</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100000</v>
+        <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>59158</v>
+        <v>3980</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4183.33</v>
+        <v>8000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>201.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>54974.67</v>
+        <v>-4020</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>51420</v>
+        <v>36400</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17000</v>
+        <v>8600</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>34420</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>88338</v>
+        <v>12000</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23174</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>65164</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>高铭瑞</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>170000</v>
+        <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>147140</v>
+        <v>3980</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>14200</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>132940</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>65920</v>
+        <v>22719</v>
       </c>
       <c r="E34" t="n">
-        <v>18796</v>
+        <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>16560</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>49360</v>
+        <v>22719</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>251860</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>58972</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>192888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>200000</v>
+        <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>213920</v>
+        <v>9960</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>46588</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>167332</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>250000</v>
+        <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>103000</v>
+        <v>9960</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>96400</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>丁蕾</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>180000</v>
+        <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>187310</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>38550</v>
+        <v>29800</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>148760</v>
+        <v>-29800</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>梁志超</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100000</v>
+        <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>46400</v>
+        <v>7760</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>41350</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5050</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>周紫姻</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>106228</v>
+        <v>3800</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>17298</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>88930</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>李洋洋</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>33380</v>
+        <v>8960</v>
       </c>
       <c r="E41" t="n">
-        <v>39588</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>33380</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>冯岚</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D42" t="n">
-        <v>29998</v>
-      </c>
-      <c r="E42" t="n">
-        <v>49218</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>66.0%</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>29998</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>郑鲁</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D43" t="n">
-        <v>90120</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16398</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>106.5%</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>90.1%</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>86120</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>张天昂</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>17200</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>-17200</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>周玉枝</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D45" t="n">
-        <v>96488</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>96.5%</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>96.5%</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>50600</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>52.4%</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>45888</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>龙少海</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>110000</v>
-      </c>
-      <c r="D46" t="n">
-        <v>119200</v>
-      </c>
-      <c r="E46" t="n">
-        <v>30398</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>136.0%</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>108.4%</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>35800</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>83400</v>
+        <v>7280</v>
       </c>
     </row>
   </sheetData>
@@ -3665,7 +3500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3713,57 +3548,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>134000</v>
+        <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>53449</v>
+        <v>36387.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>15218</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>38231</v>
+        <v>36387.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>143880</v>
+        <v>603.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>143.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3775,29 +3610,29 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>143880</v>
+        <v>603.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24000</v>
+        <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>46868</v>
+        <v>15398</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>195.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3809,29 +3644,29 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46868</v>
+        <v>15398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>林峻民</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32000</v>
+        <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>9184</v>
+        <v>290.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3843,29 +3678,29 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9184</v>
+        <v>290.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>朱锋剑</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>18796</v>
+        <v>10392.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3877,41 +3712,41 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18796</v>
+        <v>10392.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>130000</v>
+        <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>73224.69</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>72904.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3922,30 +3757,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>133200</v>
+        <v>1200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>18150</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>115050</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
@@ -3960,26 +3795,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>138885.26</v>
+        <v>8200</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>115.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>142900</v>
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>102.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-4014.739999999991</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="10">
@@ -3990,30 +3825,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>44100</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>41000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4024,18 +3859,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>胡梦莉</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4047,29 +3882,29 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>307177.14</v>
+        <v>7500</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>102.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4081,29 +3916,29 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>307177.14</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>朱锋剑</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>145375.5700000001</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4115,29 +3950,29 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>145375.5700000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>400000</v>
+        <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>468749.74</v>
+        <v>20598</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4149,33 +3984,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>468749.74</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>206846.74</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -4183,29 +4018,29 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>206846.74</v>
+        <v>-398</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>250000</v>
+        <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>190303</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4217,29 +4052,29 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>190303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>270507</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4251,29 +4086,29 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>270507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50000</v>
+        <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>19174</v>
+        <v>1500</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4285,33 +4120,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19174</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200000</v>
+        <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>127871</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4319,29 +4154,29 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>127871</v>
+        <v>-5000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>周思若</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>50000</v>
+        <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>33596</v>
+        <v>1542</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4353,29 +4188,29 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33596</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>韩雪</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>91172</v>
+        <v>7920</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4387,165 +4222,165 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>91172</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>邝玉萍</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="D22" t="n">
-        <v>57074</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12444.48</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44629.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>397384</v>
+        <v>33992</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>141.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>92388</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>304996</v>
+        <v>33992</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>白蕾</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>87986.00999999999</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6998</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>80988.00999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>73000</v>
+        <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>166949.01</v>
+        <v>2394</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>228.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>22400</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>144549.01</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>芊雅</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>11958</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4557,97 +4392,97 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>11958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>刘馨</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>143942</v>
+        <v>10000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>143.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>135942</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>陈月娇</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>270000</v>
+        <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>274354.45</v>
+        <v>398</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>101.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>40580</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>233774.45</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>118406.9</v>
+        <v>1800</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4659,199 +4494,199 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>118406.9</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>杨红瑞</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>99084</v>
+        <v>4980</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>86084</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>普元媛</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>160000</v>
+        <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>98364.2</v>
+        <v>398</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4498</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>93866.2</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>马奇君</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>130000</v>
+        <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>51804</v>
+        <v>398</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>43804</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50000</v>
+        <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>8398</v>
+        <v>10996</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8398</v>
+        <v>6996</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>148582</v>
+        <v>44562.32</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>148352</v>
+        <v>44562.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>40000</v>
+        <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>29386</v>
+        <v>10598</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4863,29 +4698,29 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29386</v>
+        <v>10598</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>110266</v>
+        <v>10000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>275.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4897,63 +4732,63 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>110266</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>张回</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>42786</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>41106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>冯兰兰</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>49192</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4965,29 +4800,29 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>49192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D39" t="n">
         <v>398</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5005,125 +4840,125 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>许冰</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>170000</v>
+        <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>140186</v>
+        <v>106598</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>131386</v>
+        <v>106598</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>白蕾</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>77782</v>
+        <v>398</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>67782</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>王芊雅</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>200000</v>
+        <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>31796</v>
+        <v>398</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6596</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>150000</v>
+        <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>105650</v>
+        <v>1980</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5135,29 +4970,29 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>105650</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>240844</v>
+        <v>1000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>160.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5169,29 +5004,29 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>240844</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>200000</v>
+        <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>194663.28</v>
+        <v>5207</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5203,29 +5038,29 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>194663.28</v>
+        <v>5207</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>韩雪</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>173294</v>
+        <v>1980</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5237,63 +5072,63 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>173294</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>101372</v>
+        <v>7810</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>84572</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>120000</v>
+        <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>72218</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5305,63 +5140,63 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>72218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>尹欢</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>120000</v>
+        <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>8398</v>
+        <v>31234</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1998</v>
+        <v>31234</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>庄鑫</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5373,29 +5208,29 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>张回</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10000</v>
+        <v>80000</v>
       </c>
       <c r="D51" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5407,97 +5242,97 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>120000</v>
+        <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>123182</v>
+        <v>33994</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>34400</v>
+        <v>0</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>88782</v>
+        <v>33994</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>210000</v>
+        <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>170862</v>
+        <v>12104.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>41600</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>129262</v>
+        <v>12104.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>107400</v>
+        <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>107592</v>
+        <v>51980</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5509,29 +5344,29 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>107592</v>
+        <v>51980</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>普元媛</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>48000</v>
+        <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>34796</v>
+        <v>398</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5543,29 +5378,29 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>34796</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>马奇君</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>7998</v>
+        <v>30796</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5577,131 +5412,131 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>7998</v>
+        <v>30796</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>马春兰</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>78682</v>
+        <v>10000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>70682</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>106370</v>
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>34800</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>71570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>150962</v>
+        <v>0</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>10200</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>140762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>吴静文</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>28584</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5713,177 +5548,109 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>28584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>334800</v>
+        <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>388931.5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>368931.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>204401</v>
+        <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>166073.12</v>
+        <v>29497</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>25212</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>140861.12</v>
+        <v>29497</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>259200</v>
+        <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>206071.48</v>
+        <v>7880</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>131.3%</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>169071.48</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>袁登玉</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>20796</v>
-      </c>
-      <c r="D64" t="n">
-        <v>796</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>3.8%</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>邝玉萍</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>15378</v>
-      </c>
-      <c r="D65" t="n">
-        <v>17394</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>113.1%</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>17394</v>
+        <v>7880</v>
       </c>
     </row>
   </sheetData>
@@ -5944,16 +5711,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2407996.07</v>
+        <v>238421</v>
       </c>
       <c r="D2" t="n">
-        <v>7879</v>
+        <v>1556</v>
       </c>
       <c r="E2" t="n">
-        <v>2124393.07</v>
+        <v>190457</v>
       </c>
       <c r="F2" t="n">
-        <v>283603</v>
+        <v>47964</v>
       </c>
     </row>
     <row r="3">
@@ -5968,16 +5735,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2185131</v>
+        <v>198156</v>
       </c>
       <c r="D3" t="n">
-        <v>555</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>1908902</v>
+        <v>153680</v>
       </c>
       <c r="F3" t="n">
-        <v>276229</v>
+        <v>44476</v>
       </c>
     </row>
     <row r="4">
@@ -5992,16 +5759,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>222865.07</v>
+        <v>40265</v>
       </c>
       <c r="D4" t="n">
-        <v>7324</v>
+        <v>1492</v>
       </c>
       <c r="E4" t="n">
-        <v>215491.07</v>
+        <v>36777</v>
       </c>
       <c r="F4" t="n">
-        <v>7374</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="5">
@@ -6016,16 +5783,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5266931.82</v>
+        <v>413862</v>
       </c>
       <c r="D5" t="n">
-        <v>981</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>1001783.8</v>
+        <v>82796</v>
       </c>
       <c r="F5" t="n">
-        <v>4265148.02</v>
+        <v>331066</v>
       </c>
     </row>
     <row r="6">
@@ -6040,16 +5807,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3687601.02</v>
+        <v>283698</v>
       </c>
       <c r="D6" t="n">
-        <v>651</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
-        <v>116440</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3571161.02</v>
+        <v>283698</v>
       </c>
     </row>
     <row r="7">
@@ -6064,16 +5831,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1559330.8</v>
+        <v>130164</v>
       </c>
       <c r="D7" t="n">
-        <v>329</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>885343.8</v>
+        <v>82796</v>
       </c>
       <c r="F7" t="n">
-        <v>673987</v>
+        <v>47368</v>
       </c>
     </row>
     <row r="8">
@@ -6088,16 +5855,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3715549.6</v>
+        <v>221048.14</v>
       </c>
       <c r="D8" t="n">
-        <v>2961</v>
+        <v>183</v>
       </c>
       <c r="E8" t="n">
-        <v>41843.55</v>
+        <v>5281.62</v>
       </c>
       <c r="F8" t="n">
-        <v>3673706.05</v>
+        <v>215766.52</v>
       </c>
     </row>
     <row r="9">
@@ -6112,16 +5879,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2200361.19</v>
+        <v>136490.54</v>
       </c>
       <c r="D9" t="n">
-        <v>1536</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>15445.18</v>
+        <v>1280.2</v>
       </c>
       <c r="F9" t="n">
-        <v>2184916.01</v>
+        <v>135210.34</v>
       </c>
     </row>
     <row r="10">
@@ -6136,16 +5903,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1511688.41</v>
+        <v>84557.60000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1423</v>
+        <v>83</v>
       </c>
       <c r="E10" t="n">
-        <v>26398.37</v>
+        <v>4001.42</v>
       </c>
       <c r="F10" t="n">
-        <v>1485290.04</v>
+        <v>80556.17999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6160,16 +5927,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1139722</v>
+        <v>95200</v>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>716322</v>
+        <v>49600</v>
       </c>
       <c r="F11" t="n">
-        <v>423400</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="12">
@@ -6184,16 +5951,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>659109.8100000001</v>
+        <v>14578</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>453084.81</v>
+        <v>13398</v>
       </c>
       <c r="F12" t="n">
-        <v>206025</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="13">
@@ -6208,16 +5975,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>342234</v>
+        <v>57600</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>222034</v>
+        <v>57600</v>
       </c>
       <c r="F13" t="n">
-        <v>120200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6232,16 +5999,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77220</v>
+        <v>23760</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>55440</v>
+        <v>5940</v>
       </c>
       <c r="F14" t="n">
-        <v>21780</v>
+        <v>17820</v>
       </c>
     </row>
   </sheetData>
@@ -6302,22 +6069,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2407996.07</v>
+        <v>238421</v>
       </c>
       <c r="C2" t="n">
-        <v>357349.91</v>
+        <v>51544</v>
       </c>
       <c r="D2" t="n">
-        <v>52625.01</v>
+        <v>3873</v>
       </c>
       <c r="E2" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="F2" t="n">
-        <v>304724.9</v>
+        <v>47671</v>
       </c>
       <c r="G2" t="n">
-        <v>12.65</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="3">
@@ -6327,22 +6094,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5266931.82</v>
+        <v>413862</v>
       </c>
       <c r="C3" t="n">
-        <v>709042.28</v>
+        <v>72898</v>
       </c>
       <c r="D3" t="n">
-        <v>39796</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>669246.28</v>
+        <v>72898</v>
       </c>
       <c r="G3" t="n">
-        <v>12.71</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="4">
@@ -6352,22 +6119,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3715549.6</v>
+        <v>221048.14</v>
       </c>
       <c r="C4" t="n">
-        <v>1305783.04</v>
+        <v>71449</v>
       </c>
       <c r="D4" t="n">
-        <v>2029</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1303754.04</v>
+        <v>71449</v>
       </c>
       <c r="G4" t="n">
-        <v>35.09</v>
+        <v>32.32</v>
       </c>
     </row>
     <row r="5">
@@ -6377,22 +6144,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1139722</v>
+        <v>95200</v>
       </c>
       <c r="C5" t="n">
-        <v>427400</v>
+        <v>45600</v>
       </c>
       <c r="D5" t="n">
-        <v>24800</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>402600</v>
+        <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>35.32</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="6">
@@ -6402,22 +6169,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>659109.8100000001</v>
+        <v>14578</v>
       </c>
       <c r="C6" t="n">
-        <v>196930.27</v>
+        <v>37200</v>
       </c>
       <c r="D6" t="n">
-        <v>2817.9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>194112.37</v>
+        <v>37200</v>
       </c>
       <c r="G6" t="n">
-        <v>29.45</v>
+        <v>255.18</v>
       </c>
     </row>
     <row r="7">
@@ -6427,22 +6194,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>342234</v>
+        <v>57600</v>
       </c>
       <c r="C7" t="n">
-        <v>529780</v>
+        <v>38400</v>
       </c>
       <c r="D7" t="n">
-        <v>49800</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>14.55</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>479980</v>
+        <v>38400</v>
       </c>
       <c r="G7" t="n">
-        <v>140.25</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="8">
@@ -6452,7 +6219,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77220</v>
+        <v>23760</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6481,7 +6248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6513,61 +6280,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>482</v>
+        <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>1202313.51</v>
+        <v>154778</v>
       </c>
       <c r="D2" t="n">
-        <v>114</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>440471</v>
+        <v>47581</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>662</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>219698.57</v>
+        <v>23998</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>106692.48</v>
+        <v>8067</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -6577,29 +6344,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>96798.67</v>
+        <v>4921</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>24541.33</v>
+        <v>4000</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -6609,13 +6376,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>14809.8</v>
+        <v>1941</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6625,26 +6392,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>10994</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2124</v>
+        <v>38</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6653,48 +6420,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>教材问题</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>67</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>未填写原因</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6709,7 +6444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6746,10 +6481,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>249820</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="3">
@@ -6760,74 +6495,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>72386</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>21950</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6836,16 +6571,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>112841.01</v>
+        <v>20170</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6854,268 +6589,268 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>66673</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>45299.66</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>16829</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>6500</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4169</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1809</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>394</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>183550</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>83883</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7124,16 +6859,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>43678.9</v>
+        <v>10913</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7142,196 +6877,196 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>28906.9</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>11738</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>8596</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>4221</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>454</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>未填写原因</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>131746</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>20444.48</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>4057</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7343,31 +7078,31 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>88502</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7376,64 +7111,64 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>39428</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>267</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="41">
@@ -7444,14 +7179,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>44282.6</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42">
@@ -7462,14 +7197,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>28806.01</v>
+        <v>347</v>
       </c>
     </row>
     <row r="43">
@@ -7480,14 +7215,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>27950</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44">
@@ -7498,14 +7233,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>6988</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -7516,14 +7251,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>4117.67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -7534,1184 +7269,68 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>4000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1353.9</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>617</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>商家操作失误</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>教材问题</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="n">
         <v>19</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>59600</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>45</v>
-      </c>
-      <c r="D53" t="n">
-        <v>34259</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>73</v>
-      </c>
-      <c r="D54" t="n">
-        <v>14681</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>价格问题</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>10</v>
-      </c>
-      <c r="D56" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>10</v>
-      </c>
-      <c r="D57" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>4</v>
-      </c>
-      <c r="D58" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>商家操作失误</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>7</v>
-      </c>
-      <c r="D60" t="n">
-        <v>68119</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" t="n">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>价格问题</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" t="n">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>9</v>
-      </c>
-      <c r="D66" t="n">
-        <v>62800</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D67" t="n">
-        <v>15200</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>4</v>
-      </c>
-      <c r="D68" t="n">
-        <v>11138</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>93</v>
-      </c>
-      <c r="D71" t="n">
-        <v>33277</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>59</v>
-      </c>
-      <c r="D72" t="n">
-        <v>30913</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" t="n">
-        <v>9163.33</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>2</v>
-      </c>
-      <c r="D74" t="n">
-        <v>6619</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>13</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2489</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>8</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>7</v>
-      </c>
-      <c r="D77" t="n">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>商家操作失误</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" t="n">
-        <v>43067</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2</v>
-      </c>
-      <c r="D80" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="n">
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>12</v>
-      </c>
-      <c r="D83" t="n">
-        <v>62837</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>4</v>
-      </c>
-      <c r="D84" t="n">
-        <v>13598</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>2</v>
-      </c>
-      <c r="D86" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>价格问题</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" t="n">
-        <v>66400</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="n">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" t="n">
-        <v>4009</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="n">
-        <v>24800</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2</v>
-      </c>
-      <c r="D94" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" t="n">
-        <v>10200</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>3</v>
-      </c>
-      <c r="D96" t="n">
-        <v>16960</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>19</v>
-      </c>
-      <c r="D97" t="n">
-        <v>14514</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>21</v>
-      </c>
-      <c r="D98" t="n">
-        <v>9187</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>5</v>
-      </c>
-      <c r="D99" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>教材问题</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>商家操作失误</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>2</v>
-      </c>
-      <c r="D104" t="n">
-        <v>15218</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>2</v>
-      </c>
-      <c r="D105" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>2</v>
-      </c>
-      <c r="D107" t="n">
-        <v>7019</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>3</v>
-      </c>
-      <c r="D108" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" t="n">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>2</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>2</v>
-      </c>
-      <c r="D111" t="n">
-        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -8752,10 +7371,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>470930.48</v>
+        <v>72898</v>
       </c>
     </row>
     <row r="3">
@@ -8765,10 +7384,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>336200</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="4">
@@ -8778,101 +7397,101 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>285400</v>
+        <v>38400</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>210505.99</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>209620</v>
+        <v>29760</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>175776</v>
+        <v>10269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>1280智慧父母成长营年卡</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>165072</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>家庭守护计划</t>
+          <t>299元青春期家庭21天陪跑</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>62486</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="C10" t="n">
-        <v>42960</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>线下产品</t>
+          <t>裴盈299青少年及儿童焦虑基础营月卡</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>33600</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -8909,196 +7528,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>307698</v>
+        <v>45899</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>304004.5</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>203450.48</v>
+        <v>30038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>193771</v>
+        <v>23938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>147897.81</v>
+        <v>21405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
-        <v>143029</v>
+        <v>16812</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>94190</v>
+        <v>16508</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>90560</v>
+        <v>13633</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>68428.99000000001</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>59199.01</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>58005</v>
+        <v>6899</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>48678.9</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>44031</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>43331</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>40734</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>30679</v>
+        <v>16198</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+130.1%</t>
+          <t>+335.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>20896</v>
+        <v>15637</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+197.1%</t>
+          <t>+297.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1279</v>
+        <v>1150</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+45.1%</t>
+          <t>+61.4%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-6622</v>
+        <v>968</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-89.4%</t>
+          <t>-172.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>38057</v>
+        <v>31443</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+61.4%</t>
+          <t>+95.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>19285</v>
+        <v>18676</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+23.4%</t>
+          <t>+27.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>15343</v>
+        <v>2114</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>+481.5%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-53797</v>
+        <v>-34487</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+59.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>74145</v>
+        <v>60976</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62577</v>
+        <v>52707</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+7.5%</t>
+          <t>+27.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>47184</v>
+        <v>32175</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+61.9%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39804</v>
+        <v>32014</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+27.1%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>35887</v>
+        <v>8952</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>+186.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>29387</v>
+        <v>3503</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>+311.4%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>86240</v>
+        <v>48000</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+30.7%</t>
+          <t>+134.8%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>51440</v>
+        <v>13200</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>+194.8%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>139700</v>
+        <v>138904</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>139700</v>
+        <v>138904</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>30026</v>
+        <v>13398</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>30026</v>
+        <v>13398</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>42706</v>
+        <v>22706</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+82.9%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42407</v>
+        <v>22407</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+85.3%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>103167</v>
+        <v>101968</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-37.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>103108</v>
+        <v>101909</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1247,19 +1247,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>41850</v>
+        <v>33850</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41684</v>
+        <v>33684</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>-82.2%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>46396</v>
+        <v>38396</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>46396</v>
+        <v>38396</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1371,19 +1371,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3301</v>
+        <v>2603</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+524.9%</t>
+          <t>+692.4%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3301</v>
+        <v>2603</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+512.8%</t>
+          <t>+677.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>54198</v>
+        <v>53402</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+41.0%</t>
+          <t>+43.1%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47499</v>
+        <v>46703</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+51.9%</t>
+          <t>+54.5%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>62607</v>
+        <v>61213</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+77.0%</t>
+          <t>+81.0%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>62551</v>
+        <v>61213</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+77.2%</t>
+          <t>+81.0%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1564,11 +1564,11 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-80949</v>
+        <v>-78449</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-125.5%</t>
+          <t>-126.3%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>81369</v>
+        <v>71350</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>79569</v>
+        <v>71350</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>760000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>70600</v>
@@ -538,14 +538,10 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9.3%</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -634,7 +630,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>760000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>61409</v>
@@ -648,14 +644,10 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>8.1%</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -691,7 +683,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>520000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>12292</v>
@@ -705,14 +697,10 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -748,7 +736,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>69704</v>
@@ -762,14 +750,10 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>11.6%</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -805,7 +789,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>52078</v>
@@ -819,14 +803,10 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>14.5%</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -862,7 +842,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>640000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>25603</v>
@@ -876,14 +856,10 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -919,7 +895,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1120000</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>112716</v>
@@ -933,14 +909,10 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>10.1%</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1731,16 +1703,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="C4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" t="n">
-        <v>1401.4</v>
+        <v>1415.4</v>
       </c>
       <c r="E4" t="n">
-        <v>4389</v>
+        <v>4441</v>
       </c>
     </row>
   </sheetData>
@@ -4369,18 +4341,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>芊雅</t>
+          <t>王芊雅</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4392,7 +4364,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="27">
@@ -5019,14 +4991,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>5207</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5053,14 +5025,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>1980</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5087,14 +5059,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>7810</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5121,7 +5093,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -5155,14 +5127,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>31234</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5189,14 +5161,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5223,7 +5195,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -5257,14 +5229,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>33994</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5291,14 +5263,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>12104.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5325,14 +5297,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>240000</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
         <v>51980</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F54" t="n">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>760000</v>
       </c>
       <c r="D2" t="n">
         <v>70600</v>
@@ -538,10 +538,14 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9.3%</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -630,7 +634,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>760000</v>
       </c>
       <c r="D4" t="n">
         <v>61409</v>
@@ -644,10 +648,14 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8.1%</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -683,7 +691,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>520000</v>
       </c>
       <c r="D5" t="n">
         <v>12292</v>
@@ -697,10 +705,14 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -736,7 +748,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="D6" t="n">
         <v>69704</v>
@@ -750,10 +762,14 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>11.6%</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -789,7 +805,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>360000</v>
       </c>
       <c r="D7" t="n">
         <v>52078</v>
@@ -803,10 +819,14 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>14.5%</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -842,7 +862,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>640000</v>
       </c>
       <c r="D8" t="n">
         <v>25603</v>
@@ -856,10 +876,14 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -895,7 +919,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1120000</v>
       </c>
       <c r="D9" t="n">
         <v>112716</v>
@@ -909,10 +933,14 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="J9" t="n">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款服务类型" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款省份" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电话" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新老客" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,6 +1644,71 @@
       </c>
       <c r="Q20" t="n">
         <v>14166</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>南区合计</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1005621</v>
+      </c>
+      <c r="E21" t="n">
+        <v>245842</v>
+      </c>
+      <c r="F21" t="n">
+        <v>759779</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>803829</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>+25.1%</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>554336</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>+37.1%</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>3196</v>
+      </c>
+      <c r="O21" t="n">
+        <v>266008</v>
+      </c>
+      <c r="P21" t="n">
+        <v>490774</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>418815</v>
       </c>
     </row>
   </sheetData>
@@ -1748,6 +1814,530 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>新客净流水(元)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>老客净流水(元)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>非1V1及菌群净(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>销售</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>133177</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19417</v>
+      </c>
+      <c r="E2" t="n">
+        <v>147298</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11116</v>
+      </c>
+      <c r="D3" t="n">
+        <v>27800</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>121714</v>
+      </c>
+      <c r="D4" t="n">
+        <v>443557</v>
+      </c>
+      <c r="E4" t="n">
+        <v>267600</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>62076</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>62076</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-839</v>
+      </c>
+      <c r="D6" t="n">
+        <v>135</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-704</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>34632</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-10835</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-54927</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-54927</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>67251</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45251</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>课程6组</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10892</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29800</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40692</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>课程7组</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14092</v>
+      </c>
+      <c r="D11" t="n">
+        <v>318</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14410</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>班主任</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11116</v>
+      </c>
+      <c r="D12" t="n">
+        <v>27800</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9692</v>
+      </c>
+      <c r="D13" t="n">
+        <v>128362</v>
+      </c>
+      <c r="E13" t="n">
+        <v>137656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5795</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2198</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>30735</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10796</v>
+      </c>
+      <c r="E15" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D16" t="n">
+        <v>60996</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-1491</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6936</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8495</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D18" t="n">
+        <v>37377</v>
+      </c>
+      <c r="E18" t="n">
+        <v>27396</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>229</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D20" t="n">
+        <v>70398</v>
+      </c>
+      <c r="E20" t="n">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>62021</v>
+      </c>
+      <c r="D21" t="n">
+        <v>48798</v>
+      </c>
+      <c r="E21" t="n">
+        <v>69407</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7519</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>徐汇</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4956</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44596</v>
+      </c>
+      <c r="E23" t="n">
+        <v>14166</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>南区合计</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>266008</v>
+      </c>
+      <c r="D24" t="n">
+        <v>490774</v>
+      </c>
+      <c r="E24" t="n">
+        <v>418815</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>70600</v>
+        <v>130635</v>
       </c>
       <c r="E2" t="n">
-        <v>8524</v>
+        <v>37302</v>
       </c>
       <c r="F2" t="n">
-        <v>62076</v>
+        <v>93333</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16198</v>
+        <v>62125</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+335.9%</t>
+          <t>+110.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>15637</v>
+        <v>48540</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+297.0%</t>
+          <t>+92.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1856</v>
+        <v>1971</v>
       </c>
       <c r="E3" t="n">
-        <v>2560</v>
+        <v>2589</v>
       </c>
       <c r="F3" t="n">
-        <v>-704</v>
+        <v>-618</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1150</v>
+        <v>9831</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+61.4%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>968</v>
+        <v>-8155</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-172.7%</t>
+          <t>-92.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>61409</v>
+        <v>91972</v>
       </c>
       <c r="E4" t="n">
-        <v>37613</v>
+        <v>58112</v>
       </c>
       <c r="F4" t="n">
-        <v>23796</v>
+        <v>33860</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>31443</v>
+        <v>97552</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+95.3%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>18676</v>
+        <v>68967</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+27.4%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>12292</v>
+        <v>21465</v>
       </c>
       <c r="E5" t="n">
-        <v>67219</v>
+        <v>80965</v>
       </c>
       <c r="F5" t="n">
-        <v>-54927</v>
+        <v>-59500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2114</v>
+        <v>16267</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+481.5%</t>
+          <t>+32.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-34487</v>
+        <v>-52891</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+59.3%</t>
+          <t>+12.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>69704</v>
+        <v>125411</v>
       </c>
       <c r="E6" t="n">
-        <v>2453</v>
+        <v>14582</v>
       </c>
       <c r="F6" t="n">
-        <v>67251</v>
+        <v>110829</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>60976</v>
+        <v>87497</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+43.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52707</v>
+        <v>72677</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+27.6%</t>
+          <t>+52.5%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>52078</v>
+        <v>91673</v>
       </c>
       <c r="E7" t="n">
-        <v>11386</v>
+        <v>21663</v>
       </c>
       <c r="F7" t="n">
-        <v>40692</v>
+        <v>70010</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>32175</v>
+        <v>102399</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+61.9%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>32014</v>
+        <v>94973</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+27.1%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>25603</v>
+        <v>57287</v>
       </c>
       <c r="E8" t="n">
-        <v>11193</v>
+        <v>16524</v>
       </c>
       <c r="F8" t="n">
-        <v>14410</v>
+        <v>40763</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8952</v>
+        <v>47912</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+186.0%</t>
+          <t>+19.6%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3503</v>
+        <v>41205</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+311.4%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>112716</v>
+        <v>282723</v>
       </c>
       <c r="E9" t="n">
-        <v>73800</v>
+        <v>129600</v>
       </c>
       <c r="F9" t="n">
-        <v>38916</v>
+        <v>153123</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>48000</v>
+        <v>218977</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+134.8%</t>
+          <t>+29.1%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>13200</v>
+        <v>165403</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+194.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>138054</v>
+        <v>406715</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>138054</v>
+        <v>406715</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>138904</v>
+        <v>274630</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+48.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>138904</v>
+        <v>274630</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>+48.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>9692</v>
+        <v>153969</v>
       </c>
       <c r="P10" t="n">
-        <v>128362</v>
+        <v>252746</v>
       </c>
       <c r="Q10" t="n">
-        <v>137656</v>
+        <v>406317</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>8203</v>
+        <v>60287</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4999</v>
       </c>
       <c r="F11" t="n">
-        <v>8203</v>
+        <v>55287</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13398</v>
+        <v>34104</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>+76.8%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>13398</v>
+        <v>34104</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>+62.1%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>5795</v>
+        <v>7495</v>
       </c>
       <c r="P11" t="n">
-        <v>2198</v>
+        <v>47582</v>
       </c>
       <c r="Q11" t="n">
-        <v>7009</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>41531</v>
+        <v>102757</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>41531</v>
+        <v>102729</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>22706</v>
+        <v>43502</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+82.9%</t>
+          <t>+136.2%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>22407</v>
+        <v>43203</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+85.3%</t>
+          <t>+137.8%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>30735</v>
+        <v>41541</v>
       </c>
       <c r="P12" t="n">
-        <v>10796</v>
+        <v>61188</v>
       </c>
       <c r="Q12" t="n">
-        <v>337</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>63793</v>
+        <v>126681</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>4523</v>
       </c>
       <c r="F13" t="n">
-        <v>63726</v>
+        <v>122158</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>101968</v>
+        <v>130045</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>101909</v>
+        <v>119986</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1677</v>
+        <v>5529</v>
       </c>
       <c r="O13" t="n">
-        <v>1053</v>
+        <v>9633</v>
       </c>
       <c r="P13" t="n">
-        <v>60996</v>
+        <v>106996</v>
       </c>
       <c r="Q13" t="n">
-        <v>2532</v>
+        <v>14266</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>10991</v>
+        <v>76719</v>
       </c>
       <c r="E14" t="n">
         <v>5000</v>
       </c>
       <c r="F14" t="n">
-        <v>5991</v>
+        <v>71719</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>33850</v>
+        <v>63850</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>+20.2%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>33684</v>
+        <v>46884</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-82.2%</t>
+          <t>+53.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>546</v>
+        <v>4236</v>
       </c>
       <c r="O14" t="n">
-        <v>-1491</v>
+        <v>29353</v>
       </c>
       <c r="P14" t="n">
-        <v>6936</v>
+        <v>38130</v>
       </c>
       <c r="Q14" t="n">
-        <v>8495</v>
+        <v>12233</v>
       </c>
     </row>
     <row r="15">
@@ -1291,50 +1291,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>37415</v>
+        <v>76236</v>
       </c>
       <c r="E15" t="n">
         <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>37396</v>
+        <v>76217</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>38396</v>
+        <v>46402</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>+64.3%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>38396</v>
+        <v>46343</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>+64.5%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="P15" t="n">
-        <v>37377</v>
+        <v>75775</v>
       </c>
       <c r="Q15" t="n">
-        <v>27396</v>
+        <v>27421</v>
       </c>
     </row>
     <row r="16">
@@ -1352,50 +1352,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>20627</v>
+        <v>54653</v>
       </c>
       <c r="E16" t="n">
         <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>20229</v>
+        <v>54255</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2603</v>
+        <v>5097</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+692.4%</t>
+          <t>+972.3%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2603</v>
+        <v>5097</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+677.1%</t>
+          <t>+964.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>229</v>
+        <v>12059</v>
       </c>
       <c r="P16" t="n">
-        <v>20000</v>
+        <v>42196</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>76394</v>
+        <v>141067</v>
       </c>
       <c r="E17" t="n">
-        <v>4248</v>
+        <v>34077</v>
       </c>
       <c r="F17" t="n">
-        <v>72146</v>
+        <v>106990</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>53402</v>
+        <v>97596</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+43.1%</t>
+          <t>+44.5%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>46703</v>
+        <v>90897</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+54.5%</t>
+          <t>+17.7%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>562</v>
+        <v>1472</v>
       </c>
       <c r="O17" t="n">
-        <v>1186</v>
+        <v>1428</v>
       </c>
       <c r="P17" t="n">
-        <v>70398</v>
+        <v>104090</v>
       </c>
       <c r="Q17" t="n">
-        <v>552</v>
+        <v>-28093</v>
       </c>
     </row>
     <row r="18">
@@ -1476,50 +1476,50 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>110819</v>
+        <v>212742</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>110819</v>
+        <v>212714</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>61213</v>
+        <v>133307</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+81.0%</t>
+          <t>+59.6%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>61213</v>
+        <v>133251</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+81.0%</t>
+          <t>+59.6%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>62021</v>
+        <v>80823</v>
       </c>
       <c r="P18" t="n">
-        <v>48798</v>
+        <v>131891</v>
       </c>
       <c r="Q18" t="n">
-        <v>69407</v>
+        <v>125114</v>
       </c>
     </row>
     <row r="19">
@@ -1537,52 +1537,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>20819</v>
+        <v>79311</v>
       </c>
       <c r="E19" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>20619</v>
+        <v>79102</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>65029</v>
+        <v>83805</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-78449</v>
+        <v>-62173</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-126.3%</t>
+          <t>-227.2%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>200</v>
+        <v>2955</v>
       </c>
       <c r="O19" t="n">
-        <v>7519</v>
+        <v>8755</v>
       </c>
       <c r="P19" t="n">
-        <v>13100</v>
+        <v>67592</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="20">
@@ -1600,50 +1600,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>70714</v>
+        <v>128080</v>
       </c>
       <c r="E20" t="n">
-        <v>21162</v>
+        <v>21247</v>
       </c>
       <c r="F20" t="n">
-        <v>49552</v>
+        <v>106833</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>71350</v>
+        <v>136960</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>71350</v>
+        <v>135160</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4956</v>
+        <v>25843</v>
       </c>
       <c r="P20" t="n">
-        <v>44596</v>
+        <v>80990</v>
       </c>
       <c r="Q20" t="n">
-        <v>14166</v>
+        <v>25053</v>
       </c>
     </row>
     <row r="21">
@@ -1661,54 +1661,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>1005621</v>
+        <v>2268390</v>
       </c>
       <c r="E21" t="n">
-        <v>245842</v>
+        <v>431865</v>
       </c>
       <c r="F21" t="n">
-        <v>759779</v>
+        <v>1836524</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>803829</v>
+        <v>1691860</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+25.1%</t>
+          <t>+34.1%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>554336</v>
+        <v>1298102</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+37.1%</t>
+          <t>+41.5%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3196</v>
+        <v>14404</v>
       </c>
       <c r="O21" t="n">
-        <v>266008</v>
+        <v>701883</v>
       </c>
       <c r="P21" t="n">
-        <v>490774</v>
+        <v>1120437</v>
       </c>
       <c r="Q21" t="n">
-        <v>418815</v>
+        <v>1011826</v>
       </c>
     </row>
   </sheetData>
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>221</v>
+        <v>380</v>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>947.7</v>
+        <v>475.5</v>
       </c>
       <c r="E2" t="n">
-        <v>86552</v>
+        <v>68094</v>
       </c>
     </row>
     <row r="3">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>332.3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8416</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>644</v>
+        <v>1089</v>
       </c>
       <c r="C4" t="n">
-        <v>133</v>
+        <v>3380</v>
       </c>
       <c r="D4" t="n">
-        <v>1415.4</v>
+        <v>667.6</v>
       </c>
       <c r="E4" t="n">
-        <v>4441</v>
+        <v>1711</v>
       </c>
     </row>
   </sheetData>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>133177</v>
+        <v>262577</v>
       </c>
       <c r="D2" t="n">
-        <v>19417</v>
+        <v>26100</v>
       </c>
       <c r="E2" t="n">
-        <v>147298</v>
+        <v>259086</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11116</v>
+        <v>67963</v>
       </c>
       <c r="D3" t="n">
-        <v>27800</v>
+        <v>85160</v>
       </c>
       <c r="E3" t="n">
-        <v>3916</v>
+        <v>118123</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121714</v>
+        <v>371342</v>
       </c>
       <c r="D4" t="n">
-        <v>443557</v>
+        <v>1009176</v>
       </c>
       <c r="E4" t="n">
-        <v>267600</v>
+        <v>634616</v>
       </c>
     </row>
     <row r="5">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62076</v>
+        <v>92315</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="E5" t="n">
-        <v>62076</v>
+        <v>93333</v>
       </c>
     </row>
     <row r="6">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-839</v>
+        <v>-753</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-704</v>
+        <v>-618</v>
       </c>
     </row>
     <row r="7">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34632</v>
+        <v>42887</v>
       </c>
       <c r="D7" t="n">
-        <v>-10835</v>
+        <v>-9027</v>
       </c>
       <c r="E7" t="n">
-        <v>40500</v>
+        <v>44166</v>
       </c>
     </row>
     <row r="8">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-54927</v>
+        <v>-63300</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E8" t="n">
-        <v>-54927</v>
+        <v>-59500</v>
       </c>
     </row>
     <row r="9">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>67251</v>
+        <v>110810</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>45251</v>
+        <v>88431</v>
       </c>
     </row>
     <row r="10">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10892</v>
+        <v>40191</v>
       </c>
       <c r="D10" t="n">
-        <v>29800</v>
+        <v>29819</v>
       </c>
       <c r="E10" t="n">
-        <v>40692</v>
+        <v>52510</v>
       </c>
     </row>
     <row r="11">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14092</v>
+        <v>40426</v>
       </c>
       <c r="D11" t="n">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="E11" t="n">
-        <v>14410</v>
+        <v>40763</v>
       </c>
     </row>
     <row r="12">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11116</v>
+        <v>67963</v>
       </c>
       <c r="D12" t="n">
-        <v>27800</v>
+        <v>85160</v>
       </c>
       <c r="E12" t="n">
-        <v>3916</v>
+        <v>118123</v>
       </c>
     </row>
     <row r="13">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9692</v>
+        <v>153969</v>
       </c>
       <c r="D13" t="n">
-        <v>128362</v>
+        <v>252746</v>
       </c>
       <c r="E13" t="n">
-        <v>137656</v>
+        <v>406317</v>
       </c>
     </row>
     <row r="14">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5795</v>
+        <v>7495</v>
       </c>
       <c r="D14" t="n">
-        <v>2198</v>
+        <v>47582</v>
       </c>
       <c r="E14" t="n">
-        <v>7009</v>
+        <v>47097</v>
       </c>
     </row>
     <row r="15">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30735</v>
+        <v>41541</v>
       </c>
       <c r="D15" t="n">
-        <v>10796</v>
+        <v>61188</v>
       </c>
       <c r="E15" t="n">
-        <v>337</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="16">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1053</v>
+        <v>9633</v>
       </c>
       <c r="D16" t="n">
-        <v>60996</v>
+        <v>106996</v>
       </c>
       <c r="E16" t="n">
-        <v>2532</v>
+        <v>14266</v>
       </c>
     </row>
     <row r="17">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1491</v>
+        <v>29353</v>
       </c>
       <c r="D17" t="n">
-        <v>6936</v>
+        <v>38130</v>
       </c>
       <c r="E17" t="n">
-        <v>8495</v>
+        <v>12233</v>
       </c>
     </row>
     <row r="18">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="D18" t="n">
-        <v>37377</v>
+        <v>75775</v>
       </c>
       <c r="E18" t="n">
-        <v>27396</v>
+        <v>27421</v>
       </c>
     </row>
     <row r="19">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>229</v>
+        <v>12059</v>
       </c>
       <c r="D19" t="n">
-        <v>20000</v>
+        <v>42196</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1186</v>
+        <v>1428</v>
       </c>
       <c r="D20" t="n">
-        <v>70398</v>
+        <v>104090</v>
       </c>
       <c r="E20" t="n">
-        <v>552</v>
+        <v>-28093</v>
       </c>
     </row>
     <row r="21">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>62021</v>
+        <v>80823</v>
       </c>
       <c r="D21" t="n">
-        <v>48798</v>
+        <v>131891</v>
       </c>
       <c r="E21" t="n">
-        <v>69407</v>
+        <v>125114</v>
       </c>
     </row>
     <row r="22">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7519</v>
+        <v>8755</v>
       </c>
       <c r="D22" t="n">
-        <v>13100</v>
+        <v>67592</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="23">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4956</v>
+        <v>25843</v>
       </c>
       <c r="D23" t="n">
-        <v>44596</v>
+        <v>80990</v>
       </c>
       <c r="E23" t="n">
-        <v>14166</v>
+        <v>25053</v>
       </c>
     </row>
     <row r="24">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>266008</v>
+        <v>701883</v>
       </c>
       <c r="D24" t="n">
-        <v>490774</v>
+        <v>1120437</v>
       </c>
       <c r="E24" t="n">
-        <v>418815</v>
+        <v>1011826</v>
       </c>
     </row>
   </sheetData>
@@ -2414,19 +2414,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>29780</v>
+        <v>75380</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>29780</v>
+        <v>75380</v>
       </c>
     </row>
     <row r="3">
@@ -2468,11 +2468,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2589</v>
+        <v>19389</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-2589</v>
+        <v>-19389</v>
       </c>
     </row>
     <row r="4">
@@ -2510,19 +2510,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>116.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9960</v>
+        <v>-1620</v>
       </c>
     </row>
     <row r="5">
@@ -2540,19 +2540,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2560,11 +2560,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16220</v>
+        <v>21200</v>
       </c>
     </row>
     <row r="6">
@@ -2624,19 +2624,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="8">
@@ -2678,11 +2678,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6600</v>
+        <v>10750</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-6600</v>
+        <v>-10750</v>
       </c>
     </row>
     <row r="9">
@@ -2750,19 +2750,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>16560</v>
+        <v>21540</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16560</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="11">
@@ -2792,19 +2792,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>11640</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2812,11 +2812,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-3980</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="12">
@@ -2834,31 +2834,31 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>10000</v>
+        <v>12490</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10000</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="13">
@@ -2876,19 +2876,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>1980</v>
+        <v>91380</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1980</v>
+        <v>91380</v>
       </c>
     </row>
     <row r="14">
@@ -2918,31 +2918,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>30000</v>
+        <v>33800</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>23400</v>
+        <v>20600</v>
       </c>
     </row>
     <row r="15">
@@ -3002,31 +3002,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>24800</v>
+        <v>28760</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24800</v>
+        <v>22160</v>
       </c>
     </row>
     <row r="17">
@@ -3086,31 +3086,31 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>13980</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-5000</v>
+        <v>-3020</v>
       </c>
     </row>
     <row r="19">
@@ -3140,19 +3140,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>16600</v>
+        <v>34000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>11200</v>
+        <v>-6200</v>
       </c>
     </row>
     <row r="20">
@@ -3296,19 +3296,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>55600</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>55600</v>
       </c>
     </row>
     <row r="24">
@@ -3380,31 +3380,31 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>398</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="26">
@@ -3434,19 +3434,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>23338</v>
+        <v>16738</v>
       </c>
     </row>
     <row r="27">
@@ -3590,31 +3590,31 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>201.0%</t>
+          <t>150.8%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-4020</v>
+        <v>-4040</v>
       </c>
     </row>
     <row r="31">
@@ -3632,31 +3632,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>36400</v>
+        <v>50570</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>8600</v>
+        <v>13100</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>27800</v>
+        <v>37470</v>
       </c>
     </row>
     <row r="32">
@@ -3674,19 +3674,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>12000</v>
+        <v>16980</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>12000</v>
+        <v>16980</v>
       </c>
     </row>
     <row r="33">
@@ -3716,31 +3716,31 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>3980</v>
+        <v>15980</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3980</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="34">
@@ -3758,19 +3758,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>22719</v>
+        <v>32679</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>22719</v>
+        <v>32679</v>
       </c>
     </row>
     <row r="35">
@@ -3800,19 +3800,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="36">
@@ -3854,19 +3854,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9960</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="37">
@@ -3884,19 +3884,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="38">
@@ -3938,11 +3938,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>29800</v>
+        <v>43708</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-29800</v>
+        <v>-43708</v>
       </c>
     </row>
     <row r="39">
@@ -3968,19 +3968,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>7760</v>
+        <v>11560</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7760</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="40">
@@ -4010,19 +4010,19 @@
         <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>3800</v>
+        <v>8780</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3800</v>
+        <v>8780</v>
       </c>
     </row>
     <row r="41">
@@ -4052,19 +4052,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>8960</v>
+        <v>18920</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4072,11 +4072,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>7280</v>
+        <v>17240</v>
       </c>
     </row>
   </sheetData>
@@ -4150,23 +4150,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>36387.2</v>
+        <v>50001.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>36387.2</v>
+        <v>47001.4</v>
       </c>
     </row>
     <row r="3">
@@ -4184,11 +4184,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>603.2</v>
+        <v>18503.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>603.2</v>
+        <v>18503.2</v>
       </c>
     </row>
     <row r="4">
@@ -4218,11 +4218,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>15398</v>
+        <v>19298</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15398</v>
+        <v>19298</v>
       </c>
     </row>
     <row r="5">
@@ -4252,23 +4252,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>290.3</v>
+        <v>6290.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>290.3</v>
+        <v>5190.3</v>
       </c>
     </row>
     <row r="6">
@@ -4286,11 +4286,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>10392.7</v>
+        <v>21230.88</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10392.7</v>
+        <v>21230.88</v>
       </c>
     </row>
     <row r="7">
@@ -4320,11 +4320,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="8">
@@ -4354,11 +4354,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>1200</v>
+        <v>13829.91</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1200</v>
+        <v>13829.91</v>
       </c>
     </row>
     <row r="9">
@@ -4388,11 +4388,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>8200</v>
+        <v>20636.43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4400,11 +4400,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8000</v>
+        <v>20436.43</v>
       </c>
     </row>
     <row r="10">
@@ -4422,11 +4422,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>18598</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>18598</v>
       </c>
     </row>
     <row r="11">
@@ -4456,11 +4456,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>3900</v>
+        <v>7000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3900</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="12">
@@ -4490,11 +4490,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>7500</v>
+        <v>18900</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7500</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="13">
@@ -4558,11 +4558,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>20598</v>
+        <v>33196</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20598</v>
+        <v>33196</v>
       </c>
     </row>
     <row r="15">
@@ -4592,11 +4592,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>9996</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4604,11 +4604,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-398</v>
+        <v>9598</v>
       </c>
     </row>
     <row r="16">
@@ -4626,11 +4626,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
     </row>
     <row r="17">
@@ -4660,11 +4660,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="18">
@@ -4694,11 +4694,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>1500</v>
+        <v>1951.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1500</v>
+        <v>1951.8</v>
       </c>
     </row>
     <row r="19">
@@ -4728,11 +4728,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>33634.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4740,11 +4740,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-5000</v>
+        <v>28634.9</v>
       </c>
     </row>
     <row r="20">
@@ -4762,11 +4762,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>1542</v>
+        <v>22737.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1542</v>
+        <v>22737.5</v>
       </c>
     </row>
     <row r="21">
@@ -4796,11 +4796,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>7920</v>
+        <v>18318</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7920</v>
+        <v>18318</v>
       </c>
     </row>
     <row r="22">
@@ -4864,11 +4864,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>33992</v>
+        <v>58390</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33992</v>
+        <v>58390</v>
       </c>
     </row>
     <row r="24">
@@ -4898,11 +4898,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="25">
@@ -4932,11 +4932,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>2394</v>
+        <v>7772</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2394</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="26">
@@ -4966,11 +4966,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>4980</v>
+        <v>20358</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4980</v>
+        <v>20358</v>
       </c>
     </row>
     <row r="27">
@@ -5038,19 +5038,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>4999.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1256.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>398</v>
+        <v>-4601.98</v>
       </c>
     </row>
     <row r="29">
@@ -5068,11 +5068,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>1800</v>
+        <v>41786</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1800</v>
+        <v>41786</v>
       </c>
     </row>
     <row r="30">
@@ -5102,11 +5102,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>4980</v>
+        <v>15378</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4980</v>
+        <v>15378</v>
       </c>
     </row>
     <row r="31">
@@ -5136,11 +5136,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>398</v>
+        <v>2098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>398</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="32">
@@ -5204,23 +5204,23 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>10996</v>
+        <v>53292</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4000</v>
+        <v>33800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6996</v>
+        <v>19492</v>
       </c>
     </row>
     <row r="34">
@@ -5238,11 +5238,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>44562.32</v>
+        <v>55715.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>44562.32</v>
+        <v>55715.6</v>
       </c>
     </row>
     <row r="35">
@@ -5272,11 +5272,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>10598</v>
+        <v>21549</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10598</v>
+        <v>21549</v>
       </c>
     </row>
     <row r="36">
@@ -5408,11 +5408,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>398</v>
+        <v>21076</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>398</v>
+        <v>21076</v>
       </c>
     </row>
     <row r="40">
@@ -5442,11 +5442,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>106598</v>
+        <v>174296</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>106598</v>
+        <v>174296</v>
       </c>
     </row>
     <row r="41">
@@ -5476,11 +5476,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>398</v>
+        <v>3097</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>398</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="42">
@@ -5510,11 +5510,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>398</v>
+        <v>9996</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5526,7 +5526,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>398</v>
+        <v>9996</v>
       </c>
     </row>
     <row r="43">
@@ -5544,11 +5544,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>1980</v>
+        <v>3174</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1980</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="44">
@@ -5612,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>5207</v>
+        <v>21352.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5207</v>
+        <v>21352.5</v>
       </c>
     </row>
     <row r="46">
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>7810</v>
+        <v>43009</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>7810</v>
+        <v>43009</v>
       </c>
     </row>
     <row r="48">
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>20573</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>20573</v>
       </c>
     </row>
     <row r="49">
@@ -5748,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>31234</v>
+        <v>69017</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>31234</v>
+        <v>69017</v>
       </c>
     </row>
     <row r="50">
@@ -5816,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="52">
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>33994</v>
+        <v>81667</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>33994</v>
+        <v>81667</v>
       </c>
     </row>
     <row r="53">
@@ -5884,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>12104.1</v>
+        <v>43848.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>12104.1</v>
+        <v>43848.1</v>
       </c>
     </row>
     <row r="54">
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>51980</v>
+        <v>93072</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>51980</v>
+        <v>93072</v>
       </c>
     </row>
     <row r="55">
@@ -5952,11 +5952,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>398</v>
+        <v>796</v>
       </c>
     </row>
     <row r="56">
@@ -6020,11 +6020,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>10000</v>
+        <v>22378</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>10000</v>
+        <v>22378</v>
       </c>
     </row>
     <row r="58">
@@ -6088,11 +6088,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>28412</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>28412</v>
       </c>
     </row>
     <row r="60">
@@ -6122,11 +6122,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="61">
@@ -6156,11 +6156,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>23398</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>23398</v>
       </c>
     </row>
     <row r="62">
@@ -6190,11 +6190,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>29497</v>
+        <v>44497</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>29497</v>
+        <v>44497</v>
       </c>
     </row>
     <row r="63">
@@ -6224,11 +6224,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>7880</v>
+        <v>8278</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>131.3%</t>
+          <t>138.0%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>7880</v>
+        <v>8278</v>
       </c>
     </row>
   </sheetData>
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>238421</v>
+        <v>397828.56</v>
       </c>
       <c r="D2" t="n">
-        <v>1556</v>
+        <v>3199</v>
       </c>
       <c r="E2" t="n">
-        <v>190457</v>
+        <v>331873.56</v>
       </c>
       <c r="F2" t="n">
-        <v>47964</v>
+        <v>65955</v>
       </c>
     </row>
     <row r="3">
@@ -6325,16 +6325,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>198156</v>
+        <v>313984</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="E3" t="n">
-        <v>153680</v>
+        <v>252872</v>
       </c>
       <c r="F3" t="n">
-        <v>44476</v>
+        <v>61112</v>
       </c>
     </row>
     <row r="4">
@@ -6349,16 +6349,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40265</v>
+        <v>83844.56</v>
       </c>
       <c r="D4" t="n">
-        <v>1492</v>
+        <v>3074</v>
       </c>
       <c r="E4" t="n">
-        <v>36777</v>
+        <v>79001.56</v>
       </c>
       <c r="F4" t="n">
-        <v>3488</v>
+        <v>4843</v>
       </c>
     </row>
     <row r="5">
@@ -6373,16 +6373,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>413862</v>
+        <v>940396</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="E5" t="n">
-        <v>82796</v>
+        <v>127592</v>
       </c>
       <c r="F5" t="n">
-        <v>331066</v>
+        <v>812804</v>
       </c>
     </row>
     <row r="6">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>283698</v>
+        <v>683766</v>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>283698</v>
+        <v>683766</v>
       </c>
     </row>
     <row r="7">
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>130164</v>
+        <v>256630</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>82796</v>
+        <v>127592</v>
       </c>
       <c r="F7" t="n">
-        <v>47368</v>
+        <v>129038</v>
       </c>
     </row>
     <row r="8">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>221048.14</v>
+        <v>798469.59</v>
       </c>
       <c r="D8" t="n">
-        <v>183</v>
+        <v>678</v>
       </c>
       <c r="E8" t="n">
-        <v>5281.62</v>
+        <v>7452.99</v>
       </c>
       <c r="F8" t="n">
-        <v>215766.52</v>
+        <v>791016.6</v>
       </c>
     </row>
     <row r="9">
@@ -6469,16 +6469,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>136490.54</v>
+        <v>449940.91</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="E9" t="n">
-        <v>1280.2</v>
+        <v>1870.82</v>
       </c>
       <c r="F9" t="n">
-        <v>135210.34</v>
+        <v>448070.09</v>
       </c>
     </row>
     <row r="10">
@@ -6493,16 +6493,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84557.60000000001</v>
+        <v>346978.08</v>
       </c>
       <c r="D10" t="n">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="E10" t="n">
-        <v>4001.42</v>
+        <v>5582.17</v>
       </c>
       <c r="F10" t="n">
-        <v>80556.17999999999</v>
+        <v>341395.91</v>
       </c>
     </row>
     <row r="11">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>140800</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
         <v>95200</v>
-      </c>
-      <c r="D11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>49600</v>
       </c>
       <c r="F11" t="n">
         <v>45600</v>
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14578</v>
+        <v>66302</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>13398</v>
+        <v>24994</v>
       </c>
       <c r="F12" t="n">
-        <v>1180</v>
+        <v>41308</v>
       </c>
     </row>
     <row r="13">
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57600</v>
+        <v>204580</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>57600</v>
+        <v>204580</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -6589,16 +6589,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23760</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
-        <v>5940</v>
+        <v>9900</v>
       </c>
       <c r="F14" t="n">
-        <v>17820</v>
+        <v>73260</v>
       </c>
     </row>
   </sheetData>
@@ -6659,22 +6659,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238421</v>
+        <v>397828.56</v>
       </c>
       <c r="C2" t="n">
-        <v>51544</v>
+        <v>140262</v>
       </c>
       <c r="D2" t="n">
-        <v>3873</v>
+        <v>10499</v>
       </c>
       <c r="E2" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="F2" t="n">
-        <v>47671</v>
+        <v>129763</v>
       </c>
       <c r="G2" t="n">
-        <v>19.99</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="3">
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>413862</v>
+        <v>940396</v>
       </c>
       <c r="C3" t="n">
-        <v>72898</v>
+        <v>102497.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>72898</v>
+        <v>102497.98</v>
       </c>
       <c r="G3" t="n">
-        <v>17.61</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="4">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221048.14</v>
+        <v>798469.59</v>
       </c>
       <c r="C4" t="n">
-        <v>71449</v>
+        <v>266398.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6721,10 +6721,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>71449</v>
+        <v>266398.42</v>
       </c>
       <c r="G4" t="n">
-        <v>32.32</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="5">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95200</v>
+        <v>140800</v>
       </c>
       <c r="C5" t="n">
         <v>45600</v>
@@ -6749,7 +6749,7 @@
         <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>47.9</v>
+        <v>32.39</v>
       </c>
     </row>
     <row r="6">
@@ -6759,22 +6759,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14578</v>
+        <v>66302</v>
       </c>
       <c r="C6" t="n">
-        <v>37200</v>
+        <v>53106</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1998</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="F6" t="n">
-        <v>37200</v>
+        <v>51108</v>
       </c>
       <c r="G6" t="n">
-        <v>255.18</v>
+        <v>77.08</v>
       </c>
     </row>
     <row r="7">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57600</v>
+        <v>204580</v>
       </c>
       <c r="C7" t="n">
-        <v>38400</v>
+        <v>90200</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6796,10 +6796,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>38400</v>
+        <v>90200</v>
       </c>
       <c r="G7" t="n">
-        <v>66.67</v>
+        <v>44.09</v>
       </c>
     </row>
     <row r="8">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23760</v>
+        <v>83160</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="C2" t="n">
-        <v>154778</v>
+        <v>289327.98</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="C3" t="n">
-        <v>47581</v>
+        <v>73223</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -6902,26 +6902,26 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40798</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>23998</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>8067</v>
+        <v>9312</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -6930,17 +6930,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>4921</v>
+        <v>9183</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6950,13 +6950,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1941</v>
+        <v>2148</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>598</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7071,10 +7071,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>67200</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="3">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -7098,19 +7098,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>37200</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="5">
@@ -7121,14 +7121,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>30000</v>
+        <v>51108</v>
       </c>
     </row>
     <row r="6">
@@ -7139,50 +7139,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>29819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>20170</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>14600</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>1280</v>
+        <v>37662</v>
       </c>
     </row>
     <row r="10">
@@ -7211,14 +7211,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1150</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="11">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="D11" t="n">
-        <v>356</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="12">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="13">
@@ -7265,313 +7265,313 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>12000</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>9000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>11789</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>8619</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2449</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>299</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10913</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>18146</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>4335</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>4113</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -7584,12 +7584,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -7602,102 +7602,102 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>12009</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>4000</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>200</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -7710,7 +7710,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7719,52 +7719,52 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D38" t="n">
-        <v>1280</v>
+        <v>15666</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D39" t="n">
-        <v>1280</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>1551</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7776,13 +7776,13 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>385</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>347</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
@@ -7809,10 +7809,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D43" t="n">
-        <v>94</v>
+        <v>8265</v>
       </c>
     </row>
     <row r="44">
@@ -7823,14 +7823,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D44" t="n">
-        <v>38</v>
+        <v>3388</v>
       </c>
     </row>
     <row r="45">
@@ -7841,14 +7841,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="46">
@@ -7859,61 +7859,61 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>423</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>398</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -7921,6 +7921,276 @@
       </c>
       <c r="D49" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4999.98</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7961,36 +8231,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>72898</v>
+        <v>101397.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>45600</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>38400</v>
+        <v>82560</v>
       </c>
     </row>
     <row r="5">
@@ -8000,23 +8270,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>37200</v>
+        <v>51108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>29760</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="7">
@@ -8026,23 +8296,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>10269</v>
+        <v>31339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1280智慧父母成长营年卡</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3840</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="9">
@@ -8052,10 +8322,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>3588</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="10">
@@ -8065,23 +8335,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>332</v>
       </c>
       <c r="C10" t="n">
-        <v>2482</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>裴盈299青少年及儿童焦虑基础营月卡</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>598</v>
+        <v>5300</v>
       </c>
     </row>
   </sheetData>
@@ -8118,157 +8388,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="C2" t="n">
-        <v>45899</v>
+        <v>52817</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>37200</v>
+        <v>51966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30038</v>
+        <v>46899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>23938</v>
+        <v>42699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>21405</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>16812</v>
+        <v>34614</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>16508</v>
+        <v>31206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>13633</v>
+        <v>26652.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>7984</v>
+        <v>26489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>7942</v>
+        <v>16742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>6899</v>
+        <v>13690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>6600</v>
+        <v>12502</v>
       </c>
     </row>
     <row r="14">
@@ -8278,36 +8548,36 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>5000</v>
+        <v>11619</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>2607</v>
+        <v>8074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆维吾尔自治区</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1272</v>
+        <v>6899</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>130635</v>
+        <v>169874</v>
       </c>
       <c r="E2" t="n">
-        <v>37302</v>
+        <v>37586</v>
       </c>
       <c r="F2" t="n">
-        <v>93333</v>
+        <v>132288</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>62125</v>
+        <v>71953</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+110.3%</t>
+          <t>+136.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>48540</v>
+        <v>28960</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+92.3%</t>
+          <t>+356.8%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1971</v>
+        <v>2009</v>
       </c>
       <c r="E3" t="n">
-        <v>2589</v>
+        <v>2618</v>
       </c>
       <c r="F3" t="n">
-        <v>-618</v>
+        <v>-609</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9831</v>
+        <v>13972</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-85.6%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-8155</v>
+        <v>-4080</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-92.4%</t>
+          <t>-85.1%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>91972</v>
+        <v>180116</v>
       </c>
       <c r="E4" t="n">
-        <v>58112</v>
+        <v>67402</v>
       </c>
       <c r="F4" t="n">
-        <v>33860</v>
+        <v>112714</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>97552</v>
+        <v>120376</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>+49.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>68967</v>
+        <v>90916</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>+24.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,25 +695,25 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>21465</v>
+        <v>61168</v>
       </c>
       <c r="E5" t="n">
-        <v>80965</v>
+        <v>122994</v>
       </c>
       <c r="F5" t="n">
-        <v>-59500</v>
+        <v>-61826</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+32.0%</t>
+          <t>+276.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+12.5%</t>
+          <t>+16.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>125411</v>
+        <v>153305</v>
       </c>
       <c r="E6" t="n">
-        <v>14582</v>
+        <v>19103</v>
       </c>
       <c r="F6" t="n">
-        <v>110829</v>
+        <v>134202</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>87497</v>
+        <v>117058</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+43.3%</t>
+          <t>+31.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>72677</v>
+        <v>102095</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+52.5%</t>
+          <t>+31.4%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>91673</v>
+        <v>111898</v>
       </c>
       <c r="E7" t="n">
-        <v>21663</v>
+        <v>22076</v>
       </c>
       <c r="F7" t="n">
-        <v>70010</v>
+        <v>89822</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>102399</v>
+        <v>102611</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>+9.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>94973</v>
+        <v>65329</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>+37.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>57287</v>
+        <v>115504</v>
       </c>
       <c r="E8" t="n">
-        <v>16524</v>
+        <v>23285</v>
       </c>
       <c r="F8" t="n">
-        <v>40763</v>
+        <v>92219</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47912</v>
+        <v>53373</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+19.6%</t>
+          <t>+116.4%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>41205</v>
+        <v>41544</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>+122.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>282723</v>
+        <v>367911</v>
       </c>
       <c r="E9" t="n">
-        <v>129600</v>
+        <v>130600</v>
       </c>
       <c r="F9" t="n">
-        <v>153123</v>
+        <v>237311</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>218977</v>
+        <v>281541</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+29.1%</t>
+          <t>+30.7%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>165403</v>
+        <v>227967</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>406715</v>
+        <v>424812</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>406715</v>
+        <v>424812</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>274630</v>
+        <v>352171</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+48.1%</t>
+          <t>+20.6%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>274630</v>
+        <v>352171</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+48.1%</t>
+          <t>+20.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>153969</v>
+        <v>164765</v>
       </c>
       <c r="P10" t="n">
-        <v>252746</v>
+        <v>260047</v>
       </c>
       <c r="Q10" t="n">
-        <v>406317</v>
+        <v>424414</v>
       </c>
     </row>
     <row r="11">
@@ -1041,49 +1041,49 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>60287</v>
+        <v>70885</v>
       </c>
       <c r="E11" t="n">
-        <v>4999</v>
+        <v>8999</v>
       </c>
       <c r="F11" t="n">
-        <v>55287</v>
+        <v>61885</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34104</v>
+        <v>34900</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+76.8%</t>
+          <t>+103.1%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>34104</v>
+        <v>34900</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+62.1%</t>
+          <t>+77.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>7495</v>
+        <v>13495</v>
       </c>
       <c r="P11" t="n">
-        <v>47582</v>
+        <v>48180</v>
       </c>
       <c r="Q11" t="n">
         <v>47097</v>
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>102757</v>
+        <v>129637</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>102729</v>
+        <v>129609</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>43502</v>
+        <v>56520</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+136.2%</t>
+          <t>+129.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>43203</v>
+        <v>56221</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+137.8%</t>
+          <t>+130.5%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>41541</v>
+        <v>41741</v>
       </c>
       <c r="P12" t="n">
-        <v>61188</v>
+        <v>87868</v>
       </c>
       <c r="Q12" t="n">
-        <v>2327</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>126681</v>
+        <v>130905</v>
       </c>
       <c r="E13" t="n">
-        <v>4523</v>
+        <v>24389</v>
       </c>
       <c r="F13" t="n">
-        <v>122158</v>
+        <v>106515</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>130045</v>
+        <v>151961</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>119986</v>
+        <v>126295</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5529</v>
+        <v>6634</v>
       </c>
       <c r="O13" t="n">
-        <v>9633</v>
+        <v>9652</v>
       </c>
       <c r="P13" t="n">
-        <v>106996</v>
+        <v>90229</v>
       </c>
       <c r="Q13" t="n">
-        <v>14266</v>
+        <v>-4476</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>76719</v>
+        <v>88341</v>
       </c>
       <c r="E14" t="n">
         <v>5000</v>
       </c>
       <c r="F14" t="n">
-        <v>71719</v>
+        <v>83341</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>63850</v>
+        <v>67489</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+20.2%</t>
+          <t>+30.9%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46884</v>
+        <v>50523</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+53.0%</t>
+          <t>+65.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4236</v>
+        <v>5431</v>
       </c>
       <c r="O14" t="n">
-        <v>29353</v>
+        <v>29382</v>
       </c>
       <c r="P14" t="n">
-        <v>38130</v>
+        <v>48528</v>
       </c>
       <c r="Q14" t="n">
-        <v>12233</v>
+        <v>13457</v>
       </c>
     </row>
     <row r="15">
@@ -1291,23 +1291,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>76236</v>
+        <v>77051</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>76217</v>
+        <v>77013</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1315,15 +1315,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+64.3%</t>
+          <t>+66.1%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>46343</v>
+        <v>31125</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+64.5%</t>
+          <t>+147.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
         <v>442</v>
       </c>
       <c r="P15" t="n">
-        <v>75775</v>
+        <v>76571</v>
       </c>
       <c r="Q15" t="n">
         <v>27421</v>
@@ -1352,50 +1352,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>54653</v>
+        <v>66672</v>
       </c>
       <c r="E16" t="n">
         <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>54255</v>
+        <v>66274</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5097</v>
+        <v>6097</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+972.3%</t>
+          <t>+993.5%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5097</v>
+        <v>6097</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+964.4%</t>
+          <t>+987.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12059</v>
+        <v>12078</v>
       </c>
       <c r="P16" t="n">
-        <v>42196</v>
+        <v>54196</v>
       </c>
       <c r="Q16" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -1413,39 +1413,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>141067</v>
+        <v>151067</v>
       </c>
       <c r="E17" t="n">
-        <v>34077</v>
+        <v>40077</v>
       </c>
       <c r="F17" t="n">
-        <v>106990</v>
+        <v>110990</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>97596</v>
+        <v>108013</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+44.5%</t>
+          <t>+39.9%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>90897</v>
+        <v>101314</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+17.7%</t>
+          <t>+9.6%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1455,7 +1455,7 @@
         <v>1428</v>
       </c>
       <c r="P17" t="n">
-        <v>104090</v>
+        <v>108090</v>
       </c>
       <c r="Q17" t="n">
         <v>-28093</v>
@@ -1476,50 +1476,50 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>212742</v>
+        <v>244813</v>
       </c>
       <c r="E18" t="n">
         <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>212714</v>
+        <v>244785</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>133307</v>
+        <v>177572</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+59.6%</t>
+          <t>+37.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>133251</v>
+        <v>173516</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+59.6%</t>
+          <t>+41.1%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>80823</v>
+        <v>82196</v>
       </c>
       <c r="P18" t="n">
-        <v>131891</v>
+        <v>162589</v>
       </c>
       <c r="Q18" t="n">
-        <v>125114</v>
+        <v>125991</v>
       </c>
     </row>
     <row r="19">
@@ -1537,52 +1537,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>79311</v>
+        <v>98055</v>
       </c>
       <c r="E19" t="n">
         <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>83805</v>
+        <v>88103</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>+11.3%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-62173</v>
+        <v>-57875</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-227.2%</t>
+          <t>-269.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2955</v>
+        <v>3303</v>
       </c>
       <c r="O19" t="n">
-        <v>8755</v>
+        <v>10351</v>
       </c>
       <c r="P19" t="n">
-        <v>67592</v>
+        <v>84392</v>
       </c>
       <c r="Q19" t="n">
-        <v>2812</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="20">
@@ -1600,50 +1600,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>128080</v>
+        <v>173468</v>
       </c>
       <c r="E20" t="n">
-        <v>21247</v>
+        <v>38547</v>
       </c>
       <c r="F20" t="n">
-        <v>106833</v>
+        <v>134921</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>136960</v>
+        <v>180170</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>135160</v>
+        <v>178370</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>25843</v>
+        <v>68853</v>
       </c>
       <c r="P20" t="n">
-        <v>80990</v>
+        <v>66068</v>
       </c>
       <c r="Q20" t="n">
-        <v>25053</v>
+        <v>17233</v>
       </c>
     </row>
     <row r="21">
@@ -1661,54 +1661,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>2268390</v>
+        <v>2817495</v>
       </c>
       <c r="E21" t="n">
-        <v>431865</v>
+        <v>543378</v>
       </c>
       <c r="F21" t="n">
-        <v>1836524</v>
+        <v>2274117</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1691860</v>
+        <v>2046553</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+34.1%</t>
+          <t>+37.7%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1298102</v>
+        <v>1552499</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+41.5%</t>
+          <t>+46.5%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>14404</v>
+        <v>17051</v>
       </c>
       <c r="O21" t="n">
-        <v>701883</v>
+        <v>1060690</v>
       </c>
       <c r="P21" t="n">
-        <v>1120437</v>
+        <v>1196574</v>
       </c>
       <c r="Q21" t="n">
-        <v>1011826</v>
+        <v>1267212</v>
       </c>
     </row>
   </sheetData>
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>380</v>
+        <v>429</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
-        <v>475.5</v>
+        <v>1514.6</v>
       </c>
       <c r="E2" t="n">
-        <v>68094</v>
+        <v>72833</v>
       </c>
     </row>
     <row r="3">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>350.9</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="4">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1089</v>
+        <v>708</v>
       </c>
       <c r="C4" t="n">
-        <v>3380</v>
+        <v>159</v>
       </c>
       <c r="D4" t="n">
-        <v>667.6</v>
+        <v>1478.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1711</v>
+        <v>1974</v>
       </c>
     </row>
   </sheetData>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>262577</v>
+        <v>474154</v>
       </c>
       <c r="D2" t="n">
-        <v>26100</v>
+        <v>24656</v>
       </c>
       <c r="E2" t="n">
-        <v>259086</v>
+        <v>444422</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67963</v>
+        <v>152151</v>
       </c>
       <c r="D3" t="n">
         <v>85160</v>
       </c>
       <c r="E3" t="n">
-        <v>118123</v>
+        <v>175491</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>371342</v>
+        <v>434384</v>
       </c>
       <c r="D4" t="n">
-        <v>1009176</v>
+        <v>1086758</v>
       </c>
       <c r="E4" t="n">
-        <v>634616</v>
+        <v>647298</v>
       </c>
     </row>
     <row r="5">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92315</v>
+        <v>131270</v>
       </c>
       <c r="D5" t="n">
         <v>1018</v>
       </c>
       <c r="E5" t="n">
-        <v>93333</v>
+        <v>132288</v>
       </c>
     </row>
     <row r="6">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-753</v>
+        <v>-744</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-618</v>
+        <v>-609</v>
       </c>
     </row>
     <row r="7">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42887</v>
+        <v>120793</v>
       </c>
       <c r="D7" t="n">
-        <v>-9027</v>
+        <v>-8079</v>
       </c>
       <c r="E7" t="n">
-        <v>44166</v>
+        <v>122622</v>
       </c>
     </row>
     <row r="8">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-63300</v>
+        <v>-63214</v>
       </c>
       <c r="D8" t="n">
-        <v>3800</v>
+        <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>-59500</v>
+        <v>-61826</v>
       </c>
     </row>
     <row r="9">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>110810</v>
+        <v>134163</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>88431</v>
+        <v>99406</v>
       </c>
     </row>
     <row r="10">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40191</v>
+        <v>60003</v>
       </c>
       <c r="D10" t="n">
         <v>29819</v>
       </c>
       <c r="E10" t="n">
-        <v>52510</v>
+        <v>60322</v>
       </c>
     </row>
     <row r="11">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40426</v>
+        <v>91882</v>
       </c>
       <c r="D11" t="n">
         <v>337</v>
       </c>
       <c r="E11" t="n">
-        <v>40763</v>
+        <v>92219</v>
       </c>
     </row>
     <row r="12">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67963</v>
+        <v>152151</v>
       </c>
       <c r="D12" t="n">
         <v>85160</v>
       </c>
       <c r="E12" t="n">
-        <v>118123</v>
+        <v>175491</v>
       </c>
     </row>
     <row r="13">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>153969</v>
+        <v>164765</v>
       </c>
       <c r="D13" t="n">
-        <v>252746</v>
+        <v>260047</v>
       </c>
       <c r="E13" t="n">
-        <v>406317</v>
+        <v>424414</v>
       </c>
     </row>
     <row r="14">
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7495</v>
+        <v>13495</v>
       </c>
       <c r="D14" t="n">
-        <v>47582</v>
+        <v>48180</v>
       </c>
       <c r="E14" t="n">
         <v>47097</v>
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>41541</v>
+        <v>41741</v>
       </c>
       <c r="D15" t="n">
-        <v>61188</v>
+        <v>87868</v>
       </c>
       <c r="E15" t="n">
-        <v>2327</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="16">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9633</v>
+        <v>9652</v>
       </c>
       <c r="D16" t="n">
-        <v>106996</v>
+        <v>90229</v>
       </c>
       <c r="E16" t="n">
-        <v>14266</v>
+        <v>-4476</v>
       </c>
     </row>
     <row r="17">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29353</v>
+        <v>29382</v>
       </c>
       <c r="D17" t="n">
-        <v>38130</v>
+        <v>48528</v>
       </c>
       <c r="E17" t="n">
-        <v>12233</v>
+        <v>13457</v>
       </c>
     </row>
     <row r="18">
@@ -2201,7 +2201,7 @@
         <v>442</v>
       </c>
       <c r="D18" t="n">
-        <v>75775</v>
+        <v>76571</v>
       </c>
       <c r="E18" t="n">
         <v>27421</v>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12059</v>
+        <v>12078</v>
       </c>
       <c r="D19" t="n">
-        <v>42196</v>
+        <v>54196</v>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -2243,7 +2243,7 @@
         <v>1428</v>
       </c>
       <c r="D20" t="n">
-        <v>104090</v>
+        <v>108090</v>
       </c>
       <c r="E20" t="n">
         <v>-28093</v>
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80823</v>
+        <v>82196</v>
       </c>
       <c r="D21" t="n">
-        <v>131891</v>
+        <v>162589</v>
       </c>
       <c r="E21" t="n">
-        <v>125114</v>
+        <v>125991</v>
       </c>
     </row>
     <row r="22">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8755</v>
+        <v>10351</v>
       </c>
       <c r="D22" t="n">
-        <v>67592</v>
+        <v>84392</v>
       </c>
       <c r="E22" t="n">
-        <v>2812</v>
+        <v>19960</v>
       </c>
     </row>
     <row r="23">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25843</v>
+        <v>68853</v>
       </c>
       <c r="D23" t="n">
-        <v>80990</v>
+        <v>66068</v>
       </c>
       <c r="E23" t="n">
-        <v>25053</v>
+        <v>17233</v>
       </c>
     </row>
     <row r="24">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>701883</v>
+        <v>1060690</v>
       </c>
       <c r="D24" t="n">
-        <v>1120437</v>
+        <v>1196574</v>
       </c>
       <c r="E24" t="n">
-        <v>1011826</v>
+        <v>1267212</v>
       </c>
     </row>
   </sheetData>
@@ -2498,19 +2498,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-1620</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="5">
@@ -2582,19 +2582,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>4980</v>
+        <v>36440</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2602,11 +2602,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3300</v>
+        <v>34760</v>
       </c>
     </row>
     <row r="7">
@@ -2624,19 +2624,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>9960</v>
+        <v>24900</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9960</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="8">
@@ -2666,31 +2666,31 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>11580</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10750</v>
+        <v>17350</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>149.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-10750</v>
+        <v>-5770</v>
       </c>
     </row>
     <row r="9">
@@ -2708,19 +2708,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="10">
@@ -2750,19 +2750,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>21540</v>
+        <v>31500</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21540</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="11">
@@ -2792,19 +2792,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>11640</v>
+        <v>21600</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2812,11 +2812,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7660</v>
+        <v>17620</v>
       </c>
     </row>
     <row r="12">
@@ -2918,19 +2918,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>33800</v>
+        <v>63600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2938,11 +2938,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>20600</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="15">
@@ -3002,19 +3002,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>28760</v>
+        <v>32540</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3022,11 +3022,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22160</v>
+        <v>25940</v>
       </c>
     </row>
     <row r="17">
@@ -3128,19 +3128,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>27800</v>
+        <v>39800</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-6200</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="20">
@@ -3170,19 +3170,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>6600</v>
+        <v>41220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6600</v>
+        <v>41220</v>
       </c>
     </row>
     <row r="21">
@@ -3266,11 +3266,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -3380,19 +3380,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>10796</v>
+        <v>15776</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3400,11 +3400,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4196</v>
+        <v>9176</v>
       </c>
     </row>
     <row r="26">
@@ -3422,31 +3422,31 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>23338</v>
+        <v>53218</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6600</v>
+        <v>9786</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>16738</v>
+        <v>43432</v>
       </c>
     </row>
     <row r="27">
@@ -3464,19 +3464,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="28">
@@ -3506,19 +3506,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>4980</v>
+        <v>14940</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3526,11 +3526,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>373.5%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-13620</v>
+        <v>-3660</v>
       </c>
     </row>
     <row r="29">
@@ -3548,19 +3548,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4980</v>
+        <v>19920</v>
       </c>
     </row>
     <row r="30">
@@ -3590,19 +3590,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>7960</v>
+        <v>17920</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3610,11 +3610,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>150.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>-4040</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="31">
@@ -3632,19 +3632,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>50570</v>
+        <v>64250</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3652,11 +3652,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>37470</v>
+        <v>51150</v>
       </c>
     </row>
     <row r="32">
@@ -3674,19 +3674,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>16980</v>
+        <v>28980</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>16980</v>
+        <v>28980</v>
       </c>
     </row>
     <row r="33">
@@ -3716,19 +3716,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>15980</v>
+        <v>21161</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3736,11 +3736,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>11000</v>
+        <v>16181</v>
       </c>
     </row>
     <row r="34">
@@ -3842,19 +3842,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>9960</v>
+        <v>16958</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5980</v>
+        <v>12978</v>
       </c>
     </row>
     <row r="37">
@@ -3938,11 +3938,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>43708</v>
+        <v>85708</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-43708</v>
+        <v>-85708</v>
       </c>
     </row>
     <row r="39">
@@ -3968,19 +3968,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>11560</v>
+        <v>51148</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>11560</v>
+        <v>51148</v>
       </c>
     </row>
     <row r="40">
@@ -4154,19 +4154,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3000</v>
+        <v>22866.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47001.4</v>
+        <v>27134.73</v>
       </c>
     </row>
     <row r="3">
@@ -4184,11 +4184,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>18503.2</v>
+        <v>21603.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18503.2</v>
+        <v>21603.2</v>
       </c>
     </row>
     <row r="4">
@@ -4286,11 +4286,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>21230.88</v>
+        <v>22335.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>21230.88</v>
+        <v>22335.36</v>
       </c>
     </row>
     <row r="7">
@@ -4388,11 +4388,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>20636.43</v>
+        <v>21382.13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4400,11 +4400,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>20436.43</v>
+        <v>21182.13</v>
       </c>
     </row>
     <row r="10">
@@ -4422,11 +4422,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>18598</v>
+        <v>35796</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>18598</v>
+        <v>35796</v>
       </c>
     </row>
     <row r="11">
@@ -4456,11 +4456,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>7000</v>
+        <v>7800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7000</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="12">
@@ -4626,11 +4626,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>996</v>
+        <v>12996</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>996</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="17">
@@ -4694,11 +4694,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>1951.8</v>
+        <v>2530.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1951.8</v>
+        <v>2530.6</v>
       </c>
     </row>
     <row r="19">
@@ -4762,11 +4762,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>22737.5</v>
+        <v>33751.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>22737.5</v>
+        <v>33751.8</v>
       </c>
     </row>
     <row r="21">
@@ -4932,23 +4932,23 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>7772</v>
+        <v>53160</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7772</v>
+        <v>43360</v>
       </c>
     </row>
     <row r="26">
@@ -5034,23 +5034,23 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>398</v>
+        <v>996</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4999.98</v>
+        <v>8999.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1256.3%</t>
+          <t>903.6%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-4601.98</v>
+        <v>-8003.98</v>
       </c>
     </row>
     <row r="29">
@@ -5136,11 +5136,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>2098</v>
+        <v>12098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2098</v>
+        <v>12098</v>
       </c>
     </row>
     <row r="32">
@@ -5242,19 +5242,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>55715.6</v>
+        <v>49715.6</v>
       </c>
     </row>
     <row r="35">
@@ -5272,11 +5272,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>21549</v>
+        <v>31549</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>21549</v>
+        <v>31549</v>
       </c>
     </row>
     <row r="36">
@@ -5408,11 +5408,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>21076</v>
+        <v>21474</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>21076</v>
+        <v>21474</v>
       </c>
     </row>
     <row r="40">
@@ -5476,11 +5476,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>3097</v>
+        <v>3795</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3097</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="42">
@@ -5544,11 +5544,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>3174</v>
+        <v>33572</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3174</v>
+        <v>33572</v>
       </c>
     </row>
     <row r="44">
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>43009</v>
+        <v>53407</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>43009</v>
+        <v>53407</v>
       </c>
     </row>
     <row r="48">
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>81667</v>
+        <v>78324</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>81667</v>
+        <v>78324</v>
       </c>
     </row>
     <row r="53">
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>93072</v>
+        <v>104114</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>93072</v>
+        <v>104114</v>
       </c>
     </row>
     <row r="55">
@@ -5952,11 +5952,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>796</v>
+        <v>5796</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>796</v>
+        <v>5796</v>
       </c>
     </row>
     <row r="56">
@@ -6020,11 +6020,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>22378</v>
+        <v>24058</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>22378</v>
+        <v>24058</v>
       </c>
     </row>
     <row r="58">
@@ -6054,11 +6054,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="59">
@@ -6088,11 +6088,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>28412</v>
+        <v>38412</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>28412</v>
+        <v>38412</v>
       </c>
     </row>
     <row r="60">
@@ -6156,11 +6156,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>23398</v>
+        <v>24194</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>23398</v>
+        <v>24194</v>
       </c>
     </row>
     <row r="62">
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>397828.56</v>
+        <v>609916.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>3199</v>
+        <v>3692</v>
       </c>
       <c r="E2" t="n">
-        <v>331873.56</v>
+        <v>541929.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>65955</v>
+        <v>67987</v>
       </c>
     </row>
     <row r="3">
@@ -6325,16 +6325,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>313984</v>
+        <v>512895</v>
       </c>
       <c r="D3" t="n">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="E3" t="n">
-        <v>252872</v>
+        <v>450065</v>
       </c>
       <c r="F3" t="n">
-        <v>61112</v>
+        <v>62830</v>
       </c>
     </row>
     <row r="4">
@@ -6349,16 +6349,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83844.56</v>
+        <v>97021.56</v>
       </c>
       <c r="D4" t="n">
-        <v>3074</v>
+        <v>3516</v>
       </c>
       <c r="E4" t="n">
-        <v>79001.56</v>
+        <v>91864.56</v>
       </c>
       <c r="F4" t="n">
-        <v>4843</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="5">
@@ -6373,16 +6373,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>940396</v>
+        <v>1140102</v>
       </c>
       <c r="D5" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E5" t="n">
-        <v>127592</v>
+        <v>179208</v>
       </c>
       <c r="F5" t="n">
-        <v>812804</v>
+        <v>960894</v>
       </c>
     </row>
     <row r="6">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>683766</v>
+        <v>776454</v>
       </c>
       <c r="D6" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>683766</v>
+        <v>776454</v>
       </c>
     </row>
     <row r="7">
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>256630</v>
+        <v>363648</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>127592</v>
+        <v>179208</v>
       </c>
       <c r="F7" t="n">
-        <v>129038</v>
+        <v>184440</v>
       </c>
     </row>
     <row r="8">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>798469.59</v>
+        <v>839309.99</v>
       </c>
       <c r="D8" t="n">
-        <v>678</v>
+        <v>714</v>
       </c>
       <c r="E8" t="n">
-        <v>7452.99</v>
+        <v>10350.49</v>
       </c>
       <c r="F8" t="n">
-        <v>791016.6</v>
+        <v>828959.5</v>
       </c>
     </row>
     <row r="9">
@@ -6469,16 +6469,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>449940.91</v>
+        <v>475663.17</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="E9" t="n">
-        <v>1870.82</v>
+        <v>1921.32</v>
       </c>
       <c r="F9" t="n">
-        <v>448070.09</v>
+        <v>473741.85</v>
       </c>
     </row>
     <row r="10">
@@ -6493,16 +6493,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>346978.08</v>
+        <v>362096.22</v>
       </c>
       <c r="D10" t="n">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="E10" t="n">
-        <v>5582.17</v>
+        <v>8429.17</v>
       </c>
       <c r="F10" t="n">
-        <v>341395.91</v>
+        <v>353667.05</v>
       </c>
     </row>
     <row r="11">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>140800</v>
+        <v>165600</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>95200</v>
+        <v>120000</v>
       </c>
       <c r="F11" t="n">
         <v>45600</v>
@@ -6541,13 +6541,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66302</v>
+        <v>105909.9</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>24994</v>
+        <v>64601.9</v>
       </c>
       <c r="F12" t="n">
         <v>41308</v>
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>204580</v>
+        <v>227780</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>204580</v>
+        <v>227780</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -6589,13 +6589,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>85140</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>9900</v>
+        <v>11880</v>
       </c>
       <c r="F14" t="n">
         <v>73260</v>
@@ -6659,22 +6659,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>397828.56</v>
+        <v>609916.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>140262</v>
+        <v>164098</v>
       </c>
       <c r="D2" t="n">
-        <v>10499</v>
+        <v>12468</v>
       </c>
       <c r="E2" t="n">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="F2" t="n">
-        <v>129763</v>
+        <v>151630</v>
       </c>
       <c r="G2" t="n">
-        <v>32.62</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="3">
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>940396</v>
+        <v>1140102</v>
       </c>
       <c r="C3" t="n">
-        <v>102497.98</v>
+        <v>119997.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>102497.98</v>
+        <v>119997.98</v>
       </c>
       <c r="G3" t="n">
-        <v>10.9</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="4">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>798469.59</v>
+        <v>839309.99</v>
       </c>
       <c r="C4" t="n">
-        <v>266398.42</v>
+        <v>267398.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6721,10 +6721,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>266398.42</v>
+        <v>267398.42</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="5">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>140800</v>
+        <v>165600</v>
       </c>
       <c r="C5" t="n">
         <v>45600</v>
@@ -6749,7 +6749,7 @@
         <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="6">
@@ -6759,22 +6759,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66302</v>
+        <v>105909.9</v>
       </c>
       <c r="C6" t="n">
-        <v>53106</v>
+        <v>95106</v>
       </c>
       <c r="D6" t="n">
         <v>1998</v>
       </c>
       <c r="E6" t="n">
-        <v>3.01</v>
+        <v>1.89</v>
       </c>
       <c r="F6" t="n">
-        <v>51108</v>
+        <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>77.08</v>
+        <v>87.91</v>
       </c>
     </row>
     <row r="7">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204580</v>
+        <v>227780</v>
       </c>
       <c r="C7" t="n">
-        <v>90200</v>
+        <v>119866.67</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6796,10 +6796,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>90200</v>
+        <v>119866.67</v>
       </c>
       <c r="G7" t="n">
-        <v>44.09</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="8">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83160</v>
+        <v>85140</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C2" t="n">
-        <v>289327.98</v>
+        <v>332159.65</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="C3" t="n">
-        <v>73223</v>
+        <v>127087</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -6902,42 +6902,42 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>43984</v>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>40798</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9312</v>
+        <v>17000</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>9183</v>
+        <v>9492</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -6946,14 +6946,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>7000</v>
+        <v>9259</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2148</v>
+        <v>2485</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -6978,30 +6978,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>1038</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>57</v>
+        <v>617</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -7010,14 +7010,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7116,19 +7116,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>51108</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6">
@@ -7143,10 +7143,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>29819</v>
+        <v>71848</v>
       </c>
     </row>
     <row r="7">
@@ -7157,14 +7157,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>51108</v>
       </c>
     </row>
     <row r="8">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -7188,19 +7188,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>37662</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -7211,14 +7211,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
-        <v>14600</v>
+        <v>42764</v>
       </c>
     </row>
     <row r="11">
@@ -7229,14 +7229,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2519</v>
+        <v>17786</v>
       </c>
     </row>
     <row r="12">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>1478</v>
+        <v>3184</v>
       </c>
     </row>
     <row r="13">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1364</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="14">
@@ -7283,14 +7283,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>451</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="15">
@@ -7301,110 +7301,110 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>16800</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>11789</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>4429</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7416,13 +7416,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7431,268 +7431,268 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>29800</v>
+        <v>29309</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>18146</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>2862</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>598</v>
+        <v>11884</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>12009</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>9000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>114</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>86</v>
+        <v>20994.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7704,13 +7704,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>15666</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39">
@@ -7733,14 +7733,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D39" t="n">
-        <v>354</v>
+        <v>22285</v>
       </c>
     </row>
     <row r="40">
@@ -7751,14 +7751,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>343</v>
+        <v>420</v>
       </c>
     </row>
     <row r="41">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>85</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42">
@@ -7787,56 +7787,56 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>76</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>8265</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>3388</v>
+        <v>18483</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7845,57 +7845,57 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>2392</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>423</v>
+        <v>598</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -7913,248 +7913,248 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="D50" t="n">
-        <v>5000</v>
+        <v>6724</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D51" t="n">
-        <v>4999.98</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>3000</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>1128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>299</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1309</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1280</v>
+        <v>4999.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>398</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>19</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63">
@@ -8169,27 +8169,99 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8231,10 +8303,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>101397.98</v>
+        <v>118897.98</v>
       </c>
     </row>
     <row r="3">
@@ -8244,36 +8316,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>86000</v>
+        <v>115666.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>82560</v>
+        <v>93108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>51108</v>
+        <v>82560</v>
       </c>
     </row>
     <row r="6">
@@ -8296,10 +8368,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>31339</v>
+        <v>43485</v>
       </c>
     </row>
     <row r="8">
@@ -8309,10 +8381,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="9">
@@ -8322,10 +8394,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>6279</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="10">
@@ -8335,10 +8407,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>332</v>
+        <v>391</v>
       </c>
       <c r="C10" t="n">
-        <v>5735</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="11">
@@ -8348,10 +8420,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>5300</v>
+        <v>6300</v>
       </c>
     </row>
   </sheetData>
@@ -8388,14 +8460,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>52817</v>
+        <v>83243</v>
       </c>
     </row>
     <row r="3">
@@ -8405,88 +8477,88 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C3" t="n">
-        <v>51966</v>
+        <v>72326.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>46899</v>
+        <v>66134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42699</v>
+        <v>51879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>37200</v>
+        <v>42718</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>34614</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>31206</v>
+        <v>36941.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>26652.98</v>
+        <v>31225</v>
       </c>
     </row>
     <row r="10">
@@ -8496,10 +8568,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>26489</v>
+        <v>26517</v>
       </c>
     </row>
     <row r="11">
@@ -8509,10 +8581,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>16742</v>
+        <v>24617</v>
       </c>
     </row>
     <row r="12">
@@ -8522,10 +8594,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>13690</v>
+        <v>13717</v>
       </c>
     </row>
     <row r="13">
@@ -8535,10 +8607,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>12502</v>
+        <v>12858</v>
       </c>
     </row>
     <row r="14">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>424812</v>
+        <v>446792</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>424812</v>
+        <v>446792</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>352171</v>
+        <v>362171</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+20.6%</t>
+          <t>+23.4%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>352171</v>
+        <v>362171</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+20.6%</t>
+          <t>+23.4%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>164765</v>
+        <v>166745</v>
       </c>
       <c r="P10" t="n">
-        <v>260047</v>
+        <v>280047</v>
       </c>
       <c r="Q10" t="n">
-        <v>424414</v>
+        <v>426394</v>
       </c>
     </row>
     <row r="11">
@@ -1600,50 +1600,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>173468</v>
+        <v>151488</v>
       </c>
       <c r="E20" t="n">
         <v>38547</v>
       </c>
       <c r="F20" t="n">
-        <v>134921</v>
+        <v>112941</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>180170</v>
+        <v>170170</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>178370</v>
+        <v>168370</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>68853</v>
+        <v>66873</v>
       </c>
       <c r="P20" t="n">
-        <v>66068</v>
+        <v>46068</v>
       </c>
       <c r="Q20" t="n">
-        <v>17233</v>
+        <v>15253</v>
       </c>
     </row>
     <row r="21">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>164765</v>
+        <v>166745</v>
       </c>
       <c r="D13" t="n">
-        <v>260047</v>
+        <v>280047</v>
       </c>
       <c r="E13" t="n">
-        <v>424414</v>
+        <v>426394</v>
       </c>
     </row>
     <row r="14">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>68853</v>
+        <v>66873</v>
       </c>
       <c r="D23" t="n">
-        <v>66068</v>
+        <v>46068</v>
       </c>
       <c r="E23" t="n">
-        <v>17233</v>
+        <v>15253</v>
       </c>
     </row>
     <row r="24">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -5609,14 +5609,14 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="D45" t="n">
         <v>21352.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5643,14 +5643,14 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>120000</v>
       </c>
       <c r="D46" t="n">
         <v>1980</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5677,14 +5677,14 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="D47" t="n">
         <v>53407</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5711,14 +5711,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>210000</v>
       </c>
       <c r="D48" t="n">
         <v>20573</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5745,14 +5745,14 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="D49" t="n">
         <v>69017</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5779,14 +5779,14 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="D50" t="n">
         <v>398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5813,14 +5813,14 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="D51" t="n">
         <v>10000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5847,14 +5847,14 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="D52" t="n">
         <v>78324</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5881,14 +5881,14 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="D53" t="n">
         <v>43848.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5915,14 +5915,14 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="D54" t="n">
         <v>104114</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F54" t="n">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>169874</v>
+        <v>186408</v>
       </c>
       <c r="E2" t="n">
-        <v>37586</v>
+        <v>37448</v>
       </c>
       <c r="F2" t="n">
-        <v>132288</v>
+        <v>148960</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>71953</v>
+        <v>73928</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+136.1%</t>
+          <t>+152.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>28960</v>
+        <v>30859</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+356.8%</t>
+          <t>+382.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2009</v>
+        <v>2327</v>
       </c>
       <c r="E3" t="n">
         <v>2618</v>
       </c>
       <c r="F3" t="n">
-        <v>-609</v>
+        <v>-291</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -607,15 +607,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>-83.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-4080</v>
+        <v>-4099</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-85.1%</t>
+          <t>-92.9%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>180116</v>
+        <v>233179</v>
       </c>
       <c r="E4" t="n">
-        <v>67402</v>
+        <v>77711</v>
       </c>
       <c r="F4" t="n">
-        <v>112714</v>
+        <v>155468</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>120376</v>
+        <v>153947</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+49.6%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>90916</v>
+        <v>123132</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+24.0%</t>
+          <t>+26.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>61168</v>
+        <v>83693</v>
       </c>
       <c r="E5" t="n">
-        <v>122994</v>
+        <v>123031</v>
       </c>
       <c r="F5" t="n">
-        <v>-61826</v>
+        <v>-39338</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16267</v>
+        <v>22906</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+276.0%</t>
+          <t>+265.4%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-52891</v>
+        <v>-46252</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>153305</v>
+        <v>177719</v>
       </c>
       <c r="E6" t="n">
-        <v>19103</v>
+        <v>23311</v>
       </c>
       <c r="F6" t="n">
-        <v>134202</v>
+        <v>154407</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>117058</v>
+        <v>118629</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+31.0%</t>
+          <t>+49.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>102095</v>
+        <v>103554</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+31.4%</t>
+          <t>+49.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>111898</v>
+        <v>124591</v>
       </c>
       <c r="E7" t="n">
-        <v>22076</v>
+        <v>22394</v>
       </c>
       <c r="F7" t="n">
-        <v>89822</v>
+        <v>102197</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>102611</v>
+        <v>103229</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+9.1%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>65329</v>
+        <v>65922</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+37.5%</t>
+          <t>+55.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>115504</v>
+        <v>183275</v>
       </c>
       <c r="E8" t="n">
-        <v>23285</v>
+        <v>27482</v>
       </c>
       <c r="F8" t="n">
-        <v>92219</v>
+        <v>155793</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>53373</v>
+        <v>68373</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+116.4%</t>
+          <t>+168.1%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>41544</v>
+        <v>56478</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+122.0%</t>
+          <t>+175.8%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>367911</v>
+        <v>391691</v>
       </c>
       <c r="E9" t="n">
-        <v>130600</v>
+        <v>137200</v>
       </c>
       <c r="F9" t="n">
-        <v>237311</v>
+        <v>254491</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>281541</v>
+        <v>289541</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+30.7%</t>
+          <t>+35.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>227967</v>
+        <v>235967</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>446792</v>
+        <v>475597</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>446792</v>
+        <v>475597</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>362171</v>
+        <v>481547</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+23.4%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>362171</v>
+        <v>481547</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+23.4%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>166745</v>
+        <v>172758</v>
       </c>
       <c r="P10" t="n">
-        <v>280047</v>
+        <v>302839</v>
       </c>
       <c r="Q10" t="n">
-        <v>426394</v>
+        <v>435199</v>
       </c>
     </row>
     <row r="11">
@@ -1041,23 +1041,23 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>70885</v>
+        <v>121716</v>
       </c>
       <c r="E11" t="n">
-        <v>8999</v>
+        <v>19399</v>
       </c>
       <c r="F11" t="n">
-        <v>61885</v>
+        <v>102316</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+103.1%</t>
+          <t>+248.8%</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1073,20 +1073,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+77.3%</t>
+          <t>+193.2%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>13495</v>
+        <v>17528</v>
       </c>
       <c r="P11" t="n">
-        <v>48180</v>
+        <v>84578</v>
       </c>
       <c r="Q11" t="n">
-        <v>47097</v>
+        <v>74932</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>129637</v>
+        <v>150140</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>129609</v>
+        <v>150112</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>56520</v>
+        <v>66520</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+129.4%</t>
+          <t>+125.7%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>56221</v>
+        <v>66221</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+130.5%</t>
+          <t>+126.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>41741</v>
+        <v>42244</v>
       </c>
       <c r="P12" t="n">
-        <v>87868</v>
+        <v>107868</v>
       </c>
       <c r="Q12" t="n">
-        <v>4207</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>130905</v>
+        <v>147703</v>
       </c>
       <c r="E13" t="n">
-        <v>24389</v>
+        <v>25908</v>
       </c>
       <c r="F13" t="n">
-        <v>106515</v>
+        <v>121794</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>151961</v>
+        <v>174245</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>126295</v>
+        <v>148464</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6634</v>
+        <v>6816</v>
       </c>
       <c r="O13" t="n">
-        <v>9652</v>
+        <v>10349</v>
       </c>
       <c r="P13" t="n">
-        <v>90229</v>
+        <v>104629</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4476</v>
+        <v>-3995</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>88341</v>
+        <v>101087</v>
       </c>
       <c r="E14" t="n">
-        <v>5000</v>
+        <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>83341</v>
+        <v>86221</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>67489</v>
+        <v>71195</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+30.9%</t>
+          <t>+42.0%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>50523</v>
+        <v>54229</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+65.0%</t>
+          <t>+59.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5431</v>
+        <v>7276</v>
       </c>
       <c r="O14" t="n">
-        <v>29382</v>
+        <v>29121</v>
       </c>
       <c r="P14" t="n">
-        <v>48528</v>
+        <v>49824</v>
       </c>
       <c r="Q14" t="n">
-        <v>13457</v>
+        <v>15041</v>
       </c>
     </row>
     <row r="15">
@@ -1294,10 +1294,10 @@
         <v>77051</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>77013</v>
+        <v>76994</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
@@ -1311,30 +1311,30 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>46402</v>
+        <v>90788</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+66.1%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31125</v>
+        <v>75511</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+147.4%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="P15" t="n">
         <v>76571</v>
       </c>
       <c r="Q15" t="n">
-        <v>27421</v>
+        <v>27402</v>
       </c>
     </row>
     <row r="16">
@@ -1352,13 +1352,13 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>66672</v>
+        <v>66691</v>
       </c>
       <c r="E16" t="n">
         <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>66274</v>
+        <v>66293</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1372,30 +1372,30 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6097</v>
+        <v>14495</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+993.5%</t>
+          <t>+360.1%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6097</v>
+        <v>14495</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+987.0%</t>
+          <t>+357.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12078</v>
+        <v>12097</v>
       </c>
       <c r="P16" t="n">
         <v>54196</v>
       </c>
       <c r="Q16" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>151067</v>
+        <v>168196</v>
       </c>
       <c r="E17" t="n">
-        <v>40077</v>
+        <v>40058</v>
       </c>
       <c r="F17" t="n">
-        <v>110990</v>
+        <v>128138</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>108013</v>
+        <v>144226</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+39.9%</t>
+          <t>+16.6%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>101314</v>
+        <v>137527</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+9.6%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1472</v>
+        <v>5210</v>
       </c>
       <c r="O17" t="n">
-        <v>1428</v>
+        <v>1644</v>
       </c>
       <c r="P17" t="n">
-        <v>108090</v>
+        <v>121284</v>
       </c>
       <c r="Q17" t="n">
-        <v>-28093</v>
+        <v>-23741</v>
       </c>
     </row>
     <row r="18">
@@ -1476,50 +1476,50 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>244813</v>
+        <v>253557</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>19666</v>
       </c>
       <c r="F18" t="n">
-        <v>244785</v>
+        <v>233891</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>177572</v>
+        <v>179170</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+37.9%</t>
+          <t>+41.5%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>173516</v>
+        <v>175114</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+41.1%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>82196</v>
+        <v>84302</v>
       </c>
       <c r="P18" t="n">
-        <v>162589</v>
+        <v>149589</v>
       </c>
       <c r="Q18" t="n">
-        <v>125991</v>
+        <v>134299</v>
       </c>
     </row>
     <row r="19">
@@ -1537,52 +1537,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>98055</v>
+        <v>103479</v>
       </c>
       <c r="E19" t="n">
         <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>97846</v>
+        <v>103270</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>88103</v>
+        <v>102337</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+11.3%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-57875</v>
+        <v>-43641</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-269.1%</t>
+          <t>-336.6%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3303</v>
+        <v>3608</v>
       </c>
       <c r="O19" t="n">
-        <v>10351</v>
+        <v>10370</v>
       </c>
       <c r="P19" t="n">
-        <v>84392</v>
+        <v>89492</v>
       </c>
       <c r="Q19" t="n">
-        <v>19960</v>
+        <v>20284</v>
       </c>
     </row>
     <row r="20">
@@ -1600,50 +1600,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>151488</v>
+        <v>180959</v>
       </c>
       <c r="E20" t="n">
-        <v>38547</v>
+        <v>38661</v>
       </c>
       <c r="F20" t="n">
-        <v>112941</v>
+        <v>142298</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>170170</v>
+        <v>193966</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>168370</v>
+        <v>192166</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>66873</v>
+        <v>75434</v>
       </c>
       <c r="P20" t="n">
-        <v>46068</v>
+        <v>66864</v>
       </c>
       <c r="Q20" t="n">
-        <v>15253</v>
+        <v>15804</v>
       </c>
     </row>
     <row r="21">
@@ -1661,54 +1661,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>2817495</v>
+        <v>3229063</v>
       </c>
       <c r="E21" t="n">
-        <v>543378</v>
+        <v>610448</v>
       </c>
       <c r="F21" t="n">
-        <v>2274117</v>
+        <v>2618614</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2046553</v>
+        <v>2397919</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>+34.7%</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1902096</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>+37.7%</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>1552499</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>+46.5%</t>
-        </is>
-      </c>
       <c r="N21" t="n">
-        <v>17051</v>
+        <v>23121</v>
       </c>
       <c r="O21" t="n">
-        <v>1060690</v>
+        <v>1274162</v>
       </c>
       <c r="P21" t="n">
-        <v>1196574</v>
+        <v>1321530</v>
       </c>
       <c r="Q21" t="n">
-        <v>1267212</v>
+        <v>1450924</v>
       </c>
     </row>
   </sheetData>
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>429</v>
+        <v>488</v>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D2" t="n">
-        <v>1514.6</v>
+        <v>821.2</v>
       </c>
       <c r="E2" t="n">
-        <v>72833</v>
+        <v>114664</v>
       </c>
     </row>
     <row r="3">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>350.9</v>
+        <v>294.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1520</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>708</v>
+        <v>608</v>
       </c>
       <c r="C4" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="D4" t="n">
-        <v>1478.2</v>
+        <v>1357.9</v>
       </c>
       <c r="E4" t="n">
-        <v>1974</v>
+        <v>2755</v>
       </c>
     </row>
   </sheetData>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>474154</v>
+        <v>648559</v>
       </c>
       <c r="D2" t="n">
-        <v>24656</v>
+        <v>28636</v>
       </c>
       <c r="E2" t="n">
-        <v>444422</v>
+        <v>578410</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>152151</v>
+        <v>169331</v>
       </c>
       <c r="D3" t="n">
         <v>85160</v>
       </c>
       <c r="E3" t="n">
-        <v>175491</v>
+        <v>172871</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>434384</v>
+        <v>456271</v>
       </c>
       <c r="D4" t="n">
-        <v>1086758</v>
+        <v>1207734</v>
       </c>
       <c r="E4" t="n">
-        <v>647298</v>
+        <v>699643</v>
       </c>
     </row>
     <row r="5">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>131270</v>
+        <v>147942</v>
       </c>
       <c r="D5" t="n">
         <v>1018</v>
       </c>
       <c r="E5" t="n">
-        <v>132288</v>
+        <v>138960</v>
       </c>
     </row>
     <row r="6">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-744</v>
+        <v>-426</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-609</v>
+        <v>-291</v>
       </c>
     </row>
     <row r="7">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>120793</v>
+        <v>163347</v>
       </c>
       <c r="D7" t="n">
-        <v>-8079</v>
+        <v>-7879</v>
       </c>
       <c r="E7" t="n">
-        <v>122622</v>
+        <v>163576</v>
       </c>
     </row>
     <row r="8">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-63214</v>
+        <v>-40726</v>
       </c>
       <c r="D8" t="n">
         <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>-61826</v>
+        <v>-39338</v>
       </c>
     </row>
     <row r="9">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>134163</v>
+        <v>150588</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>3819</v>
       </c>
       <c r="E9" t="n">
-        <v>99406</v>
+        <v>119611</v>
       </c>
     </row>
     <row r="10">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>60003</v>
+        <v>72378</v>
       </c>
       <c r="D10" t="n">
         <v>29819</v>
       </c>
       <c r="E10" t="n">
-        <v>60322</v>
+        <v>60099</v>
       </c>
     </row>
     <row r="11">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91882</v>
+        <v>155456</v>
       </c>
       <c r="D11" t="n">
         <v>337</v>
       </c>
       <c r="E11" t="n">
-        <v>92219</v>
+        <v>135793</v>
       </c>
     </row>
     <row r="12">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>152151</v>
+        <v>169331</v>
       </c>
       <c r="D12" t="n">
         <v>85160</v>
       </c>
       <c r="E12" t="n">
-        <v>175491</v>
+        <v>172871</v>
       </c>
     </row>
     <row r="13">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>166745</v>
+        <v>172758</v>
       </c>
       <c r="D13" t="n">
-        <v>280047</v>
+        <v>302839</v>
       </c>
       <c r="E13" t="n">
-        <v>426394</v>
+        <v>435199</v>
       </c>
     </row>
     <row r="14">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13495</v>
+        <v>17528</v>
       </c>
       <c r="D14" t="n">
-        <v>48180</v>
+        <v>84578</v>
       </c>
       <c r="E14" t="n">
-        <v>47097</v>
+        <v>74932</v>
       </c>
     </row>
     <row r="15">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>41741</v>
+        <v>42244</v>
       </c>
       <c r="D15" t="n">
-        <v>87868</v>
+        <v>107868</v>
       </c>
       <c r="E15" t="n">
-        <v>4207</v>
+        <v>4312</v>
       </c>
     </row>
     <row r="16">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9652</v>
+        <v>10349</v>
       </c>
       <c r="D16" t="n">
-        <v>90229</v>
+        <v>104629</v>
       </c>
       <c r="E16" t="n">
-        <v>-4476</v>
+        <v>-3995</v>
       </c>
     </row>
     <row r="17">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29382</v>
+        <v>29121</v>
       </c>
       <c r="D17" t="n">
-        <v>48528</v>
+        <v>49824</v>
       </c>
       <c r="E17" t="n">
-        <v>13457</v>
+        <v>15041</v>
       </c>
     </row>
     <row r="18">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="D18" t="n">
         <v>76571</v>
       </c>
       <c r="E18" t="n">
-        <v>27421</v>
+        <v>27402</v>
       </c>
     </row>
     <row r="19">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12078</v>
+        <v>12097</v>
       </c>
       <c r="D19" t="n">
         <v>54196</v>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1428</v>
+        <v>1644</v>
       </c>
       <c r="D20" t="n">
-        <v>108090</v>
+        <v>121284</v>
       </c>
       <c r="E20" t="n">
-        <v>-28093</v>
+        <v>-23741</v>
       </c>
     </row>
     <row r="21">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82196</v>
+        <v>84302</v>
       </c>
       <c r="D21" t="n">
-        <v>162589</v>
+        <v>149589</v>
       </c>
       <c r="E21" t="n">
-        <v>125991</v>
+        <v>134299</v>
       </c>
     </row>
     <row r="22">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10351</v>
+        <v>10370</v>
       </c>
       <c r="D22" t="n">
-        <v>84392</v>
+        <v>89492</v>
       </c>
       <c r="E22" t="n">
-        <v>19960</v>
+        <v>20284</v>
       </c>
     </row>
     <row r="23">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>66873</v>
+        <v>75434</v>
       </c>
       <c r="D23" t="n">
-        <v>46068</v>
+        <v>66864</v>
       </c>
       <c r="E23" t="n">
-        <v>15253</v>
+        <v>15804</v>
       </c>
     </row>
     <row r="24">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1060690</v>
+        <v>1274162</v>
       </c>
       <c r="D24" t="n">
-        <v>1196574</v>
+        <v>1321530</v>
       </c>
       <c r="E24" t="n">
-        <v>1267212</v>
+        <v>1450924</v>
       </c>
     </row>
   </sheetData>
@@ -2498,19 +2498,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>14940</v>
+        <v>21420</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3360</v>
+        <v>9840</v>
       </c>
     </row>
     <row r="5">
@@ -2540,19 +2540,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>24900</v>
+        <v>34900</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2560,11 +2560,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21200</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="6">
@@ -2624,19 +2624,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>24900</v>
+        <v>54820</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>24900</v>
+        <v>54820</v>
       </c>
     </row>
     <row r="8">
@@ -2708,19 +2708,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="10">
@@ -2750,31 +2750,31 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>31500</v>
+        <v>51460</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>31500</v>
+        <v>47480</v>
       </c>
     </row>
     <row r="11">
@@ -2792,19 +2792,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>21600</v>
+        <v>31560</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2812,11 +2812,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17620</v>
+        <v>27580</v>
       </c>
     </row>
     <row r="12">
@@ -2918,19 +2918,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>63600</v>
+        <v>65600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2938,11 +2938,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>50400</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="15">
@@ -3002,19 +3002,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>32540</v>
+        <v>52340</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3022,11 +3022,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>25940</v>
+        <v>45740</v>
       </c>
     </row>
     <row r="17">
@@ -3266,11 +3266,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-1000</v>
+        <v>-7600</v>
       </c>
     </row>
     <row r="23">
@@ -3296,19 +3296,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>55600</v>
+        <v>57580</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>55600</v>
+        <v>57580</v>
       </c>
     </row>
     <row r="24">
@@ -3392,19 +3392,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6600</v>
+        <v>9090</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>9176</v>
+        <v>6686</v>
       </c>
     </row>
     <row r="26">
@@ -3422,19 +3422,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>53218</v>
+        <v>64798</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3442,11 +3442,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>43432</v>
+        <v>55012</v>
       </c>
     </row>
     <row r="27">
@@ -3464,19 +3464,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>19920</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="28">
@@ -3548,31 +3548,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>19920</v>
+        <v>29880</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>19920</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="30">
@@ -3590,19 +3590,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>17920</v>
+        <v>32860</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3610,11 +3610,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>5920</v>
+        <v>20860</v>
       </c>
     </row>
     <row r="31">
@@ -3632,19 +3632,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>64250</v>
+        <v>76848</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3652,11 +3652,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>51150</v>
+        <v>63748</v>
       </c>
     </row>
     <row r="32">
@@ -3674,19 +3674,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>28980</v>
+        <v>48780</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28980</v>
+        <v>48780</v>
       </c>
     </row>
     <row r="33">
@@ -3842,19 +3842,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>16958</v>
+        <v>25738</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>12978</v>
+        <v>21758</v>
       </c>
     </row>
     <row r="37">
@@ -3968,19 +3968,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>51148</v>
+        <v>71748</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>51148</v>
+        <v>71748</v>
       </c>
     </row>
     <row r="40">
@@ -4150,11 +4150,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>50001.4</v>
+        <v>58568.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>27134.73</v>
+        <v>35701.53</v>
       </c>
     </row>
     <row r="3">
@@ -4218,11 +4218,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>19298</v>
+        <v>26798</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19298</v>
+        <v>26798</v>
       </c>
     </row>
     <row r="5">
@@ -4252,23 +4252,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>6290.3</v>
+        <v>6688.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5190.3</v>
+        <v>4088.3</v>
       </c>
     </row>
     <row r="6">
@@ -4354,11 +4354,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>13829.91</v>
+        <v>15029.91</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13829.91</v>
+        <v>15029.91</v>
       </c>
     </row>
     <row r="9">
@@ -4388,11 +4388,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>21382.13</v>
+        <v>21687.13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21182.13</v>
+        <v>21487.13</v>
       </c>
     </row>
     <row r="10">
@@ -4490,11 +4490,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>18900</v>
+        <v>22800</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18900</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="13">
@@ -4728,11 +4728,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>33634.9</v>
+        <v>45877.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4740,11 +4740,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>28634.9</v>
+        <v>40877.8</v>
       </c>
     </row>
     <row r="20">
@@ -4762,23 +4762,23 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>33751.8</v>
+        <v>34149.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33751.8</v>
+        <v>30149.8</v>
       </c>
     </row>
     <row r="21">
@@ -4864,11 +4864,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>58390</v>
+        <v>68390</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>58390</v>
+        <v>68390</v>
       </c>
     </row>
     <row r="24">
@@ -4932,11 +4932,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>53160</v>
+        <v>61966</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4944,11 +4944,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>43360</v>
+        <v>52166</v>
       </c>
     </row>
     <row r="26">
@@ -5034,23 +5034,23 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>996</v>
+        <v>12996</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8999.98</v>
+        <v>19399.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>903.6%</t>
+          <t>149.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-8003.98</v>
+        <v>-6403.98</v>
       </c>
     </row>
     <row r="29">
@@ -5068,11 +5068,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>41786</v>
+        <v>79984</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>41786</v>
+        <v>79984</v>
       </c>
     </row>
     <row r="30">
@@ -5102,11 +5102,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>15378</v>
+        <v>15976</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15378</v>
+        <v>15976</v>
       </c>
     </row>
     <row r="31">
@@ -5204,11 +5204,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>53292</v>
+        <v>57029.78</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5216,11 +5216,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>19492</v>
+        <v>23229.78</v>
       </c>
     </row>
     <row r="34">
@@ -5238,11 +5238,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>55715.6</v>
+        <v>56511.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5250,11 +5250,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>49715.6</v>
+        <v>50511.6</v>
       </c>
     </row>
     <row r="35">
@@ -5272,11 +5272,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>31549</v>
+        <v>43549</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31549</v>
+        <v>43549</v>
       </c>
     </row>
     <row r="36">
@@ -5374,23 +5374,23 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>1.7%</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>499</v>
       </c>
     </row>
     <row r="39">
@@ -5442,23 +5442,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>174296</v>
+        <v>174694</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>174296</v>
+        <v>162694</v>
       </c>
     </row>
     <row r="41">
@@ -5476,11 +5476,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>3795</v>
+        <v>10395</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3795</v>
+        <v>10395</v>
       </c>
     </row>
     <row r="42">
@@ -5514,19 +5514,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9996</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="43">
@@ -5544,11 +5544,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>33572</v>
+        <v>35252</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>33572</v>
+        <v>35252</v>
       </c>
     </row>
     <row r="44">
@@ -5612,11 +5612,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>21352.5</v>
+        <v>21906.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21352.5</v>
+        <v>21906.5</v>
       </c>
     </row>
     <row r="46">
@@ -5680,11 +5680,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>53407</v>
+        <v>61082</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>53407</v>
+        <v>61082</v>
       </c>
     </row>
     <row r="48">
@@ -5714,11 +5714,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>20573</v>
+        <v>30573</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>20573</v>
+        <v>30573</v>
       </c>
     </row>
     <row r="49">
@@ -5884,11 +5884,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>43848.1</v>
+        <v>44106.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>43848.1</v>
+        <v>44106.1</v>
       </c>
     </row>
     <row r="54">
@@ -5918,11 +5918,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>104114</v>
+        <v>114114</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>104114</v>
+        <v>114114</v>
       </c>
     </row>
     <row r="55">
@@ -6020,11 +6020,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>24058</v>
+        <v>34058</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>24058</v>
+        <v>34058</v>
       </c>
     </row>
     <row r="58">
@@ -6088,11 +6088,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>38412</v>
+        <v>48810</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>38412</v>
+        <v>48810</v>
       </c>
     </row>
     <row r="60">
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>609916.5600000001</v>
+        <v>744693.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>3692</v>
+        <v>4283</v>
       </c>
       <c r="E2" t="n">
-        <v>541929.5600000001</v>
+        <v>665921.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>67987</v>
+        <v>78772</v>
       </c>
     </row>
     <row r="3">
@@ -6325,16 +6325,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>512895</v>
+        <v>632924</v>
       </c>
       <c r="D3" t="n">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="E3" t="n">
-        <v>450065</v>
+        <v>561277</v>
       </c>
       <c r="F3" t="n">
-        <v>62830</v>
+        <v>71647</v>
       </c>
     </row>
     <row r="4">
@@ -6349,16 +6349,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>97021.56</v>
+        <v>111769.56</v>
       </c>
       <c r="D4" t="n">
-        <v>3516</v>
+        <v>4075</v>
       </c>
       <c r="E4" t="n">
-        <v>91864.56</v>
+        <v>104644.56</v>
       </c>
       <c r="F4" t="n">
-        <v>5157</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="5">
@@ -6373,16 +6373,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1140102</v>
+        <v>1341888</v>
       </c>
       <c r="D5" t="n">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="E5" t="n">
-        <v>179208</v>
+        <v>243406</v>
       </c>
       <c r="F5" t="n">
-        <v>960894</v>
+        <v>1098482</v>
       </c>
     </row>
     <row r="6">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>776454</v>
+        <v>894838</v>
       </c>
       <c r="D6" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>776454</v>
+        <v>894838</v>
       </c>
     </row>
     <row r="7">
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>363648</v>
+        <v>447050</v>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>179208</v>
+        <v>243406</v>
       </c>
       <c r="F7" t="n">
-        <v>184440</v>
+        <v>203644</v>
       </c>
     </row>
     <row r="8">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>839309.99</v>
+        <v>854984.47</v>
       </c>
       <c r="D8" t="n">
-        <v>714</v>
+        <v>778</v>
       </c>
       <c r="E8" t="n">
-        <v>10350.49</v>
+        <v>12379.49</v>
       </c>
       <c r="F8" t="n">
-        <v>828959.5</v>
+        <v>842604.98</v>
       </c>
     </row>
     <row r="9">
@@ -6469,16 +6469,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>475663.17</v>
+        <v>477175.17</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E9" t="n">
-        <v>1921.32</v>
+        <v>2121.32</v>
       </c>
       <c r="F9" t="n">
-        <v>473741.85</v>
+        <v>475053.85</v>
       </c>
     </row>
     <row r="10">
@@ -6493,16 +6493,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>362096.22</v>
+        <v>376258.7</v>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
+        <v>460</v>
       </c>
       <c r="E10" t="n">
-        <v>8429.17</v>
+        <v>10258.17</v>
       </c>
       <c r="F10" t="n">
-        <v>353667.05</v>
+        <v>366000.53</v>
       </c>
     </row>
     <row r="11">
@@ -6517,13 +6517,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>165600</v>
+        <v>167600</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>120000</v>
+        <v>122000</v>
       </c>
       <c r="F11" t="n">
         <v>45600</v>
@@ -6541,13 +6541,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105909.9</v>
+        <v>131308.9</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>64601.9</v>
+        <v>90000.89999999999</v>
       </c>
       <c r="F12" t="n">
         <v>41308</v>
@@ -6565,16 +6565,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>227780</v>
+        <v>257080</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>227780</v>
+        <v>229280</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>27800</v>
       </c>
     </row>
     <row r="14">
@@ -6589,16 +6589,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85140</v>
+        <v>89100</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
       <c r="F14" t="n">
-        <v>73260</v>
+        <v>75240</v>
       </c>
     </row>
   </sheetData>
@@ -6659,22 +6659,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>609916.5600000001</v>
+        <v>744693.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>164098</v>
+        <v>190446.9</v>
       </c>
       <c r="D2" t="n">
-        <v>12468</v>
+        <v>13815</v>
       </c>
       <c r="E2" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="F2" t="n">
-        <v>151630</v>
+        <v>176631.9</v>
       </c>
       <c r="G2" t="n">
-        <v>24.86</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="3">
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1140102</v>
+        <v>1341888</v>
       </c>
       <c r="C3" t="n">
-        <v>119997.98</v>
+        <v>160997.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>119997.98</v>
+        <v>160997.98</v>
       </c>
       <c r="G3" t="n">
-        <v>10.53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>839309.99</v>
+        <v>854984.47</v>
       </c>
       <c r="C4" t="n">
         <v>267398.42</v>
@@ -6724,7 +6724,7 @@
         <v>267398.42</v>
       </c>
       <c r="G4" t="n">
-        <v>31.86</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="5">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>165600</v>
+        <v>167600</v>
       </c>
       <c r="C5" t="n">
         <v>45600</v>
@@ -6749,7 +6749,7 @@
         <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>27.54</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="6">
@@ -6759,22 +6759,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105909.9</v>
+        <v>131308.9</v>
       </c>
       <c r="C6" t="n">
-        <v>95106</v>
+        <v>95125.89999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1998</v>
+        <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="F6" t="n">
         <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>87.91</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="7">
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>227780</v>
+        <v>257080</v>
       </c>
       <c r="C7" t="n">
         <v>119866.67</v>
@@ -6799,7 +6799,7 @@
         <v>119866.67</v>
       </c>
       <c r="G7" t="n">
-        <v>52.62</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="8">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85140</v>
+        <v>89100</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C2" t="n">
-        <v>332159.65</v>
+        <v>362853.65</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="C3" t="n">
-        <v>127087</v>
+        <v>143213.9</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -6902,13 +6902,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50584</v>
+      </c>
+      <c r="D4" t="n">
         <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>43984</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>17000</v>
+        <v>28000</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C6" t="n">
-        <v>9492</v>
+        <v>9701</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>9259</v>
+        <v>9297</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -6962,30 +6962,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>2485</v>
+        <v>3528</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>1038</v>
+        <v>2657.9</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7121,32 +7121,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>71848</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -7157,14 +7157,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>51108</v>
+        <v>71867</v>
       </c>
     </row>
     <row r="8">
@@ -7175,14 +7175,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>51108</v>
       </c>
     </row>
     <row r="9">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -7206,37 +7206,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>42764</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>17786</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="12">
@@ -7247,14 +7247,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>3184</v>
+        <v>42682</v>
       </c>
     </row>
     <row r="13">
@@ -7265,14 +7265,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1663</v>
+        <v>17786</v>
       </c>
     </row>
     <row r="14">
@@ -7283,14 +7283,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>1478</v>
+        <v>10874</v>
       </c>
     </row>
     <row r="15">
@@ -7301,14 +7301,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>489</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="16">
@@ -7319,68 +7319,68 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>29800</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>10000</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="21">
@@ -7409,68 +7409,68 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>29309</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9000</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>114</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
@@ -7481,14 +7481,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>86</v>
+        <v>29309</v>
       </c>
     </row>
     <row r="26">
@@ -7499,14 +7499,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="27">
@@ -7517,68 +7517,68 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>16800</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>11884</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>4533</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>4274</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="32">
@@ -7607,14 +7607,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>11960</v>
       </c>
     </row>
     <row r="33">
@@ -7625,14 +7625,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>4552</v>
       </c>
     </row>
     <row r="34">
@@ -7643,86 +7643,86 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>20994.67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>3000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>299</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>96</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
-        <v>22285</v>
+        <v>26398</v>
       </c>
     </row>
     <row r="40">
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D40" t="n">
-        <v>420</v>
+        <v>485</v>
       </c>
     </row>
     <row r="41">
@@ -7787,14 +7787,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
@@ -7805,20 +7805,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7827,82 +7827,82 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>18483</v>
+        <v>20994.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>2938</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>598</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>38</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>10838.9</v>
       </c>
     </row>
     <row r="49">
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D49" t="n">
-        <v>8321</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="50">
@@ -7931,14 +7931,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D50" t="n">
-        <v>6724</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="51">
@@ -7949,14 +7949,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>3464</v>
+        <v>442</v>
       </c>
     </row>
     <row r="52">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>423</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53">
@@ -7985,14 +7985,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>114</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -8034,133 +8034,133 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>18801</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D57" t="n">
-        <v>4999.98</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>4000</v>
+        <v>598</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>5000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1309</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>1309</v>
+        <v>19609</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>398</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8169,99 +8169,261 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>11399.98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8303,10 +8465,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>118897.98</v>
+        <v>159897.98</v>
       </c>
     </row>
     <row r="3">
@@ -8342,36 +8504,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>82560</v>
+        <v>89160</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>45600</v>
+        <v>61301</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>43485</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="8">
@@ -8390,27 +8552,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>299元青春期家庭21天陪跑</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>467</v>
       </c>
       <c r="C9" t="n">
-        <v>7176</v>
+        <v>8120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>299元青春期家庭21天陪跑</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>391</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>6766</v>
+        <v>7475</v>
       </c>
     </row>
     <row r="11">
@@ -8460,27 +8622,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="C2" t="n">
-        <v>83243</v>
+        <v>86129.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>72326.67</v>
+        <v>83300</v>
       </c>
     </row>
     <row r="4">
@@ -8490,62 +8652,62 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>66134</v>
+        <v>66238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>51879</v>
+        <v>60749.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>42718</v>
+        <v>51879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>37200</v>
+        <v>42737</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>36941.98</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="9">
@@ -8555,10 +8717,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>31225</v>
+        <v>35338</v>
       </c>
     </row>
     <row r="10">
@@ -8568,10 +8730,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>26517</v>
+        <v>26640</v>
       </c>
     </row>
     <row r="11">
@@ -8581,75 +8743,75 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>24617</v>
+        <v>24816</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>13717</v>
+        <v>14827</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>12858</v>
+        <v>13858.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>11619</v>
+        <v>12896</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>8074</v>
+        <v>11619</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>6899</v>
+        <v>8112</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>186408</v>
+        <v>187351</v>
       </c>
       <c r="E2" t="n">
-        <v>37448</v>
+        <v>42656</v>
       </c>
       <c r="F2" t="n">
-        <v>148960</v>
+        <v>144695</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>73928</v>
+        <v>74742</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+152.1%</t>
+          <t>+150.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>30859</v>
+        <v>31659</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+382.7%</t>
+          <t>+357.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -588,10 +588,10 @@
         <v>2327</v>
       </c>
       <c r="E3" t="n">
-        <v>2618</v>
+        <v>12618</v>
       </c>
       <c r="F3" t="n">
-        <v>-291</v>
+        <v>-10291</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>13972</v>
+        <v>14016</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-83.3%</t>
+          <t>-83.4%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-4099</v>
+        <v>-4064</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-92.9%</t>
+          <t>+153.2%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>233179</v>
+        <v>258327</v>
       </c>
       <c r="E4" t="n">
-        <v>77711</v>
+        <v>80315</v>
       </c>
       <c r="F4" t="n">
-        <v>155468</v>
+        <v>178012</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>153947</v>
+        <v>162410</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+59.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>123132</v>
+        <v>131178</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>+35.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>83693</v>
+        <v>82312</v>
       </c>
       <c r="E5" t="n">
-        <v>123031</v>
+        <v>123050</v>
       </c>
       <c r="F5" t="n">
-        <v>-39338</v>
+        <v>-40738</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>22906</v>
+        <v>22963</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+265.4%</t>
+          <t>+258.5%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-46252</v>
+        <v>-46195</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>177719</v>
+        <v>214764</v>
       </c>
       <c r="E6" t="n">
-        <v>23311</v>
+        <v>27444</v>
       </c>
       <c r="F6" t="n">
-        <v>154407</v>
+        <v>187319</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>118629</v>
+        <v>121264</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+49.8%</t>
+          <t>+77.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>103554</v>
+        <v>105845</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+49.1%</t>
+          <t>+77.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>124591</v>
+        <v>176122</v>
       </c>
       <c r="E7" t="n">
-        <v>22394</v>
+        <v>22479</v>
       </c>
       <c r="F7" t="n">
-        <v>102197</v>
+        <v>153643</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>103229</v>
+        <v>103526</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+70.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>65922</v>
+        <v>66191</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+55.0%</t>
+          <t>+132.1%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>183275</v>
+        <v>191840</v>
       </c>
       <c r="E8" t="n">
-        <v>27482</v>
+        <v>37643</v>
       </c>
       <c r="F8" t="n">
-        <v>155793</v>
+        <v>154197</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>68373</v>
+        <v>78814</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+168.1%</t>
+          <t>+143.4%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56478</v>
+        <v>63854</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+175.8%</t>
+          <t>+141.5%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>391691</v>
+        <v>435931</v>
       </c>
       <c r="E9" t="n">
         <v>137200</v>
       </c>
       <c r="F9" t="n">
-        <v>254491</v>
+        <v>298731</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>289541</v>
+        <v>295841</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+35.3%</t>
+          <t>+47.4%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>235967</v>
+        <v>242267</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+7.9%</t>
+          <t>+23.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>475597</v>
+        <v>555659</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>475597</v>
+        <v>555659</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>481547</v>
+        <v>511531</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>+8.6%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>481547</v>
+        <v>511531</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>+8.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>172758</v>
+        <v>219995</v>
       </c>
       <c r="P10" t="n">
-        <v>302839</v>
+        <v>335664</v>
       </c>
       <c r="Q10" t="n">
-        <v>435199</v>
+        <v>505261</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>121716</v>
+        <v>142633</v>
       </c>
       <c r="E11" t="n">
         <v>19399</v>
       </c>
       <c r="F11" t="n">
-        <v>102316</v>
+        <v>123233</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34900</v>
+        <v>37294</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+248.8%</t>
+          <t>+282.5%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>34900</v>
+        <v>37294</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+193.2%</t>
+          <t>+230.4%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>17528</v>
+        <v>18047</v>
       </c>
       <c r="P11" t="n">
-        <v>84578</v>
+        <v>104976</v>
       </c>
       <c r="Q11" t="n">
-        <v>74932</v>
+        <v>75451</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>150140</v>
+        <v>150178</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>10028</v>
       </c>
       <c r="F12" t="n">
-        <v>150112</v>
+        <v>140150</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>66520</v>
+        <v>96520</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+125.7%</t>
+          <t>+55.6%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>66221</v>
+        <v>96221</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+126.7%</t>
+          <t>+45.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>42244</v>
+        <v>42282</v>
       </c>
       <c r="P12" t="n">
-        <v>107868</v>
+        <v>97868</v>
       </c>
       <c r="Q12" t="n">
-        <v>4312</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>147703</v>
+        <v>184996</v>
       </c>
       <c r="E13" t="n">
         <v>25908</v>
       </c>
       <c r="F13" t="n">
-        <v>121794</v>
+        <v>159087</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>174245</v>
+        <v>174643</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>148464</v>
+        <v>148862</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>+6.9%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>6816</v>
       </c>
       <c r="O13" t="n">
-        <v>10349</v>
+        <v>16444</v>
       </c>
       <c r="P13" t="n">
-        <v>104629</v>
+        <v>135827</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3995</v>
+        <v>-3496</v>
       </c>
     </row>
     <row r="14">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>71195</v>
+        <v>96714</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+42.0%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>54229</v>
+        <v>79548</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+59.0%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1294,36 +1294,36 @@
         <v>77051</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>6857</v>
       </c>
       <c r="F15" t="n">
-        <v>76994</v>
+        <v>70194</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>90788</v>
+        <v>98788</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>75511</v>
+        <v>83511</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
         <v>423</v>
       </c>
       <c r="P15" t="n">
-        <v>76571</v>
+        <v>69771</v>
       </c>
       <c r="Q15" t="n">
         <v>27402</v>
@@ -1352,39 +1352,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>66691</v>
+        <v>106279</v>
       </c>
       <c r="E16" t="n">
         <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>66293</v>
+        <v>105881</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14495</v>
+        <v>44095</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+360.1%</t>
+          <t>+141.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>14495</v>
+        <v>44095</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+357.4%</t>
+          <t>+140.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         <v>12097</v>
       </c>
       <c r="P16" t="n">
-        <v>54196</v>
+        <v>93784</v>
       </c>
       <c r="Q16" t="n">
-        <v>105</v>
+        <v>39693</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>168196</v>
+        <v>192514</v>
       </c>
       <c r="E17" t="n">
         <v>40058</v>
       </c>
       <c r="F17" t="n">
-        <v>128138</v>
+        <v>152456</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>144226</v>
+        <v>164643</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+16.6%</t>
+          <t>+16.9%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>137527</v>
+        <v>157944</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5210</v>
+        <v>18732</v>
       </c>
       <c r="O17" t="n">
-        <v>1644</v>
+        <v>2042</v>
       </c>
       <c r="P17" t="n">
-        <v>121284</v>
+        <v>131682</v>
       </c>
       <c r="Q17" t="n">
-        <v>-23741</v>
+        <v>-10219</v>
       </c>
     </row>
     <row r="18">
@@ -1476,50 +1476,50 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>253557</v>
+        <v>261576</v>
       </c>
       <c r="E18" t="n">
         <v>19666</v>
       </c>
       <c r="F18" t="n">
-        <v>233891</v>
+        <v>241910</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>179170</v>
+        <v>214364</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+41.5%</t>
+          <t>+22.0%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>175114</v>
+        <v>210308</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>84302</v>
+        <v>91923</v>
       </c>
       <c r="P18" t="n">
-        <v>149589</v>
+        <v>149987</v>
       </c>
       <c r="Q18" t="n">
-        <v>134299</v>
+        <v>134318</v>
       </c>
     </row>
     <row r="19">
@@ -1537,52 +1537,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>103479</v>
+        <v>113505</v>
       </c>
       <c r="E19" t="n">
         <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>103270</v>
+        <v>113296</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>102337</v>
+        <v>118235</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-43641</v>
+        <v>-27743</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-336.6%</t>
+          <t>-508.4%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>3608</v>
       </c>
       <c r="O19" t="n">
-        <v>10370</v>
+        <v>12896</v>
       </c>
       <c r="P19" t="n">
-        <v>89492</v>
+        <v>96992</v>
       </c>
       <c r="Q19" t="n">
-        <v>20284</v>
+        <v>22810</v>
       </c>
     </row>
     <row r="20">
@@ -1600,50 +1600,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>180959</v>
+        <v>212068</v>
       </c>
       <c r="E20" t="n">
-        <v>38661</v>
+        <v>38699</v>
       </c>
       <c r="F20" t="n">
-        <v>142298</v>
+        <v>173369</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>193966</v>
+        <v>204364</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>192166</v>
+        <v>202564</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>75434</v>
+        <v>82105</v>
       </c>
       <c r="P20" t="n">
-        <v>66864</v>
+        <v>91264</v>
       </c>
       <c r="Q20" t="n">
-        <v>15804</v>
+        <v>31875</v>
       </c>
     </row>
     <row r="21">
@@ -1661,54 +1661,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>3229063</v>
+        <v>3646524</v>
       </c>
       <c r="E21" t="n">
-        <v>610448</v>
+        <v>659496</v>
       </c>
       <c r="F21" t="n">
-        <v>2618614</v>
+        <v>2987027</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2397919</v>
+        <v>2634772</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+34.7%</t>
+          <t>+38.4%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1902096</v>
+        <v>2134873</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+37.7%</t>
+          <t>+39.9%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>23121</v>
+        <v>36643</v>
       </c>
       <c r="O21" t="n">
-        <v>1274162</v>
+        <v>1465609</v>
       </c>
       <c r="P21" t="n">
-        <v>1321530</v>
+        <v>1484974</v>
       </c>
       <c r="Q21" t="n">
-        <v>1450924</v>
+        <v>1652393</v>
       </c>
     </row>
   </sheetData>
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>488</v>
+        <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>821.2</v>
+        <v>845.9</v>
       </c>
       <c r="E2" t="n">
-        <v>114664</v>
+        <v>142419</v>
       </c>
     </row>
     <row r="3">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>294.9</v>
+        <v>229.7</v>
       </c>
       <c r="E3" t="n">
-        <v>581</v>
+        <v>24842</v>
       </c>
     </row>
     <row r="4">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>608</v>
+        <v>712</v>
       </c>
       <c r="C4" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="D4" t="n">
-        <v>1357.9</v>
+        <v>1376.2</v>
       </c>
       <c r="E4" t="n">
-        <v>2755</v>
+        <v>8687</v>
       </c>
     </row>
   </sheetData>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>648559</v>
+        <v>724662</v>
       </c>
       <c r="D2" t="n">
-        <v>28636</v>
+        <v>42175</v>
       </c>
       <c r="E2" t="n">
-        <v>578410</v>
+        <v>630435</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>169331</v>
+        <v>213571</v>
       </c>
       <c r="D3" t="n">
         <v>85160</v>
       </c>
       <c r="E3" t="n">
-        <v>172871</v>
+        <v>179471</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>456271</v>
+        <v>527376</v>
       </c>
       <c r="D4" t="n">
-        <v>1207734</v>
+        <v>1357639</v>
       </c>
       <c r="E4" t="n">
-        <v>699643</v>
+        <v>842487</v>
       </c>
     </row>
     <row r="5">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>147942</v>
+        <v>143677</v>
       </c>
       <c r="D5" t="n">
         <v>1018</v>
       </c>
       <c r="E5" t="n">
-        <v>138960</v>
+        <v>134695</v>
       </c>
     </row>
     <row r="6">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-426</v>
+        <v>-10426</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>163347</v>
+        <v>184352</v>
       </c>
       <c r="D7" t="n">
-        <v>-7879</v>
+        <v>-6340</v>
       </c>
       <c r="E7" t="n">
-        <v>163576</v>
+        <v>187722</v>
       </c>
     </row>
     <row r="8">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-40726</v>
+        <v>-42126</v>
       </c>
       <c r="D8" t="n">
         <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>-39338</v>
+        <v>-40738</v>
       </c>
     </row>
     <row r="9">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150588</v>
+        <v>183500</v>
       </c>
       <c r="D9" t="n">
         <v>3819</v>
       </c>
       <c r="E9" t="n">
-        <v>119611</v>
+        <v>132523</v>
       </c>
     </row>
     <row r="10">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72378</v>
+        <v>111824</v>
       </c>
       <c r="D10" t="n">
-        <v>29819</v>
+        <v>41819</v>
       </c>
       <c r="E10" t="n">
-        <v>60099</v>
+        <v>72725</v>
       </c>
     </row>
     <row r="11">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>155456</v>
+        <v>153860</v>
       </c>
       <c r="D11" t="n">
         <v>337</v>
       </c>
       <c r="E11" t="n">
-        <v>135793</v>
+        <v>143799</v>
       </c>
     </row>
     <row r="12">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>169331</v>
+        <v>213571</v>
       </c>
       <c r="D12" t="n">
         <v>85160</v>
       </c>
       <c r="E12" t="n">
-        <v>172871</v>
+        <v>179471</v>
       </c>
     </row>
     <row r="13">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>172758</v>
+        <v>219995</v>
       </c>
       <c r="D13" t="n">
-        <v>302839</v>
+        <v>335664</v>
       </c>
       <c r="E13" t="n">
-        <v>435199</v>
+        <v>505261</v>
       </c>
     </row>
     <row r="14">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17528</v>
+        <v>18047</v>
       </c>
       <c r="D14" t="n">
-        <v>84578</v>
+        <v>104976</v>
       </c>
       <c r="E14" t="n">
-        <v>74932</v>
+        <v>75451</v>
       </c>
     </row>
     <row r="15">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>42244</v>
+        <v>42282</v>
       </c>
       <c r="D15" t="n">
-        <v>107868</v>
+        <v>97868</v>
       </c>
       <c r="E15" t="n">
-        <v>4312</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="16">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10349</v>
+        <v>16444</v>
       </c>
       <c r="D16" t="n">
-        <v>104629</v>
+        <v>135827</v>
       </c>
       <c r="E16" t="n">
-        <v>-3995</v>
+        <v>-3496</v>
       </c>
     </row>
     <row r="17">
@@ -2201,7 +2201,7 @@
         <v>423</v>
       </c>
       <c r="D18" t="n">
-        <v>76571</v>
+        <v>69771</v>
       </c>
       <c r="E18" t="n">
         <v>27402</v>
@@ -2222,10 +2222,10 @@
         <v>12097</v>
       </c>
       <c r="D19" t="n">
-        <v>54196</v>
+        <v>93784</v>
       </c>
       <c r="E19" t="n">
-        <v>105</v>
+        <v>39693</v>
       </c>
     </row>
     <row r="20">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1644</v>
+        <v>2042</v>
       </c>
       <c r="D20" t="n">
-        <v>121284</v>
+        <v>131682</v>
       </c>
       <c r="E20" t="n">
-        <v>-23741</v>
+        <v>-10219</v>
       </c>
     </row>
     <row r="21">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>84302</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="n">
-        <v>149589</v>
+        <v>149987</v>
       </c>
       <c r="E21" t="n">
-        <v>134299</v>
+        <v>134318</v>
       </c>
     </row>
     <row r="22">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10370</v>
+        <v>12896</v>
       </c>
       <c r="D22" t="n">
-        <v>89492</v>
+        <v>96992</v>
       </c>
       <c r="E22" t="n">
-        <v>20284</v>
+        <v>22810</v>
       </c>
     </row>
     <row r="23">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>75434</v>
+        <v>82105</v>
       </c>
       <c r="D23" t="n">
-        <v>66864</v>
+        <v>91264</v>
       </c>
       <c r="E23" t="n">
-        <v>15804</v>
+        <v>31875</v>
       </c>
     </row>
     <row r="24">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1274162</v>
+        <v>1465609</v>
       </c>
       <c r="D24" t="n">
-        <v>1321530</v>
+        <v>1484974</v>
       </c>
       <c r="E24" t="n">
-        <v>1450924</v>
+        <v>1652393</v>
       </c>
     </row>
   </sheetData>
@@ -2426,19 +2426,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>75380</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="3">
@@ -2624,31 +2624,31 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>54820</v>
+        <v>59800</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>54820</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="8">
@@ -2750,19 +2750,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>51460</v>
+        <v>51858</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47480</v>
+        <v>47878</v>
       </c>
     </row>
     <row r="11">
@@ -2876,19 +2876,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>91380</v>
+        <v>129020</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>161.3%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>161.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>91380</v>
+        <v>129020</v>
       </c>
     </row>
     <row r="14">
@@ -3254,19 +3254,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3274,11 +3274,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-7600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -3380,19 +3380,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>15776</v>
+        <v>21154</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3400,11 +3400,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6686</v>
+        <v>12064</v>
       </c>
     </row>
     <row r="26">
@@ -3590,19 +3590,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>32860</v>
+        <v>37840</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3610,11 +3610,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>20860</v>
+        <v>25840</v>
       </c>
     </row>
     <row r="31">
@@ -3632,19 +3632,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>76848</v>
+        <v>127248</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3652,11 +3652,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>63748</v>
+        <v>114148</v>
       </c>
     </row>
     <row r="32">
@@ -3758,19 +3758,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>32679</v>
+        <v>42679</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>32679</v>
+        <v>42679</v>
       </c>
     </row>
     <row r="35">
@@ -3800,19 +3800,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>19920</v>
+        <v>23720</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>19920</v>
+        <v>23720</v>
       </c>
     </row>
     <row r="36">
@@ -3842,19 +3842,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>25738</v>
+        <v>35738</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>21758</v>
+        <v>31758</v>
       </c>
     </row>
     <row r="37">
@@ -3896,19 +3896,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>14940</v>
+        <v>10960</v>
       </c>
     </row>
     <row r="38">
@@ -4150,11 +4150,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>58568.2</v>
+        <v>78568.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35701.53</v>
+        <v>55701.53</v>
       </c>
     </row>
     <row r="3">
@@ -4184,11 +4184,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>21603.2</v>
+        <v>29303.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>21603.2</v>
+        <v>29303.2</v>
       </c>
     </row>
     <row r="4">
@@ -4218,11 +4218,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>26798</v>
+        <v>29898</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>26798</v>
+        <v>29898</v>
       </c>
     </row>
     <row r="5">
@@ -4252,11 +4252,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>6688.3</v>
+        <v>7086.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4264,11 +4264,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4088.3</v>
+        <v>4486.3</v>
       </c>
     </row>
     <row r="6">
@@ -4286,11 +4286,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>22335.36</v>
+        <v>27733.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>22335.36</v>
+        <v>27733.36</v>
       </c>
     </row>
     <row r="7">
@@ -4320,11 +4320,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>10398</v>
+        <v>10796</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10398</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="8">
@@ -4456,11 +4456,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>7800</v>
+        <v>10320</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7800</v>
+        <v>10320</v>
       </c>
     </row>
     <row r="12">
@@ -4490,11 +4490,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>22800</v>
+        <v>30300</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>22800</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="13">
@@ -4558,11 +4558,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>33196</v>
+        <v>72784</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>33196</v>
+        <v>72784</v>
       </c>
     </row>
     <row r="15">
@@ -4932,11 +4932,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>61966</v>
+        <v>77966</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4944,11 +4944,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>52166</v>
+        <v>68166</v>
       </c>
     </row>
     <row r="26">
@@ -5170,11 +5170,11 @@
         <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>398</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="33">
@@ -5204,11 +5204,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>57029.78</v>
+        <v>70181.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5216,11 +5216,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23229.78</v>
+        <v>36381.64</v>
       </c>
     </row>
     <row r="34">
@@ -5238,11 +5238,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>56511.6</v>
+        <v>67279.75999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5250,11 +5250,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>50511.6</v>
+        <v>61279.75999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5306,11 +5306,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>10000</v>
+        <v>10398</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10000</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="37">
@@ -5476,11 +5476,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>10395</v>
+        <v>18395</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10395</v>
+        <v>18395</v>
       </c>
     </row>
     <row r="42">
@@ -5612,11 +5612,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>21906.5</v>
+        <v>23481.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21906.5</v>
+        <v>23481.5</v>
       </c>
     </row>
     <row r="46">
@@ -5680,11 +5680,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>61082</v>
+        <v>66477</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>61082</v>
+        <v>66477</v>
       </c>
     </row>
     <row r="48">
@@ -5714,11 +5714,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>30573</v>
+        <v>25791</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>30573</v>
+        <v>25791</v>
       </c>
     </row>
     <row r="49">
@@ -5748,11 +5748,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>69017</v>
+        <v>95807</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>69017</v>
+        <v>95807</v>
       </c>
     </row>
     <row r="50">
@@ -5816,11 +5816,11 @@
         <v>80000</v>
       </c>
       <c r="D51" t="n">
-        <v>10000</v>
+        <v>15940</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10000</v>
+        <v>15940</v>
       </c>
     </row>
     <row r="52">
@@ -5850,11 +5850,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>78324</v>
+        <v>90504</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>78324</v>
+        <v>90504</v>
       </c>
     </row>
     <row r="53">
@@ -5884,11 +5884,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>44106.1</v>
+        <v>35106.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>44106.1</v>
+        <v>35106.1</v>
       </c>
     </row>
     <row r="54">
@@ -5918,11 +5918,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>114114</v>
+        <v>130278</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>114114</v>
+        <v>130278</v>
       </c>
     </row>
     <row r="55">
@@ -5956,19 +5956,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>172.5%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5796</v>
+        <v>-4204</v>
       </c>
     </row>
     <row r="56">
@@ -6194,19 +6194,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>44497</v>
+        <v>37697</v>
       </c>
     </row>
     <row r="63">
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>744693.5600000001</v>
+        <v>822596.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4283</v>
+        <v>4778</v>
       </c>
       <c r="E2" t="n">
-        <v>665921.5600000001</v>
+        <v>730134.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>78772</v>
+        <v>92462</v>
       </c>
     </row>
     <row r="3">
@@ -6325,16 +6325,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>632924</v>
+        <v>696996</v>
       </c>
       <c r="D3" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E3" t="n">
-        <v>561277</v>
+        <v>612149</v>
       </c>
       <c r="F3" t="n">
-        <v>71647</v>
+        <v>84847</v>
       </c>
     </row>
     <row r="4">
@@ -6349,16 +6349,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>111769.56</v>
+        <v>125600.56</v>
       </c>
       <c r="D4" t="n">
-        <v>4075</v>
+        <v>4549</v>
       </c>
       <c r="E4" t="n">
-        <v>104644.56</v>
+        <v>117985.56</v>
       </c>
       <c r="F4" t="n">
-        <v>7125</v>
+        <v>7615</v>
       </c>
     </row>
     <row r="5">
@@ -6373,16 +6373,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1341888</v>
+        <v>1562632</v>
       </c>
       <c r="D5" t="n">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="E5" t="n">
-        <v>243406</v>
+        <v>340662</v>
       </c>
       <c r="F5" t="n">
-        <v>1098482</v>
+        <v>1221970</v>
       </c>
     </row>
     <row r="6">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>894838</v>
+        <v>1001530</v>
       </c>
       <c r="D6" t="n">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F6" t="n">
-        <v>894838</v>
+        <v>989530</v>
       </c>
     </row>
     <row r="7">
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>447050</v>
+        <v>546102</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E7" t="n">
-        <v>243406</v>
+        <v>328662</v>
       </c>
       <c r="F7" t="n">
-        <v>203644</v>
+        <v>217440</v>
       </c>
     </row>
     <row r="8">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>854984.47</v>
+        <v>1058465.01</v>
       </c>
       <c r="D8" t="n">
-        <v>778</v>
+        <v>908</v>
       </c>
       <c r="E8" t="n">
-        <v>12379.49</v>
+        <v>10706.74</v>
       </c>
       <c r="F8" t="n">
-        <v>842604.98</v>
+        <v>1047758.27</v>
       </c>
     </row>
     <row r="9">
@@ -6469,16 +6469,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>477175.17</v>
+        <v>631410.54</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="E9" t="n">
-        <v>2121.32</v>
+        <v>2161.37</v>
       </c>
       <c r="F9" t="n">
-        <v>475053.85</v>
+        <v>629249.17</v>
       </c>
     </row>
     <row r="10">
@@ -6493,16 +6493,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>376258.7</v>
+        <v>425503.87</v>
       </c>
       <c r="D10" t="n">
-        <v>460</v>
+        <v>510</v>
       </c>
       <c r="E10" t="n">
-        <v>10258.17</v>
+        <v>8545.370000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>366000.53</v>
+        <v>416958.5</v>
       </c>
     </row>
     <row r="11">
@@ -6520,7 +6520,7 @@
         <v>167600</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>122000</v>
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>131308.9</v>
+        <v>176691.9</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>90000.89999999999</v>
+        <v>95795.89999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>41308</v>
+        <v>80896</v>
       </c>
     </row>
     <row r="13">
@@ -6589,16 +6589,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>89100</v>
+        <v>95040</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
         <v>13860</v>
       </c>
       <c r="F14" t="n">
-        <v>75240</v>
+        <v>81180</v>
       </c>
     </row>
   </sheetData>
@@ -6659,22 +6659,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>744693.5600000001</v>
+        <v>822596.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>190446.9</v>
+        <v>200694.9</v>
       </c>
       <c r="D2" t="n">
-        <v>13815</v>
+        <v>14728</v>
       </c>
       <c r="E2" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="F2" t="n">
-        <v>176631.9</v>
+        <v>185966.9</v>
       </c>
       <c r="G2" t="n">
-        <v>23.72</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="3">
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1341888</v>
+        <v>1562632</v>
       </c>
       <c r="C3" t="n">
-        <v>160997.98</v>
+        <v>199797.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>160997.98</v>
+        <v>199797.98</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="4">
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>854984.47</v>
+        <v>1058465.01</v>
       </c>
       <c r="C4" t="n">
-        <v>267398.42</v>
+        <v>399973.42</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6721,10 +6721,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>267398.42</v>
+        <v>399973.42</v>
       </c>
       <c r="G4" t="n">
-        <v>31.28</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="5">
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>131308.9</v>
+        <v>176691.9</v>
       </c>
       <c r="C6" t="n">
         <v>95125.89999999999</v>
@@ -6768,13 +6768,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="F6" t="n">
         <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>70.91</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="7">
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89100</v>
+        <v>95040</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C2" t="n">
-        <v>362853.65</v>
+        <v>393075.65</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C3" t="n">
-        <v>143213.9</v>
+        <v>152617.9</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -6902,13 +6902,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>57384</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>50584</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>9701</v>
+        <v>11834</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
-        <v>9297</v>
+        <v>9411</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>2657.9</v>
+        <v>3032.9</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -7034,7 +7034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>42682</v>
+        <v>42819</v>
       </c>
     </row>
     <row r="13">
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>10874</v>
+        <v>10966</v>
       </c>
     </row>
     <row r="15">
@@ -7301,14 +7301,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>2490</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="16">
@@ -7319,14 +7319,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1741</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="17">
@@ -7337,14 +7337,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>1573</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="18">
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>527</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19">
@@ -7386,241 +7386,241 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>29800</v>
+        <v>17073</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>10000</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>200</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>29309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>190</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>86</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>16800</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>11960</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7629,88 +7629,88 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>4552</v>
+        <v>29309</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>4022</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>57</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D39" t="n">
-        <v>26398</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="40">
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D40" t="n">
-        <v>485</v>
+        <v>10513</v>
       </c>
     </row>
     <row r="41">
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43">
@@ -7818,73 +7818,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>20994.67</v>
+        <v>14885.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D45" t="n">
-        <v>4500</v>
+        <v>8396</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D46" t="n">
-        <v>299</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>115</v>
+        <v>490</v>
       </c>
     </row>
     <row r="48">
@@ -7895,14 +7895,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>10838.9</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49">
@@ -7913,14 +7913,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>8377</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
@@ -7931,14 +7931,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>3464</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
@@ -7949,86 +7949,86 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>442</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>114</v>
+        <v>20994.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>38</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>19</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>19</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56">
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56" t="n">
-        <v>18801</v>
+        <v>18820</v>
       </c>
     </row>
     <row r="57">
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D57" t="n">
-        <v>2938</v>
+        <v>2976</v>
       </c>
     </row>
     <row r="58">
@@ -8111,32 +8111,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>19609</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -8147,14 +8147,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>38</v>
+        <v>19609</v>
       </c>
     </row>
     <row r="63">
@@ -8165,32 +8165,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>11399.98</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -8201,32 +8201,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>8000</v>
+        <v>11399.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>9318</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="67">
@@ -8237,14 +8237,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>5500</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="68">
@@ -8255,14 +8255,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>29</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="69">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1309</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -8309,68 +8309,68 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1309</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>398</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>299</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>57</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="75">
@@ -8394,36 +8394,90 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="C80" t="n">
         <v>1</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D80" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8465,10 +8519,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>159897.98</v>
+        <v>171897.98</v>
       </c>
     </row>
     <row r="3">
@@ -8517,10 +8571,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>61301</v>
+        <v>70261</v>
       </c>
     </row>
     <row r="7">
@@ -8539,53 +8593,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>13200</v>
+        <v>33100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>467</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>8120</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>299元青春期家庭21天陪跑</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>518</v>
       </c>
       <c r="C10" t="n">
-        <v>7475</v>
+        <v>9013</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>299元青春期家庭21天陪跑</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>6300</v>
+        <v>7774</v>
       </c>
     </row>
   </sheetData>
@@ -8626,10 +8680,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C2" t="n">
-        <v>86129.67</v>
+        <v>108219.67</v>
       </c>
     </row>
     <row r="3">
@@ -8639,10 +8693,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>83300</v>
+        <v>83319</v>
       </c>
     </row>
     <row r="4">
@@ -8652,10 +8706,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>66238</v>
+        <v>66390</v>
       </c>
     </row>
     <row r="5">
@@ -8665,10 +8719,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>60749.98</v>
+        <v>60825.98</v>
       </c>
     </row>
     <row r="6">
@@ -8713,27 +8767,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>35338</v>
+        <v>36687</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>26640</v>
+        <v>35722</v>
       </c>
     </row>
     <row r="11">
@@ -8743,75 +8797,75 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>24816</v>
+        <v>28862</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>14827</v>
+        <v>18629</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C13" t="n">
-        <v>13858.9</v>
+        <v>14827</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>12896</v>
+        <v>13877.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
-        <v>11619</v>
+        <v>12934</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>8112</v>
+        <v>11619</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>187351</v>
+        <v>226185</v>
       </c>
       <c r="E2" t="n">
-        <v>42656</v>
+        <v>48873</v>
       </c>
       <c r="F2" t="n">
-        <v>144695</v>
+        <v>177311</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>74742</v>
+        <v>76972</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+150.7%</t>
+          <t>+193.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>31659</v>
+        <v>33265</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+357.0%</t>
+          <t>+433.0%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2327</v>
+        <v>2374</v>
       </c>
       <c r="E3" t="n">
-        <v>12618</v>
+        <v>17617</v>
       </c>
       <c r="F3" t="n">
-        <v>-10291</v>
+        <v>-15243</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14016</v>
+        <v>14372</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-83.5%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-4064</v>
+        <v>-10409</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+153.2%</t>
+          <t>+46.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>258327</v>
+        <v>283989</v>
       </c>
       <c r="E4" t="n">
-        <v>80315</v>
+        <v>85383</v>
       </c>
       <c r="F4" t="n">
-        <v>178012</v>
+        <v>198606</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>162410</v>
+        <v>193192</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+59.1%</t>
+          <t>+47.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>131178</v>
+        <v>111956</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+35.7%</t>
+          <t>+77.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>82312</v>
+        <v>88050</v>
       </c>
       <c r="E5" t="n">
-        <v>123050</v>
+        <v>123069</v>
       </c>
       <c r="F5" t="n">
-        <v>-40738</v>
+        <v>-35019</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>22963</v>
+        <v>23329</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+258.5%</t>
+          <t>+277.4%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-46195</v>
+        <v>-45829</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>214764</v>
+        <v>282837</v>
       </c>
       <c r="E6" t="n">
-        <v>27444</v>
+        <v>31751</v>
       </c>
       <c r="F6" t="n">
-        <v>187319</v>
+        <v>251085</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>121264</v>
+        <v>135037</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+77.1%</t>
+          <t>+109.5%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>105845</v>
+        <v>94039</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+77.0%</t>
+          <t>+167.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>176122</v>
+        <v>204887</v>
       </c>
       <c r="E7" t="n">
-        <v>22479</v>
+        <v>31890</v>
       </c>
       <c r="F7" t="n">
-        <v>153643</v>
+        <v>172997</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>103526</v>
+        <v>141875</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+70.1%</t>
+          <t>+44.4%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>66191</v>
+        <v>104515</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+132.1%</t>
+          <t>+65.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>191840</v>
+        <v>194751</v>
       </c>
       <c r="E8" t="n">
-        <v>37643</v>
+        <v>71584</v>
       </c>
       <c r="F8" t="n">
-        <v>154197</v>
+        <v>123167</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>78814</v>
+        <v>169379</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+143.4%</t>
+          <t>+15.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>63854</v>
+        <v>154372</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+141.5%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>435931</v>
+        <v>467449</v>
       </c>
       <c r="E9" t="n">
-        <v>137200</v>
+        <v>139000</v>
       </c>
       <c r="F9" t="n">
-        <v>298731</v>
+        <v>328449</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>295841</v>
+        <v>315641</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+47.4%</t>
+          <t>+48.1%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>242267</v>
+        <v>262067</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+23.3%</t>
+          <t>+25.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>555659</v>
+        <v>558851</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>555659</v>
+        <v>558851</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>511531</v>
+        <v>571948</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+8.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>511531</v>
+        <v>571948</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+8.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>219995</v>
+        <v>220995</v>
       </c>
       <c r="P10" t="n">
-        <v>335664</v>
+        <v>337856</v>
       </c>
       <c r="Q10" t="n">
-        <v>505261</v>
+        <v>508453</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>142633</v>
+        <v>143231</v>
       </c>
       <c r="E11" t="n">
-        <v>19399</v>
+        <v>26399</v>
       </c>
       <c r="F11" t="n">
-        <v>123233</v>
+        <v>116831</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>37294</v>
+        <v>40294</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+282.5%</t>
+          <t>+255.5%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>37294</v>
+        <v>40285</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+230.4%</t>
+          <t>+190.0%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>18047</v>
+        <v>18445</v>
       </c>
       <c r="P11" t="n">
-        <v>104976</v>
+        <v>98176</v>
       </c>
       <c r="Q11" t="n">
-        <v>75451</v>
+        <v>75651</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>150178</v>
+        <v>201094</v>
       </c>
       <c r="E12" t="n">
         <v>10028</v>
       </c>
       <c r="F12" t="n">
-        <v>140150</v>
+        <v>191066</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>96520</v>
+        <v>126918</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+55.6%</t>
+          <t>+58.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>96221</v>
+        <v>126619</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+45.7%</t>
+          <t>+50.9%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>42282</v>
+        <v>52699</v>
       </c>
       <c r="P12" t="n">
-        <v>97868</v>
+        <v>138367</v>
       </c>
       <c r="Q12" t="n">
-        <v>4350</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>184996</v>
+        <v>211257</v>
       </c>
       <c r="E13" t="n">
         <v>25908</v>
       </c>
       <c r="F13" t="n">
-        <v>159087</v>
+        <v>185348</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>174643</v>
+        <v>184643</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+14.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>148862</v>
+        <v>158862</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+6.9%</t>
+          <t>+16.7%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>6816</v>
       </c>
       <c r="O13" t="n">
-        <v>16444</v>
+        <v>17307</v>
       </c>
       <c r="P13" t="n">
-        <v>135827</v>
+        <v>161225</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3496</v>
+        <v>-3429</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>101087</v>
+        <v>123464</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>86221</v>
+        <v>108598</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>96714</v>
+        <v>97656</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>+26.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>79548</v>
+        <v>80490</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+8.4%</t>
+          <t>+34.9%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>7276</v>
       </c>
       <c r="O14" t="n">
-        <v>29121</v>
+        <v>49420</v>
       </c>
       <c r="P14" t="n">
-        <v>49824</v>
+        <v>51902</v>
       </c>
       <c r="Q14" t="n">
-        <v>15041</v>
+        <v>17020</v>
       </c>
     </row>
     <row r="15">
@@ -1291,50 +1291,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>77051</v>
+        <v>77070</v>
       </c>
       <c r="E15" t="n">
-        <v>6857</v>
+        <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>70194</v>
+        <v>61213</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>98788</v>
+        <v>110788</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>83511</v>
+        <v>95511</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="P15" t="n">
-        <v>69771</v>
+        <v>60771</v>
       </c>
       <c r="Q15" t="n">
-        <v>27402</v>
+        <v>27421</v>
       </c>
     </row>
     <row r="16">
@@ -1352,47 +1352,47 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>106279</v>
+        <v>107075</v>
       </c>
       <c r="E16" t="n">
         <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>105881</v>
+        <v>106677</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>44095</v>
+        <v>52693</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+141.0%</t>
+          <t>+103.2%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>44095</v>
+        <v>52693</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+140.1%</t>
+          <t>+102.5%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12097</v>
+        <v>12495</v>
       </c>
       <c r="P16" t="n">
-        <v>93784</v>
+        <v>94182</v>
       </c>
       <c r="Q16" t="n">
         <v>39693</v>
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>192514</v>
+        <v>192525</v>
       </c>
       <c r="E17" t="n">
-        <v>40058</v>
+        <v>46658</v>
       </c>
       <c r="F17" t="n">
-        <v>152456</v>
+        <v>145867</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>164643</v>
+        <v>166248</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>+15.8%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>157944</v>
+        <v>159549</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>18732</v>
       </c>
       <c r="O17" t="n">
-        <v>2042</v>
+        <v>2053</v>
       </c>
       <c r="P17" t="n">
-        <v>131682</v>
+        <v>125082</v>
       </c>
       <c r="Q17" t="n">
-        <v>-10219</v>
+        <v>-16808</v>
       </c>
     </row>
     <row r="18">
@@ -1476,50 +1476,50 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>261576</v>
+        <v>285737</v>
       </c>
       <c r="E18" t="n">
         <v>19666</v>
       </c>
       <c r="F18" t="n">
-        <v>241910</v>
+        <v>266071</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>214364</v>
+        <v>222982</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+22.0%</t>
+          <t>+28.1%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>210308</v>
+        <v>208926</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+27.4%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>91923</v>
+        <v>99340</v>
       </c>
       <c r="P18" t="n">
-        <v>149987</v>
+        <v>166731</v>
       </c>
       <c r="Q18" t="n">
-        <v>134318</v>
+        <v>148479</v>
       </c>
     </row>
     <row r="19">
@@ -1537,52 +1537,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>113505</v>
+        <v>114093</v>
       </c>
       <c r="E19" t="n">
         <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>113296</v>
+        <v>113884</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>118235</v>
+        <v>123537</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-27743</v>
+        <v>-22460</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-508.4%</t>
+          <t>-607.0%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3608</v>
+        <v>3616</v>
       </c>
       <c r="O19" t="n">
-        <v>12896</v>
+        <v>10376</v>
       </c>
       <c r="P19" t="n">
-        <v>96992</v>
+        <v>100092</v>
       </c>
       <c r="Q19" t="n">
-        <v>22810</v>
+        <v>20298</v>
       </c>
     </row>
     <row r="20">
@@ -1600,23 +1600,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>212068</v>
+        <v>228790</v>
       </c>
       <c r="E20" t="n">
-        <v>38699</v>
+        <v>40737</v>
       </c>
       <c r="F20" t="n">
-        <v>173369</v>
+        <v>188053</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1624,26 +1624,26 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+12.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>202564</v>
+        <v>195564</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>82105</v>
+        <v>82993</v>
       </c>
       <c r="P20" t="n">
-        <v>91264</v>
+        <v>105060</v>
       </c>
       <c r="Q20" t="n">
-        <v>31875</v>
+        <v>31967</v>
       </c>
     </row>
     <row r="21">
@@ -1661,54 +1661,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>3646524</v>
+        <v>3993714</v>
       </c>
       <c r="E21" t="n">
-        <v>659496</v>
+        <v>749896</v>
       </c>
       <c r="F21" t="n">
-        <v>2987027</v>
+        <v>3243817</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2634772</v>
+        <v>2971872</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+38.4%</t>
+          <t>+34.4%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2134873</v>
+        <v>2371966</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+39.9%</t>
+          <t>+36.8%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>36643</v>
+        <v>36651</v>
       </c>
       <c r="O21" t="n">
-        <v>1465609</v>
+        <v>1660765</v>
       </c>
       <c r="P21" t="n">
-        <v>1484974</v>
+        <v>1546600</v>
       </c>
       <c r="Q21" t="n">
-        <v>1652393</v>
+        <v>1762495</v>
       </c>
     </row>
   </sheetData>
@@ -1759,16 +1759,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D2" t="n">
-        <v>845.9</v>
+        <v>931.1</v>
       </c>
       <c r="E2" t="n">
-        <v>142419</v>
+        <v>128358</v>
       </c>
     </row>
     <row r="3">
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>229.7</v>
+        <v>327.6</v>
       </c>
       <c r="E3" t="n">
-        <v>24842</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>712</v>
+        <v>588</v>
       </c>
       <c r="C4" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D4" t="n">
-        <v>1376.2</v>
+        <v>1589.5</v>
       </c>
       <c r="E4" t="n">
-        <v>8687</v>
+        <v>7598</v>
       </c>
     </row>
   </sheetData>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>724662</v>
+        <v>872029</v>
       </c>
       <c r="D2" t="n">
-        <v>42175</v>
+        <v>875</v>
       </c>
       <c r="E2" t="n">
-        <v>630435</v>
+        <v>724909</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>213571</v>
+        <v>222169</v>
       </c>
       <c r="D3" t="n">
-        <v>85160</v>
+        <v>106280</v>
       </c>
       <c r="E3" t="n">
-        <v>179471</v>
+        <v>183971</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>527376</v>
+        <v>566566</v>
       </c>
       <c r="D4" t="n">
-        <v>1357639</v>
+        <v>1439445</v>
       </c>
       <c r="E4" t="n">
-        <v>842487</v>
+        <v>853614</v>
       </c>
     </row>
     <row r="5">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>143677</v>
+        <v>176293</v>
       </c>
       <c r="D5" t="n">
         <v>1018</v>
       </c>
       <c r="E5" t="n">
-        <v>134695</v>
+        <v>167311</v>
       </c>
     </row>
     <row r="6">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-10426</v>
+        <v>-15378</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-291</v>
+        <v>-5243</v>
       </c>
     </row>
     <row r="7">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>184352</v>
+        <v>204946</v>
       </c>
       <c r="D7" t="n">
         <v>-6340</v>
       </c>
       <c r="E7" t="n">
-        <v>187722</v>
+        <v>207718</v>
       </c>
     </row>
     <row r="8">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-42126</v>
+        <v>-36407</v>
       </c>
       <c r="D8" t="n">
         <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>-40738</v>
+        <v>-35019</v>
       </c>
     </row>
     <row r="9">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>183500</v>
+        <v>247266</v>
       </c>
       <c r="D9" t="n">
         <v>3819</v>
       </c>
       <c r="E9" t="n">
-        <v>132523</v>
+        <v>196289</v>
       </c>
     </row>
     <row r="10">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>111824</v>
+        <v>143178</v>
       </c>
       <c r="D10" t="n">
-        <v>41819</v>
+        <v>29819</v>
       </c>
       <c r="E10" t="n">
-        <v>72725</v>
+        <v>81083</v>
       </c>
     </row>
     <row r="11">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>153860</v>
+        <v>152130</v>
       </c>
       <c r="D11" t="n">
-        <v>337</v>
+        <v>-28963</v>
       </c>
       <c r="E11" t="n">
-        <v>143799</v>
+        <v>112769</v>
       </c>
     </row>
     <row r="12">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>213571</v>
+        <v>222169</v>
       </c>
       <c r="D12" t="n">
-        <v>85160</v>
+        <v>106280</v>
       </c>
       <c r="E12" t="n">
-        <v>179471</v>
+        <v>183971</v>
       </c>
     </row>
     <row r="13">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>219995</v>
+        <v>220995</v>
       </c>
       <c r="D13" t="n">
-        <v>335664</v>
+        <v>337856</v>
       </c>
       <c r="E13" t="n">
-        <v>505261</v>
+        <v>508453</v>
       </c>
     </row>
     <row r="14">
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18047</v>
+        <v>18445</v>
       </c>
       <c r="D14" t="n">
-        <v>104976</v>
+        <v>98176</v>
       </c>
       <c r="E14" t="n">
-        <v>75451</v>
+        <v>75651</v>
       </c>
     </row>
     <row r="15">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>42282</v>
+        <v>52699</v>
       </c>
       <c r="D15" t="n">
-        <v>97868</v>
+        <v>138367</v>
       </c>
       <c r="E15" t="n">
-        <v>4350</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="16">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16444</v>
+        <v>17307</v>
       </c>
       <c r="D16" t="n">
-        <v>135827</v>
+        <v>161225</v>
       </c>
       <c r="E16" t="n">
-        <v>-3496</v>
+        <v>-3429</v>
       </c>
     </row>
     <row r="17">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29121</v>
+        <v>49420</v>
       </c>
       <c r="D17" t="n">
-        <v>49824</v>
+        <v>51902</v>
       </c>
       <c r="E17" t="n">
-        <v>15041</v>
+        <v>17020</v>
       </c>
     </row>
     <row r="18">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="D18" t="n">
-        <v>69771</v>
+        <v>60771</v>
       </c>
       <c r="E18" t="n">
-        <v>27402</v>
+        <v>27421</v>
       </c>
     </row>
     <row r="19">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12097</v>
+        <v>12495</v>
       </c>
       <c r="D19" t="n">
-        <v>93784</v>
+        <v>94182</v>
       </c>
       <c r="E19" t="n">
         <v>39693</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2042</v>
+        <v>2053</v>
       </c>
       <c r="D20" t="n">
-        <v>131682</v>
+        <v>125082</v>
       </c>
       <c r="E20" t="n">
-        <v>-10219</v>
+        <v>-16808</v>
       </c>
     </row>
     <row r="21">
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>91923</v>
+        <v>99340</v>
       </c>
       <c r="D21" t="n">
-        <v>149987</v>
+        <v>166731</v>
       </c>
       <c r="E21" t="n">
-        <v>134318</v>
+        <v>148479</v>
       </c>
     </row>
     <row r="22">
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12896</v>
+        <v>10376</v>
       </c>
       <c r="D22" t="n">
-        <v>96992</v>
+        <v>100092</v>
       </c>
       <c r="E22" t="n">
-        <v>22810</v>
+        <v>20298</v>
       </c>
     </row>
     <row r="23">
@@ -2303,13 +2303,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>82105</v>
+        <v>82993</v>
       </c>
       <c r="D23" t="n">
-        <v>91264</v>
+        <v>105060</v>
       </c>
       <c r="E23" t="n">
-        <v>31875</v>
+        <v>31967</v>
       </c>
     </row>
     <row r="24">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1465609</v>
+        <v>1660765</v>
       </c>
       <c r="D24" t="n">
-        <v>1484974</v>
+        <v>1546600</v>
       </c>
       <c r="E24" t="n">
-        <v>1652393</v>
+        <v>1762495</v>
       </c>
     </row>
   </sheetData>
@@ -2414,31 +2414,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>75380</v>
+        <v>91940</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4980</v>
+        <v>8366.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>70400</v>
+        <v>83573.34</v>
       </c>
     </row>
     <row r="3">
@@ -2540,31 +2540,31 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>34900</v>
+        <v>54820</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3700</v>
+        <v>6397.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>31200</v>
+        <v>48422.5</v>
       </c>
     </row>
     <row r="6">
@@ -2678,19 +2678,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17350</v>
+        <v>47150</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>149.8%</t>
+          <t>407.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-5770</v>
+        <v>-35570</v>
       </c>
     </row>
     <row r="9">
@@ -2720,19 +2720,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>10960</v>
       </c>
     </row>
     <row r="10">
@@ -2918,31 +2918,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>65600</v>
+        <v>75600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>13200</v>
+        <v>15000</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>52400</v>
+        <v>60600</v>
       </c>
     </row>
     <row r="15">
@@ -3002,19 +3002,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>52340</v>
+        <v>52738</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3022,11 +3022,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>45740</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="17">
@@ -3128,19 +3128,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>39800</v>
+        <v>60920</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3148,11 +3148,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5800</v>
+        <v>26920</v>
       </c>
     </row>
     <row r="20">
@@ -3392,19 +3392,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>9090</v>
+        <v>13070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12064</v>
+        <v>8084</v>
       </c>
     </row>
     <row r="26">
@@ -3422,19 +3422,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>64798</v>
+        <v>70376</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3442,11 +3442,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>55012</v>
+        <v>60590</v>
       </c>
     </row>
     <row r="27">
@@ -3590,19 +3590,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>37840</v>
+        <v>47800</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3610,11 +3610,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>25840</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="31">
@@ -3632,31 +3632,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>127248</v>
+        <v>148204</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>13100</v>
+        <v>17080</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>114148</v>
+        <v>131124</v>
       </c>
     </row>
     <row r="32">
@@ -3674,31 +3674,31 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>48780</v>
+        <v>68700</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>48780</v>
+        <v>64720</v>
       </c>
     </row>
     <row r="33">
@@ -3716,31 +3716,31 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>21161</v>
+        <v>27761</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4980</v>
+        <v>9960</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>16181</v>
+        <v>17801</v>
       </c>
     </row>
     <row r="34">
@@ -3758,19 +3758,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>42679</v>
+        <v>57619</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>42679</v>
+        <v>57619</v>
       </c>
     </row>
     <row r="35">
@@ -3800,19 +3800,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>23720</v>
+        <v>33680</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>23720</v>
+        <v>33680</v>
       </c>
     </row>
     <row r="36">
@@ -3842,19 +3842,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>35738</v>
+        <v>45698</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3862,11 +3862,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>31758</v>
+        <v>41718</v>
       </c>
     </row>
     <row r="37">
@@ -3884,19 +3884,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>14940</v>
+        <v>29880</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3904,11 +3904,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>10960</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="38">
@@ -3926,19 +3926,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3946,11 +3946,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1503.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-85708</v>
+        <v>-80008</v>
       </c>
     </row>
     <row r="39">
@@ -4150,11 +4150,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>78568.2</v>
+        <v>83568.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55701.53</v>
+        <v>60701.53</v>
       </c>
     </row>
     <row r="3">
@@ -4218,11 +4218,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>29898</v>
+        <v>40296</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4234,7 +4234,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>29898</v>
+        <v>40296</v>
       </c>
     </row>
     <row r="5">
@@ -4286,11 +4286,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>27733.36</v>
+        <v>38529.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27733.36</v>
+        <v>38529.36</v>
       </c>
     </row>
     <row r="7">
@@ -4388,7 +4388,7 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>21687.13</v>
+        <v>21695.11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21487.13</v>
+        <v>21495.11</v>
       </c>
     </row>
     <row r="10">
@@ -4456,11 +4456,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>10320</v>
+        <v>7800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10320</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="12">
@@ -4490,11 +4490,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>30300</v>
+        <v>33400</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30300</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="13">
@@ -4660,11 +4660,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>10398</v>
+        <v>11194</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>10398</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="18">
@@ -4728,11 +4728,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>45877.8</v>
+        <v>47955.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4740,11 +4740,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>40877.8</v>
+        <v>42955.8</v>
       </c>
     </row>
     <row r="20">
@@ -4762,11 +4762,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>34149.8</v>
+        <v>54149.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4774,11 +4774,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>30149.8</v>
+        <v>50149.8</v>
       </c>
     </row>
     <row r="21">
@@ -4864,11 +4864,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>68390</v>
+        <v>74584</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>68390</v>
+        <v>74584</v>
       </c>
     </row>
     <row r="24">
@@ -5000,11 +5000,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>10000</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="28">
@@ -5068,23 +5068,23 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>79984</v>
+        <v>80382</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>79984</v>
+        <v>73382</v>
       </c>
     </row>
     <row r="30">
@@ -5102,11 +5102,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>15976</v>
+        <v>16176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15976</v>
+        <v>16176</v>
       </c>
     </row>
     <row r="31">
@@ -5276,19 +5276,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>43549</v>
+        <v>36949</v>
       </c>
     </row>
     <row r="36">
@@ -5408,11 +5408,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>21474</v>
+        <v>28074</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>21474</v>
+        <v>28074</v>
       </c>
     </row>
     <row r="40">
@@ -5476,11 +5476,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>18395</v>
+        <v>28395</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>18395</v>
+        <v>28395</v>
       </c>
     </row>
     <row r="42">
@@ -5510,11 +5510,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>9996</v>
+        <v>16596</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5522,11 +5522,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2396</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="43">
@@ -5544,11 +5544,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>35252</v>
+        <v>35751</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>35252</v>
+        <v>35751</v>
       </c>
     </row>
     <row r="44">
@@ -5714,11 +5714,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>25791</v>
+        <v>27983</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>25791</v>
+        <v>27983</v>
       </c>
     </row>
     <row r="49">
@@ -5850,11 +5850,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>90504</v>
+        <v>91504</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>90504</v>
+        <v>91504</v>
       </c>
     </row>
     <row r="53">
@@ -5952,11 +5952,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>5796</v>
+        <v>26295</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5964,11 +5964,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>172.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>-4204</v>
+        <v>16295</v>
       </c>
     </row>
     <row r="56">
@@ -6020,11 +6020,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>34058</v>
+        <v>44058</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>34058</v>
+        <v>44058</v>
       </c>
     </row>
     <row r="58">
@@ -6088,11 +6088,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>48810</v>
+        <v>69208</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>48810</v>
+        <v>69208</v>
       </c>
     </row>
     <row r="60">
@@ -6194,19 +6194,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>6800</v>
+        <v>15800</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>37697</v>
+        <v>28697</v>
       </c>
     </row>
     <row r="63">
@@ -6301,16 +6301,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>822596.5600000001</v>
+        <v>991544.5600000001</v>
       </c>
       <c r="D2" t="n">
-        <v>4778</v>
+        <v>5324</v>
       </c>
       <c r="E2" t="n">
-        <v>730134.5600000001</v>
+        <v>882370.5600000001</v>
       </c>
       <c r="F2" t="n">
-        <v>92462</v>
+        <v>109174</v>
       </c>
     </row>
     <row r="3">
@@ -6325,16 +6325,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>696996</v>
+        <v>852428</v>
       </c>
       <c r="D3" t="n">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="E3" t="n">
-        <v>612149</v>
+        <v>751703</v>
       </c>
       <c r="F3" t="n">
-        <v>84847</v>
+        <v>100725</v>
       </c>
     </row>
     <row r="4">
@@ -6349,16 +6349,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>125600.56</v>
+        <v>139116.56</v>
       </c>
       <c r="D4" t="n">
-        <v>4549</v>
+        <v>5054</v>
       </c>
       <c r="E4" t="n">
-        <v>117985.56</v>
+        <v>130667.56</v>
       </c>
       <c r="F4" t="n">
-        <v>7615</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="5">
@@ -6373,16 +6373,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1562632</v>
+        <v>1727320</v>
       </c>
       <c r="D5" t="n">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="E5" t="n">
-        <v>340662</v>
+        <v>377474</v>
       </c>
       <c r="F5" t="n">
-        <v>1221970</v>
+        <v>1349846</v>
       </c>
     </row>
     <row r="6">
@@ -6397,16 +6397,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1001530</v>
+        <v>1099440</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E6" t="n">
-        <v>12000</v>
+        <v>14820</v>
       </c>
       <c r="F6" t="n">
-        <v>989530</v>
+        <v>1084620</v>
       </c>
     </row>
     <row r="7">
@@ -6421,16 +6421,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>546102</v>
+        <v>612880</v>
       </c>
       <c r="D7" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="E7" t="n">
-        <v>328662</v>
+        <v>362654</v>
       </c>
       <c r="F7" t="n">
-        <v>217440</v>
+        <v>250226</v>
       </c>
     </row>
     <row r="8">
@@ -6445,16 +6445,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1058465.01</v>
+        <v>1062538.75</v>
       </c>
       <c r="D8" t="n">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="E8" t="n">
-        <v>10706.74</v>
+        <v>11206.74</v>
       </c>
       <c r="F8" t="n">
-        <v>1047758.27</v>
+        <v>1051332.01</v>
       </c>
     </row>
     <row r="9">
@@ -6469,16 +6469,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>631410.54</v>
+        <v>634447.3</v>
       </c>
       <c r="D9" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E9" t="n">
-        <v>2161.37</v>
+        <v>2661.37</v>
       </c>
       <c r="F9" t="n">
-        <v>629249.17</v>
+        <v>631785.9300000001</v>
       </c>
     </row>
     <row r="10">
@@ -6493,16 +6493,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>425503.87</v>
+        <v>426540.85</v>
       </c>
       <c r="D10" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E10" t="n">
         <v>8545.370000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>416958.5</v>
+        <v>417995.48</v>
       </c>
     </row>
     <row r="11">
@@ -6520,7 +6520,7 @@
         <v>167600</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
         <v>122000</v>
@@ -6541,13 +6541,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>176691.9</v>
+        <v>182391.9</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>95795.89999999999</v>
+        <v>101495.9</v>
       </c>
       <c r="F12" t="n">
         <v>80896</v>
@@ -6565,13 +6565,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>257080</v>
+        <v>263380</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>229280</v>
+        <v>235580</v>
       </c>
       <c r="F13" t="n">
         <v>27800</v>
@@ -6659,22 +6659,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>822596.5600000001</v>
+        <v>991544.5600000001</v>
       </c>
       <c r="C2" t="n">
-        <v>200694.9</v>
+        <v>241446.06</v>
       </c>
       <c r="D2" t="n">
-        <v>14728</v>
+        <v>16871</v>
       </c>
       <c r="E2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="n">
-        <v>185966.9</v>
+        <v>224575.06</v>
       </c>
       <c r="G2" t="n">
-        <v>22.61</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="3">
@@ -6684,10 +6684,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1562632</v>
+        <v>1727320</v>
       </c>
       <c r="C3" t="n">
-        <v>199797.98</v>
+        <v>228418.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>199797.98</v>
+        <v>228418.98</v>
       </c>
       <c r="G3" t="n">
-        <v>12.79</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="4">
@@ -6709,22 +6709,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1058465.01</v>
+        <v>1062538.75</v>
       </c>
       <c r="C4" t="n">
-        <v>399973.42</v>
+        <v>401822.42</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>399973.42</v>
+        <v>401773.42</v>
       </c>
       <c r="G4" t="n">
-        <v>37.79</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="5">
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>176691.9</v>
+        <v>182391.9</v>
       </c>
       <c r="C6" t="n">
         <v>95125.89999999999</v>
@@ -6768,13 +6768,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="F6" t="n">
         <v>93108</v>
       </c>
       <c r="G6" t="n">
-        <v>52.7</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="7">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>257080</v>
+        <v>263380</v>
       </c>
       <c r="C7" t="n">
-        <v>119866.67</v>
+        <v>149666.67</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6796,10 +6796,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>119866.67</v>
+        <v>149666.67</v>
       </c>
       <c r="G7" t="n">
-        <v>46.63</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="8">
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C2" t="n">
-        <v>393075.65</v>
+        <v>426898.65</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -6886,13 +6886,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="C3" t="n">
-        <v>152617.9</v>
+        <v>201352.4</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6902,13 +6902,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>61364</v>
+      </c>
+      <c r="D4" t="n">
         <v>8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>57384</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -6934,13 +6934,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C6" t="n">
-        <v>11834</v>
+        <v>15595.66</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>9411</v>
+        <v>9474</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>3032.9</v>
+        <v>3070.9</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -7034,7 +7034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>6600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="4">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>71867</v>
+        <v>71886</v>
       </c>
     </row>
     <row r="8">
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>42819</v>
+        <v>42950</v>
       </c>
     </row>
     <row r="13">
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>17786</v>
+        <v>21766</v>
       </c>
     </row>
     <row r="14">
@@ -7287,10 +7287,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>10966</v>
+        <v>11803</v>
       </c>
     </row>
     <row r="15">
@@ -7305,10 +7305,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>3630</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="16">
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>2040</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="18">
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>546</v>
+        <v>571</v>
       </c>
     </row>
     <row r="19">
@@ -7386,7 +7386,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7395,52 +7395,52 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D20" t="n">
-        <v>17073</v>
+        <v>60406</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
-        <v>16800</v>
+        <v>10522</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>4571</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7449,16 +7449,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>4060</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
@@ -7481,14 +7481,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>19865.5</v>
       </c>
     </row>
     <row r="26">
@@ -7499,14 +7499,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="27">
@@ -7517,20 +7517,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>7446.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7539,88 +7539,88 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
-        <v>29800</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>10000</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>200</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7629,82 +7629,82 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>29309</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
@@ -7715,212 +7715,212 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>31309</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>26493</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>10513</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>343</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>171</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>123</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>14885.9</v>
+        <v>27837</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D45" t="n">
-        <v>8396</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>3464</v>
+        <v>598</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>490</v>
+        <v>337</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>133</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -7931,14 +7931,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>19164.9</v>
       </c>
     </row>
     <row r="51">
@@ -7949,56 +7949,56 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D51" t="n">
-        <v>19</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D52" t="n">
-        <v>20994.67</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>4500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8007,172 +8007,172 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>299</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>115</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>18820</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>2976</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>598</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>38</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>28</v>
+        <v>20994.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>19609</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>38</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64">
@@ -8183,56 +8183,56 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>19609</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>11399.98</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>8000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8241,88 +8241,88 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>9318</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>5500</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>29</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>10000</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8331,153 +8331,171 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>1309</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>1309</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>10009</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>6800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>57</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>299</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
         <v>9</v>
       </c>
     </row>
@@ -8519,10 +8537,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>171897.98</v>
+        <v>182897.98</v>
       </c>
     </row>
     <row r="3">
@@ -8532,23 +8550,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>115666.67</v>
+        <v>145466.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>93108</v>
+        <v>102225.16</v>
       </c>
     </row>
     <row r="5">
@@ -8558,23 +8576,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>89160</v>
+        <v>95760</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>70261</v>
+        <v>93108</v>
       </c>
     </row>
     <row r="7">
@@ -8597,10 +8615,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>33100</v>
+        <v>41900</v>
       </c>
     </row>
     <row r="9">
@@ -8623,10 +8641,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>518</v>
+        <v>573</v>
       </c>
       <c r="C10" t="n">
-        <v>9013</v>
+        <v>9985</v>
       </c>
     </row>
     <row r="11">
@@ -8636,10 +8654,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>7774</v>
+        <v>8671</v>
       </c>
     </row>
   </sheetData>
@@ -8680,10 +8698,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C2" t="n">
-        <v>108219.67</v>
+        <v>132024.33</v>
       </c>
     </row>
     <row r="3">
@@ -8693,10 +8711,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>83319</v>
+        <v>90015.5</v>
       </c>
     </row>
     <row r="4">
@@ -8706,10 +8724,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>66390</v>
+        <v>73066</v>
       </c>
     </row>
     <row r="5">
@@ -8719,10 +8737,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C5" t="n">
-        <v>60825.98</v>
+        <v>65552.98</v>
       </c>
     </row>
     <row r="6">
@@ -8745,127 +8763,127 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>42737</v>
+        <v>51537</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>37200</v>
+        <v>37938</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>36687</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>35722</v>
+        <v>37108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C11" t="n">
-        <v>28862</v>
+        <v>35827</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>18629</v>
+        <v>29848</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>14827</v>
+        <v>18648</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>13877.9</v>
+        <v>14903</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>12934</v>
+        <v>13934.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C16" t="n">
-        <v>11619</v>
+        <v>12953</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -980,10 +980,10 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>558851</v>
+        <v>559150</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="F10" t="n">
         <v>558851</v>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1537,10 +1537,10 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>114093</v>
+        <v>113893</v>
       </c>
       <c r="E19" t="n">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
         <v>113884</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1661,13 +1661,13 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>3993714</v>
+        <v>4008733</v>
       </c>
       <c r="E21" t="n">
-        <v>749896</v>
+        <v>763106</v>
       </c>
       <c r="F21" t="n">
-        <v>3243817</v>
+        <v>3245626</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+34.4%</t>
+          <t>+34.9%</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1702,13 +1702,13 @@
         <v>36651</v>
       </c>
       <c r="O21" t="n">
-        <v>1660765</v>
+        <v>1649374</v>
       </c>
       <c r="P21" t="n">
-        <v>1546600</v>
+        <v>1559800</v>
       </c>
       <c r="Q21" t="n">
-        <v>1762495</v>
+        <v>1761725</v>
       </c>
     </row>
   </sheetData>
@@ -1820,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,22 +2315,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-11391</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-770</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>南区合计</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1660765</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1546600</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1762495</v>
+      <c r="C25" t="n">
+        <v>1649374</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1559800</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1761725</v>
       </c>
     </row>
   </sheetData>
@@ -6254,7 +6275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6373,16 +6394,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1727320</v>
+        <v>1722320</v>
       </c>
       <c r="D5" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E5" t="n">
         <v>377474</v>
       </c>
       <c r="F5" t="n">
-        <v>1349846</v>
+        <v>1344846</v>
       </c>
     </row>
     <row r="6">
@@ -6445,16 +6466,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1062538.75</v>
+        <v>560585.09</v>
       </c>